--- a/retirement_planner.xlsx
+++ b/retirement_planner.xlsx
@@ -1137,7 +1137,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1187,7 +1187,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>14</v>
@@ -1201,7 +1201,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>1750000</v>
+        <v>3000000</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>16</v>
@@ -1215,13 +1215,13 @@
         <v>17</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>76000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1235,7 +1235,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>11000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1251,7 +1251,7 @@
         <v>22</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>120000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1259,7 +1259,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>107000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1275,7 +1275,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1373,7 +1373,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>2250</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1381,7 +1381,7 @@
         <v>38</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>13500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1421,7 +1421,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>650000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">Inputs!B9</f>
-        <v>1750000</v>
+        <v>3000000</v>
       </c>
       <c r="C3" s="11" t="n">
         <f aca="false">IF(65&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,65-Inputs!B25),0)</f>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="J3" s="11" t="n">
         <f aca="false">MAX(0,B3-E3)</f>
-        <v>1578950</v>
+        <v>2828950</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B4" s="14" t="n">
         <f aca="false">J3</f>
-        <v>1578950</v>
+        <v>2828950</v>
       </c>
       <c r="C4" s="14" t="n">
         <f aca="false">IF(66&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,66-Inputs!B25),0)</f>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J4" s="14" t="n">
         <f aca="false">MAX(0,B4-E4)</f>
-        <v>1407900</v>
+        <v>2657900</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">J4</f>
-        <v>1407900</v>
+        <v>2657900</v>
       </c>
       <c r="C5" s="11" t="n">
         <f aca="false">IF(67&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,67-Inputs!B25),0)</f>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="J5" s="11" t="n">
         <f aca="false">MAX(0,B5-E5)</f>
-        <v>1277364.4</v>
+        <v>2527364.4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">J5</f>
-        <v>1277364.4</v>
+        <v>2527364.4</v>
       </c>
       <c r="C6" s="14" t="n">
         <f aca="false">IF(68&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,68-Inputs!B25),0)</f>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="J6" s="14" t="n">
         <f aca="false">MAX(0,B6-E6)</f>
-        <v>1147841.66</v>
+        <v>2397841.66</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">J6</f>
-        <v>1147841.66</v>
+        <v>2397841.66</v>
       </c>
       <c r="C7" s="11" t="n">
         <f aca="false">IF(69&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,69-Inputs!B25),0)</f>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="J7" s="11" t="n">
         <f aca="false">MAX(0,B7-E7)</f>
-        <v>1019357.1015</v>
+        <v>2269357.1015</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B8" s="14" t="n">
         <f aca="false">J7</f>
-        <v>1019357.1015</v>
+        <v>2269357.1015</v>
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">IF(70&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,70-Inputs!B25),0)</f>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="J8" s="14" t="n">
         <f aca="false">MAX(0,B8-E8)</f>
-        <v>891936.6790375</v>
+        <v>2141936.6790375</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">J8</f>
-        <v>891936.6790375</v>
+        <v>2141936.6790375</v>
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">IF(71&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,71-Inputs!B25),0)</f>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="J9" s="11" t="n">
         <f aca="false">MAX(0,B9-E9)</f>
-        <v>765606.996013437</v>
+        <v>2015606.99601344</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B10" s="14" t="n">
         <f aca="false">J9</f>
-        <v>765606.996013437</v>
+        <v>2015606.99601344</v>
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">IF(72&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,72-Inputs!B25),0)</f>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="J10" s="14" t="n">
         <f aca="false">MAX(0,B10-E10)</f>
-        <v>640395.320913773</v>
+        <v>1890395.32091377</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">J10</f>
-        <v>640395.320913773</v>
+        <v>1890395.32091377</v>
       </c>
       <c r="C11" s="17" t="n">
         <f aca="false">IF(73&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,73-Inputs!B25),0)</f>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="J11" s="17" t="n">
         <f aca="false">MAX(0,B11-E11)</f>
-        <v>516329.603936618</v>
+        <v>1766329.60393662</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">J11</f>
-        <v>516329.603936618</v>
+        <v>1766329.60393662</v>
       </c>
       <c r="C12" s="17" t="n">
         <f aca="false">IF(74&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,74-Inputs!B25),0)</f>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="J12" s="17" t="n">
         <f aca="false">MAX(0,B12-E12)</f>
-        <v>393438.494035033</v>
+        <v>1643438.49403503</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B13" s="17" t="n">
         <f aca="false">J12</f>
-        <v>393438.494035033</v>
+        <v>1643438.49403503</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">IF(75&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,75-Inputs!B25),0)</f>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="J13" s="17" t="n">
         <f aca="false">MAX(0,B13-E13)</f>
-        <v>271751.356385909</v>
+        <v>1521751.35638591</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B14" s="17" t="n">
         <f aca="false">J13</f>
-        <v>271751.356385909</v>
+        <v>1521751.35638591</v>
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">IF(76&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,76-Inputs!B25),0)</f>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="J14" s="17" t="n">
         <f aca="false">MAX(0,B14-E14)</f>
-        <v>151298.290295557</v>
+        <v>1401298.29029556</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B15" s="17" t="n">
         <f aca="false">J14</f>
-        <v>151298.290295557</v>
+        <v>1401298.29029556</v>
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">IF(77&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,77-Inputs!B25),0)</f>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="J15" s="17" t="n">
         <f aca="false">MAX(0,B15-E15)</f>
-        <v>32110.1475529454</v>
+        <v>1282110.14755295</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="B16" s="17" t="n">
         <f aca="false">J15</f>
-        <v>32110.1475529454</v>
+        <v>1282110.14755295</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">IF(78&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,78-Inputs!B25),0)</f>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="J16" s="17" t="n">
         <f aca="false">MAX(0,B16-E16)</f>
-        <v>0</v>
+        <v>1164218.55124177</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="B17" s="17" t="n">
         <f aca="false">J16</f>
-        <v>0</v>
+        <v>1164218.55124177</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">IF(79&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,79-Inputs!B25),0)</f>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="J17" s="17" t="n">
         <f aca="false">MAX(0,B17-E17)</f>
-        <v>0</v>
+        <v>1047655.91502281</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B18" s="17" t="n">
         <f aca="false">J17</f>
-        <v>0</v>
+        <v>1047655.91502281</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">IF(80&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,80-Inputs!B25),0)</f>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="J18" s="17" t="n">
         <f aca="false">MAX(0,B18-E18)</f>
-        <v>0</v>
+        <v>932455.462898383</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="B19" s="17" t="n">
         <f aca="false">J18</f>
-        <v>0</v>
+        <v>932455.462898383</v>
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">IF(81&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,81-Inputs!B25),0)</f>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J19" s="17" t="n">
         <f aca="false">MAX(0,B19-E19)</f>
-        <v>0</v>
+        <v>818651.249470843</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B20" s="17" t="n">
         <f aca="false">J19</f>
-        <v>0</v>
+        <v>818651.249470843</v>
       </c>
       <c r="C20" s="17" t="n">
         <f aca="false">IF(82&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,82-Inputs!B25),0)</f>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J20" s="17" t="n">
         <f aca="false">MAX(0,B20-E20)</f>
-        <v>0</v>
+        <v>706278.180707614</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="B21" s="17" t="n">
         <f aca="false">J20</f>
-        <v>0</v>
+        <v>706278.180707614</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">IF(83&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,83-Inputs!B25),0)</f>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="J21" s="17" t="n">
         <f aca="false">MAX(0,B21-E21)</f>
-        <v>0</v>
+        <v>595372.035225304</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="B22" s="17" t="n">
         <f aca="false">J21</f>
-        <v>0</v>
+        <v>595372.035225304</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">IF(84&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,84-Inputs!B25),0)</f>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="J22" s="17" t="n">
         <f aca="false">MAX(0,B22-E22)</f>
-        <v>0</v>
+        <v>485969.486105936</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B23" s="17" t="n">
         <f aca="false">J22</f>
-        <v>0</v>
+        <v>485969.486105936</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">IF(85&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,85-Inputs!B25),0)</f>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="J23" s="17" t="n">
         <f aca="false">MAX(0,B23-E23)</f>
-        <v>0</v>
+        <v>378108.123258585</v>
       </c>
     </row>
   </sheetData>
@@ -2553,11 +2553,11 @@
       </c>
       <c r="C3" s="11" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D3" s="11" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IF(55&lt;65,Inputs!B35*12,0)</f>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="G3" s="20" t="n">
         <f aca="false">B3+C3+D3+E3+F3</f>
-        <v>137820</v>
+        <v>148320</v>
       </c>
       <c r="H3" s="11" t="n">
         <f aca="false">IF(65&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,65-Inputs!B25),0)</f>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="P3" s="21" t="n">
         <f aca="false">H3+I3+J3+K3+L3-G3-N3-O3</f>
-        <v>-5402.885</v>
+        <v>-15902.885</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2618,11 +2618,11 @@
       </c>
       <c r="C4" s="14" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D4" s="14" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E4" s="14" t="n">
         <f aca="false">IF(56&lt;65,Inputs!B35*12,0)</f>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="G4" s="22" t="n">
         <f aca="false">B4+C4+D4+E4+F4</f>
-        <v>140451</v>
+        <v>150951</v>
       </c>
       <c r="H4" s="14" t="n">
         <f aca="false">IF(66&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,66-Inputs!B25),0)</f>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="P4" s="23" t="n">
         <f aca="false">H4+I4+J4+K4+L4-G4-N4-O4</f>
-        <v>-8033.885</v>
+        <v>-18533.885</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2683,11 +2683,11 @@
       </c>
       <c r="C5" s="11" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D5" s="11" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E5" s="11" t="n">
         <f aca="false">IF(57&lt;65,Inputs!B35*12,0)</f>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="G5" s="20" t="n">
         <f aca="false">B5+C5+D5+E5+F5</f>
-        <v>143163.15</v>
+        <v>153663.15</v>
       </c>
       <c r="H5" s="11" t="n">
         <f aca="false">IF(67&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,67-Inputs!B25),0)</f>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P5" s="21" t="n">
         <f aca="false">H5+I5+J5+K5+L5-G5-N5-O5</f>
-        <v>-1015.66771999996</v>
+        <v>-11515.66772</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2748,11 +2748,11 @@
       </c>
       <c r="C6" s="14" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D6" s="14" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E6" s="14" t="n">
         <f aca="false">IF(58&lt;65,Inputs!B35*12,0)</f>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="G6" s="22" t="n">
         <f aca="false">B6+C6+D6+E6+F6</f>
-        <v>145958.9955</v>
+        <v>156458.9955</v>
       </c>
       <c r="H6" s="14" t="n">
         <f aca="false">IF(68&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,68-Inputs!B25),0)</f>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="P6" s="23" t="n">
         <f aca="false">H6+I6+J6+K6+L6-G6-N6-O6</f>
-        <v>-3568.25403799999</v>
+        <v>-14068.254038</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2813,11 +2813,11 @@
       </c>
       <c r="C7" s="11" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D7" s="11" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">IF(59&lt;65,Inputs!B35*12,0)</f>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="G7" s="20" t="n">
         <f aca="false">B7+C7+D7+E7+F7</f>
-        <v>148841.163915</v>
+        <v>159341.163915</v>
       </c>
       <c r="H7" s="11" t="n">
         <f aca="false">IF(69&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,69-Inputs!B25),0)</f>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="P7" s="21" t="n">
         <f aca="false">H7+I7+J7+K7+L7-G7-N7-O7</f>
-        <v>-6201.08179145001</v>
+        <v>-16701.08179145</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2878,11 +2878,11 @@
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D8" s="14" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E8" s="14" t="n">
         <f aca="false">IF(60&lt;65,Inputs!B35*12,0)</f>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="G8" s="22" t="n">
         <f aca="false">B8+C8+D8+E8+F8</f>
-        <v>151812.36730995</v>
+        <v>162312.36730995</v>
       </c>
       <c r="H8" s="14" t="n">
         <f aca="false">IF(70&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,70-Inputs!B25),0)</f>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P8" s="23" t="n">
         <f aca="false">H8+I8+J8+K8+L8-G8-N8-O8</f>
-        <v>-8916.71100831127</v>
+        <v>-19416.7110083113</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2943,11 +2943,11 @@
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">IF(61&lt;65,Inputs!B35*12,0)</f>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="G9" s="20" t="n">
         <f aca="false">B9+C9+D9+E9+F9</f>
-        <v>154875.405230624</v>
+        <v>165375.405230624</v>
       </c>
       <c r="H9" s="11" t="n">
         <f aca="false">IF(71&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,71-Inputs!B25),0)</f>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="P9" s="21" t="n">
         <f aca="false">H9+I9+J9+K9+L9-G9-N9-O9</f>
-        <v>-11717.7853964438</v>
+        <v>-22217.7853964438</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3008,11 +3008,11 @@
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D10" s="14" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E10" s="14" t="n">
         <f aca="false">IF(62&lt;65,Inputs!B35*12,0)</f>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="G10" s="22" t="n">
         <f aca="false">B10+C10+D10+E10+F10</f>
-        <v>158033.167633986</v>
+        <v>168533.167633986</v>
       </c>
       <c r="H10" s="14" t="n">
         <f aca="false">IF(72&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,72-Inputs!B25),0)</f>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P10" s="23" t="n">
         <f aca="false">H10+I10+J10+K10+L10-G10-N10-O10</f>
-        <v>-14607.0351789518</v>
+        <v>-25107.0351789518</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3073,11 +3073,11 @@
       </c>
       <c r="C11" s="17" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D11" s="17" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E11" s="17" t="n">
         <f aca="false">IF(63&lt;65,Inputs!B35*12,0)</f>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G11" s="24" t="n">
         <f aca="false">B11+C11+D11+E11+F11</f>
-        <v>161288.637921772</v>
+        <v>171788.637921772</v>
       </c>
       <c r="H11" s="17" t="n">
         <f aca="false">IF(73&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,73-Inputs!B25),0)</f>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="P11" s="25" t="n">
         <f aca="false">H11+I11+J11+K11+L11-G11-N11-O11</f>
-        <v>-17587.2800303614</v>
+        <v>-28087.2800303614</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3138,11 +3138,11 @@
       </c>
       <c r="C12" s="17" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D12" s="17" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E12" s="17" t="n">
         <f aca="false">IF(64&lt;65,Inputs!B35*12,0)</f>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="G12" s="24" t="n">
         <f aca="false">B12+C12+D12+E12+F12</f>
-        <v>164644.896081129</v>
+        <v>175144.896081129</v>
       </c>
       <c r="H12" s="17" t="n">
         <f aca="false">IF(74&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,74-Inputs!B25),0)</f>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="P12" s="25" t="n">
         <f aca="false">H12+I12+J12+K12+L12-G12-N12-O12</f>
-        <v>-20661.4321174336</v>
+        <v>-31161.4321174336</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3203,11 +3203,11 @@
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D13" s="17" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E13" s="17" t="n">
         <f aca="false">IF(65&lt;65,Inputs!B35*12,0)</f>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G13" s="24" t="n">
         <f aca="false">B13+C13+D13+E13+F13</f>
-        <v>158505.121936352</v>
+        <v>169005.121936352</v>
       </c>
       <c r="H13" s="17" t="n">
         <f aca="false">IF(75&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,75-Inputs!B25),0)</f>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="P13" s="25" t="n">
         <f aca="false">H13+I13+J13+K13+L13-G13-N13-O13</f>
-        <v>9599.50075143549</v>
+        <v>-900.499248564507</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3268,11 +3268,11 @@
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D14" s="17" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E14" s="17" t="n">
         <f aca="false">IF(66&lt;65,Inputs!B35*12,0)</f>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="G14" s="24" t="n">
         <f aca="false">B14+C14+D14+E14+F14</f>
-        <v>162072.598515872</v>
+        <v>172572.598515872</v>
       </c>
       <c r="H14" s="17" t="n">
         <f aca="false">IF(76&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,76-Inputs!B25),0)</f>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="P14" s="25" t="n">
         <f aca="false">H14+I14+J14+K14+L14-G14-N14-O14</f>
-        <v>6924.21186411068</v>
+        <v>-3575.78813588932</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3333,11 +3333,11 @@
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D15" s="17" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E15" s="17" t="n">
         <f aca="false">IF(67&lt;65,Inputs!B35*12,0)</f>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="G15" s="24" t="n">
         <f aca="false">B15+C15+D15+E15+F15</f>
-        <v>165750.715538848</v>
+        <v>176250.715538848</v>
       </c>
       <c r="H15" s="17" t="n">
         <f aca="false">IF(77&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,77-Inputs!B25),0)</f>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="P15" s="25" t="n">
         <f aca="false">H15+I15+J15+K15+L15-G15-N15-O15</f>
-        <v>4160.5872256337</v>
+        <v>-6339.4127743663</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3398,11 +3398,11 @@
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D16" s="17" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E16" s="17" t="n">
         <f aca="false">IF(68&lt;65,Inputs!B35*12,0)</f>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G16" s="24" t="n">
         <f aca="false">B16+C16+D16+E16+F16</f>
-        <v>169542.973025889</v>
+        <v>180042.973025889</v>
       </c>
       <c r="H16" s="17" t="n">
         <f aca="false">IF(78&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,78-Inputs!B25),0)</f>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="P16" s="25" t="n">
         <f aca="false">H16+I16+J16+K16+L16-G16-N16-O16</f>
-        <v>1305.68443270496</v>
+        <v>-9194.31556729504</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3463,11 +3463,11 @@
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D17" s="17" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E17" s="17" t="n">
         <f aca="false">IF(69&lt;65,Inputs!B35*12,0)</f>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="G17" s="24" t="n">
         <f aca="false">B17+C17+D17+E17+F17</f>
-        <v>173452.985038585</v>
+        <v>183952.985038585</v>
       </c>
       <c r="H17" s="17" t="n">
         <f aca="false">IF(79&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,79-Inputs!B25),0)</f>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P17" s="25" t="n">
         <f aca="false">H17+I17+J17+K17+L17-G17-N17-O17</f>
-        <v>-1643.53901852602</v>
+        <v>-12143.539018526</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3528,11 +3528,11 @@
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D18" s="17" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E18" s="17" t="n">
         <f aca="false">IF(70&lt;65,Inputs!B35*12,0)</f>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="G18" s="24" t="n">
         <f aca="false">B18+C18+D18+E18+F18</f>
-        <v>177484.483552758</v>
+        <v>187984.483552758</v>
       </c>
       <c r="H18" s="17" t="n">
         <f aca="false">IF(80&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,80-Inputs!B25),0)</f>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="P18" s="25" t="n">
         <f aca="false">H18+I18+J18+K18+L18-G18-N18-O18</f>
-        <v>-4690.2292571972</v>
+        <v>-15190.2292571972</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3593,11 +3593,11 @@
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D19" s="17" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E19" s="17" t="n">
         <f aca="false">IF(71&lt;65,Inputs!B35*12,0)</f>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="G19" s="24" t="n">
         <f aca="false">B19+C19+D19+E19+F19</f>
-        <v>181641.322470506</v>
+        <v>192141.322470506</v>
       </c>
       <c r="H19" s="17" t="n">
         <f aca="false">IF(81&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,81-Inputs!B25),0)</f>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P19" s="25" t="n">
         <f aca="false">H19+I19+J19+K19+L19-G19-N19-O19</f>
-        <v>-7837.63969255681</v>
+        <v>-18337.6396925568</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3658,11 +3658,11 @@
       </c>
       <c r="C20" s="17" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D20" s="17" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E20" s="17" t="n">
         <f aca="false">IF(72&lt;65,Inputs!B35*12,0)</f>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G20" s="24" t="n">
         <f aca="false">B20+C20+D20+E20+F20</f>
-        <v>185927.481776345</v>
+        <v>196427.481776345</v>
       </c>
       <c r="H20" s="17" t="n">
         <f aca="false">IF(82&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,82-Inputs!B25),0)</f>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="P20" s="25" t="n">
         <f aca="false">H20+I20+J20+K20+L20-G20-N20-O20</f>
-        <v>-11089.1348039474</v>
+        <v>-21589.1348039474</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3723,11 +3723,11 @@
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D21" s="17" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E21" s="17" t="n">
         <f aca="false">IF(73&lt;65,Inputs!B35*12,0)</f>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="G21" s="24" t="n">
         <f aca="false">B21+C21+D21+E21+F21</f>
-        <v>190347.071842946</v>
+        <v>200847.071842946</v>
       </c>
       <c r="H21" s="17" t="n">
         <f aca="false">IF(83&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,83-Inputs!B25),0)</f>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="P21" s="25" t="n">
         <f aca="false">H21+I21+J21+K21+L21-G21-N21-O21</f>
-        <v>-14448.1940712382</v>
+        <v>-24948.1940712382</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3788,11 +3788,11 @@
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D22" s="17" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E22" s="17" t="n">
         <f aca="false">IF(74&lt;65,Inputs!B35*12,0)</f>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="G22" s="24" t="n">
         <f aca="false">B22+C22+D22+E22+F22</f>
-        <v>194904.33789221</v>
+        <v>205404.33789221</v>
       </c>
       <c r="H22" s="17" t="n">
         <f aca="false">IF(84&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,84-Inputs!B25),0)</f>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="P22" s="25" t="n">
         <f aca="false">H22+I22+J22+K22+L22-G22-N22-O22</f>
-        <v>-17918.4160512098</v>
+        <v>-28418.4160512098</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3853,11 +3853,11 @@
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">Inputs!B30*12</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="D23" s="17" t="n">
         <f aca="false">Inputs!B31+Inputs!B32</f>
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E23" s="17" t="n">
         <f aca="false">IF(75&lt;65,Inputs!B35*12,0)</f>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="G23" s="24" t="n">
         <f aca="false">B23+C23+D23+E23+F23</f>
-        <v>199603.664617651</v>
+        <v>210103.664617651</v>
       </c>
       <c r="H23" s="17" t="n">
         <f aca="false">IF(85&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,85-Inputs!B25),0)</f>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="P23" s="25" t="n">
         <f aca="false">H23+I23+J23+K23+L23-G23-N23-O23</f>
-        <v>-21503.5226056258</v>
+        <v>-32003.5226056258</v>
       </c>
     </row>
   </sheetData>
@@ -3987,35 +3987,35 @@
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">'Roth Conversion'!J3</f>
-        <v>1578950</v>
+        <v>2828950</v>
       </c>
       <c r="C3" s="11" t="n">
         <f aca="false">(Inputs!B10+Inputs!B13)*(1+Inputs!B19)-'Withdrawal Plan'!K3</f>
-        <v>345600</v>
+        <v>810000</v>
       </c>
       <c r="D3" s="11" t="n">
         <f aca="false">Inputs!E11*(1+Inputs!B19)</f>
-        <v>11880</v>
+        <v>10800</v>
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">Inputs!E10*(1+Inputs!B19)</f>
-        <v>82080</v>
+        <v>54000</v>
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">MAX(0,Inputs!B14*(1+Inputs!B19)-'Withdrawal Plan'!M3)</f>
-        <v>113340</v>
+        <v>105780</v>
       </c>
       <c r="G3" s="11" t="n">
         <f aca="false">MAX(0,Inputs!B16*(1+Inputs!B19)-'Withdrawal Plan'!L3)</f>
-        <v>1080000</v>
+        <v>540000</v>
       </c>
       <c r="H3" s="20" t="n">
         <f aca="false">SUM(B3:G3)</f>
-        <v>3211850</v>
+        <v>4349530</v>
       </c>
       <c r="I3" s="21" t="n">
         <f aca="false">H3+Inputs!B36</f>
-        <v>3861850</v>
+        <v>5149530</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4024,35 +4024,35 @@
       </c>
       <c r="B4" s="14" t="n">
         <f aca="false">'Roth Conversion'!J4</f>
-        <v>1407900</v>
+        <v>2657900</v>
       </c>
       <c r="C4" s="14" t="n">
         <f aca="false">MAX(0,C3*(1+Inputs!B19)-'Withdrawal Plan'!K4)</f>
-        <v>373248</v>
+        <v>874800</v>
       </c>
       <c r="D4" s="14" t="n">
         <f aca="false">D3*(1+Inputs!B19)</f>
-        <v>12830.4</v>
+        <v>11664</v>
       </c>
       <c r="E4" s="14" t="n">
         <f aca="false">E3*(1+Inputs!B19)</f>
-        <v>88646.4</v>
+        <v>58320</v>
       </c>
       <c r="F4" s="14" t="n">
         <f aca="false">MAX(0,F3*(1+Inputs!B19)-'Withdrawal Plan'!M4)</f>
-        <v>120076.2</v>
+        <v>111911.4</v>
       </c>
       <c r="G4" s="14" t="n">
         <f aca="false">MAX(0,G3*(1+Inputs!B19)-'Withdrawal Plan'!L4)</f>
-        <v>1166400</v>
+        <v>583200</v>
       </c>
       <c r="H4" s="22" t="n">
         <f aca="false">SUM(B4:G4)</f>
-        <v>3169101</v>
+        <v>4297795.4</v>
       </c>
       <c r="I4" s="23" t="n">
         <f aca="false">H4+Inputs!B36</f>
-        <v>3819101</v>
+        <v>5097795.4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4061,35 +4061,35 @@
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">'Roth Conversion'!J5</f>
-        <v>1277364.4</v>
+        <v>2527364.4</v>
       </c>
       <c r="C5" s="11" t="n">
         <f aca="false">MAX(0,C4*(1+Inputs!B19)-'Withdrawal Plan'!K5)</f>
-        <v>403107.84</v>
+        <v>944784</v>
       </c>
       <c r="D5" s="11" t="n">
         <f aca="false">D4*(1+Inputs!B19)</f>
-        <v>13856.832</v>
+        <v>12597.12</v>
       </c>
       <c r="E5" s="11" t="n">
         <f aca="false">E4*(1+Inputs!B19)</f>
-        <v>95738.112</v>
+        <v>62985.6</v>
       </c>
       <c r="F5" s="11" t="n">
         <f aca="false">MAX(0,F4*(1+Inputs!B19)-'Withdrawal Plan'!M5)</f>
-        <v>127234.746</v>
+        <v>118416.762</v>
       </c>
       <c r="G5" s="11" t="n">
         <f aca="false">MAX(0,G4*(1+Inputs!B19)-'Withdrawal Plan'!L5)</f>
-        <v>1259712</v>
+        <v>629856</v>
       </c>
       <c r="H5" s="20" t="n">
         <f aca="false">SUM(B5:G5)</f>
-        <v>3177013.93</v>
+        <v>4296003.882</v>
       </c>
       <c r="I5" s="21" t="n">
         <f aca="false">H5+Inputs!B36</f>
-        <v>3827013.93</v>
+        <v>5096003.882</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4098,35 +4098,35 @@
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">'Roth Conversion'!J6</f>
-        <v>1147841.66</v>
+        <v>2397841.66</v>
       </c>
       <c r="C6" s="14" t="n">
         <f aca="false">MAX(0,C5*(1+Inputs!B19)-'Withdrawal Plan'!K6)</f>
-        <v>435356.4672</v>
+        <v>1020366.72</v>
       </c>
       <c r="D6" s="14" t="n">
         <f aca="false">D5*(1+Inputs!B19)</f>
-        <v>14965.37856</v>
+        <v>13604.8896</v>
       </c>
       <c r="E6" s="14" t="n">
         <f aca="false">E5*(1+Inputs!B19)</f>
-        <v>103397.16096</v>
+        <v>68024.448</v>
       </c>
       <c r="F6" s="14" t="n">
         <f aca="false">MAX(0,F5*(1+Inputs!B19)-'Withdrawal Plan'!M6)</f>
-        <v>134843.59818</v>
+        <v>125320.17546</v>
       </c>
       <c r="G6" s="14" t="n">
         <f aca="false">MAX(0,G5*(1+Inputs!B19)-'Withdrawal Plan'!L6)</f>
-        <v>1360488.96</v>
+        <v>680244.48</v>
       </c>
       <c r="H6" s="22" t="n">
         <f aca="false">SUM(B6:G6)</f>
-        <v>3196893.2249</v>
+        <v>4305402.37306</v>
       </c>
       <c r="I6" s="23" t="n">
         <f aca="false">H6+Inputs!B36</f>
-        <v>3846893.2249</v>
+        <v>5105402.37306</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4135,35 +4135,35 @@
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">'Roth Conversion'!J7</f>
-        <v>1019357.1015</v>
+        <v>2269357.1015</v>
       </c>
       <c r="C7" s="11" t="n">
         <f aca="false">MAX(0,C6*(1+Inputs!B19)-'Withdrawal Plan'!K7)</f>
-        <v>470184.984576</v>
+        <v>1101996.0576</v>
       </c>
       <c r="D7" s="11" t="n">
         <f aca="false">D6*(1+Inputs!B19)</f>
-        <v>16162.6088448</v>
+        <v>14693.280768</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">E6*(1+Inputs!B19)</f>
-        <v>111668.9338368</v>
+        <v>73466.40384</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">MAX(0,F6*(1+Inputs!B19)-'Withdrawal Plan'!M7)</f>
-        <v>142932.6621594</v>
+        <v>132647.3656218</v>
       </c>
       <c r="G7" s="11" t="n">
         <f aca="false">MAX(0,G6*(1+Inputs!B19)-'Withdrawal Plan'!L7)</f>
-        <v>1469328.0768</v>
+        <v>734664.0384</v>
       </c>
       <c r="H7" s="20" t="n">
         <f aca="false">SUM(B7:G7)</f>
-        <v>3229634.367717</v>
+        <v>4326824.2477298</v>
       </c>
       <c r="I7" s="21" t="n">
         <f aca="false">H7+Inputs!B36</f>
-        <v>3879634.367717</v>
+        <v>5126824.2477298</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4172,35 +4172,35 @@
       </c>
       <c r="B8" s="14" t="n">
         <f aca="false">'Roth Conversion'!J8</f>
-        <v>891936.6790375</v>
+        <v>2141936.6790375</v>
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">MAX(0,C7*(1+Inputs!B19)-'Withdrawal Plan'!K8)</f>
-        <v>507799.78334208</v>
+        <v>1190155.742208</v>
       </c>
       <c r="D8" s="14" t="n">
         <f aca="false">D7*(1+Inputs!B19)</f>
-        <v>17455.617552384</v>
+        <v>15868.74322944</v>
       </c>
       <c r="E8" s="14" t="n">
         <f aca="false">E7*(1+Inputs!B19)</f>
-        <v>120602.448543744</v>
+        <v>79343.7161472</v>
       </c>
       <c r="F8" s="14" t="n">
         <f aca="false">MAX(0,F7*(1+Inputs!B19)-'Withdrawal Plan'!M8)</f>
-        <v>151533.930063402</v>
+        <v>140425.809802794</v>
       </c>
       <c r="G8" s="14" t="n">
         <f aca="false">MAX(0,G7*(1+Inputs!B19)-'Withdrawal Plan'!L8)</f>
-        <v>1586874.322944</v>
+        <v>793437.161472</v>
       </c>
       <c r="H8" s="22" t="n">
         <f aca="false">SUM(B8:G8)</f>
-        <v>3276202.78148311</v>
+        <v>4361167.85189694</v>
       </c>
       <c r="I8" s="23" t="n">
         <f aca="false">H8+Inputs!B36</f>
-        <v>3926202.78148311</v>
+        <v>5161167.85189694</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4209,35 +4209,35 @@
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">'Roth Conversion'!J9</f>
-        <v>765606.996013437</v>
+        <v>2015606.99601344</v>
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">MAX(0,C8*(1+Inputs!B19)-'Withdrawal Plan'!K9)</f>
-        <v>548423.766009447</v>
+        <v>1285368.20158464</v>
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">D8*(1+Inputs!B19)</f>
-        <v>18852.0669565747</v>
+        <v>17138.2426877952</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">E8*(1+Inputs!B19)</f>
-        <v>130250.644427244</v>
+        <v>85691.213438976</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">MAX(0,F8*(1+Inputs!B19)-'Withdrawal Plan'!M9)</f>
-        <v>160681.632146287</v>
+        <v>148684.86226483</v>
       </c>
       <c r="G9" s="11" t="n">
         <f aca="false">MAX(0,G8*(1+Inputs!B19)-'Withdrawal Plan'!L9)</f>
-        <v>1713824.26877952</v>
+        <v>856912.13438976</v>
       </c>
       <c r="H9" s="20" t="n">
         <f aca="false">SUM(B9:G9)</f>
-        <v>3337639.37433251</v>
+        <v>4409401.65037944</v>
       </c>
       <c r="I9" s="21" t="n">
         <f aca="false">H9+Inputs!B36</f>
-        <v>3987639.37433251</v>
+        <v>5209401.65037944</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4246,35 +4246,35 @@
       </c>
       <c r="B10" s="14" t="n">
         <f aca="false">'Roth Conversion'!J10</f>
-        <v>640395.320913773</v>
+        <v>1890395.32091377</v>
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">MAX(0,C9*(1+Inputs!B19)-'Withdrawal Plan'!K10)</f>
-        <v>592297.667290203</v>
+        <v>1388197.65771141</v>
       </c>
       <c r="D10" s="14" t="n">
         <f aca="false">D9*(1+Inputs!B19)</f>
-        <v>20360.2323131007</v>
+        <v>18509.3021028188</v>
       </c>
       <c r="E10" s="14" t="n">
         <f aca="false">E9*(1+Inputs!B19)</f>
-        <v>140670.695981423</v>
+        <v>92546.5105140941</v>
       </c>
       <c r="F10" s="14" t="n">
         <f aca="false">MAX(0,F9*(1+Inputs!B19)-'Withdrawal Plan'!M10)</f>
-        <v>170412.399779693</v>
+        <v>157455.88830772</v>
       </c>
       <c r="G10" s="14" t="n">
         <f aca="false">MAX(0,G9*(1+Inputs!B19)-'Withdrawal Plan'!L10)</f>
-        <v>1850930.21028188</v>
+        <v>925465.105140941</v>
       </c>
       <c r="H10" s="22" t="n">
         <f aca="false">SUM(B10:G10)</f>
-        <v>3415066.52656007</v>
+        <v>4472569.78469076</v>
       </c>
       <c r="I10" s="23" t="n">
         <f aca="false">H10+Inputs!B36</f>
-        <v>4065066.52656007</v>
+        <v>5272569.78469076</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4283,35 +4283,35 @@
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">'Roth Conversion'!J11</f>
-        <v>516329.603936618</v>
+        <v>1766329.60393662</v>
       </c>
       <c r="C11" s="17" t="n">
         <f aca="false">MAX(0,C10*(1+Inputs!B19)-'Withdrawal Plan'!K11)</f>
-        <v>639681.480673419</v>
+        <v>1499253.47032833</v>
       </c>
       <c r="D11" s="17" t="n">
         <f aca="false">D10*(1+Inputs!B19)</f>
-        <v>21989.0508981488</v>
+        <v>19990.0462710443</v>
       </c>
       <c r="E11" s="17" t="n">
         <f aca="false">E10*(1+Inputs!B19)</f>
-        <v>151924.351659937</v>
+        <v>99950.2313552217</v>
       </c>
       <c r="F11" s="17" t="n">
         <f aca="false">MAX(0,F10*(1+Inputs!B19)-'Withdrawal Plan'!M11)</f>
-        <v>180765.440676857</v>
+        <v>166772.408287125</v>
       </c>
       <c r="G11" s="17" t="n">
         <f aca="false">MAX(0,G10*(1+Inputs!B19)-'Withdrawal Plan'!L11)</f>
-        <v>1999004.62710443</v>
+        <v>999502.313552217</v>
       </c>
       <c r="H11" s="24" t="n">
         <f aca="false">SUM(B11:G11)</f>
-        <v>3509694.55494941</v>
+        <v>4551798.07373055</v>
       </c>
       <c r="I11" s="25" t="n">
         <f aca="false">H11+Inputs!B36</f>
-        <v>4159694.55494941</v>
+        <v>5351798.07373055</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4320,35 +4320,35 @@
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">'Roth Conversion'!J12</f>
-        <v>393438.494035033</v>
+        <v>1643438.49403503</v>
       </c>
       <c r="C12" s="17" t="n">
         <f aca="false">MAX(0,C11*(1+Inputs!B19)-'Withdrawal Plan'!K12)</f>
-        <v>690855.999127292</v>
+        <v>1619193.74795459</v>
       </c>
       <c r="D12" s="17" t="n">
         <f aca="false">D11*(1+Inputs!B19)</f>
-        <v>23748.1749700007</v>
+        <v>21589.2499727279</v>
       </c>
       <c r="E12" s="17" t="n">
         <f aca="false">E11*(1+Inputs!B19)</f>
-        <v>164078.299792732</v>
+        <v>107946.249863639</v>
       </c>
       <c r="F12" s="17" t="n">
         <f aca="false">MAX(0,F11*(1+Inputs!B19)-'Withdrawal Plan'!M12)</f>
-        <v>191782.727291533</v>
+        <v>176670.252310623</v>
       </c>
       <c r="G12" s="17" t="n">
         <f aca="false">MAX(0,G11*(1+Inputs!B19)-'Withdrawal Plan'!L12)</f>
-        <v>2158924.99727279</v>
+        <v>1079462.49863639</v>
       </c>
       <c r="H12" s="24" t="n">
         <f aca="false">SUM(B12:G12)</f>
-        <v>3622828.69248938</v>
+        <v>4648300.49277301</v>
       </c>
       <c r="I12" s="25" t="n">
         <f aca="false">H12+Inputs!B36</f>
-        <v>4272828.69248938</v>
+        <v>5448300.49277301</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4357,35 +4357,35 @@
       </c>
       <c r="B13" s="17" t="n">
         <f aca="false">'Roth Conversion'!J13</f>
-        <v>271751.356385909</v>
+        <v>1521751.35638591</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">MAX(0,C12*(1+Inputs!B19)-'Withdrawal Plan'!K13)</f>
-        <v>746124.479057476</v>
+        <v>1748729.24779096</v>
       </c>
       <c r="D13" s="17" t="n">
         <f aca="false">D12*(1+Inputs!B19)</f>
-        <v>25648.0289676007</v>
+        <v>23316.3899705461</v>
       </c>
       <c r="E13" s="17" t="n">
         <f aca="false">E12*(1+Inputs!B19)</f>
-        <v>177204.56377615</v>
+        <v>116581.949852731</v>
       </c>
       <c r="F13" s="17" t="n">
         <f aca="false">MAX(0,F12*(1+Inputs!B19)-'Withdrawal Plan'!M13)</f>
-        <v>203509.19940341</v>
+        <v>187187.726424027</v>
       </c>
       <c r="G13" s="17" t="n">
         <f aca="false">MAX(0,G12*(1+Inputs!B19)-'Withdrawal Plan'!L13)</f>
-        <v>2331638.99705461</v>
+        <v>1165819.49852731</v>
       </c>
       <c r="H13" s="24" t="n">
         <f aca="false">SUM(B13:G13)</f>
-        <v>3755876.62464516</v>
+        <v>4763386.16895148</v>
       </c>
       <c r="I13" s="25" t="n">
         <f aca="false">H13+Inputs!B36</f>
-        <v>4405876.62464516</v>
+        <v>5563386.16895148</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4394,35 +4394,35 @@
       </c>
       <c r="B14" s="17" t="n">
         <f aca="false">'Roth Conversion'!J14</f>
-        <v>151298.290295557</v>
+        <v>1401298.29029556</v>
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">MAX(0,C13*(1+Inputs!B19)-'Withdrawal Plan'!K14)</f>
-        <v>805814.437382074</v>
+        <v>1888627.58761424</v>
       </c>
       <c r="D14" s="17" t="n">
         <f aca="false">D13*(1+Inputs!B19)</f>
-        <v>27699.8712850088</v>
+        <v>25181.7011681898</v>
       </c>
       <c r="E14" s="17" t="n">
         <f aca="false">E13*(1+Inputs!B19)</f>
-        <v>191380.928878243</v>
+        <v>125908.505840949</v>
       </c>
       <c r="F14" s="17" t="n">
         <f aca="false">MAX(0,F13*(1+Inputs!B19)-'Withdrawal Plan'!M14)</f>
-        <v>215992.981980664</v>
+        <v>198365.791162931</v>
       </c>
       <c r="G14" s="17" t="n">
         <f aca="false">MAX(0,G13*(1+Inputs!B19)-'Withdrawal Plan'!L14)</f>
-        <v>2518170.11681898</v>
+        <v>1259085.05840949</v>
       </c>
       <c r="H14" s="24" t="n">
         <f aca="false">SUM(B14:G14)</f>
-        <v>3910356.62664053</v>
+        <v>4898466.93449135</v>
       </c>
       <c r="I14" s="25" t="n">
         <f aca="false">H14+Inputs!B36</f>
-        <v>4560356.62664053</v>
+        <v>5698466.93449135</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4431,35 +4431,35 @@
       </c>
       <c r="B15" s="17" t="n">
         <f aca="false">'Roth Conversion'!J15</f>
-        <v>32110.1475529454</v>
+        <v>1282110.14755295</v>
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">MAX(0,C14*(1+Inputs!B19)-'Withdrawal Plan'!K15)</f>
-        <v>870279.59237264</v>
+        <v>2039717.79462337</v>
       </c>
       <c r="D15" s="17" t="n">
         <f aca="false">D14*(1+Inputs!B19)</f>
-        <v>29915.8609878095</v>
+        <v>27196.237261645</v>
       </c>
       <c r="E15" s="17" t="n">
         <f aca="false">E14*(1+Inputs!B19)</f>
-        <v>206691.403188502</v>
+        <v>135981.186308225</v>
       </c>
       <c r="F15" s="17" t="n">
         <f aca="false">MAX(0,F14*(1+Inputs!B19)-'Withdrawal Plan'!M15)</f>
-        <v>229285.619495348</v>
+        <v>210248.253412196</v>
       </c>
       <c r="G15" s="17" t="n">
         <f aca="false">MAX(0,G14*(1+Inputs!B19)-'Withdrawal Plan'!L15)</f>
-        <v>2719623.7261645</v>
+        <v>1359811.86308225</v>
       </c>
       <c r="H15" s="24" t="n">
         <f aca="false">SUM(B15:G15)</f>
-        <v>4087906.34976174</v>
+        <v>5055065.48224064</v>
       </c>
       <c r="I15" s="25" t="n">
         <f aca="false">H15+Inputs!B36</f>
-        <v>4737906.34976174</v>
+        <v>5855065.48224064</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4468,35 +4468,35 @@
       </c>
       <c r="B16" s="17" t="n">
         <f aca="false">'Roth Conversion'!J16</f>
-        <v>0</v>
+        <v>1164218.55124177</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">MAX(0,C15*(1+Inputs!B19)-'Withdrawal Plan'!K16)</f>
-        <v>939901.959762451</v>
+        <v>2202895.21819324</v>
       </c>
       <c r="D16" s="17" t="n">
         <f aca="false">D15*(1+Inputs!B19)</f>
-        <v>32309.1298668342</v>
+        <v>29371.9362425766</v>
       </c>
       <c r="E16" s="17" t="n">
         <f aca="false">E15*(1+Inputs!B19)</f>
-        <v>223226.715443582</v>
+        <v>146859.681212883</v>
       </c>
       <c r="F16" s="17" t="n">
         <f aca="false">MAX(0,F15*(1+Inputs!B19)-'Withdrawal Plan'!M16)</f>
-        <v>243442.327959018</v>
+        <v>222881.972589215</v>
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">MAX(0,G15*(1+Inputs!B19)-'Withdrawal Plan'!L16)</f>
-        <v>2937193.62425766</v>
+        <v>1468596.81212883</v>
       </c>
       <c r="H16" s="24" t="n">
         <f aca="false">SUM(B16:G16)</f>
-        <v>4376073.75728955</v>
+        <v>5234824.17160852</v>
       </c>
       <c r="I16" s="25" t="n">
         <f aca="false">H16+Inputs!B36</f>
-        <v>5026073.75728955</v>
+        <v>6034824.17160852</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4505,35 +4505,35 @@
       </c>
       <c r="B17" s="17" t="n">
         <f aca="false">'Roth Conversion'!J17</f>
-        <v>0</v>
+        <v>1047655.91502281</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">MAX(0,C16*(1+Inputs!B19)-'Withdrawal Plan'!K17)</f>
-        <v>1015094.11654345</v>
+        <v>2379126.8356487</v>
       </c>
       <c r="D17" s="17" t="n">
         <f aca="false">D16*(1+Inputs!B19)</f>
-        <v>34893.860256181</v>
+        <v>31721.6911419827</v>
       </c>
       <c r="E17" s="17" t="n">
         <f aca="false">E16*(1+Inputs!B19)</f>
-        <v>241084.852679069</v>
+        <v>158608.455709914</v>
       </c>
       <c r="F17" s="17" t="n">
         <f aca="false">MAX(0,F16*(1+Inputs!B19)-'Withdrawal Plan'!M17)</f>
-        <v>258522.266044984</v>
+        <v>236317.082245596</v>
       </c>
       <c r="G17" s="17" t="n">
         <f aca="false">MAX(0,G16*(1+Inputs!B19)-'Withdrawal Plan'!L17)</f>
-        <v>3172169.11419827</v>
+        <v>1586084.55709914</v>
       </c>
       <c r="H17" s="24" t="n">
         <f aca="false">SUM(B17:G17)</f>
-        <v>4721764.20972195</v>
+        <v>5439514.53686815</v>
       </c>
       <c r="I17" s="25" t="n">
         <f aca="false">H17+Inputs!B36</f>
-        <v>5371764.20972195</v>
+        <v>6239514.53686815</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4542,35 +4542,35 @@
       </c>
       <c r="B18" s="17" t="n">
         <f aca="false">'Roth Conversion'!J18</f>
-        <v>0</v>
+        <v>932455.462898383</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">MAX(0,C17*(1+Inputs!B19)-'Withdrawal Plan'!K18)</f>
-        <v>1096301.64586692</v>
+        <v>2569456.9825006</v>
       </c>
       <c r="D18" s="17" t="n">
         <f aca="false">D17*(1+Inputs!B19)</f>
-        <v>37685.3690766755</v>
+        <v>34259.4264333413</v>
       </c>
       <c r="E18" s="17" t="n">
         <f aca="false">E17*(1+Inputs!B19)</f>
-        <v>260371.640893394</v>
+        <v>171297.132166707</v>
       </c>
       <c r="F18" s="17" t="n">
         <f aca="false">MAX(0,F17*(1+Inputs!B19)-'Withdrawal Plan'!M18)</f>
-        <v>274588.82677029</v>
+        <v>250607.228266951</v>
       </c>
       <c r="G18" s="17" t="n">
         <f aca="false">MAX(0,G17*(1+Inputs!B19)-'Withdrawal Plan'!L18)</f>
-        <v>3425942.64333413</v>
+        <v>1712971.32166707</v>
       </c>
       <c r="H18" s="24" t="n">
         <f aca="false">SUM(B18:G18)</f>
-        <v>5094890.12594142</v>
+        <v>5671047.55393305</v>
       </c>
       <c r="I18" s="25" t="n">
         <f aca="false">H18+Inputs!B36</f>
-        <v>5744890.12594142</v>
+        <v>6471047.55393305</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4579,35 +4579,35 @@
       </c>
       <c r="B19" s="17" t="n">
         <f aca="false">'Roth Conversion'!J19</f>
-        <v>0</v>
+        <v>818651.249470843</v>
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">MAX(0,C18*(1+Inputs!B19)-'Withdrawal Plan'!K19)</f>
-        <v>1184005.77753628</v>
+        <v>2775013.54110065</v>
       </c>
       <c r="D19" s="17" t="n">
         <f aca="false">D18*(1+Inputs!B19)</f>
-        <v>40700.1986028095</v>
+        <v>37000.1805480087</v>
       </c>
       <c r="E19" s="17" t="n">
         <f aca="false">E18*(1+Inputs!B19)</f>
-        <v>281201.372164866</v>
+        <v>185000.902740043</v>
       </c>
       <c r="F19" s="17" t="n">
         <f aca="false">MAX(0,F18*(1+Inputs!B19)-'Withdrawal Plan'!M19)</f>
-        <v>291709.951325705</v>
+        <v>265809.824942099</v>
       </c>
       <c r="G19" s="17" t="n">
         <f aca="false">MAX(0,G18*(1+Inputs!B19)-'Withdrawal Plan'!L19)</f>
-        <v>3700018.05480087</v>
+        <v>1850009.02740043</v>
       </c>
       <c r="H19" s="24" t="n">
         <f aca="false">SUM(B19:G19)</f>
-        <v>5497635.35443052</v>
+        <v>5931484.72620207</v>
       </c>
       <c r="I19" s="25" t="n">
         <f aca="false">H19+Inputs!B36</f>
-        <v>6147635.35443052</v>
+        <v>6731484.72620207</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4616,35 +4616,35 @@
       </c>
       <c r="B20" s="17" t="n">
         <f aca="false">'Roth Conversion'!J20</f>
-        <v>0</v>
+        <v>706278.180707614</v>
       </c>
       <c r="C20" s="17" t="n">
         <f aca="false">MAX(0,C19*(1+Inputs!B19)-'Withdrawal Plan'!K20)</f>
-        <v>1278726.23973918</v>
+        <v>2997014.6243887</v>
       </c>
       <c r="D20" s="17" t="n">
         <f aca="false">D19*(1+Inputs!B19)</f>
-        <v>43956.2144910343</v>
+        <v>39960.1949918494</v>
       </c>
       <c r="E20" s="17" t="n">
         <f aca="false">E19*(1+Inputs!B19)</f>
-        <v>303697.481938055</v>
+        <v>199800.974959247</v>
       </c>
       <c r="F20" s="17" t="n">
         <f aca="false">MAX(0,F19*(1+Inputs!B19)-'Withdrawal Plan'!M20)</f>
-        <v>309958.466766243</v>
+        <v>281986.330271949</v>
       </c>
       <c r="G20" s="17" t="n">
         <f aca="false">MAX(0,G19*(1+Inputs!B19)-'Withdrawal Plan'!L20)</f>
-        <v>3996019.49918493</v>
+        <v>1998009.74959247</v>
       </c>
       <c r="H20" s="24" t="n">
         <f aca="false">SUM(B20:G20)</f>
-        <v>5932357.90211945</v>
+        <v>6223050.05491183</v>
       </c>
       <c r="I20" s="25" t="n">
         <f aca="false">H20+Inputs!B36</f>
-        <v>6582357.90211945</v>
+        <v>7023050.05491183</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4653,35 +4653,35 @@
       </c>
       <c r="B21" s="17" t="n">
         <f aca="false">'Roth Conversion'!J21</f>
-        <v>0</v>
+        <v>595372.035225304</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">MAX(0,C20*(1+Inputs!B19)-'Withdrawal Plan'!K21)</f>
-        <v>1381024.33891831</v>
+        <v>3236775.7943398</v>
       </c>
       <c r="D21" s="17" t="n">
         <f aca="false">D20*(1+Inputs!B19)</f>
-        <v>47472.711650317</v>
+        <v>43157.0105911973</v>
       </c>
       <c r="E21" s="17" t="n">
         <f aca="false">E20*(1+Inputs!B19)</f>
-        <v>327993.2804931</v>
+        <v>215785.052955986</v>
       </c>
       <c r="F21" s="17" t="n">
         <f aca="false">MAX(0,F20*(1+Inputs!B19)-'Withdrawal Plan'!M21)</f>
-        <v>329412.449408749</v>
+        <v>299202.54199491</v>
       </c>
       <c r="G21" s="17" t="n">
         <f aca="false">MAX(0,G20*(1+Inputs!B19)-'Withdrawal Plan'!L21)</f>
-        <v>4315701.05911973</v>
+        <v>2157850.52955986</v>
       </c>
       <c r="H21" s="24" t="n">
         <f aca="false">SUM(B21:G21)</f>
-        <v>6401603.83959021</v>
+        <v>6548142.96466706</v>
       </c>
       <c r="I21" s="25" t="n">
         <f aca="false">H21+Inputs!B36</f>
-        <v>7051603.83959021</v>
+        <v>7348142.96466706</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4690,35 +4690,35 @@
       </c>
       <c r="B22" s="17" t="n">
         <f aca="false">'Roth Conversion'!J22</f>
-        <v>0</v>
+        <v>485969.486105936</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">MAX(0,C21*(1+Inputs!B19)-'Withdrawal Plan'!K22)</f>
-        <v>1491506.28603178</v>
+        <v>3495717.85788698</v>
       </c>
       <c r="D22" s="17" t="n">
         <f aca="false">D21*(1+Inputs!B19)</f>
-        <v>51270.5285823424</v>
+        <v>46609.5714384931</v>
       </c>
       <c r="E22" s="17" t="n">
         <f aca="false">E21*(1+Inputs!B19)</f>
-        <v>354232.742932547</v>
+        <v>233047.857192465</v>
       </c>
       <c r="F22" s="17" t="n">
         <f aca="false">MAX(0,F21*(1+Inputs!B19)-'Withdrawal Plan'!M22)</f>
-        <v>350155.615927715</v>
+        <v>317528.915920769</v>
       </c>
       <c r="G22" s="17" t="n">
         <f aca="false">MAX(0,G21*(1+Inputs!B19)-'Withdrawal Plan'!L22)</f>
-        <v>4660957.14384931</v>
+        <v>2330478.57192465</v>
       </c>
       <c r="H22" s="24" t="n">
         <f aca="false">SUM(B22:G22)</f>
-        <v>6908122.31732369</v>
+        <v>6909352.2604693</v>
       </c>
       <c r="I22" s="25" t="n">
         <f aca="false">H22+Inputs!B36</f>
-        <v>7558122.31732369</v>
+        <v>7709352.2604693</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4727,35 +4727,35 @@
       </c>
       <c r="B23" s="17" t="n">
         <f aca="false">'Roth Conversion'!J23</f>
-        <v>0</v>
+        <v>378108.123258585</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">MAX(0,C22*(1+Inputs!B19)-'Withdrawal Plan'!K23)</f>
-        <v>1610826.78891432</v>
+        <v>3775375.28651794</v>
       </c>
       <c r="D23" s="17" t="n">
         <f aca="false">D22*(1+Inputs!B19)</f>
-        <v>55372.1708689298</v>
+        <v>50338.3371535725</v>
       </c>
       <c r="E23" s="17" t="n">
         <f aca="false">E22*(1+Inputs!B19)</f>
-        <v>382571.362367151</v>
+        <v>251691.685767863</v>
       </c>
       <c r="F23" s="17" t="n">
         <f aca="false">MAX(0,F22*(1+Inputs!B19)-'Withdrawal Plan'!M23)</f>
-        <v>372277.744296511</v>
+        <v>337040.90828901</v>
       </c>
       <c r="G23" s="17" t="n">
         <f aca="false">MAX(0,G22*(1+Inputs!B19)-'Withdrawal Plan'!L23)</f>
-        <v>5033833.71535725</v>
+        <v>2516916.85767863</v>
       </c>
       <c r="H23" s="24" t="n">
         <f aca="false">SUM(B23:G23)</f>
-        <v>7454881.78180417</v>
+        <v>7309471.1986656</v>
       </c>
       <c r="I23" s="25" t="n">
         <f aca="false">H23+Inputs!B36</f>
-        <v>8104881.78180417</v>
+        <v>8109471.1986656</v>
       </c>
     </row>
   </sheetData>

--- a/retirement_planner.xlsx
+++ b/retirement_planner.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="128">
   <si>
     <t xml:space="preserve">RETIREMENT PLANNING MODEL — INPUTS</t>
   </si>
@@ -282,7 +282,7 @@
 Surplus ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">PORTFOLIO BALANCE PROJECTION  (Ages 65–85)</t>
+    <t xml:space="preserve">PORTFOLIO BALANCE PROJECTION  (Ages 56–85)</t>
   </si>
   <si>
     <t xml:space="preserve">Trad 401k
@@ -315,6 +315,9 @@
   <si>
     <t xml:space="preserve">Net Worth
 +Home ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue rows = working years (accumulation)  ·  Orange rows = RMD years (age 73+)  ·  White/cream = retirement years</t>
   </si>
   <si>
     <t xml:space="preserve">SOCIAL SECURITY START AGE COMPARISON</t>
@@ -446,7 +449,7 @@
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -557,6 +560,14 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF1A3A6B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -570,7 +581,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -616,6 +627,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF0E8"/>
+        <bgColor rgb="FFF8F4ED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF0FB"/>
         <bgColor rgb="FFF8F4ED"/>
       </patternFill>
     </fill>
@@ -682,7 +699,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -787,7 +804,27 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -811,11 +848,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -865,7 +902,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFDF7"/>
-      <rgbColor rgb="FFF8F4ED"/>
+      <rgbColor rgb="FFEAF0FB"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -879,7 +916,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF8F4ED"/>
       <rgbColor rgb="FFEFE9DF"/>
       <rgbColor rgb="FFFFF0E8"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -1131,7 +1168,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>5</v>
@@ -2560,7 +2597,7 @@
         <v>16500</v>
       </c>
       <c r="E3" s="11" t="n">
-        <f aca="false">IF(55&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(60&lt;65,Inputs!B35*12,0)</f>
         <v>9600</v>
       </c>
       <c r="F3" s="11" t="n">
@@ -2576,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="11" t="n">
-        <f aca="false">IF(55&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,55-Inputs!B26),0)</f>
+        <f aca="false">IF(60&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,60-Inputs!B26),0)</f>
         <v>0</v>
       </c>
       <c r="J3" s="11" t="n">
@@ -2625,7 +2662,7 @@
         <v>16500</v>
       </c>
       <c r="E4" s="14" t="n">
-        <f aca="false">IF(56&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(61&lt;65,Inputs!B35*12,0)</f>
         <v>9600</v>
       </c>
       <c r="F4" s="14" t="n">
@@ -2641,7 +2678,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="14" t="n">
-        <f aca="false">IF(56&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,56-Inputs!B26),0)</f>
+        <f aca="false">IF(61&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,61-Inputs!B26),0)</f>
         <v>0</v>
       </c>
       <c r="J4" s="14" t="n">
@@ -2690,7 +2727,7 @@
         <v>16500</v>
       </c>
       <c r="E5" s="11" t="n">
-        <f aca="false">IF(57&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(62&lt;65,Inputs!B35*12,0)</f>
         <v>9600</v>
       </c>
       <c r="F5" s="11" t="n">
@@ -2706,7 +2743,7 @@
         <v>47664</v>
       </c>
       <c r="I5" s="11" t="n">
-        <f aca="false">IF(57&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,57-Inputs!B26),0)</f>
+        <f aca="false">IF(62&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,62-Inputs!B26),0)</f>
         <v>0</v>
       </c>
       <c r="J5" s="11" t="n">
@@ -2755,7 +2792,7 @@
         <v>16500</v>
       </c>
       <c r="E6" s="14" t="n">
-        <f aca="false">IF(58&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(63&lt;65,Inputs!B35*12,0)</f>
         <v>9600</v>
       </c>
       <c r="F6" s="14" t="n">
@@ -2771,7 +2808,7 @@
         <v>48855.6</v>
       </c>
       <c r="I6" s="14" t="n">
-        <f aca="false">IF(58&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,58-Inputs!B26),0)</f>
+        <f aca="false">IF(63&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,63-Inputs!B26),0)</f>
         <v>0</v>
       </c>
       <c r="J6" s="14" t="n">
@@ -2820,7 +2857,7 @@
         <v>16500</v>
       </c>
       <c r="E7" s="11" t="n">
-        <f aca="false">IF(59&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(64&lt;65,Inputs!B35*12,0)</f>
         <v>9600</v>
       </c>
       <c r="F7" s="11" t="n">
@@ -2836,7 +2873,7 @@
         <v>50076.99</v>
       </c>
       <c r="I7" s="11" t="n">
-        <f aca="false">IF(59&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,59-Inputs!B26),0)</f>
+        <f aca="false">IF(64&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,64-Inputs!B26),0)</f>
         <v>0</v>
       </c>
       <c r="J7" s="11" t="n">
@@ -2885,8 +2922,8 @@
         <v>16500</v>
       </c>
       <c r="E8" s="14" t="n">
-        <f aca="false">IF(60&lt;65,Inputs!B35*12,0)</f>
-        <v>9600</v>
+        <f aca="false">IF(65&lt;65,Inputs!B35*12,0)</f>
+        <v>0</v>
       </c>
       <c r="F8" s="14" t="n">
         <f aca="false">Inputs!B33*12*(1+Inputs!B34)^5</f>
@@ -2894,15 +2931,15 @@
       </c>
       <c r="G8" s="22" t="n">
         <f aca="false">B8+C8+D8+E8+F8</f>
-        <v>162312.36730995</v>
+        <v>152712.36730995</v>
       </c>
       <c r="H8" s="14" t="n">
         <f aca="false">IF(70&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,70-Inputs!B25),0)</f>
         <v>51328.91475</v>
       </c>
       <c r="I8" s="14" t="n">
-        <f aca="false">IF(60&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,60-Inputs!B26),0)</f>
-        <v>0</v>
+        <f aca="false">IF(65&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,65-Inputs!B26),0)</f>
+        <v>23832</v>
       </c>
       <c r="J8" s="14" t="n">
         <f aca="false">'Roth Conversion'!E8</f>
@@ -2930,7 +2967,7 @@
       </c>
       <c r="P8" s="23" t="n">
         <f aca="false">H8+I8+J8+K8+L8-G8-N8-O8</f>
-        <v>-19416.7110083113</v>
+        <v>14015.2889916887</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2950,8 +2987,8 @@
         <v>16500</v>
       </c>
       <c r="E9" s="11" t="n">
-        <f aca="false">IF(61&lt;65,Inputs!B35*12,0)</f>
-        <v>9600</v>
+        <f aca="false">IF(66&lt;65,Inputs!B35*12,0)</f>
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">Inputs!B33*12*(1+Inputs!B34)^6</f>
@@ -2959,15 +2996,15 @@
       </c>
       <c r="G9" s="20" t="n">
         <f aca="false">B9+C9+D9+E9+F9</f>
-        <v>165375.405230624</v>
+        <v>155775.405230624</v>
       </c>
       <c r="H9" s="11" t="n">
         <f aca="false">IF(71&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,71-Inputs!B25),0)</f>
         <v>52612.13761875</v>
       </c>
       <c r="I9" s="11" t="n">
-        <f aca="false">IF(61&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,61-Inputs!B26),0)</f>
-        <v>0</v>
+        <f aca="false">IF(66&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,66-Inputs!B26),0)</f>
+        <v>24427.8</v>
       </c>
       <c r="J9" s="11" t="n">
         <f aca="false">'Roth Conversion'!E9</f>
@@ -2995,7 +3032,7 @@
       </c>
       <c r="P9" s="21" t="n">
         <f aca="false">H9+I9+J9+K9+L9-G9-N9-O9</f>
-        <v>-22217.7853964438</v>
+        <v>11810.0146035562</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3015,8 +3052,8 @@
         <v>16500</v>
       </c>
       <c r="E10" s="14" t="n">
-        <f aca="false">IF(62&lt;65,Inputs!B35*12,0)</f>
-        <v>9600</v>
+        <f aca="false">IF(67&lt;65,Inputs!B35*12,0)</f>
+        <v>0</v>
       </c>
       <c r="F10" s="14" t="n">
         <f aca="false">Inputs!B33*12*(1+Inputs!B34)^7</f>
@@ -3024,15 +3061,15 @@
       </c>
       <c r="G10" s="22" t="n">
         <f aca="false">B10+C10+D10+E10+F10</f>
-        <v>168533.167633986</v>
+        <v>158933.167633986</v>
       </c>
       <c r="H10" s="14" t="n">
         <f aca="false">IF(72&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,72-Inputs!B25),0)</f>
         <v>53927.4410592187</v>
       </c>
       <c r="I10" s="14" t="n">
-        <f aca="false">IF(62&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,62-Inputs!B26),0)</f>
-        <v>0</v>
+        <f aca="false">IF(67&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,67-Inputs!B26),0)</f>
+        <v>25038.495</v>
       </c>
       <c r="J10" s="14" t="n">
         <f aca="false">'Roth Conversion'!E10</f>
@@ -3060,7 +3097,7 @@
       </c>
       <c r="P10" s="23" t="n">
         <f aca="false">H10+I10+J10+K10+L10-G10-N10-O10</f>
-        <v>-25107.0351789518</v>
+        <v>9531.45982104821</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3080,8 +3117,8 @@
         <v>16500</v>
       </c>
       <c r="E11" s="17" t="n">
-        <f aca="false">IF(63&lt;65,Inputs!B35*12,0)</f>
-        <v>9600</v>
+        <f aca="false">IF(68&lt;65,Inputs!B35*12,0)</f>
+        <v>0</v>
       </c>
       <c r="F11" s="17" t="n">
         <f aca="false">Inputs!B33*12*(1+Inputs!B34)^8</f>
@@ -3089,15 +3126,15 @@
       </c>
       <c r="G11" s="24" t="n">
         <f aca="false">B11+C11+D11+E11+F11</f>
-        <v>171788.637921772</v>
+        <v>162188.637921772</v>
       </c>
       <c r="H11" s="17" t="n">
         <f aca="false">IF(73&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,73-Inputs!B25),0)</f>
         <v>55275.6270856992</v>
       </c>
       <c r="I11" s="17" t="n">
-        <f aca="false">IF(63&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,63-Inputs!B26),0)</f>
-        <v>0</v>
+        <f aca="false">IF(68&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,68-Inputs!B26),0)</f>
+        <v>25664.457375</v>
       </c>
       <c r="J11" s="17" t="n">
         <f aca="false">'Roth Conversion'!E11</f>
@@ -3125,7 +3162,7 @@
       </c>
       <c r="P11" s="25" t="n">
         <f aca="false">H11+I11+J11+K11+L11-G11-N11-O11</f>
-        <v>-28087.2800303614</v>
+        <v>7177.17734463854</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3145,8 +3182,8 @@
         <v>16500</v>
       </c>
       <c r="E12" s="17" t="n">
-        <f aca="false">IF(64&lt;65,Inputs!B35*12,0)</f>
-        <v>9600</v>
+        <f aca="false">IF(69&lt;65,Inputs!B35*12,0)</f>
+        <v>0</v>
       </c>
       <c r="F12" s="17" t="n">
         <f aca="false">Inputs!B33*12*(1+Inputs!B34)^9</f>
@@ -3154,15 +3191,15 @@
       </c>
       <c r="G12" s="24" t="n">
         <f aca="false">B12+C12+D12+E12+F12</f>
-        <v>175144.896081129</v>
+        <v>165544.896081129</v>
       </c>
       <c r="H12" s="17" t="n">
         <f aca="false">IF(74&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,74-Inputs!B25),0)</f>
         <v>56657.5177628417</v>
       </c>
       <c r="I12" s="17" t="n">
-        <f aca="false">IF(64&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,64-Inputs!B26),0)</f>
-        <v>0</v>
+        <f aca="false">IF(69&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,69-Inputs!B26),0)</f>
+        <v>26306.068809375</v>
       </c>
       <c r="J12" s="17" t="n">
         <f aca="false">'Roth Conversion'!E12</f>
@@ -3190,7 +3227,7 @@
       </c>
       <c r="P12" s="25" t="n">
         <f aca="false">H12+I12+J12+K12+L12-G12-N12-O12</f>
-        <v>-31161.4321174336</v>
+        <v>4744.63669194142</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3210,7 +3247,7 @@
         <v>16500</v>
       </c>
       <c r="E13" s="17" t="n">
-        <f aca="false">IF(65&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(70&lt;65,Inputs!B35*12,0)</f>
         <v>0</v>
       </c>
       <c r="F13" s="17" t="n">
@@ -3226,8 +3263,8 @@
         <v>58073.9557069127</v>
       </c>
       <c r="I13" s="17" t="n">
-        <f aca="false">IF(65&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,65-Inputs!B26),0)</f>
-        <v>23832</v>
+        <f aca="false">IF(70&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,70-Inputs!B26),0)</f>
+        <v>26963.7205296094</v>
       </c>
       <c r="J13" s="17" t="n">
         <f aca="false">'Roth Conversion'!E13</f>
@@ -3255,7 +3292,7 @@
       </c>
       <c r="P13" s="25" t="n">
         <f aca="false">H13+I13+J13+K13+L13-G13-N13-O13</f>
-        <v>-900.499248564507</v>
+        <v>2231.22128104485</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3275,7 +3312,7 @@
         <v>16500</v>
       </c>
       <c r="E14" s="17" t="n">
-        <f aca="false">IF(66&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(71&lt;65,Inputs!B35*12,0)</f>
         <v>0</v>
       </c>
       <c r="F14" s="17" t="n">
@@ -3291,8 +3328,8 @@
         <v>59525.8045995855</v>
       </c>
       <c r="I14" s="17" t="n">
-        <f aca="false">IF(66&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,66-Inputs!B26),0)</f>
-        <v>24427.8</v>
+        <f aca="false">IF(71&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,71-Inputs!B26),0)</f>
+        <v>27637.8135428496</v>
       </c>
       <c r="J14" s="17" t="n">
         <f aca="false">'Roth Conversion'!E14</f>
@@ -3320,7 +3357,7 @@
       </c>
       <c r="P14" s="25" t="n">
         <f aca="false">H14+I14+J14+K14+L14-G14-N14-O14</f>
-        <v>-3575.78813588932</v>
+        <v>-365.774593039748</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3340,7 +3377,7 @@
         <v>16500</v>
       </c>
       <c r="E15" s="17" t="n">
-        <f aca="false">IF(67&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(72&lt;65,Inputs!B35*12,0)</f>
         <v>0</v>
       </c>
       <c r="F15" s="17" t="n">
@@ -3356,8 +3393,8 @@
         <v>61013.9497145751</v>
       </c>
       <c r="I15" s="17" t="n">
-        <f aca="false">IF(67&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,67-Inputs!B26),0)</f>
-        <v>25038.495</v>
+        <f aca="false">IF(72&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,72-Inputs!B26),0)</f>
+        <v>28328.7588814208</v>
       </c>
       <c r="J15" s="17" t="n">
         <f aca="false">'Roth Conversion'!E15</f>
@@ -3385,7 +3422,7 @@
       </c>
       <c r="P15" s="25" t="n">
         <f aca="false">H15+I15+J15+K15+L15-G15-N15-O15</f>
-        <v>-6339.4127743663</v>
+        <v>-3049.14889294547</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3405,7 +3442,7 @@
         <v>16500</v>
       </c>
       <c r="E16" s="17" t="n">
-        <f aca="false">IF(68&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(73&lt;65,Inputs!B35*12,0)</f>
         <v>0</v>
       </c>
       <c r="F16" s="17" t="n">
@@ -3421,8 +3458,8 @@
         <v>62539.2984574395</v>
       </c>
       <c r="I16" s="17" t="n">
-        <f aca="false">IF(68&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,68-Inputs!B26),0)</f>
-        <v>25664.457375</v>
+        <f aca="false">IF(73&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,73-Inputs!B26),0)</f>
+        <v>29036.9778534564</v>
       </c>
       <c r="J16" s="17" t="n">
         <f aca="false">'Roth Conversion'!E16</f>
@@ -3450,7 +3487,7 @@
       </c>
       <c r="P16" s="25" t="n">
         <f aca="false">H16+I16+J16+K16+L16-G16-N16-O16</f>
-        <v>-9194.31556729504</v>
+        <v>-5821.79508883867</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3470,7 +3507,7 @@
         <v>16500</v>
       </c>
       <c r="E17" s="17" t="n">
-        <f aca="false">IF(69&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(74&lt;65,Inputs!B35*12,0)</f>
         <v>0</v>
       </c>
       <c r="F17" s="17" t="n">
@@ -3486,8 +3523,8 @@
         <v>64102.7809188755</v>
       </c>
       <c r="I17" s="17" t="n">
-        <f aca="false">IF(69&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,69-Inputs!B26),0)</f>
-        <v>26306.068809375</v>
+        <f aca="false">IF(74&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,74-Inputs!B26),0)</f>
+        <v>29762.9022997928</v>
       </c>
       <c r="J17" s="17" t="n">
         <f aca="false">'Roth Conversion'!E17</f>
@@ -3515,7 +3552,7 @@
       </c>
       <c r="P17" s="25" t="n">
         <f aca="false">H17+I17+J17+K17+L17-G17-N17-O17</f>
-        <v>-12143.539018526</v>
+        <v>-8686.70552810827</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3535,7 +3572,7 @@
         <v>16500</v>
       </c>
       <c r="E18" s="17" t="n">
-        <f aca="false">IF(70&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(75&lt;65,Inputs!B35*12,0)</f>
         <v>0</v>
       </c>
       <c r="F18" s="17" t="n">
@@ -3551,8 +3588,8 @@
         <v>65705.3504418474</v>
       </c>
       <c r="I18" s="17" t="n">
-        <f aca="false">IF(70&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,70-Inputs!B26),0)</f>
-        <v>26963.7205296094</v>
+        <f aca="false">IF(75&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,75-Inputs!B26),0)</f>
+        <v>30506.9748572876</v>
       </c>
       <c r="J18" s="17" t="n">
         <f aca="false">'Roth Conversion'!E18</f>
@@ -3580,7 +3617,7 @@
       </c>
       <c r="P18" s="25" t="n">
         <f aca="false">H18+I18+J18+K18+L18-G18-N18-O18</f>
-        <v>-15190.2292571972</v>
+        <v>-11646.974929519</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3600,7 +3637,7 @@
         <v>16500</v>
       </c>
       <c r="E19" s="17" t="n">
-        <f aca="false">IF(71&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(76&lt;65,Inputs!B35*12,0)</f>
         <v>0</v>
       </c>
       <c r="F19" s="17" t="n">
@@ -3616,8 +3653,8 @@
         <v>67347.9842028936</v>
       </c>
       <c r="I19" s="17" t="n">
-        <f aca="false">IF(71&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,71-Inputs!B26),0)</f>
-        <v>27637.8135428496</v>
+        <f aca="false">IF(76&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,76-Inputs!B26),0)</f>
+        <v>31269.6492287198</v>
       </c>
       <c r="J19" s="17" t="n">
         <f aca="false">'Roth Conversion'!E19</f>
@@ -3645,7 +3682,7 @@
       </c>
       <c r="P19" s="25" t="n">
         <f aca="false">H19+I19+J19+K19+L19-G19-N19-O19</f>
-        <v>-18337.6396925568</v>
+        <v>-14705.8040066866</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3665,7 +3702,7 @@
         <v>16500</v>
       </c>
       <c r="E20" s="17" t="n">
-        <f aca="false">IF(72&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(77&lt;65,Inputs!B35*12,0)</f>
         <v>0</v>
       </c>
       <c r="F20" s="17" t="n">
@@ -3681,8 +3718,8 @@
         <v>69031.6838079659</v>
       </c>
       <c r="I20" s="17" t="n">
-        <f aca="false">IF(72&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,72-Inputs!B26),0)</f>
-        <v>28328.7588814208</v>
+        <f aca="false">IF(77&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,77-Inputs!B26),0)</f>
+        <v>32051.3904594378</v>
       </c>
       <c r="J20" s="17" t="n">
         <f aca="false">'Roth Conversion'!E20</f>
@@ -3710,7 +3747,7 @@
       </c>
       <c r="P20" s="25" t="n">
         <f aca="false">H20+I20+J20+K20+L20-G20-N20-O20</f>
-        <v>-21589.1348039474</v>
+        <v>-17866.5032259305</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3730,7 +3767,7 @@
         <v>16500</v>
       </c>
       <c r="E21" s="17" t="n">
-        <f aca="false">IF(73&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(78&lt;65,Inputs!B35*12,0)</f>
         <v>0</v>
       </c>
       <c r="F21" s="17" t="n">
@@ -3746,8 +3783,8 @@
         <v>70757.475903165</v>
       </c>
       <c r="I21" s="17" t="n">
-        <f aca="false">IF(73&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,73-Inputs!B26),0)</f>
-        <v>29036.9778534564</v>
+        <f aca="false">IF(78&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,78-Inputs!B26),0)</f>
+        <v>32852.6752209237</v>
       </c>
       <c r="J21" s="17" t="n">
         <f aca="false">'Roth Conversion'!E21</f>
@@ -3775,7 +3812,7 @@
       </c>
       <c r="P21" s="25" t="n">
         <f aca="false">H21+I21+J21+K21+L21-G21-N21-O21</f>
-        <v>-24948.1940712382</v>
+        <v>-21132.4967037709</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3795,7 +3832,7 @@
         <v>16500</v>
       </c>
       <c r="E22" s="17" t="n">
-        <f aca="false">IF(74&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(79&lt;65,Inputs!B35*12,0)</f>
         <v>0</v>
       </c>
       <c r="F22" s="17" t="n">
@@ -3811,8 +3848,8 @@
         <v>72526.4128007442</v>
       </c>
       <c r="I22" s="17" t="n">
-        <f aca="false">IF(74&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,74-Inputs!B26),0)</f>
-        <v>29762.9022997928</v>
+        <f aca="false">IF(79&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,79-Inputs!B26),0)</f>
+        <v>33673.9921014468</v>
       </c>
       <c r="J22" s="17" t="n">
         <f aca="false">'Roth Conversion'!E22</f>
@@ -3840,7 +3877,7 @@
       </c>
       <c r="P22" s="25" t="n">
         <f aca="false">H22+I22+J22+K22+L22-G22-N22-O22</f>
-        <v>-28418.4160512098</v>
+        <v>-24507.3262495558</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3860,7 +3897,7 @@
         <v>16500</v>
       </c>
       <c r="E23" s="17" t="n">
-        <f aca="false">IF(75&lt;65,Inputs!B35*12,0)</f>
+        <f aca="false">IF(80&lt;65,Inputs!B35*12,0)</f>
         <v>0</v>
       </c>
       <c r="F23" s="17" t="n">
@@ -3876,8 +3913,8 @@
         <v>74339.5731207628</v>
       </c>
       <c r="I23" s="17" t="n">
-        <f aca="false">IF(75&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,75-Inputs!B26),0)</f>
-        <v>30506.9748572876</v>
+        <f aca="false">IF(80&gt;=Inputs!B26,Inputs!B23*12*0.5*(1+Inputs!B21)^MAX(0,80-Inputs!B26),0)</f>
+        <v>34515.8419039829</v>
       </c>
       <c r="J23" s="17" t="n">
         <f aca="false">'Roth Conversion'!E23</f>
@@ -3905,7 +3942,7 @@
       </c>
       <c r="P23" s="25" t="n">
         <f aca="false">H23+I23+J23+K23+L23-G23-N23-O23</f>
-        <v>-32003.5226056258</v>
+        <v>-27994.6555589304</v>
       </c>
     </row>
   </sheetData>
@@ -3928,7 +3965,7 @@
     <tabColor rgb="FF1A3A6B"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -3982,644 +4019,644 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="n">
+      <c r="A3" s="26" t="n">
+        <v>56</v>
+      </c>
+      <c r="B3" s="27" t="n">
+        <f aca="false">Inputs!B9+Inputs!B11*(1+Inputs!B12/100)</f>
+        <v>3037518.75</v>
+      </c>
+      <c r="C3" s="27" t="n">
+        <f aca="false">(Inputs!B10+Inputs!B13)*(1+Inputs!B19)</f>
+        <v>810000</v>
+      </c>
+      <c r="D3" s="27" t="n">
+        <f aca="false">Inputs!E11*(1+Inputs!B19)</f>
+        <v>10800</v>
+      </c>
+      <c r="E3" s="27" t="n">
+        <f aca="false">Inputs!E10*(1+Inputs!B19)</f>
+        <v>54000</v>
+      </c>
+      <c r="F3" s="27" t="n">
+        <f aca="false">(Inputs!B14+Inputs!B15)*(1+Inputs!B19)</f>
+        <v>116640</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <f aca="false">Inputs!B16*(1+Inputs!B19)</f>
+        <v>540000</v>
+      </c>
+      <c r="H3" s="28" t="n">
+        <f aca="false">SUM(B3:G3)</f>
+        <v>4568958.75</v>
+      </c>
+      <c r="I3" s="29" t="n">
+        <f aca="false">H3+Inputs!B36</f>
+        <v>5368958.75</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="B4" s="27" t="n">
+        <f aca="false">B3*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <v>3318039</v>
+      </c>
+      <c r="C4" s="27" t="n">
+        <f aca="false">C3*(1+Inputs!B19)</f>
+        <v>874800</v>
+      </c>
+      <c r="D4" s="27" t="n">
+        <f aca="false">D3*(1+Inputs!B19)</f>
+        <v>11664</v>
+      </c>
+      <c r="E4" s="27" t="n">
+        <f aca="false">E3*(1+Inputs!B19)</f>
+        <v>58320</v>
+      </c>
+      <c r="F4" s="27" t="n">
+        <f aca="false">(F3+Inputs!B15)*(1+Inputs!B19)</f>
+        <v>134611.2</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <f aca="false">G3*(1+Inputs!B19)</f>
+        <v>583200</v>
+      </c>
+      <c r="H4" s="28" t="n">
+        <f aca="false">SUM(B4:G4)</f>
+        <v>4980634.2</v>
+      </c>
+      <c r="I4" s="29" t="n">
+        <f aca="false">H4+Inputs!B36</f>
+        <v>5780634.2</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="26" t="n">
+        <v>58</v>
+      </c>
+      <c r="B5" s="27" t="n">
+        <f aca="false">B4*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <v>3621000.87</v>
+      </c>
+      <c r="C5" s="27" t="n">
+        <f aca="false">C4*(1+Inputs!B19)</f>
+        <v>944784</v>
+      </c>
+      <c r="D5" s="27" t="n">
+        <f aca="false">D4*(1+Inputs!B19)</f>
+        <v>12597.12</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <f aca="false">E4*(1+Inputs!B19)</f>
+        <v>62985.6</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <f aca="false">(F4+Inputs!B15)*(1+Inputs!B19)</f>
+        <v>154020.096</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <f aca="false">G4*(1+Inputs!B19)</f>
+        <v>629856</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <f aca="false">SUM(B5:G5)</f>
+        <v>5425243.686</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <f aca="false">H5+Inputs!B36</f>
+        <v>6225243.686</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="B6" s="27" t="n">
+        <f aca="false">B5*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <v>3948199.6896</v>
+      </c>
+      <c r="C6" s="27" t="n">
+        <f aca="false">C5*(1+Inputs!B19)</f>
+        <v>1020366.72</v>
+      </c>
+      <c r="D6" s="27" t="n">
+        <f aca="false">D5*(1+Inputs!B19)</f>
+        <v>13604.8896</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <f aca="false">E5*(1+Inputs!B19)</f>
+        <v>68024.448</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <f aca="false">(F5+Inputs!B15)*(1+Inputs!B19)</f>
+        <v>174981.70368</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <f aca="false">G5*(1+Inputs!B19)</f>
+        <v>680244.48</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <f aca="false">SUM(B6:G6)</f>
+        <v>5905421.93088</v>
+      </c>
+      <c r="I6" s="29" t="n">
+        <f aca="false">H6+Inputs!B36</f>
+        <v>6705421.93088</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="26" t="n">
+        <v>60</v>
+      </c>
+      <c r="B7" s="27" t="n">
+        <f aca="false">B6*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <v>4301574.414768</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <f aca="false">C6*(1+Inputs!B19)</f>
+        <v>1101996.0576</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <f aca="false">D6*(1+Inputs!B19)</f>
+        <v>14693.280768</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <f aca="false">E6*(1+Inputs!B19)</f>
+        <v>73466.40384</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <f aca="false">(F6+Inputs!B15)*(1+Inputs!B19)</f>
+        <v>197620.2399744</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <f aca="false">G6*(1+Inputs!B19)</f>
+        <v>734664.0384</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <f aca="false">SUM(B7:G7)</f>
+        <v>6424014.4353504</v>
+      </c>
+      <c r="I7" s="29" t="n">
+        <f aca="false">H7+Inputs!B36</f>
+        <v>7224014.4353504</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="26" t="n">
+        <v>61</v>
+      </c>
+      <c r="B8" s="27" t="n">
+        <f aca="false">B7*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <v>4683219.11794944</v>
+      </c>
+      <c r="C8" s="27" t="n">
+        <f aca="false">C7*(1+Inputs!B19)</f>
+        <v>1190155.742208</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <f aca="false">D7*(1+Inputs!B19)</f>
+        <v>15868.74322944</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <f aca="false">E7*(1+Inputs!B19)</f>
+        <v>79343.7161472</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <f aca="false">(F7+Inputs!B15)*(1+Inputs!B19)</f>
+        <v>222069.859172352</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <f aca="false">G7*(1+Inputs!B19)</f>
+        <v>793437.161472</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <f aca="false">SUM(B8:G8)</f>
+        <v>6984094.34017843</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <f aca="false">H8+Inputs!B36</f>
+        <v>7784094.34017843</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="B9" s="27" t="n">
+        <f aca="false">B8*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <v>5095395.3973854</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <f aca="false">C8*(1+Inputs!B19)</f>
+        <v>1285368.20158464</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <f aca="false">D8*(1+Inputs!B19)</f>
+        <v>17138.2426877952</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <f aca="false">E8*(1+Inputs!B19)</f>
+        <v>85691.213438976</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <f aca="false">(F8+Inputs!B15)*(1+Inputs!B19)</f>
+        <v>248475.44790614</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <f aca="false">G8*(1+Inputs!B19)</f>
+        <v>856912.13438976</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <f aca="false">SUM(B9:G9)</f>
+        <v>7588980.63739271</v>
+      </c>
+      <c r="I9" s="29" t="n">
+        <f aca="false">H9+Inputs!B36</f>
+        <v>8388980.63739271</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26" t="n">
+        <v>63</v>
+      </c>
+      <c r="B10" s="27" t="n">
+        <f aca="false">B9*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <v>5540545.77917623</v>
+      </c>
+      <c r="C10" s="27" t="n">
+        <f aca="false">C9*(1+Inputs!B19)</f>
+        <v>1388197.65771141</v>
+      </c>
+      <c r="D10" s="27" t="n">
+        <f aca="false">D9*(1+Inputs!B19)</f>
+        <v>18509.3021028188</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <f aca="false">E9*(1+Inputs!B19)</f>
+        <v>92546.5105140941</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <f aca="false">(F9+Inputs!B15)*(1+Inputs!B19)</f>
+        <v>276993.483738632</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <f aca="false">G9*(1+Inputs!B19)</f>
+        <v>925465.105140941</v>
+      </c>
+      <c r="H10" s="28" t="n">
+        <f aca="false">SUM(B10:G10)</f>
+        <v>8242257.83838413</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <f aca="false">H10+Inputs!B36</f>
+        <v>9042257.83838413</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="n">
+        <v>64</v>
+      </c>
+      <c r="B11" s="27" t="n">
+        <f aca="false">B10*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <v>6021308.19151033</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <f aca="false">C10*(1+Inputs!B19)</f>
+        <v>1499253.47032833</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <f aca="false">D10*(1+Inputs!B19)</f>
+        <v>19990.0462710443</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <f aca="false">E10*(1+Inputs!B19)</f>
+        <v>99950.2313552217</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <f aca="false">(F10+Inputs!B15)*(1+Inputs!B19)</f>
+        <v>307792.962437722</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <f aca="false">G10*(1+Inputs!B19)</f>
+        <v>999502.313552217</v>
+      </c>
+      <c r="H11" s="28" t="n">
+        <f aca="false">SUM(B11:G11)</f>
+        <v>8947797.21545486</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <f aca="false">H11+Inputs!B36</f>
+        <v>9747797.21545486</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="B3" s="11" t="n">
+      <c r="B12" s="14" t="n">
         <f aca="false">'Roth Conversion'!J3</f>
         <v>2828950</v>
       </c>
-      <c r="C3" s="11" t="n">
-        <f aca="false">(Inputs!B10+Inputs!B13)*(1+Inputs!B19)-'Withdrawal Plan'!K3</f>
-        <v>810000</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <f aca="false">Inputs!E11*(1+Inputs!B19)</f>
-        <v>10800</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <f aca="false">Inputs!E10*(1+Inputs!B19)</f>
-        <v>54000</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <f aca="false">MAX(0,Inputs!B14*(1+Inputs!B19)-'Withdrawal Plan'!M3)</f>
-        <v>105780</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <f aca="false">MAX(0,Inputs!B16*(1+Inputs!B19)-'Withdrawal Plan'!L3)</f>
-        <v>540000</v>
-      </c>
-      <c r="H3" s="20" t="n">
-        <f aca="false">SUM(B3:G3)</f>
-        <v>4349530</v>
-      </c>
-      <c r="I3" s="21" t="n">
-        <f aca="false">H3+Inputs!B36</f>
-        <v>5149530</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="n">
+      <c r="C12" s="14" t="n">
+        <f aca="false">MAX(0,C11*(1+Inputs!B19)-'Withdrawal Plan'!K3)</f>
+        <v>1619193.74795459</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <f aca="false">D11*(1+Inputs!B19)</f>
+        <v>21589.2499727279</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <f aca="false">E11*(1+Inputs!B19)</f>
+        <v>107946.249863639</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <f aca="false">MAX(0,F11*(1+Inputs!B19)-'Withdrawal Plan'!M3)</f>
+        <v>330196.39943274</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <f aca="false">MAX(0,G11*(1+Inputs!B19)-'Withdrawal Plan'!L3)</f>
+        <v>1079462.49863639</v>
+      </c>
+      <c r="H12" s="22" t="n">
+        <f aca="false">SUM(B12:G12)</f>
+        <v>5987338.14586009</v>
+      </c>
+      <c r="I12" s="23" t="n">
+        <f aca="false">H12+Inputs!B36</f>
+        <v>6787338.14586009</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B13" s="11" t="n">
         <f aca="false">'Roth Conversion'!J4</f>
         <v>2657900</v>
       </c>
-      <c r="C4" s="14" t="n">
-        <f aca="false">MAX(0,C3*(1+Inputs!B19)-'Withdrawal Plan'!K4)</f>
-        <v>874800</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <f aca="false">D3*(1+Inputs!B19)</f>
-        <v>11664</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <f aca="false">E3*(1+Inputs!B19)</f>
-        <v>58320</v>
-      </c>
-      <c r="F4" s="14" t="n">
-        <f aca="false">MAX(0,F3*(1+Inputs!B19)-'Withdrawal Plan'!M4)</f>
-        <v>111911.4</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <f aca="false">MAX(0,G3*(1+Inputs!B19)-'Withdrawal Plan'!L4)</f>
-        <v>583200</v>
-      </c>
-      <c r="H4" s="22" t="n">
-        <f aca="false">SUM(B4:G4)</f>
-        <v>4297795.4</v>
-      </c>
-      <c r="I4" s="23" t="n">
-        <f aca="false">H4+Inputs!B36</f>
-        <v>5097795.4</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="n">
+      <c r="C13" s="11" t="n">
+        <f aca="false">MAX(0,C12*(1+Inputs!B19)-'Withdrawal Plan'!K4)</f>
+        <v>1748729.24779096</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <f aca="false">D12*(1+Inputs!B19)</f>
+        <v>23316.3899705461</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <f aca="false">E12*(1+Inputs!B19)</f>
+        <v>116581.949852731</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <f aca="false">MAX(0,F12*(1+Inputs!B19)-'Withdrawal Plan'!M4)</f>
+        <v>354281.111387359</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <f aca="false">MAX(0,G12*(1+Inputs!B19)-'Withdrawal Plan'!L4)</f>
+        <v>1165819.49852731</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <f aca="false">SUM(B13:G13)</f>
+        <v>6066628.1975289</v>
+      </c>
+      <c r="I13" s="21" t="n">
+        <f aca="false">H13+Inputs!B36</f>
+        <v>6866628.1975289</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B14" s="14" t="n">
         <f aca="false">'Roth Conversion'!J5</f>
         <v>2527364.4</v>
       </c>
-      <c r="C5" s="11" t="n">
-        <f aca="false">MAX(0,C4*(1+Inputs!B19)-'Withdrawal Plan'!K5)</f>
-        <v>944784</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <f aca="false">D4*(1+Inputs!B19)</f>
-        <v>12597.12</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <f aca="false">E4*(1+Inputs!B19)</f>
-        <v>62985.6</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <f aca="false">MAX(0,F4*(1+Inputs!B19)-'Withdrawal Plan'!M5)</f>
-        <v>118416.762</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <f aca="false">MAX(0,G4*(1+Inputs!B19)-'Withdrawal Plan'!L5)</f>
-        <v>629856</v>
-      </c>
-      <c r="H5" s="20" t="n">
-        <f aca="false">SUM(B5:G5)</f>
-        <v>4296003.882</v>
-      </c>
-      <c r="I5" s="21" t="n">
-        <f aca="false">H5+Inputs!B36</f>
-        <v>5096003.882</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="n">
+      <c r="C14" s="14" t="n">
+        <f aca="false">MAX(0,C13*(1+Inputs!B19)-'Withdrawal Plan'!K5)</f>
+        <v>1888627.58761424</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <f aca="false">D13*(1+Inputs!B19)</f>
+        <v>25181.7011681898</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <f aca="false">E13*(1+Inputs!B19)</f>
+        <v>125908.505840949</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <f aca="false">MAX(0,F13*(1+Inputs!B19)-'Withdrawal Plan'!M5)</f>
+        <v>380176.050298348</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <f aca="false">MAX(0,G13*(1+Inputs!B19)-'Withdrawal Plan'!L5)</f>
+        <v>1259085.05840949</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <f aca="false">SUM(B14:G14)</f>
+        <v>6206343.30333121</v>
+      </c>
+      <c r="I14" s="23" t="n">
+        <f aca="false">H14+Inputs!B36</f>
+        <v>7006343.30333121</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B15" s="11" t="n">
         <f aca="false">'Roth Conversion'!J6</f>
         <v>2397841.66</v>
       </c>
-      <c r="C6" s="14" t="n">
-        <f aca="false">MAX(0,C5*(1+Inputs!B19)-'Withdrawal Plan'!K6)</f>
-        <v>1020366.72</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <f aca="false">D5*(1+Inputs!B19)</f>
-        <v>13604.8896</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <f aca="false">E5*(1+Inputs!B19)</f>
-        <v>68024.448</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <f aca="false">MAX(0,F5*(1+Inputs!B19)-'Withdrawal Plan'!M6)</f>
-        <v>125320.17546</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <f aca="false">MAX(0,G5*(1+Inputs!B19)-'Withdrawal Plan'!L6)</f>
-        <v>680244.48</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <f aca="false">SUM(B6:G6)</f>
-        <v>4305402.37306</v>
-      </c>
-      <c r="I6" s="23" t="n">
-        <f aca="false">H6+Inputs!B36</f>
-        <v>5105402.37306</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="n">
+      <c r="C15" s="11" t="n">
+        <f aca="false">MAX(0,C14*(1+Inputs!B19)-'Withdrawal Plan'!K6)</f>
+        <v>2039717.79462337</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <f aca="false">D14*(1+Inputs!B19)</f>
+        <v>27196.237261645</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <f aca="false">E14*(1+Inputs!B19)</f>
+        <v>135981.186308225</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <f aca="false">MAX(0,F14*(1+Inputs!B19)-'Withdrawal Plan'!M6)</f>
+        <v>408020.206822216</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <f aca="false">MAX(0,G14*(1+Inputs!B19)-'Withdrawal Plan'!L6)</f>
+        <v>1359811.86308225</v>
+      </c>
+      <c r="H15" s="20" t="n">
+        <f aca="false">SUM(B15:G15)</f>
+        <v>6368568.94809771</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <f aca="false">H15+Inputs!B36</f>
+        <v>7168568.94809771</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="n">
         <v>69</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B16" s="14" t="n">
         <f aca="false">'Roth Conversion'!J7</f>
         <v>2269357.1015</v>
       </c>
-      <c r="C7" s="11" t="n">
-        <f aca="false">MAX(0,C6*(1+Inputs!B19)-'Withdrawal Plan'!K7)</f>
-        <v>1101996.0576</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <f aca="false">D6*(1+Inputs!B19)</f>
-        <v>14693.280768</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <f aca="false">E6*(1+Inputs!B19)</f>
-        <v>73466.40384</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <f aca="false">MAX(0,F6*(1+Inputs!B19)-'Withdrawal Plan'!M7)</f>
-        <v>132647.3656218</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <f aca="false">MAX(0,G6*(1+Inputs!B19)-'Withdrawal Plan'!L7)</f>
-        <v>734664.0384</v>
-      </c>
-      <c r="H7" s="20" t="n">
-        <f aca="false">SUM(B7:G7)</f>
-        <v>4326824.2477298</v>
-      </c>
-      <c r="I7" s="21" t="n">
-        <f aca="false">H7+Inputs!B36</f>
-        <v>5126824.2477298</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="n">
+      <c r="C16" s="14" t="n">
+        <f aca="false">MAX(0,C15*(1+Inputs!B19)-'Withdrawal Plan'!K7)</f>
+        <v>2202895.21819324</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <f aca="false">D15*(1+Inputs!B19)</f>
+        <v>29371.9362425766</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <f aca="false">E15*(1+Inputs!B19)</f>
+        <v>146859.681212883</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <f aca="false">MAX(0,F15*(1+Inputs!B19)-'Withdrawal Plan'!M7)</f>
+        <v>437963.399492993</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <f aca="false">MAX(0,G15*(1+Inputs!B19)-'Withdrawal Plan'!L7)</f>
+        <v>1468596.81212883</v>
+      </c>
+      <c r="H16" s="22" t="n">
+        <f aca="false">SUM(B16:G16)</f>
+        <v>6555044.14877053</v>
+      </c>
+      <c r="I16" s="23" t="n">
+        <f aca="false">H16+Inputs!B36</f>
+        <v>7355044.14877053</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B17" s="11" t="n">
         <f aca="false">'Roth Conversion'!J8</f>
         <v>2141936.6790375</v>
       </c>
-      <c r="C8" s="14" t="n">
-        <f aca="false">MAX(0,C7*(1+Inputs!B19)-'Withdrawal Plan'!K8)</f>
-        <v>1190155.742208</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <f aca="false">D7*(1+Inputs!B19)</f>
-        <v>15868.74322944</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <f aca="false">E7*(1+Inputs!B19)</f>
-        <v>79343.7161472</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <f aca="false">MAX(0,F7*(1+Inputs!B19)-'Withdrawal Plan'!M8)</f>
-        <v>140425.809802794</v>
-      </c>
-      <c r="G8" s="14" t="n">
-        <f aca="false">MAX(0,G7*(1+Inputs!B19)-'Withdrawal Plan'!L8)</f>
-        <v>793437.161472</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <f aca="false">SUM(B8:G8)</f>
-        <v>4361167.85189694</v>
-      </c>
-      <c r="I8" s="23" t="n">
-        <f aca="false">H8+Inputs!B36</f>
-        <v>5161167.85189694</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="n">
+      <c r="C17" s="11" t="n">
+        <f aca="false">MAX(0,C16*(1+Inputs!B19)-'Withdrawal Plan'!K8)</f>
+        <v>2379126.8356487</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <f aca="false">D16*(1+Inputs!B19)</f>
+        <v>31721.6911419827</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <f aca="false">E16*(1+Inputs!B19)</f>
+        <v>158608.455709914</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <f aca="false">MAX(0,F16*(1+Inputs!B19)-'Withdrawal Plan'!M8)</f>
+        <v>470167.126383683</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <f aca="false">MAX(0,G16*(1+Inputs!B19)-'Withdrawal Plan'!L8)</f>
+        <v>1586084.55709914</v>
+      </c>
+      <c r="H17" s="20" t="n">
+        <f aca="false">SUM(B17:G17)</f>
+        <v>6767645.34502092</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <f aca="false">H17+Inputs!B36</f>
+        <v>7567645.34502092</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="n">
         <v>71</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B18" s="14" t="n">
         <f aca="false">'Roth Conversion'!J9</f>
         <v>2015606.99601344</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <f aca="false">MAX(0,C8*(1+Inputs!B19)-'Withdrawal Plan'!K9)</f>
-        <v>1285368.20158464</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <f aca="false">D8*(1+Inputs!B19)</f>
-        <v>17138.2426877952</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <f aca="false">E8*(1+Inputs!B19)</f>
-        <v>85691.213438976</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <f aca="false">MAX(0,F8*(1+Inputs!B19)-'Withdrawal Plan'!M9)</f>
-        <v>148684.86226483</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <f aca="false">MAX(0,G8*(1+Inputs!B19)-'Withdrawal Plan'!L9)</f>
-        <v>856912.13438976</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <f aca="false">SUM(B9:G9)</f>
-        <v>4409401.65037944</v>
-      </c>
-      <c r="I9" s="21" t="n">
-        <f aca="false">H9+Inputs!B36</f>
-        <v>5209401.65037944</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="n">
+      <c r="C18" s="14" t="n">
+        <f aca="false">MAX(0,C17*(1+Inputs!B19)-'Withdrawal Plan'!K9)</f>
+        <v>2569456.9825006</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <f aca="false">D17*(1+Inputs!B19)</f>
+        <v>34259.4264333413</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <f aca="false">E17*(1+Inputs!B19)</f>
+        <v>171297.132166707</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <f aca="false">MAX(0,F17*(1+Inputs!B19)-'Withdrawal Plan'!M9)</f>
+        <v>504805.48417219</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <f aca="false">MAX(0,G17*(1+Inputs!B19)-'Withdrawal Plan'!L9)</f>
+        <v>1712971.32166707</v>
+      </c>
+      <c r="H18" s="22" t="n">
+        <f aca="false">SUM(B18:G18)</f>
+        <v>7008397.34295334</v>
+      </c>
+      <c r="I18" s="23" t="n">
+        <f aca="false">H18+Inputs!B36</f>
+        <v>7808397.34295334</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10" t="n">
         <v>72</v>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B19" s="11" t="n">
         <f aca="false">'Roth Conversion'!J10</f>
         <v>1890395.32091377</v>
       </c>
-      <c r="C10" s="14" t="n">
-        <f aca="false">MAX(0,C9*(1+Inputs!B19)-'Withdrawal Plan'!K10)</f>
-        <v>1388197.65771141</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <f aca="false">D9*(1+Inputs!B19)</f>
-        <v>18509.3021028188</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <f aca="false">E9*(1+Inputs!B19)</f>
-        <v>92546.5105140941</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <f aca="false">MAX(0,F9*(1+Inputs!B19)-'Withdrawal Plan'!M10)</f>
-        <v>157455.88830772</v>
-      </c>
-      <c r="G10" s="14" t="n">
-        <f aca="false">MAX(0,G9*(1+Inputs!B19)-'Withdrawal Plan'!L10)</f>
-        <v>925465.105140941</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <f aca="false">SUM(B10:G10)</f>
-        <v>4472569.78469076</v>
-      </c>
-      <c r="I10" s="23" t="n">
-        <f aca="false">H10+Inputs!B36</f>
-        <v>5272569.78469076</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="n">
+      <c r="C19" s="11" t="n">
+        <f aca="false">MAX(0,C18*(1+Inputs!B19)-'Withdrawal Plan'!K10)</f>
+        <v>2775013.54110065</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <f aca="false">D18*(1+Inputs!B19)</f>
+        <v>37000.1805480087</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <f aca="false">E18*(1+Inputs!B19)</f>
+        <v>185000.902740043</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <f aca="false">MAX(0,F18*(1+Inputs!B19)-'Withdrawal Plan'!M10)</f>
+        <v>542066.159967668</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <f aca="false">MAX(0,G18*(1+Inputs!B19)-'Withdrawal Plan'!L10)</f>
+        <v>1850009.02740043</v>
+      </c>
+      <c r="H19" s="20" t="n">
+        <f aca="false">SUM(B19:G19)</f>
+        <v>7279485.13267057</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <f aca="false">H19+Inputs!B36</f>
+        <v>8079485.13267057</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B20" s="17" t="n">
         <f aca="false">'Roth Conversion'!J11</f>
         <v>1766329.60393662</v>
       </c>
-      <c r="C11" s="17" t="n">
-        <f aca="false">MAX(0,C10*(1+Inputs!B19)-'Withdrawal Plan'!K11)</f>
-        <v>1499253.47032833</v>
-      </c>
-      <c r="D11" s="17" t="n">
-        <f aca="false">D10*(1+Inputs!B19)</f>
-        <v>19990.0462710443</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <f aca="false">E10*(1+Inputs!B19)</f>
-        <v>99950.2313552217</v>
-      </c>
-      <c r="F11" s="17" t="n">
-        <f aca="false">MAX(0,F10*(1+Inputs!B19)-'Withdrawal Plan'!M11)</f>
-        <v>166772.408287125</v>
-      </c>
-      <c r="G11" s="17" t="n">
-        <f aca="false">MAX(0,G10*(1+Inputs!B19)-'Withdrawal Plan'!L11)</f>
-        <v>999502.313552217</v>
-      </c>
-      <c r="H11" s="24" t="n">
-        <f aca="false">SUM(B11:G11)</f>
-        <v>4551798.07373055</v>
-      </c>
-      <c r="I11" s="25" t="n">
-        <f aca="false">H11+Inputs!B36</f>
-        <v>5351798.07373055</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="n">
-        <v>74</v>
-      </c>
-      <c r="B12" s="17" t="n">
-        <f aca="false">'Roth Conversion'!J12</f>
-        <v>1643438.49403503</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <f aca="false">MAX(0,C11*(1+Inputs!B19)-'Withdrawal Plan'!K12)</f>
-        <v>1619193.74795459</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <f aca="false">D11*(1+Inputs!B19)</f>
-        <v>21589.2499727279</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <f aca="false">E11*(1+Inputs!B19)</f>
-        <v>107946.249863639</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <f aca="false">MAX(0,F11*(1+Inputs!B19)-'Withdrawal Plan'!M12)</f>
-        <v>176670.252310623</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <f aca="false">MAX(0,G11*(1+Inputs!B19)-'Withdrawal Plan'!L12)</f>
-        <v>1079462.49863639</v>
-      </c>
-      <c r="H12" s="24" t="n">
-        <f aca="false">SUM(B12:G12)</f>
-        <v>4648300.49277301</v>
-      </c>
-      <c r="I12" s="25" t="n">
-        <f aca="false">H12+Inputs!B36</f>
-        <v>5448300.49277301</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="B13" s="17" t="n">
-        <f aca="false">'Roth Conversion'!J13</f>
-        <v>1521751.35638591</v>
-      </c>
-      <c r="C13" s="17" t="n">
-        <f aca="false">MAX(0,C12*(1+Inputs!B19)-'Withdrawal Plan'!K13)</f>
-        <v>1748729.24779096</v>
-      </c>
-      <c r="D13" s="17" t="n">
-        <f aca="false">D12*(1+Inputs!B19)</f>
-        <v>23316.3899705461</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <f aca="false">E12*(1+Inputs!B19)</f>
-        <v>116581.949852731</v>
-      </c>
-      <c r="F13" s="17" t="n">
-        <f aca="false">MAX(0,F12*(1+Inputs!B19)-'Withdrawal Plan'!M13)</f>
-        <v>187187.726424027</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <f aca="false">MAX(0,G12*(1+Inputs!B19)-'Withdrawal Plan'!L13)</f>
-        <v>1165819.49852731</v>
-      </c>
-      <c r="H13" s="24" t="n">
-        <f aca="false">SUM(B13:G13)</f>
-        <v>4763386.16895148</v>
-      </c>
-      <c r="I13" s="25" t="n">
-        <f aca="false">H13+Inputs!B36</f>
-        <v>5563386.16895148</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="n">
-        <v>76</v>
-      </c>
-      <c r="B14" s="17" t="n">
-        <f aca="false">'Roth Conversion'!J14</f>
-        <v>1401298.29029556</v>
-      </c>
-      <c r="C14" s="17" t="n">
-        <f aca="false">MAX(0,C13*(1+Inputs!B19)-'Withdrawal Plan'!K14)</f>
-        <v>1888627.58761424</v>
-      </c>
-      <c r="D14" s="17" t="n">
-        <f aca="false">D13*(1+Inputs!B19)</f>
-        <v>25181.7011681898</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <f aca="false">E13*(1+Inputs!B19)</f>
-        <v>125908.505840949</v>
-      </c>
-      <c r="F14" s="17" t="n">
-        <f aca="false">MAX(0,F13*(1+Inputs!B19)-'Withdrawal Plan'!M14)</f>
-        <v>198365.791162931</v>
-      </c>
-      <c r="G14" s="17" t="n">
-        <f aca="false">MAX(0,G13*(1+Inputs!B19)-'Withdrawal Plan'!L14)</f>
-        <v>1259085.05840949</v>
-      </c>
-      <c r="H14" s="24" t="n">
-        <f aca="false">SUM(B14:G14)</f>
-        <v>4898466.93449135</v>
-      </c>
-      <c r="I14" s="25" t="n">
-        <f aca="false">H14+Inputs!B36</f>
-        <v>5698466.93449135</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="n">
-        <v>77</v>
-      </c>
-      <c r="B15" s="17" t="n">
-        <f aca="false">'Roth Conversion'!J15</f>
-        <v>1282110.14755295</v>
-      </c>
-      <c r="C15" s="17" t="n">
-        <f aca="false">MAX(0,C14*(1+Inputs!B19)-'Withdrawal Plan'!K15)</f>
-        <v>2039717.79462337</v>
-      </c>
-      <c r="D15" s="17" t="n">
-        <f aca="false">D14*(1+Inputs!B19)</f>
-        <v>27196.237261645</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <f aca="false">E14*(1+Inputs!B19)</f>
-        <v>135981.186308225</v>
-      </c>
-      <c r="F15" s="17" t="n">
-        <f aca="false">MAX(0,F14*(1+Inputs!B19)-'Withdrawal Plan'!M15)</f>
-        <v>210248.253412196</v>
-      </c>
-      <c r="G15" s="17" t="n">
-        <f aca="false">MAX(0,G14*(1+Inputs!B19)-'Withdrawal Plan'!L15)</f>
-        <v>1359811.86308225</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <f aca="false">SUM(B15:G15)</f>
-        <v>5055065.48224064</v>
-      </c>
-      <c r="I15" s="25" t="n">
-        <f aca="false">H15+Inputs!B36</f>
-        <v>5855065.48224064</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="B16" s="17" t="n">
-        <f aca="false">'Roth Conversion'!J16</f>
-        <v>1164218.55124177</v>
-      </c>
-      <c r="C16" s="17" t="n">
-        <f aca="false">MAX(0,C15*(1+Inputs!B19)-'Withdrawal Plan'!K16)</f>
-        <v>2202895.21819324</v>
-      </c>
-      <c r="D16" s="17" t="n">
-        <f aca="false">D15*(1+Inputs!B19)</f>
-        <v>29371.9362425766</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <f aca="false">E15*(1+Inputs!B19)</f>
-        <v>146859.681212883</v>
-      </c>
-      <c r="F16" s="17" t="n">
-        <f aca="false">MAX(0,F15*(1+Inputs!B19)-'Withdrawal Plan'!M16)</f>
-        <v>222881.972589215</v>
-      </c>
-      <c r="G16" s="17" t="n">
-        <f aca="false">MAX(0,G15*(1+Inputs!B19)-'Withdrawal Plan'!L16)</f>
-        <v>1468596.81212883</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <f aca="false">SUM(B16:G16)</f>
-        <v>5234824.17160852</v>
-      </c>
-      <c r="I16" s="25" t="n">
-        <f aca="false">H16+Inputs!B36</f>
-        <v>6034824.17160852</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="n">
-        <v>79</v>
-      </c>
-      <c r="B17" s="17" t="n">
-        <f aca="false">'Roth Conversion'!J17</f>
-        <v>1047655.91502281</v>
-      </c>
-      <c r="C17" s="17" t="n">
-        <f aca="false">MAX(0,C16*(1+Inputs!B19)-'Withdrawal Plan'!K17)</f>
-        <v>2379126.8356487</v>
-      </c>
-      <c r="D17" s="17" t="n">
-        <f aca="false">D16*(1+Inputs!B19)</f>
-        <v>31721.6911419827</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <f aca="false">E16*(1+Inputs!B19)</f>
-        <v>158608.455709914</v>
-      </c>
-      <c r="F17" s="17" t="n">
-        <f aca="false">MAX(0,F16*(1+Inputs!B19)-'Withdrawal Plan'!M17)</f>
-        <v>236317.082245596</v>
-      </c>
-      <c r="G17" s="17" t="n">
-        <f aca="false">MAX(0,G16*(1+Inputs!B19)-'Withdrawal Plan'!L17)</f>
-        <v>1586084.55709914</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <f aca="false">SUM(B17:G17)</f>
-        <v>5439514.53686815</v>
-      </c>
-      <c r="I17" s="25" t="n">
-        <f aca="false">H17+Inputs!B36</f>
-        <v>6239514.53686815</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="B18" s="17" t="n">
-        <f aca="false">'Roth Conversion'!J18</f>
-        <v>932455.462898383</v>
-      </c>
-      <c r="C18" s="17" t="n">
-        <f aca="false">MAX(0,C17*(1+Inputs!B19)-'Withdrawal Plan'!K18)</f>
-        <v>2569456.9825006</v>
-      </c>
-      <c r="D18" s="17" t="n">
-        <f aca="false">D17*(1+Inputs!B19)</f>
-        <v>34259.4264333413</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <f aca="false">E17*(1+Inputs!B19)</f>
-        <v>171297.132166707</v>
-      </c>
-      <c r="F18" s="17" t="n">
-        <f aca="false">MAX(0,F17*(1+Inputs!B19)-'Withdrawal Plan'!M18)</f>
-        <v>250607.228266951</v>
-      </c>
-      <c r="G18" s="17" t="n">
-        <f aca="false">MAX(0,G17*(1+Inputs!B19)-'Withdrawal Plan'!L18)</f>
-        <v>1712971.32166707</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <f aca="false">SUM(B18:G18)</f>
-        <v>5671047.55393305</v>
-      </c>
-      <c r="I18" s="25" t="n">
-        <f aca="false">H18+Inputs!B36</f>
-        <v>6471047.55393305</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="n">
-        <v>81</v>
-      </c>
-      <c r="B19" s="17" t="n">
-        <f aca="false">'Roth Conversion'!J19</f>
-        <v>818651.249470843</v>
-      </c>
-      <c r="C19" s="17" t="n">
-        <f aca="false">MAX(0,C18*(1+Inputs!B19)-'Withdrawal Plan'!K19)</f>
-        <v>2775013.54110065</v>
-      </c>
-      <c r="D19" s="17" t="n">
-        <f aca="false">D18*(1+Inputs!B19)</f>
-        <v>37000.1805480087</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <f aca="false">E18*(1+Inputs!B19)</f>
-        <v>185000.902740043</v>
-      </c>
-      <c r="F19" s="17" t="n">
-        <f aca="false">MAX(0,F18*(1+Inputs!B19)-'Withdrawal Plan'!M19)</f>
-        <v>265809.824942099</v>
-      </c>
-      <c r="G19" s="17" t="n">
-        <f aca="false">MAX(0,G18*(1+Inputs!B19)-'Withdrawal Plan'!L19)</f>
-        <v>1850009.02740043</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <f aca="false">SUM(B19:G19)</f>
-        <v>5931484.72620207</v>
-      </c>
-      <c r="I19" s="25" t="n">
-        <f aca="false">H19+Inputs!B36</f>
-        <v>6731484.72620207</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="B20" s="17" t="n">
-        <f aca="false">'Roth Conversion'!J20</f>
-        <v>706278.180707614</v>
-      </c>
       <c r="C20" s="17" t="n">
-        <f aca="false">MAX(0,C19*(1+Inputs!B19)-'Withdrawal Plan'!K20)</f>
+        <f aca="false">MAX(0,C19*(1+Inputs!B19)-'Withdrawal Plan'!K11)</f>
         <v>2997014.6243887</v>
       </c>
       <c r="D20" s="17" t="n">
@@ -4631,32 +4668,32 @@
         <v>199800.974959247</v>
       </c>
       <c r="F20" s="17" t="n">
-        <f aca="false">MAX(0,F19*(1+Inputs!B19)-'Withdrawal Plan'!M20)</f>
-        <v>281986.330271949</v>
+        <f aca="false">MAX(0,F19*(1+Inputs!B19)-'Withdrawal Plan'!M11)</f>
+        <v>582151.50167987</v>
       </c>
       <c r="G20" s="17" t="n">
-        <f aca="false">MAX(0,G19*(1+Inputs!B19)-'Withdrawal Plan'!L20)</f>
+        <f aca="false">MAX(0,G19*(1+Inputs!B19)-'Withdrawal Plan'!L11)</f>
         <v>1998009.74959247</v>
       </c>
       <c r="H20" s="24" t="n">
         <f aca="false">SUM(B20:G20)</f>
-        <v>6223050.05491183</v>
+        <v>7583266.64954875</v>
       </c>
       <c r="I20" s="25" t="n">
         <f aca="false">H20+Inputs!B36</f>
-        <v>7023050.05491183</v>
+        <v>8383266.64954875</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B21" s="17" t="n">
-        <f aca="false">'Roth Conversion'!J21</f>
-        <v>595372.035225304</v>
+        <f aca="false">'Roth Conversion'!J12</f>
+        <v>1643438.49403503</v>
       </c>
       <c r="C21" s="17" t="n">
-        <f aca="false">MAX(0,C20*(1+Inputs!B19)-'Withdrawal Plan'!K21)</f>
+        <f aca="false">MAX(0,C20*(1+Inputs!B19)-'Withdrawal Plan'!K12)</f>
         <v>3236775.7943398</v>
       </c>
       <c r="D21" s="17" t="n">
@@ -4668,32 +4705,32 @@
         <v>215785.052955986</v>
       </c>
       <c r="F21" s="17" t="n">
-        <f aca="false">MAX(0,F20*(1+Inputs!B19)-'Withdrawal Plan'!M21)</f>
-        <v>299202.54199491</v>
+        <f aca="false">MAX(0,F20*(1+Inputs!B19)-'Withdrawal Plan'!M12)</f>
+        <v>625279.673174787</v>
       </c>
       <c r="G21" s="17" t="n">
-        <f aca="false">MAX(0,G20*(1+Inputs!B19)-'Withdrawal Plan'!L21)</f>
+        <f aca="false">MAX(0,G20*(1+Inputs!B19)-'Withdrawal Plan'!L12)</f>
         <v>2157850.52955986</v>
       </c>
       <c r="H21" s="24" t="n">
         <f aca="false">SUM(B21:G21)</f>
-        <v>6548142.96466706</v>
+        <v>7922286.55465667</v>
       </c>
       <c r="I21" s="25" t="n">
         <f aca="false">H21+Inputs!B36</f>
-        <v>7348142.96466706</v>
+        <v>8722286.55465667</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B22" s="17" t="n">
-        <f aca="false">'Roth Conversion'!J22</f>
-        <v>485969.486105936</v>
+        <f aca="false">'Roth Conversion'!J13</f>
+        <v>1521751.35638591</v>
       </c>
       <c r="C22" s="17" t="n">
-        <f aca="false">MAX(0,C21*(1+Inputs!B19)-'Withdrawal Plan'!K22)</f>
+        <f aca="false">MAX(0,C21*(1+Inputs!B19)-'Withdrawal Plan'!K13)</f>
         <v>3495717.85788698</v>
       </c>
       <c r="D22" s="17" t="n">
@@ -4705,32 +4742,32 @@
         <v>233047.857192465</v>
       </c>
       <c r="F22" s="17" t="n">
-        <f aca="false">MAX(0,F21*(1+Inputs!B19)-'Withdrawal Plan'!M22)</f>
-        <v>317528.915920769</v>
+        <f aca="false">MAX(0,F21*(1+Inputs!B19)-'Withdrawal Plan'!M13)</f>
+        <v>671685.900957324</v>
       </c>
       <c r="G22" s="17" t="n">
-        <f aca="false">MAX(0,G21*(1+Inputs!B19)-'Withdrawal Plan'!L22)</f>
+        <f aca="false">MAX(0,G21*(1+Inputs!B19)-'Withdrawal Plan'!L13)</f>
         <v>2330478.57192465</v>
       </c>
       <c r="H22" s="24" t="n">
         <f aca="false">SUM(B22:G22)</f>
-        <v>6909352.2604693</v>
+        <v>8299291.11578583</v>
       </c>
       <c r="I22" s="25" t="n">
         <f aca="false">H22+Inputs!B36</f>
-        <v>7709352.2604693</v>
+        <v>9099291.11578583</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B23" s="17" t="n">
-        <f aca="false">'Roth Conversion'!J23</f>
-        <v>378108.123258585</v>
+        <f aca="false">'Roth Conversion'!J14</f>
+        <v>1401298.29029556</v>
       </c>
       <c r="C23" s="17" t="n">
-        <f aca="false">MAX(0,C22*(1+Inputs!B19)-'Withdrawal Plan'!K23)</f>
+        <f aca="false">MAX(0,C22*(1+Inputs!B19)-'Withdrawal Plan'!K14)</f>
         <v>3775375.28651794</v>
       </c>
       <c r="D23" s="17" t="n">
@@ -4742,25 +4779,372 @@
         <v>251691.685767863</v>
       </c>
       <c r="F23" s="17" t="n">
-        <f aca="false">MAX(0,F22*(1+Inputs!B19)-'Withdrawal Plan'!M23)</f>
-        <v>337040.90828901</v>
+        <f aca="false">MAX(0,F22*(1+Inputs!B19)-'Withdrawal Plan'!M14)</f>
+        <v>721623.819658892</v>
       </c>
       <c r="G23" s="17" t="n">
-        <f aca="false">MAX(0,G22*(1+Inputs!B19)-'Withdrawal Plan'!L23)</f>
+        <f aca="false">MAX(0,G22*(1+Inputs!B19)-'Withdrawal Plan'!L14)</f>
         <v>2516916.85767863</v>
       </c>
       <c r="H23" s="24" t="n">
         <f aca="false">SUM(B23:G23)</f>
-        <v>7309471.1986656</v>
+        <v>8717244.27707245</v>
       </c>
       <c r="I23" s="25" t="n">
         <f aca="false">H23+Inputs!B36</f>
-        <v>8109471.1986656</v>
-      </c>
+        <v>9517244.27707245</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="n">
+        <v>77</v>
+      </c>
+      <c r="B24" s="17" t="n">
+        <f aca="false">'Roth Conversion'!J15</f>
+        <v>1282110.14755295</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <f aca="false">MAX(0,C23*(1+Inputs!B19)-'Withdrawal Plan'!K15)</f>
+        <v>4077405.30943937</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <f aca="false">D23*(1+Inputs!B19)</f>
+        <v>54365.4041258583</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <f aca="false">E23*(1+Inputs!B19)</f>
+        <v>271827.020629292</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <f aca="false">MAX(0,F23*(1+Inputs!B19)-'Withdrawal Plan'!M15)</f>
+        <v>775366.924187834</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <f aca="false">MAX(0,G23*(1+Inputs!B19)-'Withdrawal Plan'!L15)</f>
+        <v>2718270.20629292</v>
+      </c>
+      <c r="H24" s="24" t="n">
+        <f aca="false">SUM(B24:G24)</f>
+        <v>9179345.01222822</v>
+      </c>
+      <c r="I24" s="25" t="n">
+        <f aca="false">H24+Inputs!B36</f>
+        <v>9979345.01222822</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="B25" s="17" t="n">
+        <f aca="false">'Roth Conversion'!J16</f>
+        <v>1164218.55124177</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <f aca="false">MAX(0,C24*(1+Inputs!B19)-'Withdrawal Plan'!K16)</f>
+        <v>4403597.73419453</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <f aca="false">D24*(1+Inputs!B19)</f>
+        <v>58714.636455927</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <f aca="false">E24*(1+Inputs!B19)</f>
+        <v>293573.182279635</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <f aca="false">MAX(0,F24*(1+Inputs!B19)-'Withdrawal Plan'!M16)</f>
+        <v>833210.137026903</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <f aca="false">MAX(0,G24*(1+Inputs!B19)-'Withdrawal Plan'!L16)</f>
+        <v>2935731.82279635</v>
+      </c>
+      <c r="H25" s="24" t="n">
+        <f aca="false">SUM(B25:G25)</f>
+        <v>9689046.06399511</v>
+      </c>
+      <c r="I25" s="25" t="n">
+        <f aca="false">H25+Inputs!B36</f>
+        <v>10489046.0639951</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="B26" s="17" t="n">
+        <f aca="false">'Roth Conversion'!J17</f>
+        <v>1047655.91502281</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <f aca="false">MAX(0,C25*(1+Inputs!B19)-'Withdrawal Plan'!K17)</f>
+        <v>4755885.55293009</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <f aca="false">D25*(1+Inputs!B19)</f>
+        <v>63411.8073724012</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <f aca="false">E25*(1+Inputs!B19)</f>
+        <v>317059.036862006</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <f aca="false">MAX(0,F25*(1+Inputs!B19)-'Withdrawal Plan'!M17)</f>
+        <v>895471.4998383</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <f aca="false">MAX(0,G25*(1+Inputs!B19)-'Withdrawal Plan'!L17)</f>
+        <v>3170590.36862006</v>
+      </c>
+      <c r="H26" s="24" t="n">
+        <f aca="false">SUM(B26:G26)</f>
+        <v>10250074.1806457</v>
+      </c>
+      <c r="I26" s="25" t="n">
+        <f aca="false">H26+Inputs!B36</f>
+        <v>11050074.1806457</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="B27" s="17" t="n">
+        <f aca="false">'Roth Conversion'!J18</f>
+        <v>932455.462898383</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <f aca="false">MAX(0,C26*(1+Inputs!B19)-'Withdrawal Plan'!K18)</f>
+        <v>5136356.39716449</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <f aca="false">D26*(1+Inputs!B19)</f>
+        <v>68484.7519621933</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <f aca="false">E26*(1+Inputs!B19)</f>
+        <v>342423.759810966</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <f aca="false">MAX(0,F26*(1+Inputs!B19)-'Withdrawal Plan'!M18)</f>
+        <v>962493.999267071</v>
+      </c>
+      <c r="G27" s="17" t="n">
+        <f aca="false">MAX(0,G26*(1+Inputs!B19)-'Withdrawal Plan'!L18)</f>
+        <v>3424237.59810966</v>
+      </c>
+      <c r="H27" s="24" t="n">
+        <f aca="false">SUM(B27:G27)</f>
+        <v>10866451.9692128</v>
+      </c>
+      <c r="I27" s="25" t="n">
+        <f aca="false">H27+Inputs!B36</f>
+        <v>11666451.9692128</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="B28" s="17" t="n">
+        <f aca="false">'Roth Conversion'!J19</f>
+        <v>818651.249470843</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <f aca="false">MAX(0,C27*(1+Inputs!B19)-'Withdrawal Plan'!K19)</f>
+        <v>5547264.90893765</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <f aca="false">D27*(1+Inputs!B19)</f>
+        <v>73963.5321191687</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <f aca="false">E27*(1+Inputs!B19)</f>
+        <v>369817.660595844</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <f aca="false">MAX(0,F27*(1+Inputs!B19)-'Withdrawal Plan'!M19)</f>
+        <v>1034647.53762223</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <f aca="false">MAX(0,G27*(1+Inputs!B19)-'Withdrawal Plan'!L19)</f>
+        <v>3698176.60595844</v>
+      </c>
+      <c r="H28" s="24" t="n">
+        <f aca="false">SUM(B28:G28)</f>
+        <v>11542521.4947042</v>
+      </c>
+      <c r="I28" s="25" t="n">
+        <f aca="false">H28+Inputs!B36</f>
+        <v>12342521.4947042</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="B29" s="17" t="n">
+        <f aca="false">'Roth Conversion'!J20</f>
+        <v>706278.180707614</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <f aca="false">MAX(0,C28*(1+Inputs!B19)-'Withdrawal Plan'!K20)</f>
+        <v>5991046.10165267</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <f aca="false">D28*(1+Inputs!B19)</f>
+        <v>79880.6146887023</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <f aca="false">E28*(1+Inputs!B19)</f>
+        <v>399403.073443511</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <f aca="false">MAX(0,F28*(1+Inputs!B19)-'Withdrawal Plan'!M20)</f>
+        <v>1112331.05996649</v>
+      </c>
+      <c r="G29" s="17" t="n">
+        <f aca="false">MAX(0,G28*(1+Inputs!B19)-'Withdrawal Plan'!L20)</f>
+        <v>3994030.73443511</v>
+      </c>
+      <c r="H29" s="24" t="n">
+        <f aca="false">SUM(B29:G29)</f>
+        <v>12282969.7648941</v>
+      </c>
+      <c r="I29" s="25" t="n">
+        <f aca="false">H29+Inputs!B36</f>
+        <v>13082969.7648941</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="B30" s="17" t="n">
+        <f aca="false">'Roth Conversion'!J21</f>
+        <v>595372.035225304</v>
+      </c>
+      <c r="C30" s="17" t="n">
+        <f aca="false">MAX(0,C29*(1+Inputs!B19)-'Withdrawal Plan'!K21)</f>
+        <v>6470329.78978488</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <f aca="false">D29*(1+Inputs!B19)</f>
+        <v>86271.0638637984</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <f aca="false">E29*(1+Inputs!B19)</f>
+        <v>431355.319318992</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <f aca="false">MAX(0,F29*(1+Inputs!B19)-'Withdrawal Plan'!M21)</f>
+        <v>1195974.85006501</v>
+      </c>
+      <c r="G30" s="17" t="n">
+        <f aca="false">MAX(0,G29*(1+Inputs!B19)-'Withdrawal Plan'!L21)</f>
+        <v>4313553.19318992</v>
+      </c>
+      <c r="H30" s="24" t="n">
+        <f aca="false">SUM(B30:G30)</f>
+        <v>13092856.2514479</v>
+      </c>
+      <c r="I30" s="25" t="n">
+        <f aca="false">H30+Inputs!B36</f>
+        <v>13892856.2514479</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="B31" s="17" t="n">
+        <f aca="false">'Roth Conversion'!J22</f>
+        <v>485969.486105936</v>
+      </c>
+      <c r="C31" s="17" t="n">
+        <f aca="false">MAX(0,C30*(1+Inputs!B19)-'Withdrawal Plan'!K22)</f>
+        <v>6987956.17296767</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <f aca="false">D30*(1+Inputs!B19)</f>
+        <v>93172.7489729023</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <f aca="false">E30*(1+Inputs!B19)</f>
+        <v>465863.744864511</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <f aca="false">MAX(0,F30*(1+Inputs!B19)-'Withdrawal Plan'!M22)</f>
+        <v>1286043.00863648</v>
+      </c>
+      <c r="G31" s="17" t="n">
+        <f aca="false">MAX(0,G30*(1+Inputs!B19)-'Withdrawal Plan'!L22)</f>
+        <v>4658637.44864512</v>
+      </c>
+      <c r="H31" s="24" t="n">
+        <f aca="false">SUM(B31:G31)</f>
+        <v>13977642.6101926</v>
+      </c>
+      <c r="I31" s="25" t="n">
+        <f aca="false">H31+Inputs!B36</f>
+        <v>14777642.6101926</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="B32" s="17" t="n">
+        <f aca="false">'Roth Conversion'!J23</f>
+        <v>378108.123258585</v>
+      </c>
+      <c r="C32" s="17" t="n">
+        <f aca="false">MAX(0,C31*(1+Inputs!B19)-'Withdrawal Plan'!K23)</f>
+        <v>7546992.66680509</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <f aca="false">D31*(1+Inputs!B19)</f>
+        <v>100626.568890735</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <f aca="false">E31*(1+Inputs!B19)</f>
+        <v>503132.844453672</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <f aca="false">MAX(0,F31*(1+Inputs!B19)-'Withdrawal Plan'!M23)</f>
+        <v>1383036.12842198</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <f aca="false">MAX(0,G31*(1+Inputs!B19)-'Withdrawal Plan'!L23)</f>
+        <v>5031328.44453672</v>
+      </c>
+      <c r="H32" s="24" t="n">
+        <f aca="false">SUM(B32:G32)</f>
+        <v>14943224.7763668</v>
+      </c>
+      <c r="I32" s="25" t="n">
+        <f aca="false">H32+Inputs!B36</f>
+        <v>15743224.7763668</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A34:I34"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4787,120 +5171,120 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="B2" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="C2" s="31" t="s">
         <v>91</v>
       </c>
+      <c r="D2" s="31" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="B3" s="28" t="n">
+      <c r="A3" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="33" t="n">
         <f aca="false">Inputs!B22</f>
         <v>3330</v>
       </c>
-      <c r="C3" s="28" t="n">
+      <c r="C3" s="33" t="n">
         <f aca="false">Inputs!B23</f>
         <v>3972</v>
       </c>
-      <c r="D3" s="28" t="n">
+      <c r="D3" s="33" t="n">
         <f aca="false">Inputs!B24</f>
         <v>5200</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="29" t="n">
+      <c r="A4" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="34" t="n">
         <f aca="false">Inputs!B22*12</f>
         <v>39960</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="34" t="n">
         <f aca="false">Inputs!B23*12</f>
         <v>47664</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="34" t="n">
         <f aca="false">Inputs!B24*12</f>
         <v>62400</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" s="30" t="n">
+      <c r="A5" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="35" t="n">
         <f aca="false">85-65</f>
         <v>20</v>
       </c>
-      <c r="C5" s="30" t="n">
+      <c r="C5" s="35" t="n">
         <f aca="false">85-67</f>
         <v>18</v>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="35" t="n">
         <f aca="false">85-70</f>
         <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" s="29" t="n">
+      <c r="A6" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="34" t="n">
         <f aca="false">Inputs!B22*12*20</f>
         <v>799200</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="34" t="n">
         <f aca="false">Inputs!B23*12*18</f>
         <v>857952</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="34" t="n">
         <f aca="false">Inputs!B24*12*15</f>
         <v>936000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="30" t="s">
+      <c r="A7" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="B7" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="C7" s="35" t="s">
         <v>99</v>
       </c>
+      <c r="D7" s="35" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="B8" s="31" t="s">
+      <c r="A8" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="B8" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="C8" s="36" t="s">
         <v>103</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -4932,96 +5316,96 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="B2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>106</v>
       </c>
+      <c r="B2" s="38" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="B3" s="35" t="s">
+      <c r="A3" s="39" t="s">
         <v>108</v>
       </c>
+      <c r="B3" s="40" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="37" t="s">
+      <c r="A4" s="41" t="s">
         <v>110</v>
       </c>
+      <c r="B4" s="42" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5" s="35" t="s">
+      <c r="A5" s="39" t="s">
         <v>112</v>
       </c>
+      <c r="B5" s="40" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="B6" s="37" t="s">
+      <c r="A6" s="41" t="s">
         <v>114</v>
       </c>
+      <c r="B6" s="42" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" s="35" t="s">
+      <c r="A7" s="39" t="s">
         <v>116</v>
       </c>
+      <c r="B7" s="40" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="B8" s="37" t="s">
+      <c r="A8" s="41" t="s">
         <v>118</v>
       </c>
+      <c r="B8" s="42" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="B9" s="35" t="s">
+      <c r="A9" s="39" t="s">
         <v>120</v>
       </c>
+      <c r="B9" s="40" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="s">
-        <v>121</v>
-      </c>
-      <c r="B10" s="37" t="s">
+      <c r="A10" s="41" t="s">
         <v>122</v>
       </c>
+      <c r="B10" s="42" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="35" t="s">
+      <c r="A11" s="39" t="s">
         <v>124</v>
       </c>
+      <c r="B11" s="40" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="37" t="s">
+      <c r="A12" s="41" t="s">
         <v>126</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/retirement_planner.xlsx
+++ b/retirement_planner.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="211">
   <si>
     <t xml:space="preserve">RETIREMENT PLANNING MODEL — INPUTS</t>
   </si>
@@ -665,14 +665,65 @@
     <t xml:space="preserve">Wife needs private health insurance from YOUR retirement until she turns 65 (~$800/mo). Fund from brokerage — NOT HSA (spouse insurance is not an HSA-qualified expense).</t>
   </si>
   <si>
-    <t xml:space="preserve">RETIREMENT CHARTS</t>
+    <t xml:space="preserve">RETIREMENT CHARTS  —  data pulls live from other tabs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trad 401k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your Roth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wife Roth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wife Trad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brokerage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Worth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your SS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wife SS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trad Draw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roth Draw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brok Draw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Needs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fed Tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State Tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surplus</t>
   </si>
   <si>
     <t xml:space="preserve">Withdrawal
-Rate (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4% Guideline</t>
+Rate %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4% Guide</t>
   </si>
 </sst>
 </file>
@@ -685,10 +736,10 @@
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="\$#,##0"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="\$#,##0"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0"/>
-    <numFmt numFmtId="172" formatCode="0%"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0"/>
+    <numFmt numFmtId="171" formatCode="0%"/>
+    <numFmt numFmtId="172" formatCode="\$#,##0"/>
   </numFmts>
   <fonts count="41">
     <font>
@@ -970,8 +1021,9 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="8"/>
-      <name val="Cambria"/>
+      <sz val="9"/>
+      <color rgb="FF1A3A6B"/>
+      <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -996,7 +1048,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1060,13 +1112,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F4FF"/>
-        <bgColor rgb="FFEAF0FB"/>
+        <bgColor rgb="FFE8F0FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF0FB"/>
-        <bgColor rgb="FFE8F4FF"/>
+        <bgColor rgb="FFE8F0FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F0FF"/>
+        <bgColor rgb="FFEAF0FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -1147,7 +1205,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="88">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1312,7 +1370,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1328,35 +1386,35 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="169" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="29" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="29" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1384,31 +1442,31 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="30" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="30" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="33" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="33" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1480,7 +1538,23 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1500,7 +1574,7 @@
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFF8F4ED"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
@@ -1528,11 +1602,11 @@
       <rgbColor rgb="FF2D6A4F"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFE8F0FF"/>
       <rgbColor rgb="FFEAF0FB"/>
-      <rgbColor rgb="FFEFE9DF"/>
       <rgbColor rgb="FFFFF0E8"/>
       <rgbColor rgb="FFD4C9B8"/>
-      <rgbColor rgb="FFF8F4ED"/>
+      <rgbColor rgb="FFEFE9DF"/>
       <rgbColor rgb="FFEFF4FF"/>
       <rgbColor rgb="FFE8C96A"/>
       <rgbColor rgb="FF4F81BD"/>
@@ -1598,7 +1672,7 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:barChart>
-        <c:barDir val="bar"/>
+        <c:barDir val="col"/>
         <c:grouping val="stacked"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -1606,12 +1680,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Portfolio!B2</c:f>
+              <c:f>Charts!B3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Trad 401k
-($)</c:v>
+                  <c:v>Trad 401k</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1664,7 +1737,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Portfolio!$A$3:$A$32</c:f>
+              <c:f>Charts!$A$4:$A$33</c:f>
               <c:strCache>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
@@ -1762,9 +1835,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Portfolio!$B$3:$B$32</c:f>
+              <c:f>Charts!$B$4:$B$33</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
+                <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>3037518.75</c:v>
@@ -1865,12 +1938,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Portfolio!C2</c:f>
+              <c:f>Charts!C3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Your Roth
-($)</c:v>
+                  <c:v>Your Roth</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1923,7 +1995,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Portfolio!$A$3:$A$32</c:f>
+              <c:f>Charts!$A$4:$A$33</c:f>
               <c:strCache>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
@@ -2021,9 +2093,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Portfolio!$C$3:$C$32</c:f>
+              <c:f>Charts!$C$4:$C$33</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
+                <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>810000</c:v>
@@ -2124,12 +2196,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Portfolio!D2</c:f>
+              <c:f>Charts!D3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Wife Roth
-($)</c:v>
+                  <c:v>Wife Roth</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2182,7 +2253,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Portfolio!$A$3:$A$32</c:f>
+              <c:f>Charts!$A$4:$A$33</c:f>
               <c:strCache>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
@@ -2280,9 +2351,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Portfolio!$D$3:$D$32</c:f>
+              <c:f>Charts!$D$4:$D$33</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
+                <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>10800</c:v>
@@ -2383,12 +2454,11 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Portfolio!E2</c:f>
+              <c:f>Charts!E3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Wife Trad
-($)</c:v>
+                  <c:v>Wife Trad</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2441,7 +2511,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Portfolio!$A$3:$A$32</c:f>
+              <c:f>Charts!$A$4:$A$33</c:f>
               <c:strCache>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
@@ -2539,9 +2609,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Portfolio!$E$3:$E$32</c:f>
+              <c:f>Charts!$E$4:$E$33</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
+                <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>54000</c:v>
@@ -2642,12 +2712,11 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Portfolio!F2</c:f>
+              <c:f>Charts!F3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>HSA
-($)</c:v>
+                  <c:v>HSA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2700,7 +2769,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Portfolio!$A$3:$A$32</c:f>
+              <c:f>Charts!$A$4:$A$33</c:f>
               <c:strCache>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
@@ -2798,9 +2867,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Portfolio!$F$3:$F$32</c:f>
+              <c:f>Charts!$F$4:$F$33</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
+                <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>116640</c:v>
@@ -2901,12 +2970,11 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Portfolio!G2</c:f>
+              <c:f>Charts!G3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Brokerage
-($)</c:v>
+                  <c:v>Brokerage</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2959,7 +3027,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Portfolio!$A$3:$A$32</c:f>
+              <c:f>Charts!$A$4:$A$33</c:f>
               <c:strCache>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
@@ -3057,9 +3125,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Portfolio!$G$3:$G$32</c:f>
+              <c:f>Charts!$G$4:$G$33</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
+                <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>540000</c:v>
@@ -3157,11 +3225,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="41991080"/>
-        <c:axId val="6747855"/>
+        <c:axId val="67194089"/>
+        <c:axId val="5062873"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="41991080"/>
+        <c:axId val="67194089"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3170,7 +3238,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="-5400000"/>
+              <a:bodyPr rot="0"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -3200,7 +3268,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3226,7 +3294,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6747855"/>
+        <c:crossAx val="5062873"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3234,7 +3302,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6747855"/>
+        <c:axId val="5062873"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3252,7 +3320,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0"/>
+              <a:bodyPr rot="-5400000"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -3282,7 +3350,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="\$#,##0;&quot;($&quot;#,##0\);\-" sourceLinked="1"/>
+        <c:numFmt formatCode="\$#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3308,7 +3376,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41991080"/>
+        <c:crossAx val="67194089"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3389,7 +3457,7 @@
                 <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Withdrawal Rate (% of Portfolio)</a:t>
+              <a:t>Annual Income Sources in Retirement ($)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3404,37 +3472,35 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Charts!O2</c:f>
+              <c:f>Charts!B35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Withdrawal
-Rate (%)</c:v>
+                  <c:v>Your SS</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="FFFFFF"/>
+              <a:srgbClr val="4F81BD"/>
             </a:solidFill>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
               <a:bodyPr wrap="none"/>
@@ -3472,7 +3538,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Charts!$N$3:$N$23</c:f>
+              <c:f>Charts!$A$36:$A$56</c:f>
               <c:strCache>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
@@ -3543,105 +3609,102 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Charts!$O$3:$O$23</c:f>
+              <c:f>Charts!$B$36:$B$56</c:f>
               <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
+                <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>2.89394044196095</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.85794669385908</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.14269729372886</c:v>
+                  <c:v>47664</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.07413421408362</c:v>
+                  <c:v>48855.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.00125246142858</c:v>
+                  <c:v>50076.99</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.92465415799426</c:v>
+                  <c:v>51328.91475</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.84499663787272</c:v>
+                  <c:v>52612.13761875</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.76297410735805</c:v>
+                  <c:v>53927.4410592187</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.67929830174105</c:v>
+                  <c:v>55275.6270856992</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.59467923394917</c:v>
+                  <c:v>56657.5177628417</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.50980706631961</c:v>
+                  <c:v>58073.9557069127</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.4253359836682</c:v>
+                  <c:v>59525.8045995855</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.34187072849199</c:v>
+                  <c:v>61013.9497145751</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.25995620828742</c:v>
+                  <c:v>62539.2984574395</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.18007033156995</c:v>
+                  <c:v>64102.7809188755</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.10261999981401</c:v>
+                  <c:v>65705.3504418474</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.02793999619742</c:v>
+                  <c:v>67347.9842028936</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.956294378941346</c:v>
+                  <c:v>69031.6838079659</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.887879909078267</c:v>
+                  <c:v>70757.475903165</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.822831014932614</c:v>
+                  <c:v>72526.4128007442</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.761225809389379</c:v>
+                  <c:v>74339.5731207628</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Charts!P2</c:f>
+              <c:f>Charts!C35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4% Guideline</c:v>
+                  <c:v>Wife SS</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="FFFFFF"/>
+              <a:srgbClr val="C0504D"/>
             </a:solidFill>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
               <a:bodyPr wrap="none"/>
@@ -3679,7 +3742,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Charts!$N$3:$N$23</c:f>
+              <c:f>Charts!$A$36:$A$56</c:f>
               <c:strCache>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
@@ -3750,91 +3813,696 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Charts!$P$3:$P$23</c:f>
+              <c:f>Charts!$C$36:$C$56</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4</c:v>
+                  <c:v>23832</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4</c:v>
+                  <c:v>24427.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4</c:v>
+                  <c:v>25038.495</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4</c:v>
+                  <c:v>25664.457375</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4</c:v>
+                  <c:v>26306.068809375</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4</c:v>
+                  <c:v>26963.7205296094</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4</c:v>
+                  <c:v>27637.8135428496</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4</c:v>
+                  <c:v>28328.7588814208</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4</c:v>
+                  <c:v>29036.9778534564</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4</c:v>
+                  <c:v>29762.9022997928</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4</c:v>
+                  <c:v>30506.9748572876</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4</c:v>
+                  <c:v>31269.6492287198</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4</c:v>
+                  <c:v>32051.3904594378</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4</c:v>
+                  <c:v>32852.6752209237</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4</c:v>
+                  <c:v>33673.9921014468</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4</c:v>
+                  <c:v>34515.8419039829</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="1"/>
         </c:ser>
-        <c:hiLowLines>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Charts!D35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Trad Draw</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9BBB59"/>
+            </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
-        </c:hiLowLines>
-        <c:marker val="0"/>
-        <c:axId val="74478733"/>
-        <c:axId val="78399825"/>
-      </c:lineChart>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Charts!$A$36:$A$56</c:f>
+              <c:strCache>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>85</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Charts!$D$36:$D$56</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>171050</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>171050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>130535.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>129522.74</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>128484.5585</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>127420.4224625</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>126329.683024063</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>125211.675099664</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>124065.716977156</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>122891.109901585</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>121687.137649124</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>120453.066090352</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>119188.142742611</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>117891.596311176</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>116562.636218956</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>115200.45212443</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>113804.21342754</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>112373.068763229</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>110906.14548231</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>109402.549119367</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>107861.362847352</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Charts!E35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Roth Draw</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="8064A2"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Charts!$A$36:$A$56</c:f>
+              <c:strCache>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>85</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Charts!$E$36:$E$56</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Charts!F35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Brok Draw</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4BACC6"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Charts!$A$36:$A$56</c:f>
+              <c:strCache>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>85</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Charts!$F$36:$F$56</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="8645488"/>
+        <c:axId val="91649147"/>
+      </c:barChart>
       <c:catAx>
-        <c:axId val="74478733"/>
+        <c:axId val="8645488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3873,7 +4541,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3899,7 +4567,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78399825"/>
+        <c:crossAx val="91649147"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3907,7 +4575,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78399825"/>
+        <c:axId val="91649147"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3942,7 +4610,7 @@
                     <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
-                  <a:t>Rate (%)</a:t>
+                  <a:t>Income ($)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -3955,7 +4623,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="\$#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3981,7 +4649,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74478733"/>
+        <c:crossAx val="8645488"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4062,7 +4730,7 @@
                 <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Portfolio Under 4 Growth Scenarios</a:t>
+              <a:t>Portfolio Stress Test (4% / 8% / 10% Growth)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4085,12 +4753,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Stress Test'!C3</c:f>
+              <c:f>Charts!B58</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Bear 4%
-Portfolio ($)</c:v>
+                  <c:v>Bear 4%</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4145,7 +4812,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Stress Test'!$A$4:$A$24</c:f>
+              <c:f>Charts!$A$59:$A$79</c:f>
               <c:strCache>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
@@ -4216,7 +4883,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Stress Test'!$C$4:$C$24</c:f>
+              <c:f>Charts!$B$59:$B$79</c:f>
               <c:numCache>
                 <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="21"/>
@@ -4293,12 +4960,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Stress Test'!D3</c:f>
+              <c:f>Charts!C58</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Conservative 6%
-Portfolio ($)</c:v>
+                  <c:v>Base 8%</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4353,7 +5019,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Stress Test'!$A$4:$A$24</c:f>
+              <c:f>Charts!$A$59:$A$79</c:f>
               <c:strCache>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
@@ -4424,72 +5090,72 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Stress Test'!$D$4:$D$24</c:f>
+              <c:f>Charts!$C$59:$C$79</c:f>
               <c:numCache>
                 <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>9311395.04838215</c:v>
+                  <c:v>9490350.99269125</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9696697.75128508</c:v>
+                  <c:v>10076198.0721065</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10145516.4663622</c:v>
+                  <c:v>10749310.7678751</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10622154.7868439</c:v>
+                  <c:v>11477162.9618051</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11128301.0916795</c:v>
+                  <c:v>12264153.0163745</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11665745.3896491</c:v>
+                  <c:v>13115031.4901532</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>12236385.4176818</c:v>
+                  <c:v>14034929.3140192</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12842233.1047047</c:v>
+                  <c:v>15029388.2211028</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>13485421.4229246</c:v>
+                  <c:v>16104393.6107286</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>14168211.6497591</c:v>
+                  <c:v>17266410.0410459</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14893001.065024</c:v>
+                  <c:v>18522419.560609</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>15662331.1094601</c:v>
+                  <c:v>19879963.1059923</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>16478896.0322413</c:v>
+                  <c:v>21347185.2106853</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>17345552.0567687</c:v>
+                  <c:v>22932882.290133</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>18265327.0958051</c:v>
+                  <c:v>24646554.7889739</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>19241431.0488707</c:v>
+                  <c:v>26498463.4994091</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>20277266.7167892</c:v>
+                  <c:v>28499690.3843481</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>21376441.3703678</c:v>
+                  <c:v>30662204.2656672</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>22542779.0124087</c:v>
+                  <c:v>32998931.7667395</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>23780333.3746002</c:v>
+                  <c:v>35523833.9295256</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>25093401.6933234</c:v>
+                  <c:v>38251988.9601348</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4501,12 +5167,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Stress Test'!E3</c:f>
+              <c:f>Charts!D58</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Base 8%
-Portfolio ($)</c:v>
+                  <c:v>Bull 10%</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4561,7 +5226,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Stress Test'!$A$4:$A$24</c:f>
+              <c:f>Charts!$A$59:$A$79</c:f>
               <c:strCache>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
@@ -4632,215 +5297,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Stress Test'!$E$4:$E$24</c:f>
-              <c:numCache>
-                <c:formatCode>\$#,##0</c:formatCode>
-                <c:ptCount val="21"/>
-                <c:pt idx="0">
-                  <c:v>9490350.99269125</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10076198.0721065</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10749310.7678751</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>11477162.9618051</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>12264153.0163745</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>13115031.4901532</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>14034929.3140192</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>15029388.2211028</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>16104393.6107286</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>17266410.0410459</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>18522419.560609</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>19879963.1059923</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>21347185.2106853</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>22932882.290133</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>24646554.7889739</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>26498463.4994091</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>28499690.3843481</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>30662204.2656672</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>32998931.7667395</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>35523833.9295256</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38251988.9601348</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Stress Test'!F3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Bull 10%
-Portfolio ($)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Stress Test'!$A$4:$A$24</c:f>
-              <c:strCache>
-                <c:ptCount val="21"/>
-                <c:pt idx="0">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>66</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>74</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>76</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>79</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>81</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>82</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>83</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>84</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>85</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Stress Test'!$F$4:$F$24</c:f>
+              <c:f>Charts!$D$59:$D$79</c:f>
               <c:numCache>
                 <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="21"/>
@@ -4920,11 +5377,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="30422047"/>
-        <c:axId val="89478834"/>
+        <c:axId val="83039156"/>
+        <c:axId val="64966211"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="30422047"/>
+        <c:axId val="83039156"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4963,7 +5420,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4989,7 +5446,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89478834"/>
+        <c:crossAx val="64966211"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4997,7 +5454,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89478834"/>
+        <c:axId val="64966211"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5071,7 +5528,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30422047"/>
+        <c:crossAx val="83039156"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5152,7 +5609,7 @@
                 <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Annual Income Sources in Retirement ($)</a:t>
+              <a:t>Withdrawal Rate vs 4% Guideline</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -5167,36 +5624,37 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Withdrawal Plan'!H2</c:f>
+              <c:f>Charts!E58</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Your SS
-($)</c:v>
+                  <c:v>Withdrawal
+Rate %</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4F81BD"/>
+              <a:srgbClr val="FFFFFF"/>
             </a:solidFill>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:dLbls>
             <c:txPr>
               <a:bodyPr wrap="none"/>
@@ -5234,7 +5692,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Withdrawal Plan'!$A$3:$A$23</c:f>
+              <c:f>Charts!$A$59:$A$79</c:f>
               <c:strCache>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
@@ -5305,103 +5763,105 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Withdrawal Plan'!$H$3:$H$23</c:f>
+              <c:f>Charts!$E$59:$E$79</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>2.89394044196095</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>2.85794669385908</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>47664</c:v>
+                  <c:v>2.14269729372886</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>48855.6</c:v>
+                  <c:v>2.07413421408362</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>50076.99</c:v>
+                  <c:v>2.00125246142858</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>51328.91475</c:v>
+                  <c:v>1.92465415799426</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>52612.13761875</c:v>
+                  <c:v>1.84499663787272</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>53927.4410592187</c:v>
+                  <c:v>1.76297410735805</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>55275.6270856992</c:v>
+                  <c:v>1.67929830174105</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>56657.5177628417</c:v>
+                  <c:v>1.59467923394917</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>58073.9557069127</c:v>
+                  <c:v>1.50980706631961</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>59525.8045995855</c:v>
+                  <c:v>1.4253359836682</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>61013.9497145751</c:v>
+                  <c:v>1.34187072849199</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>62539.2984574395</c:v>
+                  <c:v>1.25995620828742</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>64102.7809188755</c:v>
+                  <c:v>1.18007033156995</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>65705.3504418474</c:v>
+                  <c:v>1.10261999981401</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>67347.9842028936</c:v>
+                  <c:v>1.02793999619742</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>69031.6838079659</c:v>
+                  <c:v>0.956294378941346</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>70757.475903165</c:v>
+                  <c:v>0.887879909078267</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>72526.4128007442</c:v>
+                  <c:v>0.822831014932614</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>74339.5731207628</c:v>
+                  <c:v>0.761225809389379</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Withdrawal Plan'!I2</c:f>
+              <c:f>Charts!F58</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Wife SS
-($)</c:v>
+                  <c:v>4% Guide</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="C0504D"/>
+              <a:srgbClr val="FFFFFF"/>
             </a:solidFill>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:dLbls>
             <c:txPr>
               <a:bodyPr wrap="none"/>
@@ -5439,7 +5899,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Withdrawal Plan'!$A$3:$A$23</c:f>
+              <c:f>Charts!$A$59:$A$79</c:f>
               <c:strCache>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
@@ -5510,699 +5970,91 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Withdrawal Plan'!$I$3:$I$23</c:f>
+              <c:f>Charts!$F$59:$F$79</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>23832</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>24427.8</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25038.495</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25664.457375</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>26306.068809375</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>26963.7205296094</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>27637.8135428496</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>28328.7588814208</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>29036.9778534564</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>29762.9022997928</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>30506.9748572876</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>31269.6492287198</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>32051.3904594378</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>32852.6752209237</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>33673.9921014468</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>34515.8419039829</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="1"/>
         </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Withdrawal Plan'!J2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Trad 401k
-Draw ($)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
+        <c:hiLowLines>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="9BBB59"/>
-            </a:solidFill>
             <a:ln w="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
+              <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Withdrawal Plan'!$A$3:$A$23</c:f>
-              <c:strCache>
-                <c:ptCount val="21"/>
-                <c:pt idx="0">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>66</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>74</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>76</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>79</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>81</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>82</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>83</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>84</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>85</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Withdrawal Plan'!$J$3:$J$23</c:f>
-              <c:numCache>
-                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
-                <c:ptCount val="21"/>
-                <c:pt idx="0">
-                  <c:v>171050</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>171050</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>130535.6</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>129522.74</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>128484.5585</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>127420.4224625</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>126329.683024063</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>125211.675099664</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>124065.716977156</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>122891.109901585</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>121687.137649124</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>120453.066090352</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>119188.142742611</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>117891.596311176</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>116562.636218956</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>115200.45212443</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>113804.21342754</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>112373.068763229</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>110906.14548231</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>109402.549119367</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>107861.362847352</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Withdrawal Plan'!K2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Roth IRA
-Draw ($)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="8064A2"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Withdrawal Plan'!$A$3:$A$23</c:f>
-              <c:strCache>
-                <c:ptCount val="21"/>
-                <c:pt idx="0">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>66</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>74</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>76</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>79</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>81</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>82</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>83</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>84</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>85</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Withdrawal Plan'!$K$3:$K$23</c:f>
-              <c:numCache>
-                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
-                <c:ptCount val="21"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Withdrawal Plan'!L2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Brokerage
-Draw ($)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4BACC6"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Withdrawal Plan'!$A$3:$A$23</c:f>
-              <c:strCache>
-                <c:ptCount val="21"/>
-                <c:pt idx="0">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>66</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>74</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>76</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>79</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>81</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>82</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>83</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>84</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>85</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Withdrawal Plan'!$L$3:$L$23</c:f>
-              <c:numCache>
-                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
-                <c:ptCount val="21"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="25388829"/>
-        <c:axId val="98847719"/>
-      </c:barChart>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="64165522"/>
+        <c:axId val="66198551"/>
+      </c:lineChart>
       <c:catAx>
-        <c:axId val="25388829"/>
+        <c:axId val="64165522"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6241,7 +6093,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -6267,7 +6119,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98847719"/>
+        <c:crossAx val="66198551"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6275,7 +6127,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="98847719"/>
+        <c:axId val="66198551"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6310,7 +6162,7 @@
                     <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
-                  <a:t>Income ($)</a:t>
+                  <a:t>Rate (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -6323,7 +6175,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="\$#,##0;&quot;($&quot;#,##0\);\-" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -6349,7 +6201,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25388829"/>
+        <c:crossAx val="64165522"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7272,16 +7124,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>25200</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>86400</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>551160</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>44640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7289,8 +7141,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="466560"/>
-        <a:ext cx="7919640" cy="5039640"/>
+        <a:off x="8881200" y="438120"/>
+        <a:ext cx="8639640" cy="5759640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7302,16 +7154,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>25200</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>86760</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>551160</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>44640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7319,8 +7171,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="6562800"/>
-        <a:ext cx="7919640" cy="5039640"/>
+        <a:off x="8881200" y="6534000"/>
+        <a:ext cx="8639640" cy="5759640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7332,16 +7184,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>160560</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>86400</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>745200</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>44640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7349,8 +7201,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="13533120" y="466560"/>
-        <a:ext cx="7919640" cy="5039640"/>
+        <a:off x="0" y="15487560"/>
+        <a:ext cx="8639640" cy="5759640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7362,16 +7214,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>160560</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>86760</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>551160</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>44640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7379,8 +7231,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="13533120" y="6562800"/>
-        <a:ext cx="7919640" cy="5039640"/>
+        <a:off x="8881200" y="15487560"/>
+        <a:ext cx="8639640" cy="5759640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8176,296 +8028,2631 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:T79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="1" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="83" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N2" s="83" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
+      <c r="T1" s="83"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="O2" s="83" t="s">
+      <c r="B3" s="84" t="s">
         <v>192</v>
       </c>
-      <c r="P2" s="83" t="s">
+      <c r="C3" s="84" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N3" s="0" t="n">
+      <c r="D3" s="84" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="84" t="s">
+        <v>195</v>
+      </c>
+      <c r="F3" s="84" t="s">
+        <v>196</v>
+      </c>
+      <c r="G3" s="84" t="s">
+        <v>197</v>
+      </c>
+      <c r="H3" s="84" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="85" t="n">
+        <f aca="false">Portfolio!A3</f>
+        <v>56</v>
+      </c>
+      <c r="B4" s="86" t="n">
+        <f aca="false">Portfolio!B3</f>
+        <v>3037518.75</v>
+      </c>
+      <c r="C4" s="86" t="n">
+        <f aca="false">Portfolio!C3</f>
+        <v>810000</v>
+      </c>
+      <c r="D4" s="86" t="n">
+        <f aca="false">Portfolio!D3</f>
+        <v>10800</v>
+      </c>
+      <c r="E4" s="86" t="n">
+        <f aca="false">Portfolio!E3</f>
+        <v>54000</v>
+      </c>
+      <c r="F4" s="86" t="n">
+        <f aca="false">Portfolio!F3</f>
+        <v>116640</v>
+      </c>
+      <c r="G4" s="86" t="n">
+        <f aca="false">Portfolio!G3</f>
+        <v>540000</v>
+      </c>
+      <c r="H4" s="86" t="n">
+        <f aca="false">Portfolio!I3</f>
+        <v>5368958.75</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="85" t="n">
+        <f aca="false">Portfolio!A4</f>
+        <v>57</v>
+      </c>
+      <c r="B5" s="86" t="n">
+        <f aca="false">Portfolio!B4</f>
+        <v>3318039</v>
+      </c>
+      <c r="C5" s="86" t="n">
+        <f aca="false">Portfolio!C4</f>
+        <v>874800</v>
+      </c>
+      <c r="D5" s="86" t="n">
+        <f aca="false">Portfolio!D4</f>
+        <v>11664</v>
+      </c>
+      <c r="E5" s="86" t="n">
+        <f aca="false">Portfolio!E4</f>
+        <v>58320</v>
+      </c>
+      <c r="F5" s="86" t="n">
+        <f aca="false">Portfolio!F4</f>
+        <v>134611.2</v>
+      </c>
+      <c r="G5" s="86" t="n">
+        <f aca="false">Portfolio!G4</f>
+        <v>583200</v>
+      </c>
+      <c r="H5" s="86" t="n">
+        <f aca="false">Portfolio!I4</f>
+        <v>5816634.2</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="85" t="n">
+        <f aca="false">Portfolio!A5</f>
+        <v>58</v>
+      </c>
+      <c r="B6" s="86" t="n">
+        <f aca="false">Portfolio!B5</f>
+        <v>3621000.87</v>
+      </c>
+      <c r="C6" s="86" t="n">
+        <f aca="false">Portfolio!C5</f>
+        <v>944784</v>
+      </c>
+      <c r="D6" s="86" t="n">
+        <f aca="false">Portfolio!D5</f>
+        <v>12597.12</v>
+      </c>
+      <c r="E6" s="86" t="n">
+        <f aca="false">Portfolio!E5</f>
+        <v>62985.6</v>
+      </c>
+      <c r="F6" s="86" t="n">
+        <f aca="false">Portfolio!F5</f>
+        <v>154020.096</v>
+      </c>
+      <c r="G6" s="86" t="n">
+        <f aca="false">Portfolio!G5</f>
+        <v>629856</v>
+      </c>
+      <c r="H6" s="86" t="n">
+        <f aca="false">Portfolio!I5</f>
+        <v>6298863.686</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="85" t="n">
+        <f aca="false">Portfolio!A6</f>
+        <v>59</v>
+      </c>
+      <c r="B7" s="86" t="n">
+        <f aca="false">Portfolio!B6</f>
+        <v>3948199.6896</v>
+      </c>
+      <c r="C7" s="86" t="n">
+        <f aca="false">Portfolio!C6</f>
+        <v>1020366.72</v>
+      </c>
+      <c r="D7" s="86" t="n">
+        <f aca="false">Portfolio!D6</f>
+        <v>13604.8896</v>
+      </c>
+      <c r="E7" s="86" t="n">
+        <f aca="false">Portfolio!E6</f>
+        <v>68024.448</v>
+      </c>
+      <c r="F7" s="86" t="n">
+        <f aca="false">Portfolio!F6</f>
+        <v>174981.70368</v>
+      </c>
+      <c r="G7" s="86" t="n">
+        <f aca="false">Portfolio!G6</f>
+        <v>680244.48</v>
+      </c>
+      <c r="H7" s="86" t="n">
+        <f aca="false">Portfolio!I6</f>
+        <v>6818354.83088</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="85" t="n">
+        <f aca="false">Portfolio!A7</f>
+        <v>60</v>
+      </c>
+      <c r="B8" s="86" t="n">
+        <f aca="false">Portfolio!B7</f>
+        <v>4301574.414768</v>
+      </c>
+      <c r="C8" s="86" t="n">
+        <f aca="false">Portfolio!C7</f>
+        <v>1101996.0576</v>
+      </c>
+      <c r="D8" s="86" t="n">
+        <f aca="false">Portfolio!D7</f>
+        <v>14693.280768</v>
+      </c>
+      <c r="E8" s="86" t="n">
+        <f aca="false">Portfolio!E7</f>
+        <v>73466.40384</v>
+      </c>
+      <c r="F8" s="86" t="n">
+        <f aca="false">Portfolio!F7</f>
+        <v>197620.2399744</v>
+      </c>
+      <c r="G8" s="86" t="n">
+        <f aca="false">Portfolio!G7</f>
+        <v>734664.0384</v>
+      </c>
+      <c r="H8" s="86" t="n">
+        <f aca="false">Portfolio!I7</f>
+        <v>7378029.3158504</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="85" t="n">
+        <f aca="false">Portfolio!A8</f>
+        <v>61</v>
+      </c>
+      <c r="B9" s="86" t="n">
+        <f aca="false">Portfolio!B8</f>
+        <v>4683219.11794944</v>
+      </c>
+      <c r="C9" s="86" t="n">
+        <f aca="false">Portfolio!C8</f>
+        <v>1190155.742208</v>
+      </c>
+      <c r="D9" s="86" t="n">
+        <f aca="false">Portfolio!D8</f>
+        <v>15868.74322944</v>
+      </c>
+      <c r="E9" s="86" t="n">
+        <f aca="false">Portfolio!E8</f>
+        <v>79343.7161472</v>
+      </c>
+      <c r="F9" s="86" t="n">
+        <f aca="false">Portfolio!F8</f>
+        <v>222069.859172352</v>
+      </c>
+      <c r="G9" s="86" t="n">
+        <f aca="false">Portfolio!G8</f>
+        <v>793437.161472</v>
+      </c>
+      <c r="H9" s="86" t="n">
+        <f aca="false">Portfolio!I8</f>
+        <v>7981039.89030093</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="85" t="n">
+        <f aca="false">Portfolio!A9</f>
+        <v>62</v>
+      </c>
+      <c r="B10" s="86" t="n">
+        <f aca="false">Portfolio!B9</f>
+        <v>5095395.3973854</v>
+      </c>
+      <c r="C10" s="86" t="n">
+        <f aca="false">Portfolio!C9</f>
+        <v>1285368.20158464</v>
+      </c>
+      <c r="D10" s="86" t="n">
+        <f aca="false">Portfolio!D9</f>
+        <v>17138.2426877952</v>
+      </c>
+      <c r="E10" s="86" t="n">
+        <f aca="false">Portfolio!E9</f>
+        <v>85691.213438976</v>
+      </c>
+      <c r="F10" s="86" t="n">
+        <f aca="false">Portfolio!F9</f>
+        <v>248475.44790614</v>
+      </c>
+      <c r="G10" s="86" t="n">
+        <f aca="false">Portfolio!G9</f>
+        <v>856912.13438976</v>
+      </c>
+      <c r="H10" s="86" t="n">
+        <f aca="false">Portfolio!I9</f>
+        <v>8630788.73727072</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="85" t="n">
+        <f aca="false">Portfolio!A10</f>
+        <v>63</v>
+      </c>
+      <c r="B11" s="86" t="n">
+        <f aca="false">Portfolio!B10</f>
+        <v>5540545.77917623</v>
+      </c>
+      <c r="C11" s="86" t="n">
+        <f aca="false">Portfolio!C10</f>
+        <v>1388197.65771141</v>
+      </c>
+      <c r="D11" s="86" t="n">
+        <f aca="false">Portfolio!D10</f>
+        <v>18509.3021028188</v>
+      </c>
+      <c r="E11" s="86" t="n">
+        <f aca="false">Portfolio!E10</f>
+        <v>92546.5105140941</v>
+      </c>
+      <c r="F11" s="86" t="n">
+        <f aca="false">Portfolio!F10</f>
+        <v>276993.483738632</v>
+      </c>
+      <c r="G11" s="86" t="n">
+        <f aca="false">Portfolio!G10</f>
+        <v>925465.105140941</v>
+      </c>
+      <c r="H11" s="86" t="n">
+        <f aca="false">Portfolio!I10</f>
+        <v>9330947.30275665</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="85" t="n">
+        <f aca="false">Portfolio!A11</f>
+        <v>64</v>
+      </c>
+      <c r="B12" s="86" t="n">
+        <f aca="false">Portfolio!B11</f>
+        <v>6021308.19151033</v>
+      </c>
+      <c r="C12" s="86" t="n">
+        <f aca="false">Portfolio!C11</f>
+        <v>1499253.47032833</v>
+      </c>
+      <c r="D12" s="86" t="n">
+        <f aca="false">Portfolio!D11</f>
+        <v>19990.0462710443</v>
+      </c>
+      <c r="E12" s="86" t="n">
+        <f aca="false">Portfolio!E11</f>
+        <v>99950.2313552217</v>
+      </c>
+      <c r="F12" s="86" t="n">
+        <f aca="false">Portfolio!F11</f>
+        <v>307792.962437722</v>
+      </c>
+      <c r="G12" s="86" t="n">
+        <f aca="false">Portfolio!G11</f>
+        <v>999502.313552217</v>
+      </c>
+      <c r="H12" s="86" t="n">
+        <f aca="false">Portfolio!I11</f>
+        <v>10085477.7057241</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="85" t="n">
+        <f aca="false">Portfolio!A12</f>
         <v>65</v>
       </c>
-      <c r="O3" s="48" t="n">
+      <c r="B13" s="86" t="n">
+        <f aca="false">Portfolio!B12</f>
+        <v>2828950</v>
+      </c>
+      <c r="C13" s="86" t="n">
+        <f aca="false">Portfolio!C12</f>
+        <v>1619193.74795459</v>
+      </c>
+      <c r="D13" s="86" t="n">
+        <f aca="false">Portfolio!D12</f>
+        <v>21589.2499727279</v>
+      </c>
+      <c r="E13" s="86" t="n">
+        <f aca="false">Portfolio!E12</f>
+        <v>107946.249863639</v>
+      </c>
+      <c r="F13" s="86" t="n">
+        <f aca="false">Portfolio!F12</f>
+        <v>330196.39943274</v>
+      </c>
+      <c r="G13" s="86" t="n">
+        <f aca="false">Portfolio!G12</f>
+        <v>1079462.49863639</v>
+      </c>
+      <c r="H13" s="86" t="n">
+        <f aca="false">Portfolio!I12</f>
+        <v>7176214.2581915</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="85" t="n">
+        <f aca="false">Portfolio!A13</f>
+        <v>66</v>
+      </c>
+      <c r="B14" s="86" t="n">
+        <f aca="false">Portfolio!B13</f>
+        <v>2657900</v>
+      </c>
+      <c r="C14" s="86" t="n">
+        <f aca="false">Portfolio!C13</f>
+        <v>1748729.24779096</v>
+      </c>
+      <c r="D14" s="86" t="n">
+        <f aca="false">Portfolio!D13</f>
+        <v>23316.3899705461</v>
+      </c>
+      <c r="E14" s="86" t="n">
+        <f aca="false">Portfolio!E13</f>
+        <v>116581.949852731</v>
+      </c>
+      <c r="F14" s="86" t="n">
+        <f aca="false">Portfolio!F13</f>
+        <v>354281.111387359</v>
+      </c>
+      <c r="G14" s="86" t="n">
+        <f aca="false">Portfolio!G13</f>
+        <v>1165819.49852731</v>
+      </c>
+      <c r="H14" s="86" t="n">
+        <f aca="false">Portfolio!I13</f>
+        <v>7309003.73491522</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="85" t="n">
+        <f aca="false">Portfolio!A14</f>
+        <v>67</v>
+      </c>
+      <c r="B15" s="86" t="n">
+        <f aca="false">Portfolio!B14</f>
+        <v>2527364.4</v>
+      </c>
+      <c r="C15" s="86" t="n">
+        <f aca="false">Portfolio!C14</f>
+        <v>1888627.58761424</v>
+      </c>
+      <c r="D15" s="86" t="n">
+        <f aca="false">Portfolio!D14</f>
+        <v>25181.7011681898</v>
+      </c>
+      <c r="E15" s="86" t="n">
+        <f aca="false">Portfolio!E14</f>
+        <v>125908.505840949</v>
+      </c>
+      <c r="F15" s="86" t="n">
+        <f aca="false">Portfolio!F14</f>
+        <v>380176.050298348</v>
+      </c>
+      <c r="G15" s="86" t="n">
+        <f aca="false">Portfolio!G14</f>
+        <v>1259085.05840949</v>
+      </c>
+      <c r="H15" s="86" t="n">
+        <f aca="false">Portfolio!I14</f>
+        <v>7504625.73989991</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="85" t="n">
+        <f aca="false">Portfolio!A15</f>
+        <v>68</v>
+      </c>
+      <c r="B16" s="86" t="n">
+        <f aca="false">Portfolio!B15</f>
+        <v>2397841.66</v>
+      </c>
+      <c r="C16" s="86" t="n">
+        <f aca="false">Portfolio!C15</f>
+        <v>2039717.79462337</v>
+      </c>
+      <c r="D16" s="86" t="n">
+        <f aca="false">Portfolio!D15</f>
+        <v>27196.237261645</v>
+      </c>
+      <c r="E16" s="86" t="n">
+        <f aca="false">Portfolio!E15</f>
+        <v>135981.186308225</v>
+      </c>
+      <c r="F16" s="86" t="n">
+        <f aca="false">Portfolio!F15</f>
+        <v>408020.206822216</v>
+      </c>
+      <c r="G16" s="86" t="n">
+        <f aca="false">Portfolio!G15</f>
+        <v>1359811.86308225</v>
+      </c>
+      <c r="H16" s="86" t="n">
+        <f aca="false">Portfolio!I15</f>
+        <v>7725274.094312</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="85" t="n">
+        <f aca="false">Portfolio!A16</f>
+        <v>69</v>
+      </c>
+      <c r="B17" s="86" t="n">
+        <f aca="false">Portfolio!B16</f>
+        <v>2269357.1015</v>
+      </c>
+      <c r="C17" s="86" t="n">
+        <f aca="false">Portfolio!C16</f>
+        <v>2202895.21819324</v>
+      </c>
+      <c r="D17" s="86" t="n">
+        <f aca="false">Portfolio!D16</f>
+        <v>29371.9362425766</v>
+      </c>
+      <c r="E17" s="86" t="n">
+        <f aca="false">Portfolio!E16</f>
+        <v>146859.681212883</v>
+      </c>
+      <c r="F17" s="86" t="n">
+        <f aca="false">Portfolio!F16</f>
+        <v>437963.399492993</v>
+      </c>
+      <c r="G17" s="86" t="n">
+        <f aca="false">Portfolio!G16</f>
+        <v>1468596.81212883</v>
+      </c>
+      <c r="H17" s="86" t="n">
+        <f aca="false">Portfolio!I16</f>
+        <v>7972801.02656446</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="85" t="n">
+        <f aca="false">Portfolio!A17</f>
+        <v>70</v>
+      </c>
+      <c r="B18" s="86" t="n">
+        <f aca="false">Portfolio!B17</f>
+        <v>2141936.6790375</v>
+      </c>
+      <c r="C18" s="86" t="n">
+        <f aca="false">Portfolio!C17</f>
+        <v>2379126.8356487</v>
+      </c>
+      <c r="D18" s="86" t="n">
+        <f aca="false">Portfolio!D17</f>
+        <v>31721.6911419827</v>
+      </c>
+      <c r="E18" s="86" t="n">
+        <f aca="false">Portfolio!E17</f>
+        <v>158608.455709914</v>
+      </c>
+      <c r="F18" s="86" t="n">
+        <f aca="false">Portfolio!F17</f>
+        <v>470167.126383683</v>
+      </c>
+      <c r="G18" s="86" t="n">
+        <f aca="false">Portfolio!G17</f>
+        <v>1586084.55709914</v>
+      </c>
+      <c r="H18" s="86" t="n">
+        <f aca="false">Portfolio!I17</f>
+        <v>8249201.28231558</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="85" t="n">
+        <f aca="false">Portfolio!A18</f>
+        <v>71</v>
+      </c>
+      <c r="B19" s="86" t="n">
+        <f aca="false">Portfolio!B18</f>
+        <v>2015606.99601344</v>
+      </c>
+      <c r="C19" s="86" t="n">
+        <f aca="false">Portfolio!C18</f>
+        <v>2569456.9825006</v>
+      </c>
+      <c r="D19" s="86" t="n">
+        <f aca="false">Portfolio!D18</f>
+        <v>34259.4264333413</v>
+      </c>
+      <c r="E19" s="86" t="n">
+        <f aca="false">Portfolio!E18</f>
+        <v>171297.132166707</v>
+      </c>
+      <c r="F19" s="86" t="n">
+        <f aca="false">Portfolio!F18</f>
+        <v>504805.48417219</v>
+      </c>
+      <c r="G19" s="86" t="n">
+        <f aca="false">Portfolio!G18</f>
+        <v>1712971.32166707</v>
+      </c>
+      <c r="H19" s="86" t="n">
+        <f aca="false">Portfolio!I18</f>
+        <v>8556623.29742627</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="85" t="n">
+        <f aca="false">Portfolio!A19</f>
+        <v>72</v>
+      </c>
+      <c r="B20" s="86" t="n">
+        <f aca="false">Portfolio!B19</f>
+        <v>1890395.32091377</v>
+      </c>
+      <c r="C20" s="86" t="n">
+        <f aca="false">Portfolio!C19</f>
+        <v>2775013.54110065</v>
+      </c>
+      <c r="D20" s="86" t="n">
+        <f aca="false">Portfolio!D19</f>
+        <v>37000.1805480087</v>
+      </c>
+      <c r="E20" s="86" t="n">
+        <f aca="false">Portfolio!E19</f>
+        <v>185000.902740043</v>
+      </c>
+      <c r="F20" s="86" t="n">
+        <f aca="false">Portfolio!F19</f>
+        <v>542066.159967668</v>
+      </c>
+      <c r="G20" s="86" t="n">
+        <f aca="false">Portfolio!G19</f>
+        <v>1850009.02740043</v>
+      </c>
+      <c r="H20" s="86" t="n">
+        <f aca="false">Portfolio!I19</f>
+        <v>8897381.25509478</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="85" t="n">
+        <f aca="false">Portfolio!A20</f>
+        <v>73</v>
+      </c>
+      <c r="B21" s="86" t="n">
+        <f aca="false">Portfolio!B20</f>
+        <v>1766329.60393662</v>
+      </c>
+      <c r="C21" s="86" t="n">
+        <f aca="false">Portfolio!C20</f>
+        <v>2997014.6243887</v>
+      </c>
+      <c r="D21" s="86" t="n">
+        <f aca="false">Portfolio!D20</f>
+        <v>39960.1949918494</v>
+      </c>
+      <c r="E21" s="86" t="n">
+        <f aca="false">Portfolio!E20</f>
+        <v>199800.974959247</v>
+      </c>
+      <c r="F21" s="86" t="n">
+        <f aca="false">Portfolio!F20</f>
+        <v>582151.50167987</v>
+      </c>
+      <c r="G21" s="86" t="n">
+        <f aca="false">Portfolio!G20</f>
+        <v>1998009.74959247</v>
+      </c>
+      <c r="H21" s="86" t="n">
+        <f aca="false">Portfolio!I20</f>
+        <v>9273968.09748204</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="85" t="n">
+        <f aca="false">Portfolio!A21</f>
+        <v>74</v>
+      </c>
+      <c r="B22" s="86" t="n">
+        <f aca="false">Portfolio!B21</f>
+        <v>1643438.49403503</v>
+      </c>
+      <c r="C22" s="86" t="n">
+        <f aca="false">Portfolio!C21</f>
+        <v>3236775.7943398</v>
+      </c>
+      <c r="D22" s="86" t="n">
+        <f aca="false">Portfolio!D21</f>
+        <v>43157.0105911973</v>
+      </c>
+      <c r="E22" s="86" t="n">
+        <f aca="false">Portfolio!E21</f>
+        <v>215785.052955986</v>
+      </c>
+      <c r="F22" s="86" t="n">
+        <f aca="false">Portfolio!F21</f>
+        <v>625279.673174787</v>
+      </c>
+      <c r="G22" s="86" t="n">
+        <f aca="false">Portfolio!G21</f>
+        <v>2157850.52955986</v>
+      </c>
+      <c r="H22" s="86" t="n">
+        <f aca="false">Portfolio!I21</f>
+        <v>9689069.56774696</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="85" t="n">
+        <f aca="false">Portfolio!A22</f>
+        <v>75</v>
+      </c>
+      <c r="B23" s="86" t="n">
+        <f aca="false">Portfolio!B22</f>
+        <v>1521751.35638591</v>
+      </c>
+      <c r="C23" s="86" t="n">
+        <f aca="false">Portfolio!C22</f>
+        <v>3495717.85788698</v>
+      </c>
+      <c r="D23" s="86" t="n">
+        <f aca="false">Portfolio!D22</f>
+        <v>46609.5714384931</v>
+      </c>
+      <c r="E23" s="86" t="n">
+        <f aca="false">Portfolio!E22</f>
+        <v>233047.857192465</v>
+      </c>
+      <c r="F23" s="86" t="n">
+        <f aca="false">Portfolio!F22</f>
+        <v>671685.900957324</v>
+      </c>
+      <c r="G23" s="86" t="n">
+        <f aca="false">Portfolio!G22</f>
+        <v>2330478.57192465</v>
+      </c>
+      <c r="H23" s="86" t="n">
+        <f aca="false">Portfolio!I22</f>
+        <v>10145579.3644652</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="85" t="n">
+        <f aca="false">Portfolio!A23</f>
+        <v>76</v>
+      </c>
+      <c r="B24" s="86" t="n">
+        <f aca="false">Portfolio!B23</f>
+        <v>1401298.29029556</v>
+      </c>
+      <c r="C24" s="86" t="n">
+        <f aca="false">Portfolio!C23</f>
+        <v>3775375.28651794</v>
+      </c>
+      <c r="D24" s="86" t="n">
+        <f aca="false">Portfolio!D23</f>
+        <v>50338.3371535725</v>
+      </c>
+      <c r="E24" s="86" t="n">
+        <f aca="false">Portfolio!E23</f>
+        <v>251691.685767863</v>
+      </c>
+      <c r="F24" s="86" t="n">
+        <f aca="false">Portfolio!F23</f>
+        <v>721623.819658892</v>
+      </c>
+      <c r="G24" s="86" t="n">
+        <f aca="false">Portfolio!G23</f>
+        <v>2516916.85767863</v>
+      </c>
+      <c r="H24" s="86" t="n">
+        <f aca="false">Portfolio!I23</f>
+        <v>10646615.4969424</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="85" t="n">
+        <f aca="false">Portfolio!A24</f>
+        <v>77</v>
+      </c>
+      <c r="B25" s="86" t="n">
+        <f aca="false">Portfolio!B24</f>
+        <v>1282110.14755295</v>
+      </c>
+      <c r="C25" s="86" t="n">
+        <f aca="false">Portfolio!C24</f>
+        <v>4077405.30943937</v>
+      </c>
+      <c r="D25" s="86" t="n">
+        <f aca="false">Portfolio!D24</f>
+        <v>54365.4041258583</v>
+      </c>
+      <c r="E25" s="86" t="n">
+        <f aca="false">Portfolio!E24</f>
+        <v>271827.020629292</v>
+      </c>
+      <c r="F25" s="86" t="n">
+        <f aca="false">Portfolio!F24</f>
+        <v>775366.924187834</v>
+      </c>
+      <c r="G25" s="86" t="n">
+        <f aca="false">Portfolio!G24</f>
+        <v>2718270.20629292</v>
+      </c>
+      <c r="H25" s="86" t="n">
+        <f aca="false">Portfolio!I24</f>
+        <v>11195537.9369923</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="85" t="n">
+        <f aca="false">Portfolio!A25</f>
+        <v>78</v>
+      </c>
+      <c r="B26" s="86" t="n">
+        <f aca="false">Portfolio!B25</f>
+        <v>1164218.55124177</v>
+      </c>
+      <c r="C26" s="86" t="n">
+        <f aca="false">Portfolio!C25</f>
+        <v>4403597.73419453</v>
+      </c>
+      <c r="D26" s="86" t="n">
+        <f aca="false">Portfolio!D25</f>
+        <v>58714.636455927</v>
+      </c>
+      <c r="E26" s="86" t="n">
+        <f aca="false">Portfolio!E25</f>
+        <v>293573.182279635</v>
+      </c>
+      <c r="F26" s="86" t="n">
+        <f aca="false">Portfolio!F25</f>
+        <v>833210.137026903</v>
+      </c>
+      <c r="G26" s="86" t="n">
+        <f aca="false">Portfolio!G25</f>
+        <v>2935731.82279635</v>
+      </c>
+      <c r="H26" s="86" t="n">
+        <f aca="false">Portfolio!I25</f>
+        <v>11795967.6703736</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="85" t="n">
+        <f aca="false">Portfolio!A26</f>
+        <v>79</v>
+      </c>
+      <c r="B27" s="86" t="n">
+        <f aca="false">Portfolio!B26</f>
+        <v>1047655.91502281</v>
+      </c>
+      <c r="C27" s="86" t="n">
+        <f aca="false">Portfolio!C26</f>
+        <v>4755885.55293009</v>
+      </c>
+      <c r="D27" s="86" t="n">
+        <f aca="false">Portfolio!D26</f>
+        <v>63411.8073724012</v>
+      </c>
+      <c r="E27" s="86" t="n">
+        <f aca="false">Portfolio!E26</f>
+        <v>317059.036862006</v>
+      </c>
+      <c r="F27" s="86" t="n">
+        <f aca="false">Portfolio!F26</f>
+        <v>895471.4998383</v>
+      </c>
+      <c r="G27" s="86" t="n">
+        <f aca="false">Portfolio!G26</f>
+        <v>3170590.36862006</v>
+      </c>
+      <c r="H27" s="86" t="n">
+        <f aca="false">Portfolio!I26</f>
+        <v>12451807.2593111</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="85" t="n">
+        <f aca="false">Portfolio!A27</f>
+        <v>80</v>
+      </c>
+      <c r="B28" s="86" t="n">
+        <f aca="false">Portfolio!B27</f>
+        <v>932455.462898383</v>
+      </c>
+      <c r="C28" s="86" t="n">
+        <f aca="false">Portfolio!C27</f>
+        <v>5136356.39716449</v>
+      </c>
+      <c r="D28" s="86" t="n">
+        <f aca="false">Portfolio!D27</f>
+        <v>68484.7519621933</v>
+      </c>
+      <c r="E28" s="86" t="n">
+        <f aca="false">Portfolio!E27</f>
+        <v>342423.759810966</v>
+      </c>
+      <c r="F28" s="86" t="n">
+        <f aca="false">Portfolio!F27</f>
+        <v>962493.999267071</v>
+      </c>
+      <c r="G28" s="86" t="n">
+        <f aca="false">Portfolio!G27</f>
+        <v>3424237.59810966</v>
+      </c>
+      <c r="H28" s="86" t="n">
+        <f aca="false">Portfolio!I27</f>
+        <v>13167263.0364182</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="85" t="n">
+        <f aca="false">Portfolio!A28</f>
+        <v>81</v>
+      </c>
+      <c r="B29" s="86" t="n">
+        <f aca="false">Portfolio!B28</f>
+        <v>818651.249470843</v>
+      </c>
+      <c r="C29" s="86" t="n">
+        <f aca="false">Portfolio!C28</f>
+        <v>5547264.90893765</v>
+      </c>
+      <c r="D29" s="86" t="n">
+        <f aca="false">Portfolio!D28</f>
+        <v>73963.5321191687</v>
+      </c>
+      <c r="E29" s="86" t="n">
+        <f aca="false">Portfolio!E28</f>
+        <v>369817.660595844</v>
+      </c>
+      <c r="F29" s="86" t="n">
+        <f aca="false">Portfolio!F28</f>
+        <v>1034647.53762223</v>
+      </c>
+      <c r="G29" s="86" t="n">
+        <f aca="false">Portfolio!G28</f>
+        <v>3698176.60595844</v>
+      </c>
+      <c r="H29" s="86" t="n">
+        <f aca="false">Portfolio!I28</f>
+        <v>13946869.0599338</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="85" t="n">
+        <f aca="false">Portfolio!A29</f>
+        <v>82</v>
+      </c>
+      <c r="B30" s="86" t="n">
+        <f aca="false">Portfolio!B29</f>
+        <v>706278.180707614</v>
+      </c>
+      <c r="C30" s="86" t="n">
+        <f aca="false">Portfolio!C29</f>
+        <v>5991046.10165267</v>
+      </c>
+      <c r="D30" s="86" t="n">
+        <f aca="false">Portfolio!D29</f>
+        <v>79880.6146887023</v>
+      </c>
+      <c r="E30" s="86" t="n">
+        <f aca="false">Portfolio!E29</f>
+        <v>399403.073443511</v>
+      </c>
+      <c r="F30" s="86" t="n">
+        <f aca="false">Portfolio!F29</f>
+        <v>1112331.05996649</v>
+      </c>
+      <c r="G30" s="86" t="n">
+        <f aca="false">Portfolio!G29</f>
+        <v>3994030.73443511</v>
+      </c>
+      <c r="H30" s="86" t="n">
+        <f aca="false">Portfolio!I29</f>
+        <v>14795512.9705591</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="85" t="n">
+        <f aca="false">Portfolio!A30</f>
+        <v>83</v>
+      </c>
+      <c r="B31" s="86" t="n">
+        <f aca="false">Portfolio!B30</f>
+        <v>595372.035225304</v>
+      </c>
+      <c r="C31" s="86" t="n">
+        <f aca="false">Portfolio!C30</f>
+        <v>6470329.78978488</v>
+      </c>
+      <c r="D31" s="86" t="n">
+        <f aca="false">Portfolio!D30</f>
+        <v>86271.0638637984</v>
+      </c>
+      <c r="E31" s="86" t="n">
+        <f aca="false">Portfolio!E30</f>
+        <v>431355.319318992</v>
+      </c>
+      <c r="F31" s="86" t="n">
+        <f aca="false">Portfolio!F30</f>
+        <v>1195974.85006501</v>
+      </c>
+      <c r="G31" s="86" t="n">
+        <f aca="false">Portfolio!G30</f>
+        <v>4313553.19318992</v>
+      </c>
+      <c r="H31" s="86" t="n">
+        <f aca="false">Portfolio!I30</f>
+        <v>15718463.9013678</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="85" t="n">
+        <f aca="false">Portfolio!A31</f>
+        <v>84</v>
+      </c>
+      <c r="B32" s="86" t="n">
+        <f aca="false">Portfolio!B31</f>
+        <v>485969.486105936</v>
+      </c>
+      <c r="C32" s="86" t="n">
+        <f aca="false">Portfolio!C31</f>
+        <v>6987956.17296767</v>
+      </c>
+      <c r="D32" s="86" t="n">
+        <f aca="false">Portfolio!D31</f>
+        <v>93172.7489729023</v>
+      </c>
+      <c r="E32" s="86" t="n">
+        <f aca="false">Portfolio!E31</f>
+        <v>465863.744864511</v>
+      </c>
+      <c r="F32" s="86" t="n">
+        <f aca="false">Portfolio!F31</f>
+        <v>1286043.00863648</v>
+      </c>
+      <c r="G32" s="86" t="n">
+        <f aca="false">Portfolio!G31</f>
+        <v>4658637.44864512</v>
+      </c>
+      <c r="H32" s="86" t="n">
+        <f aca="false">Portfolio!I31</f>
+        <v>16721402.604359</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="85" t="n">
+        <f aca="false">Portfolio!A32</f>
+        <v>85</v>
+      </c>
+      <c r="B33" s="86" t="n">
+        <f aca="false">Portfolio!B32</f>
+        <v>378108.123258585</v>
+      </c>
+      <c r="C33" s="86" t="n">
+        <f aca="false">Portfolio!C32</f>
+        <v>7546992.66680509</v>
+      </c>
+      <c r="D33" s="86" t="n">
+        <f aca="false">Portfolio!D32</f>
+        <v>100626.568890735</v>
+      </c>
+      <c r="E33" s="86" t="n">
+        <f aca="false">Portfolio!E32</f>
+        <v>503132.844453672</v>
+      </c>
+      <c r="F33" s="86" t="n">
+        <f aca="false">Portfolio!F32</f>
+        <v>1383036.12842198</v>
+      </c>
+      <c r="G33" s="86" t="n">
+        <f aca="false">Portfolio!G32</f>
+        <v>5031328.44453672</v>
+      </c>
+      <c r="H33" s="86" t="n">
+        <f aca="false">Portfolio!I32</f>
+        <v>17810453.9702706</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="84" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="84" t="s">
+        <v>199</v>
+      </c>
+      <c r="C35" s="84" t="s">
+        <v>200</v>
+      </c>
+      <c r="D35" s="84" t="s">
+        <v>201</v>
+      </c>
+      <c r="E35" s="84" t="s">
+        <v>202</v>
+      </c>
+      <c r="F35" s="84" t="s">
+        <v>203</v>
+      </c>
+      <c r="G35" s="84" t="s">
+        <v>204</v>
+      </c>
+      <c r="H35" s="84" t="s">
+        <v>205</v>
+      </c>
+      <c r="I35" s="84" t="s">
+        <v>206</v>
+      </c>
+      <c r="J35" s="84" t="s">
+        <v>207</v>
+      </c>
+      <c r="K35" s="84" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A3</f>
+        <v>65</v>
+      </c>
+      <c r="B36" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H3</f>
+        <v>0</v>
+      </c>
+      <c r="C36" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I3</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J3</f>
+        <v>171050</v>
+      </c>
+      <c r="E36" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K3</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L3</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="86" t="n">
+        <f aca="false">B36+C36+D36+E36+F36</f>
+        <v>171050</v>
+      </c>
+      <c r="H36" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G3</f>
+        <v>148320</v>
+      </c>
+      <c r="I36" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N3</f>
+        <v>27737</v>
+      </c>
+      <c r="J36" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O3</f>
+        <v>10895.885</v>
+      </c>
+      <c r="K36" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P3</f>
+        <v>-15902.885</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A4</f>
+        <v>66</v>
+      </c>
+      <c r="B37" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H4</f>
+        <v>0</v>
+      </c>
+      <c r="C37" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I4</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J4</f>
+        <v>171050</v>
+      </c>
+      <c r="E37" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K4</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L4</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="86" t="n">
+        <f aca="false">B37+C37+D37+E37+F37</f>
+        <v>171050</v>
+      </c>
+      <c r="H37" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G4</f>
+        <v>150951</v>
+      </c>
+      <c r="I37" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N4</f>
+        <v>27737</v>
+      </c>
+      <c r="J37" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O4</f>
+        <v>10895.885</v>
+      </c>
+      <c r="K37" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P4</f>
+        <v>-18533.885</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A5</f>
+        <v>67</v>
+      </c>
+      <c r="B38" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H5</f>
+        <v>47664</v>
+      </c>
+      <c r="C38" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I5</f>
+        <v>0</v>
+      </c>
+      <c r="D38" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J5</f>
+        <v>130535.6</v>
+      </c>
+      <c r="E38" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K5</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L5</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="86" t="n">
+        <f aca="false">B38+C38+D38+E38+F38</f>
+        <v>178199.6</v>
+      </c>
+      <c r="H38" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G5</f>
+        <v>153663.15</v>
+      </c>
+      <c r="I38" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N5</f>
+        <v>27737</v>
+      </c>
+      <c r="J38" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O5</f>
+        <v>8315.11772</v>
+      </c>
+      <c r="K38" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P5</f>
+        <v>-11515.66772</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A6</f>
+        <v>68</v>
+      </c>
+      <c r="B39" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H6</f>
+        <v>48855.6</v>
+      </c>
+      <c r="C39" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I6</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J6</f>
+        <v>129522.74</v>
+      </c>
+      <c r="E39" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K6</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L6</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="86" t="n">
+        <f aca="false">B39+C39+D39+E39+F39</f>
+        <v>178378.34</v>
+      </c>
+      <c r="H39" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G6</f>
+        <v>156458.9955</v>
+      </c>
+      <c r="I39" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N6</f>
+        <v>27737</v>
+      </c>
+      <c r="J39" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O6</f>
+        <v>8250.598538</v>
+      </c>
+      <c r="K39" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P6</f>
+        <v>-14068.254038</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A7</f>
+        <v>69</v>
+      </c>
+      <c r="B40" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H7</f>
+        <v>50076.99</v>
+      </c>
+      <c r="C40" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I7</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J7</f>
+        <v>128484.5585</v>
+      </c>
+      <c r="E40" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K7</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L7</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="86" t="n">
+        <f aca="false">B40+C40+D40+E40+F40</f>
+        <v>178561.5485</v>
+      </c>
+      <c r="H40" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G7</f>
+        <v>159341.163915</v>
+      </c>
+      <c r="I40" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N7</f>
+        <v>27737</v>
+      </c>
+      <c r="J40" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O7</f>
+        <v>8184.46637645</v>
+      </c>
+      <c r="K40" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P7</f>
+        <v>-16701.08179145</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A8</f>
+        <v>70</v>
+      </c>
+      <c r="B41" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H8</f>
+        <v>51328.91475</v>
+      </c>
+      <c r="C41" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I8</f>
+        <v>23832</v>
+      </c>
+      <c r="D41" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J8</f>
+        <v>127420.4224625</v>
+      </c>
+      <c r="E41" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K8</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L8</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="86" t="n">
+        <f aca="false">B41+C41+D41+E41+F41</f>
+        <v>202581.3372125</v>
+      </c>
+      <c r="H41" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G8</f>
+        <v>152712.36730995</v>
+      </c>
+      <c r="I41" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N8</f>
+        <v>27737</v>
+      </c>
+      <c r="J41" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O8</f>
+        <v>8116.68091086125</v>
+      </c>
+      <c r="K41" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P8</f>
+        <v>14015.2889916887</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A9</f>
+        <v>71</v>
+      </c>
+      <c r="B42" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H9</f>
+        <v>52612.13761875</v>
+      </c>
+      <c r="C42" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I9</f>
+        <v>24427.8</v>
+      </c>
+      <c r="D42" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J9</f>
+        <v>126329.683024063</v>
+      </c>
+      <c r="E42" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K9</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L9</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="86" t="n">
+        <f aca="false">B42+C42+D42+E42+F42</f>
+        <v>203369.620642813</v>
+      </c>
+      <c r="H42" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G9</f>
+        <v>155775.405230624</v>
+      </c>
+      <c r="I42" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N9</f>
+        <v>27737</v>
+      </c>
+      <c r="J42" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O9</f>
+        <v>8047.20080863278</v>
+      </c>
+      <c r="K42" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P9</f>
+        <v>11810.0146035562</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A10</f>
+        <v>72</v>
+      </c>
+      <c r="B43" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H10</f>
+        <v>53927.4410592187</v>
+      </c>
+      <c r="C43" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I10</f>
+        <v>25038.495</v>
+      </c>
+      <c r="D43" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J10</f>
+        <v>125211.675099664</v>
+      </c>
+      <c r="E43" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K10</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L10</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="86" t="n">
+        <f aca="false">B43+C43+D43+E43+F43</f>
+        <v>204177.611158883</v>
+      </c>
+      <c r="H43" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G10</f>
+        <v>158933.167633986</v>
+      </c>
+      <c r="I43" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N10</f>
+        <v>27737</v>
+      </c>
+      <c r="J43" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O10</f>
+        <v>7975.9837038486</v>
+      </c>
+      <c r="K43" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P10</f>
+        <v>9531.45982104821</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A11</f>
+        <v>73</v>
+      </c>
+      <c r="B44" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H11</f>
+        <v>55275.6270856992</v>
+      </c>
+      <c r="C44" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I11</f>
+        <v>25664.457375</v>
+      </c>
+      <c r="D44" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J11</f>
+        <v>124065.716977156</v>
+      </c>
+      <c r="E44" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K11</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L11</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="86" t="n">
+        <f aca="false">B44+C44+D44+E44+F44</f>
+        <v>205005.801437855</v>
+      </c>
+      <c r="H44" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G11</f>
+        <v>162188.637921772</v>
+      </c>
+      <c r="I44" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N11</f>
+        <v>27737</v>
+      </c>
+      <c r="J44" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O11</f>
+        <v>7902.98617144482</v>
+      </c>
+      <c r="K44" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P11</f>
+        <v>7177.17734463854</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A12</f>
+        <v>74</v>
+      </c>
+      <c r="B45" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H12</f>
+        <v>56657.5177628417</v>
+      </c>
+      <c r="C45" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I12</f>
+        <v>26306.068809375</v>
+      </c>
+      <c r="D45" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J12</f>
+        <v>122891.109901585</v>
+      </c>
+      <c r="E45" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K12</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L12</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="86" t="n">
+        <f aca="false">B45+C45+D45+E45+F45</f>
+        <v>205854.696473801</v>
+      </c>
+      <c r="H45" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G12</f>
+        <v>165544.896081129</v>
+      </c>
+      <c r="I45" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N12</f>
+        <v>27737</v>
+      </c>
+      <c r="J45" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O12</f>
+        <v>7828.16370073094</v>
+      </c>
+      <c r="K45" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P12</f>
+        <v>4744.63669194142</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A13</f>
+        <v>75</v>
+      </c>
+      <c r="B46" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H13</f>
+        <v>58073.9557069127</v>
+      </c>
+      <c r="C46" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I13</f>
+        <v>26963.7205296094</v>
+      </c>
+      <c r="D46" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J13</f>
+        <v>121687.137649124</v>
+      </c>
+      <c r="E46" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K13</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L13</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="86" t="n">
+        <f aca="false">B46+C46+D46+E46+F46</f>
+        <v>206724.813885646</v>
+      </c>
+      <c r="H46" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G13</f>
+        <v>169005.121936352</v>
+      </c>
+      <c r="I46" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N13</f>
+        <v>27737</v>
+      </c>
+      <c r="J46" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O13</f>
+        <v>7751.47066824921</v>
+      </c>
+      <c r="K46" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P13</f>
+        <v>2231.22128104485</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A14</f>
+        <v>76</v>
+      </c>
+      <c r="B47" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H14</f>
+        <v>59525.8045995855</v>
+      </c>
+      <c r="C47" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I14</f>
+        <v>27637.8135428496</v>
+      </c>
+      <c r="D47" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J14</f>
+        <v>120453.066090352</v>
+      </c>
+      <c r="E47" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K14</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L14</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="86" t="n">
+        <f aca="false">B47+C47+D47+E47+F47</f>
+        <v>207616.684232787</v>
+      </c>
+      <c r="H47" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G14</f>
+        <v>172572.598515872</v>
+      </c>
+      <c r="I47" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N14</f>
+        <v>27737</v>
+      </c>
+      <c r="J47" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O14</f>
+        <v>7672.86030995544</v>
+      </c>
+      <c r="K47" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P14</f>
+        <v>-365.774593039748</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A15</f>
+        <v>77</v>
+      </c>
+      <c r="B48" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H15</f>
+        <v>61013.9497145751</v>
+      </c>
+      <c r="C48" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I15</f>
+        <v>28328.7588814208</v>
+      </c>
+      <c r="D48" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J15</f>
+        <v>119188.142742611</v>
+      </c>
+      <c r="E48" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K15</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L15</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="86" t="n">
+        <f aca="false">B48+C48+D48+E48+F48</f>
+        <v>208530.851338607</v>
+      </c>
+      <c r="H48" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G15</f>
+        <v>176250.715538848</v>
+      </c>
+      <c r="I48" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N15</f>
+        <v>27737</v>
+      </c>
+      <c r="J48" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O15</f>
+        <v>7592.28469270433</v>
+      </c>
+      <c r="K48" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P15</f>
+        <v>-3049.14889294547</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A16</f>
+        <v>78</v>
+      </c>
+      <c r="B49" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H16</f>
+        <v>62539.2984574395</v>
+      </c>
+      <c r="C49" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I16</f>
+        <v>29036.9778534564</v>
+      </c>
+      <c r="D49" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J16</f>
+        <v>117891.596311176</v>
+      </c>
+      <c r="E49" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K16</f>
+        <v>0</v>
+      </c>
+      <c r="F49" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L16</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="86" t="n">
+        <f aca="false">B49+C49+D49+E49+F49</f>
+        <v>209467.872622072</v>
+      </c>
+      <c r="H49" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G16</f>
+        <v>144042.973025889</v>
+      </c>
+      <c r="I49" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N16</f>
+        <v>27737</v>
+      </c>
+      <c r="J49" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O16</f>
+        <v>7509.69468502194</v>
+      </c>
+      <c r="K49" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P16</f>
+        <v>30178.2049111613</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A17</f>
+        <v>79</v>
+      </c>
+      <c r="B50" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H17</f>
+        <v>64102.7809188755</v>
+      </c>
+      <c r="C50" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I17</f>
+        <v>29762.9022997928</v>
+      </c>
+      <c r="D50" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J17</f>
+        <v>116562.636218956</v>
+      </c>
+      <c r="E50" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K17</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L17</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="86" t="n">
+        <f aca="false">B50+C50+D50+E50+F50</f>
+        <v>210428.319437624</v>
+      </c>
+      <c r="H50" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G17</f>
+        <v>147952.985038585</v>
+      </c>
+      <c r="I50" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N17</f>
+        <v>27737</v>
+      </c>
+      <c r="J50" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O17</f>
+        <v>7425.03992714749</v>
+      </c>
+      <c r="K50" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P17</f>
+        <v>27313.2944718917</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A18</f>
+        <v>80</v>
+      </c>
+      <c r="B51" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H18</f>
+        <v>65705.3504418474</v>
+      </c>
+      <c r="C51" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I18</f>
+        <v>30506.9748572876</v>
+      </c>
+      <c r="D51" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J18</f>
+        <v>115200.45212443</v>
+      </c>
+      <c r="E51" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K18</f>
+        <v>0</v>
+      </c>
+      <c r="F51" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L18</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="86" t="n">
+        <f aca="false">B51+C51+D51+E51+F51</f>
+        <v>211412.777423565</v>
+      </c>
+      <c r="H51" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G18</f>
+        <v>151984.483552758</v>
+      </c>
+      <c r="I51" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N18</f>
+        <v>27737</v>
+      </c>
+      <c r="J51" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O18</f>
+        <v>7338.26880032618</v>
+      </c>
+      <c r="K51" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P18</f>
+        <v>24353.025070481</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A19</f>
+        <v>81</v>
+      </c>
+      <c r="B52" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H19</f>
+        <v>67347.9842028936</v>
+      </c>
+      <c r="C52" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I19</f>
+        <v>31269.6492287198</v>
+      </c>
+      <c r="D52" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J19</f>
+        <v>113804.21342754</v>
+      </c>
+      <c r="E52" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K19</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L19</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="86" t="n">
+        <f aca="false">B52+C52+D52+E52+F52</f>
+        <v>212421.846859154</v>
+      </c>
+      <c r="H52" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G19</f>
+        <v>156141.322470506</v>
+      </c>
+      <c r="I52" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N19</f>
+        <v>27737</v>
+      </c>
+      <c r="J52" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O19</f>
+        <v>7249.32839533433</v>
+      </c>
+      <c r="K52" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P19</f>
+        <v>21294.1959933134</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A20</f>
+        <v>82</v>
+      </c>
+      <c r="B53" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H20</f>
+        <v>69031.6838079659</v>
+      </c>
+      <c r="C53" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I20</f>
+        <v>32051.3904594378</v>
+      </c>
+      <c r="D53" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J20</f>
+        <v>112373.068763229</v>
+      </c>
+      <c r="E53" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K20</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L20</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="86" t="n">
+        <f aca="false">B53+C53+D53+E53+F53</f>
+        <v>213456.143030633</v>
+      </c>
+      <c r="H53" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G20</f>
+        <v>160427.481776345</v>
+      </c>
+      <c r="I53" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N20</f>
+        <v>27737</v>
+      </c>
+      <c r="J53" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O20</f>
+        <v>7158.16448021769</v>
+      </c>
+      <c r="K53" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P20</f>
+        <v>18133.4967740695</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A21</f>
+        <v>83</v>
+      </c>
+      <c r="B54" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H21</f>
+        <v>70757.475903165</v>
+      </c>
+      <c r="C54" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I21</f>
+        <v>32852.6752209237</v>
+      </c>
+      <c r="D54" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J21</f>
+        <v>110906.14548231</v>
+      </c>
+      <c r="E54" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K21</f>
+        <v>0</v>
+      </c>
+      <c r="F54" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L21</f>
+        <v>0</v>
+      </c>
+      <c r="G54" s="86" t="n">
+        <f aca="false">B54+C54+D54+E54+F54</f>
+        <v>214516.296606398</v>
+      </c>
+      <c r="H54" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G21</f>
+        <v>164847.071842946</v>
+      </c>
+      <c r="I54" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N21</f>
+        <v>27737</v>
+      </c>
+      <c r="J54" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O21</f>
+        <v>7064.72146722313</v>
+      </c>
+      <c r="K54" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P21</f>
+        <v>14867.5032962291</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A22</f>
+        <v>84</v>
+      </c>
+      <c r="B55" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H22</f>
+        <v>72526.4128007442</v>
+      </c>
+      <c r="C55" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I22</f>
+        <v>33673.9921014468</v>
+      </c>
+      <c r="D55" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J22</f>
+        <v>109402.549119367</v>
+      </c>
+      <c r="E55" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K22</f>
+        <v>0</v>
+      </c>
+      <c r="F55" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L22</f>
+        <v>0</v>
+      </c>
+      <c r="G55" s="86" t="n">
+        <f aca="false">B55+C55+D55+E55+F55</f>
+        <v>215602.954021558</v>
+      </c>
+      <c r="H55" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G22</f>
+        <v>169404.33789221</v>
+      </c>
+      <c r="I55" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N22</f>
+        <v>27737</v>
+      </c>
+      <c r="J55" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O22</f>
+        <v>6968.94237890371</v>
+      </c>
+      <c r="K55" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P22</f>
+        <v>11492.6737504442</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="85" t="n">
+        <f aca="false">'Withdrawal Plan'!A23</f>
+        <v>85</v>
+      </c>
+      <c r="B56" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!H23</f>
+        <v>74339.5731207628</v>
+      </c>
+      <c r="C56" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!I23</f>
+        <v>34515.8419039829</v>
+      </c>
+      <c r="D56" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!J23</f>
+        <v>107861.362847352</v>
+      </c>
+      <c r="E56" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!K23</f>
+        <v>0</v>
+      </c>
+      <c r="F56" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!L23</f>
+        <v>0</v>
+      </c>
+      <c r="G56" s="86" t="n">
+        <f aca="false">B56+C56+D56+E56+F56</f>
+        <v>216716.777872097</v>
+      </c>
+      <c r="H56" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!G23</f>
+        <v>174103.664617651</v>
+      </c>
+      <c r="I56" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!N23</f>
+        <v>27737</v>
+      </c>
+      <c r="J56" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!O23</f>
+        <v>6870.7688133763</v>
+      </c>
+      <c r="K56" s="86" t="n">
+        <f aca="false">'Withdrawal Plan'!P23</f>
+        <v>8005.34444106957</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="84" t="s">
+        <v>60</v>
+      </c>
+      <c r="B58" s="84" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="84" t="s">
+        <v>126</v>
+      </c>
+      <c r="D58" s="84" t="s">
+        <v>127</v>
+      </c>
+      <c r="E58" s="84" t="s">
+        <v>209</v>
+      </c>
+      <c r="F58" s="84" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="85" t="n">
+        <f aca="false">'Stress Test'!A4</f>
+        <v>65</v>
+      </c>
+      <c r="B59" s="86" t="n">
+        <f aca="false">'Stress Test'!C4</f>
+        <v>9132439.10407305</v>
+      </c>
+      <c r="C59" s="86" t="n">
+        <f aca="false">'Stress Test'!E4</f>
+        <v>9490350.99269125</v>
+      </c>
+      <c r="D59" s="86" t="n">
+        <f aca="false">'Stress Test'!F4</f>
+        <v>9669306.93700034</v>
+      </c>
+      <c r="E59" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J3+'Withdrawal Plan'!K3+'Withdrawal Plan'!L3+'Withdrawal Plan'!M3)/Portfolio!H12*100,0)</f>
         <v>2.89394044196095</v>
       </c>
-      <c r="P3" s="0" t="n">
+      <c r="F59" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N4" s="0" t="n">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="85" t="n">
+        <f aca="false">'Stress Test'!A5</f>
         <v>66</v>
       </c>
-      <c r="O4" s="48" t="n">
+      <c r="B60" s="86" t="n">
+        <f aca="false">'Stress Test'!C5</f>
+        <v>9324355.66823597</v>
+      </c>
+      <c r="C60" s="86" t="n">
+        <f aca="false">'Stress Test'!E5</f>
+        <v>10076198.0721065</v>
+      </c>
+      <c r="D60" s="86" t="n">
+        <f aca="false">'Stress Test'!F5</f>
+        <v>10462856.6307004</v>
+      </c>
+      <c r="E60" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J4+'Withdrawal Plan'!K4+'Withdrawal Plan'!L4+'Withdrawal Plan'!M4)/Portfolio!H13*100,0)</f>
         <v>2.85794669385908</v>
       </c>
-      <c r="P4" s="0" t="n">
+      <c r="F60" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N5" s="0" t="n">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="85" t="n">
+        <f aca="false">'Stress Test'!A6</f>
         <v>67</v>
       </c>
-      <c r="O5" s="48" t="n">
+      <c r="B61" s="86" t="n">
+        <f aca="false">'Stress Test'!C6</f>
+        <v>9564346.74496541</v>
+      </c>
+      <c r="C61" s="86" t="n">
+        <f aca="false">'Stress Test'!E6</f>
+        <v>10749310.7678751</v>
+      </c>
+      <c r="D61" s="86" t="n">
+        <f aca="false">'Stress Test'!F6</f>
+        <v>11376159.1437704</v>
+      </c>
+      <c r="E61" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J5+'Withdrawal Plan'!K5+'Withdrawal Plan'!L5+'Withdrawal Plan'!M5)/Portfolio!H14*100,0)</f>
         <v>2.14269729372886</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="F61" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N6" s="0" t="n">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="85" t="n">
+        <f aca="false">'Stress Test'!A7</f>
         <v>68</v>
       </c>
-      <c r="O6" s="48" t="n">
+      <c r="B62" s="86" t="n">
+        <f aca="false">'Stress Test'!C7</f>
+        <v>9814827.94726403</v>
+      </c>
+      <c r="C62" s="86" t="n">
+        <f aca="false">'Stress Test'!E7</f>
+        <v>11477162.9618051</v>
+      </c>
+      <c r="D62" s="86" t="n">
+        <f aca="false">'Stress Test'!F7</f>
+        <v>12381682.3906475</v>
+      </c>
+      <c r="E62" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J6+'Withdrawal Plan'!K6+'Withdrawal Plan'!L6+'Withdrawal Plan'!M6)/Portfolio!H15*100,0)</f>
         <v>2.07413421408362</v>
       </c>
-      <c r="P6" s="0" t="n">
+      <c r="F62" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N7" s="0" t="n">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="85" t="n">
+        <f aca="false">'Stress Test'!A8</f>
         <v>69</v>
       </c>
-      <c r="O7" s="48" t="n">
+      <c r="B63" s="86" t="n">
+        <f aca="false">'Stress Test'!C8</f>
+        <v>10076238.0827796</v>
+      </c>
+      <c r="C63" s="86" t="n">
+        <f aca="false">'Stress Test'!E8</f>
+        <v>12264153.0163745</v>
+      </c>
+      <c r="D63" s="86" t="n">
+        <f aca="false">'Stress Test'!F8</f>
+        <v>13488667.6473372</v>
+      </c>
+      <c r="E63" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J7+'Withdrawal Plan'!K7+'Withdrawal Plan'!L7+'Withdrawal Plan'!M7)/Portfolio!H16*100,0)</f>
         <v>2.00125246142858</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="F63" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N8" s="0" t="n">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="85" t="n">
+        <f aca="false">'Stress Test'!A9</f>
         <v>70</v>
       </c>
-      <c r="O8" s="48" t="n">
+      <c r="B64" s="86" t="n">
+        <f aca="false">'Stress Test'!C9</f>
+        <v>10349033.8385595</v>
+      </c>
+      <c r="C64" s="86" t="n">
+        <f aca="false">'Stress Test'!E9</f>
+        <v>13115031.4901532</v>
+      </c>
+      <c r="D64" s="86" t="n">
+        <f aca="false">'Stress Test'!F9</f>
+        <v>14707280.6445397</v>
+      </c>
+      <c r="E64" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J8+'Withdrawal Plan'!K8+'Withdrawal Plan'!L8+'Withdrawal Plan'!M8)/Portfolio!H17*100,0)</f>
         <v>1.92465415799426</v>
       </c>
-      <c r="P8" s="0" t="n">
+      <c r="F64" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N9" s="0" t="n">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="85" t="n">
+        <f aca="false">'Stress Test'!A10</f>
         <v>71</v>
       </c>
-      <c r="O9" s="48" t="n">
+      <c r="B65" s="86" t="n">
+        <f aca="false">'Stress Test'!C10</f>
+        <v>10633690.4967557</v>
+      </c>
+      <c r="C65" s="86" t="n">
+        <f aca="false">'Stress Test'!E10</f>
+        <v>14034929.3140192</v>
+      </c>
+      <c r="D65" s="86" t="n">
+        <f aca="false">'Stress Test'!F10</f>
+        <v>16048704.0136474</v>
+      </c>
+      <c r="E65" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J9+'Withdrawal Plan'!K9+'Withdrawal Plan'!L9+'Withdrawal Plan'!M9)/Portfolio!H18*100,0)</f>
         <v>1.84499663787272</v>
       </c>
-      <c r="P9" s="0" t="n">
+      <c r="F65" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N10" s="0" t="n">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="85" t="n">
+        <f aca="false">'Stress Test'!A11</f>
         <v>72</v>
       </c>
-      <c r="O10" s="48" t="n">
+      <c r="B66" s="86" t="n">
+        <f aca="false">'Stress Test'!C11</f>
+        <v>10930702.6785879</v>
+      </c>
+      <c r="C66" s="86" t="n">
+        <f aca="false">'Stress Test'!E11</f>
+        <v>15029388.2211028</v>
+      </c>
+      <c r="D66" s="86" t="n">
+        <f aca="false">'Stress Test'!F11</f>
+        <v>17525238.9769742</v>
+      </c>
+      <c r="E66" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J10+'Withdrawal Plan'!K10+'Withdrawal Plan'!L10+'Withdrawal Plan'!M10)/Portfolio!H19*100,0)</f>
         <v>1.76297410735805</v>
       </c>
-      <c r="P10" s="0" t="n">
+      <c r="F66" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N11" s="0" t="n">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="85" t="n">
+        <f aca="false">'Stress Test'!A12</f>
         <v>73</v>
       </c>
-      <c r="O11" s="48" t="n">
+      <c r="B67" s="86" t="n">
+        <f aca="false">'Stress Test'!C12</f>
+        <v>11240585.1176691</v>
+      </c>
+      <c r="C67" s="86" t="n">
+        <f aca="false">'Stress Test'!E12</f>
+        <v>16104393.6107286</v>
+      </c>
+      <c r="D67" s="86" t="n">
+        <f aca="false">'Stress Test'!F12</f>
+        <v>19150417.2066092</v>
+      </c>
+      <c r="E67" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J11+'Withdrawal Plan'!K11+'Withdrawal Plan'!L11+'Withdrawal Plan'!M11)/Portfolio!H20*100,0)</f>
         <v>1.67929830174105</v>
       </c>
-      <c r="P11" s="0" t="n">
+      <c r="F67" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N12" s="0" t="n">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="85" t="n">
+        <f aca="false">'Stress Test'!A13</f>
         <v>74</v>
       </c>
-      <c r="O12" s="48" t="n">
+      <c r="B68" s="86" t="n">
+        <f aca="false">'Stress Test'!C13</f>
+        <v>11563873.4638348</v>
+      </c>
+      <c r="C68" s="86" t="n">
+        <f aca="false">'Stress Test'!E13</f>
+        <v>17266410.0410459</v>
+      </c>
+      <c r="D68" s="86" t="n">
+        <f aca="false">'Stress Test'!F13</f>
+        <v>20939123.8687291</v>
+      </c>
+      <c r="E68" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J12+'Withdrawal Plan'!K12+'Withdrawal Plan'!L12+'Withdrawal Plan'!M12)/Portfolio!H21*100,0)</f>
         <v>1.59467923394917</v>
       </c>
-      <c r="P12" s="0" t="n">
+      <c r="F68" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N13" s="0" t="n">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="85" t="n">
+        <f aca="false">'Stress Test'!A14</f>
         <v>75</v>
       </c>
-      <c r="O13" s="48" t="n">
+      <c r="B69" s="86" t="n">
+        <f aca="false">'Stress Test'!C14</f>
+        <v>11901125.1186676</v>
+      </c>
+      <c r="C69" s="86" t="n">
+        <f aca="false">'Stress Test'!E14</f>
+        <v>18522419.560609</v>
+      </c>
+      <c r="D69" s="86" t="n">
+        <f aca="false">'Stress Test'!F14</f>
+        <v>22907732.9718814</v>
+      </c>
+      <c r="E69" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J13+'Withdrawal Plan'!K13+'Withdrawal Plan'!L13+'Withdrawal Plan'!M13)/Portfolio!H22*100,0)</f>
         <v>1.50980706631961</v>
       </c>
-      <c r="P13" s="0" t="n">
+      <c r="F69" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N14" s="0" t="n">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="85" t="n">
+        <f aca="false">'Stress Test'!A15</f>
         <v>76</v>
       </c>
-      <c r="O14" s="48" t="n">
+      <c r="B70" s="86" t="n">
+        <f aca="false">'Stress Test'!C15</f>
+        <v>12252920.1039489</v>
+      </c>
+      <c r="C70" s="86" t="n">
+        <f aca="false">'Stress Test'!E15</f>
+        <v>19879963.1059923</v>
+      </c>
+      <c r="D70" s="86" t="n">
+        <f aca="false">'Stress Test'!F15</f>
+        <v>25074256.2496042</v>
+      </c>
+      <c r="E70" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J14+'Withdrawal Plan'!K14+'Withdrawal Plan'!L14+'Withdrawal Plan'!M14)/Portfolio!H23*100,0)</f>
         <v>1.4253359836682</v>
       </c>
-      <c r="P14" s="0" t="n">
+      <c r="F70" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N15" s="0" t="n">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="85" t="n">
+        <f aca="false">'Stress Test'!A16</f>
         <v>77</v>
       </c>
-      <c r="O15" s="48" t="n">
+      <c r="B71" s="86" t="n">
+        <f aca="false">'Stress Test'!C16</f>
+        <v>12619861.9643205</v>
+      </c>
+      <c r="C71" s="86" t="n">
+        <f aca="false">'Stress Test'!E16</f>
+        <v>21347185.2106853</v>
+      </c>
+      <c r="D71" s="86" t="n">
+        <f aca="false">'Stress Test'!F16</f>
+        <v>27458506.9307783</v>
+      </c>
+      <c r="E71" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J15+'Withdrawal Plan'!K15+'Withdrawal Plan'!L15+'Withdrawal Plan'!M15)/Portfolio!H24*100,0)</f>
         <v>1.34187072849199</v>
       </c>
-      <c r="P15" s="0" t="n">
+      <c r="F71" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N16" s="0" t="n">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="85" t="n">
+        <f aca="false">'Stress Test'!A17</f>
         <v>78</v>
       </c>
-      <c r="O16" s="48" t="n">
+      <c r="B72" s="86" t="n">
+        <f aca="false">'Stress Test'!C17</f>
+        <v>13002578.7054862</v>
+      </c>
+      <c r="C72" s="86" t="n">
+        <f aca="false">'Stress Test'!E17</f>
+        <v>22932882.290133</v>
+      </c>
+      <c r="D72" s="86" t="n">
+        <f aca="false">'Stress Test'!F17</f>
+        <v>30082279.8864489</v>
+      </c>
+      <c r="E72" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J16+'Withdrawal Plan'!K16+'Withdrawal Plan'!L16+'Withdrawal Plan'!M16)/Portfolio!H25*100,0)</f>
         <v>1.25995620828742</v>
       </c>
-      <c r="P16" s="0" t="n">
+      <c r="F72" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N17" s="0" t="n">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="85" t="n">
+        <f aca="false">'Stress Test'!A18</f>
         <v>79</v>
       </c>
-      <c r="O17" s="48" t="n">
+      <c r="B73" s="86" t="n">
+        <f aca="false">'Stress Test'!C18</f>
+        <v>13401723.7693359</v>
+      </c>
+      <c r="C73" s="86" t="n">
+        <f aca="false">'Stress Test'!E18</f>
+        <v>24646554.7889739</v>
+      </c>
+      <c r="D73" s="86" t="n">
+        <f aca="false">'Stress Test'!F18</f>
+        <v>32969549.7907241</v>
+      </c>
+      <c r="E73" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J17+'Withdrawal Plan'!K17+'Withdrawal Plan'!L17+'Withdrawal Plan'!M17)/Portfolio!H26*100,0)</f>
         <v>1.18007033156995</v>
       </c>
-      <c r="P17" s="0" t="n">
+      <c r="F73" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N18" s="0" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="85" t="n">
+        <f aca="false">'Stress Test'!A19</f>
         <v>80</v>
       </c>
-      <c r="O18" s="48" t="n">
+      <c r="B74" s="86" t="n">
+        <f aca="false">'Stress Test'!C19</f>
+        <v>13817977.0474267</v>
+      </c>
+      <c r="C74" s="86" t="n">
+        <f aca="false">'Stress Test'!E19</f>
+        <v>26498463.4994091</v>
+      </c>
+      <c r="D74" s="86" t="n">
+        <f aca="false">'Stress Test'!F19</f>
+        <v>36146689.0971138</v>
+      </c>
+      <c r="E74" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J18+'Withdrawal Plan'!K18+'Withdrawal Plan'!L18+'Withdrawal Plan'!M18)/Portfolio!H27*100,0)</f>
         <v>1.10261999981401</v>
       </c>
-      <c r="P18" s="0" t="n">
+      <c r="F74" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N19" s="0" t="n">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="85" t="n">
+        <f aca="false">'Stress Test'!A20</f>
         <v>81</v>
       </c>
-      <c r="O19" s="48" t="n">
+      <c r="B75" s="86" t="n">
+        <f aca="false">'Stress Test'!C20</f>
+        <v>14252045.93431</v>
+      </c>
+      <c r="C75" s="86" t="n">
+        <f aca="false">'Stress Test'!E20</f>
+        <v>28499690.3843481</v>
+      </c>
+      <c r="D75" s="86" t="n">
+        <f aca="false">'Stress Test'!F20</f>
+        <v>39642707.8118115</v>
+      </c>
+      <c r="E75" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J19+'Withdrawal Plan'!K19+'Withdrawal Plan'!L19+'Withdrawal Plan'!M19)/Portfolio!H28*100,0)</f>
         <v>1.02793999619742</v>
       </c>
-      <c r="P19" s="0" t="n">
+      <c r="F75" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N20" s="0" t="n">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="85" t="n">
+        <f aca="false">'Stress Test'!A21</f>
         <v>82</v>
       </c>
-      <c r="O20" s="48" t="n">
+      <c r="B76" s="86" t="n">
+        <f aca="false">'Stress Test'!C21</f>
+        <v>14704666.4222536</v>
+      </c>
+      <c r="C76" s="86" t="n">
+        <f aca="false">'Stress Test'!E21</f>
+        <v>30662204.2656672</v>
+      </c>
+      <c r="D76" s="86" t="n">
+        <f aca="false">'Stress Test'!F21</f>
+        <v>43489517.2435639</v>
+      </c>
+      <c r="E76" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J20+'Withdrawal Plan'!K20+'Withdrawal Plan'!L20+'Withdrawal Plan'!M20)/Portfolio!H29*100,0)</f>
         <v>0.956294378941346</v>
       </c>
-      <c r="P20" s="0" t="n">
+      <c r="F76" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N21" s="0" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="85" t="n">
+        <f aca="false">'Stress Test'!A22</f>
         <v>83</v>
       </c>
-      <c r="O21" s="48" t="n">
+      <c r="B77" s="86" t="n">
+        <f aca="false">'Stress Test'!C22</f>
+        <v>15176604.2389627</v>
+      </c>
+      <c r="C77" s="86" t="n">
+        <f aca="false">'Stress Test'!E22</f>
+        <v>32998931.7667395</v>
+      </c>
+      <c r="D77" s="86" t="n">
+        <f aca="false">'Stress Test'!F22</f>
+        <v>47722220.1277392</v>
+      </c>
+      <c r="E77" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J21+'Withdrawal Plan'!K21+'Withdrawal Plan'!L21+'Withdrawal Plan'!M21)/Portfolio!H30*100,0)</f>
         <v>0.887879909078267</v>
       </c>
-      <c r="P21" s="0" t="n">
+      <c r="F77" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N22" s="0" t="n">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="85" t="n">
+        <f aca="false">'Stress Test'!A23</f>
         <v>84</v>
       </c>
-      <c r="O22" s="48" t="n">
+      <c r="B78" s="86" t="n">
+        <f aca="false">'Stress Test'!C23</f>
+        <v>15668656.0299681</v>
+      </c>
+      <c r="C78" s="86" t="n">
+        <f aca="false">'Stress Test'!E23</f>
+        <v>35523833.9295256</v>
+      </c>
+      <c r="D78" s="86" t="n">
+        <f aca="false">'Stress Test'!F23</f>
+        <v>52379429.76196</v>
+      </c>
+      <c r="E78" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J22+'Withdrawal Plan'!K22+'Withdrawal Plan'!L22+'Withdrawal Plan'!M22)/Portfolio!H31*100,0)</f>
         <v>0.822831014932614</v>
       </c>
-      <c r="P22" s="0" t="n">
+      <c r="F78" s="87" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N23" s="0" t="n">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="85" t="n">
+        <f aca="false">'Stress Test'!A24</f>
         <v>85</v>
       </c>
-      <c r="O23" s="48" t="n">
+      <c r="B79" s="86" t="n">
+        <f aca="false">'Stress Test'!C24</f>
+        <v>16181650.587414</v>
+      </c>
+      <c r="C79" s="86" t="n">
+        <f aca="false">'Stress Test'!E24</f>
+        <v>38251988.9601348</v>
+      </c>
+      <c r="D79" s="86" t="n">
+        <f aca="false">'Stress Test'!F24</f>
+        <v>57503621.0544032</v>
+      </c>
+      <c r="E79" s="87" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J23+'Withdrawal Plan'!K23+'Withdrawal Plan'!L23+'Withdrawal Plan'!M23)/Portfolio!H32*100,0)</f>
         <v>0.761225809389379</v>
       </c>
-      <c r="P23" s="0" t="n">
+      <c r="F79" s="87" t="n">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:T1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10934,14 +13121,14 @@
   <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11007,7 +13194,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="44" t="n">
         <v>73</v>
       </c>
@@ -11054,7 +13241,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="n">
         <v>74</v>
       </c>
@@ -11101,7 +13288,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="44" t="n">
         <v>75</v>
       </c>
@@ -11148,7 +13335,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="44" t="n">
         <v>76</v>
       </c>
@@ -11195,7 +13382,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="44" t="n">
         <v>77</v>
       </c>
@@ -11242,7 +13429,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="44" t="n">
         <v>78</v>
       </c>
@@ -11289,7 +13476,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="44" t="n">
         <v>79</v>
       </c>
@@ -11336,7 +13523,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="44" t="n">
         <v>80</v>
       </c>
@@ -11383,7 +13570,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="44" t="n">
         <v>81</v>
       </c>
@@ -11430,7 +13617,7 @@
         <v>19.4</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="44" t="n">
         <v>82</v>
       </c>
@@ -11477,7 +13664,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="44" t="n">
         <v>83</v>
       </c>
@@ -11524,7 +13711,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="44" t="n">
         <v>84</v>
       </c>
@@ -11571,7 +13758,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="44" t="n">
         <v>85</v>
       </c>
@@ -11618,7 +13805,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="51" t="s">
         <v>103</v>
       </c>
@@ -11682,19 +13869,19 @@
   <dimension ref="A1:N24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="40" t="s">
         <v>104</v>
       </c>
@@ -11772,7 +13959,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="53" t="n">
         <v>65</v>
       </c>
@@ -11829,7 +14016,7 @@
         <v>32033</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="56" t="n">
         <v>66</v>
       </c>
@@ -11886,7 +14073,7 @@
         <v>32033</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="53" t="n">
         <v>67</v>
       </c>
@@ -11943,7 +14130,7 @@
         <v>29452</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="56" t="n">
         <v>68</v>
       </c>
@@ -12000,7 +14187,7 @@
         <v>29388</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="53" t="n">
         <v>69</v>
       </c>
@@ -12057,7 +14244,7 @@
         <v>29321</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="56" t="n">
         <v>70</v>
       </c>
@@ -12114,7 +14301,7 @@
         <v>33710.584</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="53" t="n">
         <v>71</v>
       </c>
@@ -12171,7 +14358,7 @@
         <v>33751.9986</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="56" t="n">
         <v>72</v>
       </c>
@@ -12228,7 +14415,7 @@
         <v>33795.198565</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="44" t="n">
         <v>73</v>
       </c>
@@ -12285,7 +14472,7 @@
         <v>33839.253529125</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="44" t="n">
         <v>74</v>
       </c>
@@ -12342,7 +14529,7 @@
         <v>33884.2348673531</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="44" t="n">
         <v>75</v>
       </c>
@@ -12399,7 +14586,7 @@
         <v>33930.215739037</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="44" t="n">
         <v>76</v>
       </c>
@@ -12456,7 +14643,7 @@
         <v>33978.2711325129</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="44" t="n">
         <v>77</v>
       </c>
@@ -12513,7 +14700,7 @@
         <v>34026.4779108257</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="44" t="n">
         <v>78</v>
       </c>
@@ -12570,7 +14757,7 @@
         <v>34076.9148585963</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="44" t="n">
         <v>79</v>
       </c>
@@ -12627,7 +14814,7 @@
         <v>34127.6627300612</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="44" t="n">
         <v>80</v>
       </c>
@@ -12684,7 +14871,7 @@
         <v>34179.8042983128</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="44" t="n">
         <v>81</v>
       </c>
@@ -12741,7 +14928,7 @@
         <v>34233.4244057706</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="44" t="n">
         <v>82</v>
       </c>
@@ -12798,7 +14985,7 @@
         <v>34288.6100159149</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="44" t="n">
         <v>83</v>
       </c>
@@ -12855,7 +15042,7 @@
         <v>34345.4502663127</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="44" t="n">
         <v>84</v>
       </c>
@@ -12912,7 +15099,7 @@
         <v>34403.0365229706</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="44" t="n">
         <v>85</v>
       </c>
@@ -12992,15 +15179,15 @@
   <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="40" t="s">
         <v>114</v>
       </c>
@@ -13052,7 +15239,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="53" t="n">
         <v>65</v>
       </c>
@@ -13085,7 +15272,7 @@
         <v>178955.944309097</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="56" t="n">
         <v>66</v>
       </c>
@@ -13118,7 +15305,7 @@
         <v>386658.55859383</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="53" t="n">
         <v>67</v>
       </c>
@@ -13151,7 +15338,7 @@
         <v>626848.375895344</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="56" t="n">
         <v>68</v>
       </c>
@@ -13184,7 +15371,7 @@
         <v>904519.428842381</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="53" t="n">
         <v>69</v>
       </c>
@@ -13217,7 +15404,7 @@
         <v>1224514.63096272</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="56" t="n">
         <v>70</v>
       </c>
@@ -13250,7 +15437,7 @@
         <v>1592249.15438649</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="53" t="n">
         <v>71</v>
       </c>
@@ -13283,7 +15470,7 @@
         <v>2013774.6996282</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="56" t="n">
         <v>72</v>
       </c>
@@ -13316,7 +15503,7 @@
         <v>2495850.7558714</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="44" t="n">
         <v>73</v>
       </c>
@@ -13349,7 +15536,7 @@
         <v>3046023.5958806</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="44" t="n">
         <v>74</v>
       </c>
@@ -13382,7 +15569,7 @@
         <v>3672713.82768323</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="44" t="n">
         <v>75</v>
       </c>
@@ -13415,7 +15602,7 @@
         <v>4385313.41127247</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="44" t="n">
         <v>76</v>
       </c>
@@ -13448,7 +15635,7 @@
         <v>5194293.1436119</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="44" t="n">
         <v>77</v>
       </c>
@@ -13481,7 +15668,7 @@
         <v>6111321.72009293</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="44" t="n">
         <v>78</v>
       </c>
@@ -13514,7 +15701,7 @@
         <v>7149397.59631594</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="44" t="n">
         <v>79</v>
       </c>
@@ -13547,7 +15734,7 @@
         <v>8322995.00175019</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="44" t="n">
         <v>80</v>
       </c>
@@ -13580,7 +15767,7 @@
         <v>9648225.59770469</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="44" t="n">
         <v>81</v>
       </c>
@@ -13613,7 +15800,7 @@
         <v>11143017.4274633</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="44" t="n">
         <v>82</v>
       </c>
@@ -13646,7 +15833,7 @@
         <v>12827312.9778966</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="44" t="n">
         <v>83</v>
       </c>
@@ -13679,7 +15866,7 @@
         <v>14723288.3609996</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="44" t="n">
         <v>84</v>
       </c>
@@ -13712,7 +15899,7 @@
         <v>16855595.8324344</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="44" t="n">
         <v>85</v>
       </c>
@@ -13745,7 +15932,7 @@
         <v>19251632.0942683</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="59" t="s">
         <v>123</v>
       </c>
@@ -13762,7 +15949,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C27" s="61" t="n">
         <f aca="false">C24</f>
         <v>16181650.587414</v>
@@ -13816,19 +16003,19 @@
   <dimension ref="A1:L27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="40" t="s">
         <v>129</v>
       </c>
@@ -13860,7 +16047,7 @@
       <c r="K2" s="42"/>
       <c r="L2" s="42"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="62" t="s">
         <v>131</v>
       </c>
@@ -13871,7 +16058,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="62" t="s">
         <v>133</v>
       </c>
@@ -13920,7 +16107,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="56" t="n">
         <v>65</v>
       </c>
@@ -13969,7 +16156,7 @@
         <v>-9303</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="53" t="n">
         <v>66</v>
       </c>
@@ -14018,7 +16205,7 @@
         <v>-11934</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="56" t="n">
         <v>67</v>
       </c>
@@ -14067,7 +16254,7 @@
         <v>-4915.54999999996</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="53" t="n">
         <v>68</v>
       </c>
@@ -14116,7 +16303,7 @@
         <v>-7468.65549999999</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="56" t="n">
         <v>69</v>
       </c>
@@ -14165,7 +16352,7 @@
         <v>-10100.615415</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="53" t="n">
         <v>70</v>
       </c>
@@ -14214,7 +16401,7 @@
         <v>16158.38590255</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="56" t="n">
         <v>71</v>
       </c>
@@ -14263,7 +16450,7 @@
         <v>13842.216812189</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="53" t="n">
         <v>72</v>
       </c>
@@ -14312,7 +16499,7 @@
         <v>11449.2449598968</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="44" t="n">
         <v>73</v>
       </c>
@@ -14361,7 +16548,7 @@
         <v>8977.90998695836</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="44" t="n">
         <v>74</v>
       </c>
@@ -14410,7 +16597,7 @@
         <v>6425.56552531924</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="44" t="n">
         <v>75</v>
       </c>
@@ -14459,7 +16646,7 @@
         <v>-1311.73340733405</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="44" t="n">
         <v>76</v>
       </c>
@@ -14508,7 +16695,7 @@
         <v>-3906.09879776317</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="44" t="n">
         <v>77</v>
       </c>
@@ -14557,7 +16744,7 @@
         <v>-6582.34018264615</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="44" t="n">
         <v>78</v>
       </c>
@@ -14606,7 +16793,7 @@
         <v>26654.7881287132</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="44" t="n">
         <v>79</v>
       </c>
@@ -14655,7 +16842,7 @@
         <v>23804.4394768123</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="44" t="n">
         <v>80</v>
       </c>
@@ -14704,7 +16891,7 @@
         <v>20862.6716124125</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="44" t="n">
         <v>81</v>
       </c>
@@ -14753,7 +16940,7 @@
         <v>17826.4433367876</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="44" t="n">
         <v>82</v>
       </c>
@@ -14802,7 +16989,7 @@
         <v>14692.6110170149</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="44" t="n">
         <v>83</v>
       </c>
@@ -14851,7 +17038,7 @@
         <v>11457.9249713589</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="44" t="n">
         <v>84</v>
       </c>
@@ -14900,7 +17087,7 @@
         <v>8120.02571959645</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="44" t="n">
         <v>85</v>
       </c>

--- a/retirement_planner.xlsx
+++ b/retirement_planner.xlsx
@@ -730,7 +730,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
@@ -739,7 +739,6 @@
     <numFmt numFmtId="169" formatCode="0.0"/>
     <numFmt numFmtId="170" formatCode="0"/>
     <numFmt numFmtId="171" formatCode="0%"/>
-    <numFmt numFmtId="172" formatCode="\$#,##0"/>
   </numFmts>
   <fonts count="41">
     <font>
@@ -1205,7 +1204,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="86">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1538,23 +1537,15 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1634,7 +1625,6 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="10"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1702,23 +1692,27 @@
           <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -1960,23 +1954,27 @@
           <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -2218,23 +2216,27 @@
           <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -2476,23 +2478,27 @@
           <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -2734,23 +2740,27 @@
           <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -2992,23 +3002,27 @@
           <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -3225,11 +3239,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="67194089"/>
-        <c:axId val="5062873"/>
+        <c:axId val="25963316"/>
+        <c:axId val="99463107"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="67194089"/>
+        <c:axId val="25963316"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3268,7 +3282,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3294,7 +3308,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5062873"/>
+        <c:crossAx val="99463107"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3302,7 +3316,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="5062873"/>
+        <c:axId val="99463107"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3350,7 +3364,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="\$#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="\$#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3376,7 +3390,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67194089"/>
+        <c:crossAx val="25963316"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3435,7 +3449,6 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="10"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -3503,23 +3516,27 @@
           <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -3707,23 +3724,27 @@
           <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -3911,23 +3932,27 @@
           <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -4115,23 +4140,27 @@
           <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -4319,23 +4348,27 @@
           <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -4498,11 +4531,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="8645488"/>
-        <c:axId val="91649147"/>
+        <c:axId val="94463532"/>
+        <c:axId val="24927322"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="8645488"/>
+        <c:axId val="94463532"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4541,7 +4574,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4567,7 +4600,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91649147"/>
+        <c:crossAx val="24927322"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4575,7 +4608,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="91649147"/>
+        <c:axId val="24927322"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4623,7 +4656,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="\$#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="\$#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4649,7 +4682,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8645488"/>
+        <c:crossAx val="94463532"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5377,11 +5410,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="83039156"/>
-        <c:axId val="64966211"/>
+        <c:axId val="92312010"/>
+        <c:axId val="20534526"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="83039156"/>
+        <c:axId val="92312010"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5446,7 +5479,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64966211"/>
+        <c:crossAx val="20534526"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5454,7 +5487,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64966211"/>
+        <c:axId val="20534526"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5528,7 +5561,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83039156"/>
+        <c:crossAx val="92312010"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6050,11 +6083,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="64165522"/>
-        <c:axId val="66198551"/>
+        <c:axId val="40997645"/>
+        <c:axId val="34236095"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="64165522"/>
+        <c:axId val="40997645"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6119,7 +6152,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66198551"/>
+        <c:crossAx val="34236095"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6127,7 +6160,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66198551"/>
+        <c:axId val="34236095"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6201,7 +6234,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64165522"/>
+        <c:crossAx val="40997645"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7131,9 +7164,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>551160</xdr:colOff>
+      <xdr:colOff>550800</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>44640</xdr:rowOff>
+      <xdr:rowOff>44280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7142,7 +7175,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8881200" y="438120"/>
-        <a:ext cx="8639640" cy="5759640"/>
+        <a:ext cx="8639280" cy="5759280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7161,9 +7194,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>551160</xdr:colOff>
+      <xdr:colOff>550800</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>44640</xdr:rowOff>
+      <xdr:rowOff>44280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7172,7 +7205,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8881200" y="6534000"/>
-        <a:ext cx="8639640" cy="5759640"/>
+        <a:ext cx="8639280" cy="5759280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8031,7 +8064,7 @@
   <dimension ref="A1:T79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="1" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8058,7 +8091,7 @@
       <c r="S1" s="83"/>
       <c r="T1" s="83"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="84" t="s">
         <v>60</v>
       </c>
@@ -8084,1027 +8117,1027 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="85" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="47" t="n">
         <f aca="false">Portfolio!A3</f>
         <v>56</v>
       </c>
-      <c r="B4" s="86" t="n">
+      <c r="B4" s="85" t="n">
         <f aca="false">Portfolio!B3</f>
         <v>3037518.75</v>
       </c>
-      <c r="C4" s="86" t="n">
+      <c r="C4" s="85" t="n">
         <f aca="false">Portfolio!C3</f>
         <v>810000</v>
       </c>
-      <c r="D4" s="86" t="n">
+      <c r="D4" s="85" t="n">
         <f aca="false">Portfolio!D3</f>
         <v>10800</v>
       </c>
-      <c r="E4" s="86" t="n">
+      <c r="E4" s="85" t="n">
         <f aca="false">Portfolio!E3</f>
         <v>54000</v>
       </c>
-      <c r="F4" s="86" t="n">
+      <c r="F4" s="85" t="n">
         <f aca="false">Portfolio!F3</f>
         <v>116640</v>
       </c>
-      <c r="G4" s="86" t="n">
+      <c r="G4" s="85" t="n">
         <f aca="false">Portfolio!G3</f>
         <v>540000</v>
       </c>
-      <c r="H4" s="86" t="n">
+      <c r="H4" s="85" t="n">
         <f aca="false">Portfolio!I3</f>
         <v>5368958.75</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="85" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="47" t="n">
         <f aca="false">Portfolio!A4</f>
         <v>57</v>
       </c>
-      <c r="B5" s="86" t="n">
+      <c r="B5" s="85" t="n">
         <f aca="false">Portfolio!B4</f>
         <v>3318039</v>
       </c>
-      <c r="C5" s="86" t="n">
+      <c r="C5" s="85" t="n">
         <f aca="false">Portfolio!C4</f>
         <v>874800</v>
       </c>
-      <c r="D5" s="86" t="n">
+      <c r="D5" s="85" t="n">
         <f aca="false">Portfolio!D4</f>
         <v>11664</v>
       </c>
-      <c r="E5" s="86" t="n">
+      <c r="E5" s="85" t="n">
         <f aca="false">Portfolio!E4</f>
         <v>58320</v>
       </c>
-      <c r="F5" s="86" t="n">
+      <c r="F5" s="85" t="n">
         <f aca="false">Portfolio!F4</f>
         <v>134611.2</v>
       </c>
-      <c r="G5" s="86" t="n">
+      <c r="G5" s="85" t="n">
         <f aca="false">Portfolio!G4</f>
         <v>583200</v>
       </c>
-      <c r="H5" s="86" t="n">
+      <c r="H5" s="85" t="n">
         <f aca="false">Portfolio!I4</f>
         <v>5816634.2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="85" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="47" t="n">
         <f aca="false">Portfolio!A5</f>
         <v>58</v>
       </c>
-      <c r="B6" s="86" t="n">
+      <c r="B6" s="85" t="n">
         <f aca="false">Portfolio!B5</f>
         <v>3621000.87</v>
       </c>
-      <c r="C6" s="86" t="n">
+      <c r="C6" s="85" t="n">
         <f aca="false">Portfolio!C5</f>
         <v>944784</v>
       </c>
-      <c r="D6" s="86" t="n">
+      <c r="D6" s="85" t="n">
         <f aca="false">Portfolio!D5</f>
         <v>12597.12</v>
       </c>
-      <c r="E6" s="86" t="n">
+      <c r="E6" s="85" t="n">
         <f aca="false">Portfolio!E5</f>
         <v>62985.6</v>
       </c>
-      <c r="F6" s="86" t="n">
+      <c r="F6" s="85" t="n">
         <f aca="false">Portfolio!F5</f>
         <v>154020.096</v>
       </c>
-      <c r="G6" s="86" t="n">
+      <c r="G6" s="85" t="n">
         <f aca="false">Portfolio!G5</f>
         <v>629856</v>
       </c>
-      <c r="H6" s="86" t="n">
+      <c r="H6" s="85" t="n">
         <f aca="false">Portfolio!I5</f>
         <v>6298863.686</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="85" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="47" t="n">
         <f aca="false">Portfolio!A6</f>
         <v>59</v>
       </c>
-      <c r="B7" s="86" t="n">
+      <c r="B7" s="85" t="n">
         <f aca="false">Portfolio!B6</f>
         <v>3948199.6896</v>
       </c>
-      <c r="C7" s="86" t="n">
+      <c r="C7" s="85" t="n">
         <f aca="false">Portfolio!C6</f>
         <v>1020366.72</v>
       </c>
-      <c r="D7" s="86" t="n">
+      <c r="D7" s="85" t="n">
         <f aca="false">Portfolio!D6</f>
         <v>13604.8896</v>
       </c>
-      <c r="E7" s="86" t="n">
+      <c r="E7" s="85" t="n">
         <f aca="false">Portfolio!E6</f>
         <v>68024.448</v>
       </c>
-      <c r="F7" s="86" t="n">
+      <c r="F7" s="85" t="n">
         <f aca="false">Portfolio!F6</f>
         <v>174981.70368</v>
       </c>
-      <c r="G7" s="86" t="n">
+      <c r="G7" s="85" t="n">
         <f aca="false">Portfolio!G6</f>
         <v>680244.48</v>
       </c>
-      <c r="H7" s="86" t="n">
+      <c r="H7" s="85" t="n">
         <f aca="false">Portfolio!I6</f>
         <v>6818354.83088</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="85" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="47" t="n">
         <f aca="false">Portfolio!A7</f>
         <v>60</v>
       </c>
-      <c r="B8" s="86" t="n">
+      <c r="B8" s="85" t="n">
         <f aca="false">Portfolio!B7</f>
         <v>4301574.414768</v>
       </c>
-      <c r="C8" s="86" t="n">
+      <c r="C8" s="85" t="n">
         <f aca="false">Portfolio!C7</f>
         <v>1101996.0576</v>
       </c>
-      <c r="D8" s="86" t="n">
+      <c r="D8" s="85" t="n">
         <f aca="false">Portfolio!D7</f>
         <v>14693.280768</v>
       </c>
-      <c r="E8" s="86" t="n">
+      <c r="E8" s="85" t="n">
         <f aca="false">Portfolio!E7</f>
         <v>73466.40384</v>
       </c>
-      <c r="F8" s="86" t="n">
+      <c r="F8" s="85" t="n">
         <f aca="false">Portfolio!F7</f>
         <v>197620.2399744</v>
       </c>
-      <c r="G8" s="86" t="n">
+      <c r="G8" s="85" t="n">
         <f aca="false">Portfolio!G7</f>
         <v>734664.0384</v>
       </c>
-      <c r="H8" s="86" t="n">
+      <c r="H8" s="85" t="n">
         <f aca="false">Portfolio!I7</f>
         <v>7378029.3158504</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="85" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="47" t="n">
         <f aca="false">Portfolio!A8</f>
         <v>61</v>
       </c>
-      <c r="B9" s="86" t="n">
+      <c r="B9" s="85" t="n">
         <f aca="false">Portfolio!B8</f>
         <v>4683219.11794944</v>
       </c>
-      <c r="C9" s="86" t="n">
+      <c r="C9" s="85" t="n">
         <f aca="false">Portfolio!C8</f>
         <v>1190155.742208</v>
       </c>
-      <c r="D9" s="86" t="n">
+      <c r="D9" s="85" t="n">
         <f aca="false">Portfolio!D8</f>
         <v>15868.74322944</v>
       </c>
-      <c r="E9" s="86" t="n">
+      <c r="E9" s="85" t="n">
         <f aca="false">Portfolio!E8</f>
         <v>79343.7161472</v>
       </c>
-      <c r="F9" s="86" t="n">
+      <c r="F9" s="85" t="n">
         <f aca="false">Portfolio!F8</f>
         <v>222069.859172352</v>
       </c>
-      <c r="G9" s="86" t="n">
+      <c r="G9" s="85" t="n">
         <f aca="false">Portfolio!G8</f>
         <v>793437.161472</v>
       </c>
-      <c r="H9" s="86" t="n">
+      <c r="H9" s="85" t="n">
         <f aca="false">Portfolio!I8</f>
         <v>7981039.89030093</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="85" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="47" t="n">
         <f aca="false">Portfolio!A9</f>
         <v>62</v>
       </c>
-      <c r="B10" s="86" t="n">
+      <c r="B10" s="85" t="n">
         <f aca="false">Portfolio!B9</f>
         <v>5095395.3973854</v>
       </c>
-      <c r="C10" s="86" t="n">
+      <c r="C10" s="85" t="n">
         <f aca="false">Portfolio!C9</f>
         <v>1285368.20158464</v>
       </c>
-      <c r="D10" s="86" t="n">
+      <c r="D10" s="85" t="n">
         <f aca="false">Portfolio!D9</f>
         <v>17138.2426877952</v>
       </c>
-      <c r="E10" s="86" t="n">
+      <c r="E10" s="85" t="n">
         <f aca="false">Portfolio!E9</f>
         <v>85691.213438976</v>
       </c>
-      <c r="F10" s="86" t="n">
+      <c r="F10" s="85" t="n">
         <f aca="false">Portfolio!F9</f>
         <v>248475.44790614</v>
       </c>
-      <c r="G10" s="86" t="n">
+      <c r="G10" s="85" t="n">
         <f aca="false">Portfolio!G9</f>
         <v>856912.13438976</v>
       </c>
-      <c r="H10" s="86" t="n">
+      <c r="H10" s="85" t="n">
         <f aca="false">Portfolio!I9</f>
         <v>8630788.73727072</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="85" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="47" t="n">
         <f aca="false">Portfolio!A10</f>
         <v>63</v>
       </c>
-      <c r="B11" s="86" t="n">
+      <c r="B11" s="85" t="n">
         <f aca="false">Portfolio!B10</f>
         <v>5540545.77917623</v>
       </c>
-      <c r="C11" s="86" t="n">
+      <c r="C11" s="85" t="n">
         <f aca="false">Portfolio!C10</f>
         <v>1388197.65771141</v>
       </c>
-      <c r="D11" s="86" t="n">
+      <c r="D11" s="85" t="n">
         <f aca="false">Portfolio!D10</f>
         <v>18509.3021028188</v>
       </c>
-      <c r="E11" s="86" t="n">
+      <c r="E11" s="85" t="n">
         <f aca="false">Portfolio!E10</f>
         <v>92546.5105140941</v>
       </c>
-      <c r="F11" s="86" t="n">
+      <c r="F11" s="85" t="n">
         <f aca="false">Portfolio!F10</f>
         <v>276993.483738632</v>
       </c>
-      <c r="G11" s="86" t="n">
+      <c r="G11" s="85" t="n">
         <f aca="false">Portfolio!G10</f>
         <v>925465.105140941</v>
       </c>
-      <c r="H11" s="86" t="n">
+      <c r="H11" s="85" t="n">
         <f aca="false">Portfolio!I10</f>
         <v>9330947.30275665</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="85" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="47" t="n">
         <f aca="false">Portfolio!A11</f>
         <v>64</v>
       </c>
-      <c r="B12" s="86" t="n">
+      <c r="B12" s="85" t="n">
         <f aca="false">Portfolio!B11</f>
         <v>6021308.19151033</v>
       </c>
-      <c r="C12" s="86" t="n">
+      <c r="C12" s="85" t="n">
         <f aca="false">Portfolio!C11</f>
         <v>1499253.47032833</v>
       </c>
-      <c r="D12" s="86" t="n">
+      <c r="D12" s="85" t="n">
         <f aca="false">Portfolio!D11</f>
         <v>19990.0462710443</v>
       </c>
-      <c r="E12" s="86" t="n">
+      <c r="E12" s="85" t="n">
         <f aca="false">Portfolio!E11</f>
         <v>99950.2313552217</v>
       </c>
-      <c r="F12" s="86" t="n">
+      <c r="F12" s="85" t="n">
         <f aca="false">Portfolio!F11</f>
         <v>307792.962437722</v>
       </c>
-      <c r="G12" s="86" t="n">
+      <c r="G12" s="85" t="n">
         <f aca="false">Portfolio!G11</f>
         <v>999502.313552217</v>
       </c>
-      <c r="H12" s="86" t="n">
+      <c r="H12" s="85" t="n">
         <f aca="false">Portfolio!I11</f>
         <v>10085477.7057241</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="85" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="47" t="n">
         <f aca="false">Portfolio!A12</f>
         <v>65</v>
       </c>
-      <c r="B13" s="86" t="n">
+      <c r="B13" s="85" t="n">
         <f aca="false">Portfolio!B12</f>
         <v>2828950</v>
       </c>
-      <c r="C13" s="86" t="n">
+      <c r="C13" s="85" t="n">
         <f aca="false">Portfolio!C12</f>
         <v>1619193.74795459</v>
       </c>
-      <c r="D13" s="86" t="n">
+      <c r="D13" s="85" t="n">
         <f aca="false">Portfolio!D12</f>
         <v>21589.2499727279</v>
       </c>
-      <c r="E13" s="86" t="n">
+      <c r="E13" s="85" t="n">
         <f aca="false">Portfolio!E12</f>
         <v>107946.249863639</v>
       </c>
-      <c r="F13" s="86" t="n">
+      <c r="F13" s="85" t="n">
         <f aca="false">Portfolio!F12</f>
         <v>330196.39943274</v>
       </c>
-      <c r="G13" s="86" t="n">
+      <c r="G13" s="85" t="n">
         <f aca="false">Portfolio!G12</f>
         <v>1079462.49863639</v>
       </c>
-      <c r="H13" s="86" t="n">
+      <c r="H13" s="85" t="n">
         <f aca="false">Portfolio!I12</f>
         <v>7176214.2581915</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="85" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="47" t="n">
         <f aca="false">Portfolio!A13</f>
         <v>66</v>
       </c>
-      <c r="B14" s="86" t="n">
+      <c r="B14" s="85" t="n">
         <f aca="false">Portfolio!B13</f>
         <v>2657900</v>
       </c>
-      <c r="C14" s="86" t="n">
+      <c r="C14" s="85" t="n">
         <f aca="false">Portfolio!C13</f>
         <v>1748729.24779096</v>
       </c>
-      <c r="D14" s="86" t="n">
+      <c r="D14" s="85" t="n">
         <f aca="false">Portfolio!D13</f>
         <v>23316.3899705461</v>
       </c>
-      <c r="E14" s="86" t="n">
+      <c r="E14" s="85" t="n">
         <f aca="false">Portfolio!E13</f>
         <v>116581.949852731</v>
       </c>
-      <c r="F14" s="86" t="n">
+      <c r="F14" s="85" t="n">
         <f aca="false">Portfolio!F13</f>
         <v>354281.111387359</v>
       </c>
-      <c r="G14" s="86" t="n">
+      <c r="G14" s="85" t="n">
         <f aca="false">Portfolio!G13</f>
         <v>1165819.49852731</v>
       </c>
-      <c r="H14" s="86" t="n">
+      <c r="H14" s="85" t="n">
         <f aca="false">Portfolio!I13</f>
         <v>7309003.73491522</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="85" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="47" t="n">
         <f aca="false">Portfolio!A14</f>
         <v>67</v>
       </c>
-      <c r="B15" s="86" t="n">
+      <c r="B15" s="85" t="n">
         <f aca="false">Portfolio!B14</f>
         <v>2527364.4</v>
       </c>
-      <c r="C15" s="86" t="n">
+      <c r="C15" s="85" t="n">
         <f aca="false">Portfolio!C14</f>
         <v>1888627.58761424</v>
       </c>
-      <c r="D15" s="86" t="n">
+      <c r="D15" s="85" t="n">
         <f aca="false">Portfolio!D14</f>
         <v>25181.7011681898</v>
       </c>
-      <c r="E15" s="86" t="n">
+      <c r="E15" s="85" t="n">
         <f aca="false">Portfolio!E14</f>
         <v>125908.505840949</v>
       </c>
-      <c r="F15" s="86" t="n">
+      <c r="F15" s="85" t="n">
         <f aca="false">Portfolio!F14</f>
         <v>380176.050298348</v>
       </c>
-      <c r="G15" s="86" t="n">
+      <c r="G15" s="85" t="n">
         <f aca="false">Portfolio!G14</f>
         <v>1259085.05840949</v>
       </c>
-      <c r="H15" s="86" t="n">
+      <c r="H15" s="85" t="n">
         <f aca="false">Portfolio!I14</f>
         <v>7504625.73989991</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="85" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="47" t="n">
         <f aca="false">Portfolio!A15</f>
         <v>68</v>
       </c>
-      <c r="B16" s="86" t="n">
+      <c r="B16" s="85" t="n">
         <f aca="false">Portfolio!B15</f>
         <v>2397841.66</v>
       </c>
-      <c r="C16" s="86" t="n">
+      <c r="C16" s="85" t="n">
         <f aca="false">Portfolio!C15</f>
         <v>2039717.79462337</v>
       </c>
-      <c r="D16" s="86" t="n">
+      <c r="D16" s="85" t="n">
         <f aca="false">Portfolio!D15</f>
         <v>27196.237261645</v>
       </c>
-      <c r="E16" s="86" t="n">
+      <c r="E16" s="85" t="n">
         <f aca="false">Portfolio!E15</f>
         <v>135981.186308225</v>
       </c>
-      <c r="F16" s="86" t="n">
+      <c r="F16" s="85" t="n">
         <f aca="false">Portfolio!F15</f>
         <v>408020.206822216</v>
       </c>
-      <c r="G16" s="86" t="n">
+      <c r="G16" s="85" t="n">
         <f aca="false">Portfolio!G15</f>
         <v>1359811.86308225</v>
       </c>
-      <c r="H16" s="86" t="n">
+      <c r="H16" s="85" t="n">
         <f aca="false">Portfolio!I15</f>
         <v>7725274.094312</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="85" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="47" t="n">
         <f aca="false">Portfolio!A16</f>
         <v>69</v>
       </c>
-      <c r="B17" s="86" t="n">
+      <c r="B17" s="85" t="n">
         <f aca="false">Portfolio!B16</f>
         <v>2269357.1015</v>
       </c>
-      <c r="C17" s="86" t="n">
+      <c r="C17" s="85" t="n">
         <f aca="false">Portfolio!C16</f>
         <v>2202895.21819324</v>
       </c>
-      <c r="D17" s="86" t="n">
+      <c r="D17" s="85" t="n">
         <f aca="false">Portfolio!D16</f>
         <v>29371.9362425766</v>
       </c>
-      <c r="E17" s="86" t="n">
+      <c r="E17" s="85" t="n">
         <f aca="false">Portfolio!E16</f>
         <v>146859.681212883</v>
       </c>
-      <c r="F17" s="86" t="n">
+      <c r="F17" s="85" t="n">
         <f aca="false">Portfolio!F16</f>
         <v>437963.399492993</v>
       </c>
-      <c r="G17" s="86" t="n">
+      <c r="G17" s="85" t="n">
         <f aca="false">Portfolio!G16</f>
         <v>1468596.81212883</v>
       </c>
-      <c r="H17" s="86" t="n">
+      <c r="H17" s="85" t="n">
         <f aca="false">Portfolio!I16</f>
         <v>7972801.02656446</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="85" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="47" t="n">
         <f aca="false">Portfolio!A17</f>
         <v>70</v>
       </c>
-      <c r="B18" s="86" t="n">
+      <c r="B18" s="85" t="n">
         <f aca="false">Portfolio!B17</f>
         <v>2141936.6790375</v>
       </c>
-      <c r="C18" s="86" t="n">
+      <c r="C18" s="85" t="n">
         <f aca="false">Portfolio!C17</f>
         <v>2379126.8356487</v>
       </c>
-      <c r="D18" s="86" t="n">
+      <c r="D18" s="85" t="n">
         <f aca="false">Portfolio!D17</f>
         <v>31721.6911419827</v>
       </c>
-      <c r="E18" s="86" t="n">
+      <c r="E18" s="85" t="n">
         <f aca="false">Portfolio!E17</f>
         <v>158608.455709914</v>
       </c>
-      <c r="F18" s="86" t="n">
+      <c r="F18" s="85" t="n">
         <f aca="false">Portfolio!F17</f>
         <v>470167.126383683</v>
       </c>
-      <c r="G18" s="86" t="n">
+      <c r="G18" s="85" t="n">
         <f aca="false">Portfolio!G17</f>
         <v>1586084.55709914</v>
       </c>
-      <c r="H18" s="86" t="n">
+      <c r="H18" s="85" t="n">
         <f aca="false">Portfolio!I17</f>
         <v>8249201.28231558</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="85" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="47" t="n">
         <f aca="false">Portfolio!A18</f>
         <v>71</v>
       </c>
-      <c r="B19" s="86" t="n">
+      <c r="B19" s="85" t="n">
         <f aca="false">Portfolio!B18</f>
         <v>2015606.99601344</v>
       </c>
-      <c r="C19" s="86" t="n">
+      <c r="C19" s="85" t="n">
         <f aca="false">Portfolio!C18</f>
         <v>2569456.9825006</v>
       </c>
-      <c r="D19" s="86" t="n">
+      <c r="D19" s="85" t="n">
         <f aca="false">Portfolio!D18</f>
         <v>34259.4264333413</v>
       </c>
-      <c r="E19" s="86" t="n">
+      <c r="E19" s="85" t="n">
         <f aca="false">Portfolio!E18</f>
         <v>171297.132166707</v>
       </c>
-      <c r="F19" s="86" t="n">
+      <c r="F19" s="85" t="n">
         <f aca="false">Portfolio!F18</f>
         <v>504805.48417219</v>
       </c>
-      <c r="G19" s="86" t="n">
+      <c r="G19" s="85" t="n">
         <f aca="false">Portfolio!G18</f>
         <v>1712971.32166707</v>
       </c>
-      <c r="H19" s="86" t="n">
+      <c r="H19" s="85" t="n">
         <f aca="false">Portfolio!I18</f>
         <v>8556623.29742627</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="85" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="47" t="n">
         <f aca="false">Portfolio!A19</f>
         <v>72</v>
       </c>
-      <c r="B20" s="86" t="n">
+      <c r="B20" s="85" t="n">
         <f aca="false">Portfolio!B19</f>
         <v>1890395.32091377</v>
       </c>
-      <c r="C20" s="86" t="n">
+      <c r="C20" s="85" t="n">
         <f aca="false">Portfolio!C19</f>
         <v>2775013.54110065</v>
       </c>
-      <c r="D20" s="86" t="n">
+      <c r="D20" s="85" t="n">
         <f aca="false">Portfolio!D19</f>
         <v>37000.1805480087</v>
       </c>
-      <c r="E20" s="86" t="n">
+      <c r="E20" s="85" t="n">
         <f aca="false">Portfolio!E19</f>
         <v>185000.902740043</v>
       </c>
-      <c r="F20" s="86" t="n">
+      <c r="F20" s="85" t="n">
         <f aca="false">Portfolio!F19</f>
         <v>542066.159967668</v>
       </c>
-      <c r="G20" s="86" t="n">
+      <c r="G20" s="85" t="n">
         <f aca="false">Portfolio!G19</f>
         <v>1850009.02740043</v>
       </c>
-      <c r="H20" s="86" t="n">
+      <c r="H20" s="85" t="n">
         <f aca="false">Portfolio!I19</f>
         <v>8897381.25509478</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="85" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="47" t="n">
         <f aca="false">Portfolio!A20</f>
         <v>73</v>
       </c>
-      <c r="B21" s="86" t="n">
+      <c r="B21" s="85" t="n">
         <f aca="false">Portfolio!B20</f>
         <v>1766329.60393662</v>
       </c>
-      <c r="C21" s="86" t="n">
+      <c r="C21" s="85" t="n">
         <f aca="false">Portfolio!C20</f>
         <v>2997014.6243887</v>
       </c>
-      <c r="D21" s="86" t="n">
+      <c r="D21" s="85" t="n">
         <f aca="false">Portfolio!D20</f>
         <v>39960.1949918494</v>
       </c>
-      <c r="E21" s="86" t="n">
+      <c r="E21" s="85" t="n">
         <f aca="false">Portfolio!E20</f>
         <v>199800.974959247</v>
       </c>
-      <c r="F21" s="86" t="n">
+      <c r="F21" s="85" t="n">
         <f aca="false">Portfolio!F20</f>
         <v>582151.50167987</v>
       </c>
-      <c r="G21" s="86" t="n">
+      <c r="G21" s="85" t="n">
         <f aca="false">Portfolio!G20</f>
         <v>1998009.74959247</v>
       </c>
-      <c r="H21" s="86" t="n">
+      <c r="H21" s="85" t="n">
         <f aca="false">Portfolio!I20</f>
         <v>9273968.09748204</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="85" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="47" t="n">
         <f aca="false">Portfolio!A21</f>
         <v>74</v>
       </c>
-      <c r="B22" s="86" t="n">
+      <c r="B22" s="85" t="n">
         <f aca="false">Portfolio!B21</f>
         <v>1643438.49403503</v>
       </c>
-      <c r="C22" s="86" t="n">
+      <c r="C22" s="85" t="n">
         <f aca="false">Portfolio!C21</f>
         <v>3236775.7943398</v>
       </c>
-      <c r="D22" s="86" t="n">
+      <c r="D22" s="85" t="n">
         <f aca="false">Portfolio!D21</f>
         <v>43157.0105911973</v>
       </c>
-      <c r="E22" s="86" t="n">
+      <c r="E22" s="85" t="n">
         <f aca="false">Portfolio!E21</f>
         <v>215785.052955986</v>
       </c>
-      <c r="F22" s="86" t="n">
+      <c r="F22" s="85" t="n">
         <f aca="false">Portfolio!F21</f>
         <v>625279.673174787</v>
       </c>
-      <c r="G22" s="86" t="n">
+      <c r="G22" s="85" t="n">
         <f aca="false">Portfolio!G21</f>
         <v>2157850.52955986</v>
       </c>
-      <c r="H22" s="86" t="n">
+      <c r="H22" s="85" t="n">
         <f aca="false">Portfolio!I21</f>
         <v>9689069.56774696</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="85" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="47" t="n">
         <f aca="false">Portfolio!A22</f>
         <v>75</v>
       </c>
-      <c r="B23" s="86" t="n">
+      <c r="B23" s="85" t="n">
         <f aca="false">Portfolio!B22</f>
         <v>1521751.35638591</v>
       </c>
-      <c r="C23" s="86" t="n">
+      <c r="C23" s="85" t="n">
         <f aca="false">Portfolio!C22</f>
         <v>3495717.85788698</v>
       </c>
-      <c r="D23" s="86" t="n">
+      <c r="D23" s="85" t="n">
         <f aca="false">Portfolio!D22</f>
         <v>46609.5714384931</v>
       </c>
-      <c r="E23" s="86" t="n">
+      <c r="E23" s="85" t="n">
         <f aca="false">Portfolio!E22</f>
         <v>233047.857192465</v>
       </c>
-      <c r="F23" s="86" t="n">
+      <c r="F23" s="85" t="n">
         <f aca="false">Portfolio!F22</f>
         <v>671685.900957324</v>
       </c>
-      <c r="G23" s="86" t="n">
+      <c r="G23" s="85" t="n">
         <f aca="false">Portfolio!G22</f>
         <v>2330478.57192465</v>
       </c>
-      <c r="H23" s="86" t="n">
+      <c r="H23" s="85" t="n">
         <f aca="false">Portfolio!I22</f>
         <v>10145579.3644652</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="85" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="47" t="n">
         <f aca="false">Portfolio!A23</f>
         <v>76</v>
       </c>
-      <c r="B24" s="86" t="n">
+      <c r="B24" s="85" t="n">
         <f aca="false">Portfolio!B23</f>
         <v>1401298.29029556</v>
       </c>
-      <c r="C24" s="86" t="n">
+      <c r="C24" s="85" t="n">
         <f aca="false">Portfolio!C23</f>
         <v>3775375.28651794</v>
       </c>
-      <c r="D24" s="86" t="n">
+      <c r="D24" s="85" t="n">
         <f aca="false">Portfolio!D23</f>
         <v>50338.3371535725</v>
       </c>
-      <c r="E24" s="86" t="n">
+      <c r="E24" s="85" t="n">
         <f aca="false">Portfolio!E23</f>
         <v>251691.685767863</v>
       </c>
-      <c r="F24" s="86" t="n">
+      <c r="F24" s="85" t="n">
         <f aca="false">Portfolio!F23</f>
         <v>721623.819658892</v>
       </c>
-      <c r="G24" s="86" t="n">
+      <c r="G24" s="85" t="n">
         <f aca="false">Portfolio!G23</f>
         <v>2516916.85767863</v>
       </c>
-      <c r="H24" s="86" t="n">
+      <c r="H24" s="85" t="n">
         <f aca="false">Portfolio!I23</f>
         <v>10646615.4969424</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="85" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="47" t="n">
         <f aca="false">Portfolio!A24</f>
         <v>77</v>
       </c>
-      <c r="B25" s="86" t="n">
+      <c r="B25" s="85" t="n">
         <f aca="false">Portfolio!B24</f>
         <v>1282110.14755295</v>
       </c>
-      <c r="C25" s="86" t="n">
+      <c r="C25" s="85" t="n">
         <f aca="false">Portfolio!C24</f>
         <v>4077405.30943937</v>
       </c>
-      <c r="D25" s="86" t="n">
+      <c r="D25" s="85" t="n">
         <f aca="false">Portfolio!D24</f>
         <v>54365.4041258583</v>
       </c>
-      <c r="E25" s="86" t="n">
+      <c r="E25" s="85" t="n">
         <f aca="false">Portfolio!E24</f>
         <v>271827.020629292</v>
       </c>
-      <c r="F25" s="86" t="n">
+      <c r="F25" s="85" t="n">
         <f aca="false">Portfolio!F24</f>
         <v>775366.924187834</v>
       </c>
-      <c r="G25" s="86" t="n">
+      <c r="G25" s="85" t="n">
         <f aca="false">Portfolio!G24</f>
         <v>2718270.20629292</v>
       </c>
-      <c r="H25" s="86" t="n">
+      <c r="H25" s="85" t="n">
         <f aca="false">Portfolio!I24</f>
         <v>11195537.9369923</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="85" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="47" t="n">
         <f aca="false">Portfolio!A25</f>
         <v>78</v>
       </c>
-      <c r="B26" s="86" t="n">
+      <c r="B26" s="85" t="n">
         <f aca="false">Portfolio!B25</f>
         <v>1164218.55124177</v>
       </c>
-      <c r="C26" s="86" t="n">
+      <c r="C26" s="85" t="n">
         <f aca="false">Portfolio!C25</f>
         <v>4403597.73419453</v>
       </c>
-      <c r="D26" s="86" t="n">
+      <c r="D26" s="85" t="n">
         <f aca="false">Portfolio!D25</f>
         <v>58714.636455927</v>
       </c>
-      <c r="E26" s="86" t="n">
+      <c r="E26" s="85" t="n">
         <f aca="false">Portfolio!E25</f>
         <v>293573.182279635</v>
       </c>
-      <c r="F26" s="86" t="n">
+      <c r="F26" s="85" t="n">
         <f aca="false">Portfolio!F25</f>
         <v>833210.137026903</v>
       </c>
-      <c r="G26" s="86" t="n">
+      <c r="G26" s="85" t="n">
         <f aca="false">Portfolio!G25</f>
         <v>2935731.82279635</v>
       </c>
-      <c r="H26" s="86" t="n">
+      <c r="H26" s="85" t="n">
         <f aca="false">Portfolio!I25</f>
         <v>11795967.6703736</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="85" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="47" t="n">
         <f aca="false">Portfolio!A26</f>
         <v>79</v>
       </c>
-      <c r="B27" s="86" t="n">
+      <c r="B27" s="85" t="n">
         <f aca="false">Portfolio!B26</f>
         <v>1047655.91502281</v>
       </c>
-      <c r="C27" s="86" t="n">
+      <c r="C27" s="85" t="n">
         <f aca="false">Portfolio!C26</f>
         <v>4755885.55293009</v>
       </c>
-      <c r="D27" s="86" t="n">
+      <c r="D27" s="85" t="n">
         <f aca="false">Portfolio!D26</f>
         <v>63411.8073724012</v>
       </c>
-      <c r="E27" s="86" t="n">
+      <c r="E27" s="85" t="n">
         <f aca="false">Portfolio!E26</f>
         <v>317059.036862006</v>
       </c>
-      <c r="F27" s="86" t="n">
+      <c r="F27" s="85" t="n">
         <f aca="false">Portfolio!F26</f>
         <v>895471.4998383</v>
       </c>
-      <c r="G27" s="86" t="n">
+      <c r="G27" s="85" t="n">
         <f aca="false">Portfolio!G26</f>
         <v>3170590.36862006</v>
       </c>
-      <c r="H27" s="86" t="n">
+      <c r="H27" s="85" t="n">
         <f aca="false">Portfolio!I26</f>
         <v>12451807.2593111</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="85" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="47" t="n">
         <f aca="false">Portfolio!A27</f>
         <v>80</v>
       </c>
-      <c r="B28" s="86" t="n">
+      <c r="B28" s="85" t="n">
         <f aca="false">Portfolio!B27</f>
         <v>932455.462898383</v>
       </c>
-      <c r="C28" s="86" t="n">
+      <c r="C28" s="85" t="n">
         <f aca="false">Portfolio!C27</f>
         <v>5136356.39716449</v>
       </c>
-      <c r="D28" s="86" t="n">
+      <c r="D28" s="85" t="n">
         <f aca="false">Portfolio!D27</f>
         <v>68484.7519621933</v>
       </c>
-      <c r="E28" s="86" t="n">
+      <c r="E28" s="85" t="n">
         <f aca="false">Portfolio!E27</f>
         <v>342423.759810966</v>
       </c>
-      <c r="F28" s="86" t="n">
+      <c r="F28" s="85" t="n">
         <f aca="false">Portfolio!F27</f>
         <v>962493.999267071</v>
       </c>
-      <c r="G28" s="86" t="n">
+      <c r="G28" s="85" t="n">
         <f aca="false">Portfolio!G27</f>
         <v>3424237.59810966</v>
       </c>
-      <c r="H28" s="86" t="n">
+      <c r="H28" s="85" t="n">
         <f aca="false">Portfolio!I27</f>
         <v>13167263.0364182</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="85" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="47" t="n">
         <f aca="false">Portfolio!A28</f>
         <v>81</v>
       </c>
-      <c r="B29" s="86" t="n">
+      <c r="B29" s="85" t="n">
         <f aca="false">Portfolio!B28</f>
         <v>818651.249470843</v>
       </c>
-      <c r="C29" s="86" t="n">
+      <c r="C29" s="85" t="n">
         <f aca="false">Portfolio!C28</f>
         <v>5547264.90893765</v>
       </c>
-      <c r="D29" s="86" t="n">
+      <c r="D29" s="85" t="n">
         <f aca="false">Portfolio!D28</f>
         <v>73963.5321191687</v>
       </c>
-      <c r="E29" s="86" t="n">
+      <c r="E29" s="85" t="n">
         <f aca="false">Portfolio!E28</f>
         <v>369817.660595844</v>
       </c>
-      <c r="F29" s="86" t="n">
+      <c r="F29" s="85" t="n">
         <f aca="false">Portfolio!F28</f>
         <v>1034647.53762223</v>
       </c>
-      <c r="G29" s="86" t="n">
+      <c r="G29" s="85" t="n">
         <f aca="false">Portfolio!G28</f>
         <v>3698176.60595844</v>
       </c>
-      <c r="H29" s="86" t="n">
+      <c r="H29" s="85" t="n">
         <f aca="false">Portfolio!I28</f>
         <v>13946869.0599338</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="85" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="47" t="n">
         <f aca="false">Portfolio!A29</f>
         <v>82</v>
       </c>
-      <c r="B30" s="86" t="n">
+      <c r="B30" s="85" t="n">
         <f aca="false">Portfolio!B29</f>
         <v>706278.180707614</v>
       </c>
-      <c r="C30" s="86" t="n">
+      <c r="C30" s="85" t="n">
         <f aca="false">Portfolio!C29</f>
         <v>5991046.10165267</v>
       </c>
-      <c r="D30" s="86" t="n">
+      <c r="D30" s="85" t="n">
         <f aca="false">Portfolio!D29</f>
         <v>79880.6146887023</v>
       </c>
-      <c r="E30" s="86" t="n">
+      <c r="E30" s="85" t="n">
         <f aca="false">Portfolio!E29</f>
         <v>399403.073443511</v>
       </c>
-      <c r="F30" s="86" t="n">
+      <c r="F30" s="85" t="n">
         <f aca="false">Portfolio!F29</f>
         <v>1112331.05996649</v>
       </c>
-      <c r="G30" s="86" t="n">
+      <c r="G30" s="85" t="n">
         <f aca="false">Portfolio!G29</f>
         <v>3994030.73443511</v>
       </c>
-      <c r="H30" s="86" t="n">
+      <c r="H30" s="85" t="n">
         <f aca="false">Portfolio!I29</f>
         <v>14795512.9705591</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="85" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="47" t="n">
         <f aca="false">Portfolio!A30</f>
         <v>83</v>
       </c>
-      <c r="B31" s="86" t="n">
+      <c r="B31" s="85" t="n">
         <f aca="false">Portfolio!B30</f>
         <v>595372.035225304</v>
       </c>
-      <c r="C31" s="86" t="n">
+      <c r="C31" s="85" t="n">
         <f aca="false">Portfolio!C30</f>
         <v>6470329.78978488</v>
       </c>
-      <c r="D31" s="86" t="n">
+      <c r="D31" s="85" t="n">
         <f aca="false">Portfolio!D30</f>
         <v>86271.0638637984</v>
       </c>
-      <c r="E31" s="86" t="n">
+      <c r="E31" s="85" t="n">
         <f aca="false">Portfolio!E30</f>
         <v>431355.319318992</v>
       </c>
-      <c r="F31" s="86" t="n">
+      <c r="F31" s="85" t="n">
         <f aca="false">Portfolio!F30</f>
         <v>1195974.85006501</v>
       </c>
-      <c r="G31" s="86" t="n">
+      <c r="G31" s="85" t="n">
         <f aca="false">Portfolio!G30</f>
         <v>4313553.19318992</v>
       </c>
-      <c r="H31" s="86" t="n">
+      <c r="H31" s="85" t="n">
         <f aca="false">Portfolio!I30</f>
         <v>15718463.9013678</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="85" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="47" t="n">
         <f aca="false">Portfolio!A31</f>
         <v>84</v>
       </c>
-      <c r="B32" s="86" t="n">
+      <c r="B32" s="85" t="n">
         <f aca="false">Portfolio!B31</f>
         <v>485969.486105936</v>
       </c>
-      <c r="C32" s="86" t="n">
+      <c r="C32" s="85" t="n">
         <f aca="false">Portfolio!C31</f>
         <v>6987956.17296767</v>
       </c>
-      <c r="D32" s="86" t="n">
+      <c r="D32" s="85" t="n">
         <f aca="false">Portfolio!D31</f>
         <v>93172.7489729023</v>
       </c>
-      <c r="E32" s="86" t="n">
+      <c r="E32" s="85" t="n">
         <f aca="false">Portfolio!E31</f>
         <v>465863.744864511</v>
       </c>
-      <c r="F32" s="86" t="n">
+      <c r="F32" s="85" t="n">
         <f aca="false">Portfolio!F31</f>
         <v>1286043.00863648</v>
       </c>
-      <c r="G32" s="86" t="n">
+      <c r="G32" s="85" t="n">
         <f aca="false">Portfolio!G31</f>
         <v>4658637.44864512</v>
       </c>
-      <c r="H32" s="86" t="n">
+      <c r="H32" s="85" t="n">
         <f aca="false">Portfolio!I31</f>
         <v>16721402.604359</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="85" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="47" t="n">
         <f aca="false">Portfolio!A32</f>
         <v>85</v>
       </c>
-      <c r="B33" s="86" t="n">
+      <c r="B33" s="85" t="n">
         <f aca="false">Portfolio!B32</f>
         <v>378108.123258585</v>
       </c>
-      <c r="C33" s="86" t="n">
+      <c r="C33" s="85" t="n">
         <f aca="false">Portfolio!C32</f>
         <v>7546992.66680509</v>
       </c>
-      <c r="D33" s="86" t="n">
+      <c r="D33" s="85" t="n">
         <f aca="false">Portfolio!D32</f>
         <v>100626.568890735</v>
       </c>
-      <c r="E33" s="86" t="n">
+      <c r="E33" s="85" t="n">
         <f aca="false">Portfolio!E32</f>
         <v>503132.844453672</v>
       </c>
-      <c r="F33" s="86" t="n">
+      <c r="F33" s="85" t="n">
         <f aca="false">Portfolio!F32</f>
         <v>1383036.12842198</v>
       </c>
-      <c r="G33" s="86" t="n">
+      <c r="G33" s="85" t="n">
         <f aca="false">Portfolio!G32</f>
         <v>5031328.44453672</v>
       </c>
-      <c r="H33" s="86" t="n">
+      <c r="H33" s="85" t="n">
         <f aca="false">Portfolio!I32</f>
         <v>17810453.9702706</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="84" t="s">
         <v>60</v>
       </c>
@@ -9139,973 +9172,973 @@
         <v>208</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="85" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A3</f>
         <v>65</v>
       </c>
-      <c r="B36" s="86" t="n">
+      <c r="B36" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H3</f>
         <v>0</v>
       </c>
-      <c r="C36" s="86" t="n">
+      <c r="C36" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I3</f>
         <v>0</v>
       </c>
-      <c r="D36" s="86" t="n">
+      <c r="D36" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J3</f>
         <v>171050</v>
       </c>
-      <c r="E36" s="86" t="n">
+      <c r="E36" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K3</f>
         <v>0</v>
       </c>
-      <c r="F36" s="86" t="n">
+      <c r="F36" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L3</f>
         <v>0</v>
       </c>
-      <c r="G36" s="86" t="n">
+      <c r="G36" s="85" t="n">
         <f aca="false">B36+C36+D36+E36+F36</f>
         <v>171050</v>
       </c>
-      <c r="H36" s="86" t="n">
+      <c r="H36" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G3</f>
         <v>148320</v>
       </c>
-      <c r="I36" s="86" t="n">
+      <c r="I36" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N3</f>
         <v>27737</v>
       </c>
-      <c r="J36" s="86" t="n">
+      <c r="J36" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O3</f>
         <v>10895.885</v>
       </c>
-      <c r="K36" s="86" t="n">
+      <c r="K36" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P3</f>
         <v>-15902.885</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="85" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A4</f>
         <v>66</v>
       </c>
-      <c r="B37" s="86" t="n">
+      <c r="B37" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H4</f>
         <v>0</v>
       </c>
-      <c r="C37" s="86" t="n">
+      <c r="C37" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I4</f>
         <v>0</v>
       </c>
-      <c r="D37" s="86" t="n">
+      <c r="D37" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J4</f>
         <v>171050</v>
       </c>
-      <c r="E37" s="86" t="n">
+      <c r="E37" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K4</f>
         <v>0</v>
       </c>
-      <c r="F37" s="86" t="n">
+      <c r="F37" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L4</f>
         <v>0</v>
       </c>
-      <c r="G37" s="86" t="n">
+      <c r="G37" s="85" t="n">
         <f aca="false">B37+C37+D37+E37+F37</f>
         <v>171050</v>
       </c>
-      <c r="H37" s="86" t="n">
+      <c r="H37" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G4</f>
         <v>150951</v>
       </c>
-      <c r="I37" s="86" t="n">
+      <c r="I37" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N4</f>
         <v>27737</v>
       </c>
-      <c r="J37" s="86" t="n">
+      <c r="J37" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O4</f>
         <v>10895.885</v>
       </c>
-      <c r="K37" s="86" t="n">
+      <c r="K37" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P4</f>
         <v>-18533.885</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="85" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A5</f>
         <v>67</v>
       </c>
-      <c r="B38" s="86" t="n">
+      <c r="B38" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H5</f>
         <v>47664</v>
       </c>
-      <c r="C38" s="86" t="n">
+      <c r="C38" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I5</f>
         <v>0</v>
       </c>
-      <c r="D38" s="86" t="n">
+      <c r="D38" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J5</f>
         <v>130535.6</v>
       </c>
-      <c r="E38" s="86" t="n">
+      <c r="E38" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K5</f>
         <v>0</v>
       </c>
-      <c r="F38" s="86" t="n">
+      <c r="F38" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L5</f>
         <v>0</v>
       </c>
-      <c r="G38" s="86" t="n">
+      <c r="G38" s="85" t="n">
         <f aca="false">B38+C38+D38+E38+F38</f>
         <v>178199.6</v>
       </c>
-      <c r="H38" s="86" t="n">
+      <c r="H38" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G5</f>
         <v>153663.15</v>
       </c>
-      <c r="I38" s="86" t="n">
+      <c r="I38" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N5</f>
         <v>27737</v>
       </c>
-      <c r="J38" s="86" t="n">
+      <c r="J38" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O5</f>
         <v>8315.11772</v>
       </c>
-      <c r="K38" s="86" t="n">
+      <c r="K38" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P5</f>
         <v>-11515.66772</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="85" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A6</f>
         <v>68</v>
       </c>
-      <c r="B39" s="86" t="n">
+      <c r="B39" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H6</f>
         <v>48855.6</v>
       </c>
-      <c r="C39" s="86" t="n">
+      <c r="C39" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I6</f>
         <v>0</v>
       </c>
-      <c r="D39" s="86" t="n">
+      <c r="D39" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J6</f>
         <v>129522.74</v>
       </c>
-      <c r="E39" s="86" t="n">
+      <c r="E39" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K6</f>
         <v>0</v>
       </c>
-      <c r="F39" s="86" t="n">
+      <c r="F39" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L6</f>
         <v>0</v>
       </c>
-      <c r="G39" s="86" t="n">
+      <c r="G39" s="85" t="n">
         <f aca="false">B39+C39+D39+E39+F39</f>
         <v>178378.34</v>
       </c>
-      <c r="H39" s="86" t="n">
+      <c r="H39" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G6</f>
         <v>156458.9955</v>
       </c>
-      <c r="I39" s="86" t="n">
+      <c r="I39" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N6</f>
         <v>27737</v>
       </c>
-      <c r="J39" s="86" t="n">
+      <c r="J39" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O6</f>
         <v>8250.598538</v>
       </c>
-      <c r="K39" s="86" t="n">
+      <c r="K39" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P6</f>
         <v>-14068.254038</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="85" t="n">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A7</f>
         <v>69</v>
       </c>
-      <c r="B40" s="86" t="n">
+      <c r="B40" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H7</f>
         <v>50076.99</v>
       </c>
-      <c r="C40" s="86" t="n">
+      <c r="C40" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I7</f>
         <v>0</v>
       </c>
-      <c r="D40" s="86" t="n">
+      <c r="D40" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J7</f>
         <v>128484.5585</v>
       </c>
-      <c r="E40" s="86" t="n">
+      <c r="E40" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K7</f>
         <v>0</v>
       </c>
-      <c r="F40" s="86" t="n">
+      <c r="F40" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L7</f>
         <v>0</v>
       </c>
-      <c r="G40" s="86" t="n">
+      <c r="G40" s="85" t="n">
         <f aca="false">B40+C40+D40+E40+F40</f>
         <v>178561.5485</v>
       </c>
-      <c r="H40" s="86" t="n">
+      <c r="H40" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G7</f>
         <v>159341.163915</v>
       </c>
-      <c r="I40" s="86" t="n">
+      <c r="I40" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N7</f>
         <v>27737</v>
       </c>
-      <c r="J40" s="86" t="n">
+      <c r="J40" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O7</f>
         <v>8184.46637645</v>
       </c>
-      <c r="K40" s="86" t="n">
+      <c r="K40" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P7</f>
         <v>-16701.08179145</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="85" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A8</f>
         <v>70</v>
       </c>
-      <c r="B41" s="86" t="n">
+      <c r="B41" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H8</f>
         <v>51328.91475</v>
       </c>
-      <c r="C41" s="86" t="n">
+      <c r="C41" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I8</f>
         <v>23832</v>
       </c>
-      <c r="D41" s="86" t="n">
+      <c r="D41" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J8</f>
         <v>127420.4224625</v>
       </c>
-      <c r="E41" s="86" t="n">
+      <c r="E41" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K8</f>
         <v>0</v>
       </c>
-      <c r="F41" s="86" t="n">
+      <c r="F41" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L8</f>
         <v>0</v>
       </c>
-      <c r="G41" s="86" t="n">
+      <c r="G41" s="85" t="n">
         <f aca="false">B41+C41+D41+E41+F41</f>
         <v>202581.3372125</v>
       </c>
-      <c r="H41" s="86" t="n">
+      <c r="H41" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G8</f>
         <v>152712.36730995</v>
       </c>
-      <c r="I41" s="86" t="n">
+      <c r="I41" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N8</f>
         <v>27737</v>
       </c>
-      <c r="J41" s="86" t="n">
+      <c r="J41" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O8</f>
         <v>8116.68091086125</v>
       </c>
-      <c r="K41" s="86" t="n">
+      <c r="K41" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P8</f>
         <v>14015.2889916887</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="85" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A9</f>
         <v>71</v>
       </c>
-      <c r="B42" s="86" t="n">
+      <c r="B42" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H9</f>
         <v>52612.13761875</v>
       </c>
-      <c r="C42" s="86" t="n">
+      <c r="C42" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I9</f>
         <v>24427.8</v>
       </c>
-      <c r="D42" s="86" t="n">
+      <c r="D42" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J9</f>
         <v>126329.683024063</v>
       </c>
-      <c r="E42" s="86" t="n">
+      <c r="E42" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K9</f>
         <v>0</v>
       </c>
-      <c r="F42" s="86" t="n">
+      <c r="F42" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L9</f>
         <v>0</v>
       </c>
-      <c r="G42" s="86" t="n">
+      <c r="G42" s="85" t="n">
         <f aca="false">B42+C42+D42+E42+F42</f>
         <v>203369.620642813</v>
       </c>
-      <c r="H42" s="86" t="n">
+      <c r="H42" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G9</f>
         <v>155775.405230624</v>
       </c>
-      <c r="I42" s="86" t="n">
+      <c r="I42" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N9</f>
         <v>27737</v>
       </c>
-      <c r="J42" s="86" t="n">
+      <c r="J42" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O9</f>
         <v>8047.20080863278</v>
       </c>
-      <c r="K42" s="86" t="n">
+      <c r="K42" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P9</f>
         <v>11810.0146035562</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="85" t="n">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A10</f>
         <v>72</v>
       </c>
-      <c r="B43" s="86" t="n">
+      <c r="B43" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H10</f>
         <v>53927.4410592187</v>
       </c>
-      <c r="C43" s="86" t="n">
+      <c r="C43" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I10</f>
         <v>25038.495</v>
       </c>
-      <c r="D43" s="86" t="n">
+      <c r="D43" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J10</f>
         <v>125211.675099664</v>
       </c>
-      <c r="E43" s="86" t="n">
+      <c r="E43" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K10</f>
         <v>0</v>
       </c>
-      <c r="F43" s="86" t="n">
+      <c r="F43" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L10</f>
         <v>0</v>
       </c>
-      <c r="G43" s="86" t="n">
+      <c r="G43" s="85" t="n">
         <f aca="false">B43+C43+D43+E43+F43</f>
         <v>204177.611158883</v>
       </c>
-      <c r="H43" s="86" t="n">
+      <c r="H43" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G10</f>
         <v>158933.167633986</v>
       </c>
-      <c r="I43" s="86" t="n">
+      <c r="I43" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N10</f>
         <v>27737</v>
       </c>
-      <c r="J43" s="86" t="n">
+      <c r="J43" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O10</f>
         <v>7975.9837038486</v>
       </c>
-      <c r="K43" s="86" t="n">
+      <c r="K43" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P10</f>
         <v>9531.45982104821</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="85" t="n">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A11</f>
         <v>73</v>
       </c>
-      <c r="B44" s="86" t="n">
+      <c r="B44" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H11</f>
         <v>55275.6270856992</v>
       </c>
-      <c r="C44" s="86" t="n">
+      <c r="C44" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I11</f>
         <v>25664.457375</v>
       </c>
-      <c r="D44" s="86" t="n">
+      <c r="D44" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J11</f>
         <v>124065.716977156</v>
       </c>
-      <c r="E44" s="86" t="n">
+      <c r="E44" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K11</f>
         <v>0</v>
       </c>
-      <c r="F44" s="86" t="n">
+      <c r="F44" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L11</f>
         <v>0</v>
       </c>
-      <c r="G44" s="86" t="n">
+      <c r="G44" s="85" t="n">
         <f aca="false">B44+C44+D44+E44+F44</f>
         <v>205005.801437855</v>
       </c>
-      <c r="H44" s="86" t="n">
+      <c r="H44" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G11</f>
         <v>162188.637921772</v>
       </c>
-      <c r="I44" s="86" t="n">
+      <c r="I44" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N11</f>
         <v>27737</v>
       </c>
-      <c r="J44" s="86" t="n">
+      <c r="J44" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O11</f>
         <v>7902.98617144482</v>
       </c>
-      <c r="K44" s="86" t="n">
+      <c r="K44" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P11</f>
         <v>7177.17734463854</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="85" t="n">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A12</f>
         <v>74</v>
       </c>
-      <c r="B45" s="86" t="n">
+      <c r="B45" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H12</f>
         <v>56657.5177628417</v>
       </c>
-      <c r="C45" s="86" t="n">
+      <c r="C45" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I12</f>
         <v>26306.068809375</v>
       </c>
-      <c r="D45" s="86" t="n">
+      <c r="D45" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J12</f>
         <v>122891.109901585</v>
       </c>
-      <c r="E45" s="86" t="n">
+      <c r="E45" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K12</f>
         <v>0</v>
       </c>
-      <c r="F45" s="86" t="n">
+      <c r="F45" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L12</f>
         <v>0</v>
       </c>
-      <c r="G45" s="86" t="n">
+      <c r="G45" s="85" t="n">
         <f aca="false">B45+C45+D45+E45+F45</f>
         <v>205854.696473801</v>
       </c>
-      <c r="H45" s="86" t="n">
+      <c r="H45" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G12</f>
         <v>165544.896081129</v>
       </c>
-      <c r="I45" s="86" t="n">
+      <c r="I45" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N12</f>
         <v>27737</v>
       </c>
-      <c r="J45" s="86" t="n">
+      <c r="J45" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O12</f>
         <v>7828.16370073094</v>
       </c>
-      <c r="K45" s="86" t="n">
+      <c r="K45" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P12</f>
         <v>4744.63669194142</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="85" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A13</f>
         <v>75</v>
       </c>
-      <c r="B46" s="86" t="n">
+      <c r="B46" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H13</f>
         <v>58073.9557069127</v>
       </c>
-      <c r="C46" s="86" t="n">
+      <c r="C46" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I13</f>
         <v>26963.7205296094</v>
       </c>
-      <c r="D46" s="86" t="n">
+      <c r="D46" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J13</f>
         <v>121687.137649124</v>
       </c>
-      <c r="E46" s="86" t="n">
+      <c r="E46" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K13</f>
         <v>0</v>
       </c>
-      <c r="F46" s="86" t="n">
+      <c r="F46" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L13</f>
         <v>0</v>
       </c>
-      <c r="G46" s="86" t="n">
+      <c r="G46" s="85" t="n">
         <f aca="false">B46+C46+D46+E46+F46</f>
         <v>206724.813885646</v>
       </c>
-      <c r="H46" s="86" t="n">
+      <c r="H46" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G13</f>
         <v>169005.121936352</v>
       </c>
-      <c r="I46" s="86" t="n">
+      <c r="I46" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N13</f>
         <v>27737</v>
       </c>
-      <c r="J46" s="86" t="n">
+      <c r="J46" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O13</f>
         <v>7751.47066824921</v>
       </c>
-      <c r="K46" s="86" t="n">
+      <c r="K46" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P13</f>
         <v>2231.22128104485</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="85" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A14</f>
         <v>76</v>
       </c>
-      <c r="B47" s="86" t="n">
+      <c r="B47" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H14</f>
         <v>59525.8045995855</v>
       </c>
-      <c r="C47" s="86" t="n">
+      <c r="C47" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I14</f>
         <v>27637.8135428496</v>
       </c>
-      <c r="D47" s="86" t="n">
+      <c r="D47" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J14</f>
         <v>120453.066090352</v>
       </c>
-      <c r="E47" s="86" t="n">
+      <c r="E47" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K14</f>
         <v>0</v>
       </c>
-      <c r="F47" s="86" t="n">
+      <c r="F47" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L14</f>
         <v>0</v>
       </c>
-      <c r="G47" s="86" t="n">
+      <c r="G47" s="85" t="n">
         <f aca="false">B47+C47+D47+E47+F47</f>
         <v>207616.684232787</v>
       </c>
-      <c r="H47" s="86" t="n">
+      <c r="H47" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G14</f>
         <v>172572.598515872</v>
       </c>
-      <c r="I47" s="86" t="n">
+      <c r="I47" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N14</f>
         <v>27737</v>
       </c>
-      <c r="J47" s="86" t="n">
+      <c r="J47" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O14</f>
         <v>7672.86030995544</v>
       </c>
-      <c r="K47" s="86" t="n">
+      <c r="K47" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P14</f>
         <v>-365.774593039748</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="85" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A15</f>
         <v>77</v>
       </c>
-      <c r="B48" s="86" t="n">
+      <c r="B48" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H15</f>
         <v>61013.9497145751</v>
       </c>
-      <c r="C48" s="86" t="n">
+      <c r="C48" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I15</f>
         <v>28328.7588814208</v>
       </c>
-      <c r="D48" s="86" t="n">
+      <c r="D48" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J15</f>
         <v>119188.142742611</v>
       </c>
-      <c r="E48" s="86" t="n">
+      <c r="E48" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K15</f>
         <v>0</v>
       </c>
-      <c r="F48" s="86" t="n">
+      <c r="F48" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L15</f>
         <v>0</v>
       </c>
-      <c r="G48" s="86" t="n">
+      <c r="G48" s="85" t="n">
         <f aca="false">B48+C48+D48+E48+F48</f>
         <v>208530.851338607</v>
       </c>
-      <c r="H48" s="86" t="n">
+      <c r="H48" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G15</f>
         <v>176250.715538848</v>
       </c>
-      <c r="I48" s="86" t="n">
+      <c r="I48" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N15</f>
         <v>27737</v>
       </c>
-      <c r="J48" s="86" t="n">
+      <c r="J48" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O15</f>
         <v>7592.28469270433</v>
       </c>
-      <c r="K48" s="86" t="n">
+      <c r="K48" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P15</f>
         <v>-3049.14889294547</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="85" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A16</f>
         <v>78</v>
       </c>
-      <c r="B49" s="86" t="n">
+      <c r="B49" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H16</f>
         <v>62539.2984574395</v>
       </c>
-      <c r="C49" s="86" t="n">
+      <c r="C49" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I16</f>
         <v>29036.9778534564</v>
       </c>
-      <c r="D49" s="86" t="n">
+      <c r="D49" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J16</f>
         <v>117891.596311176</v>
       </c>
-      <c r="E49" s="86" t="n">
+      <c r="E49" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K16</f>
         <v>0</v>
       </c>
-      <c r="F49" s="86" t="n">
+      <c r="F49" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L16</f>
         <v>0</v>
       </c>
-      <c r="G49" s="86" t="n">
+      <c r="G49" s="85" t="n">
         <f aca="false">B49+C49+D49+E49+F49</f>
         <v>209467.872622072</v>
       </c>
-      <c r="H49" s="86" t="n">
+      <c r="H49" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G16</f>
         <v>144042.973025889</v>
       </c>
-      <c r="I49" s="86" t="n">
+      <c r="I49" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N16</f>
         <v>27737</v>
       </c>
-      <c r="J49" s="86" t="n">
+      <c r="J49" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O16</f>
         <v>7509.69468502194</v>
       </c>
-      <c r="K49" s="86" t="n">
+      <c r="K49" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P16</f>
         <v>30178.2049111613</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="85" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A17</f>
         <v>79</v>
       </c>
-      <c r="B50" s="86" t="n">
+      <c r="B50" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H17</f>
         <v>64102.7809188755</v>
       </c>
-      <c r="C50" s="86" t="n">
+      <c r="C50" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I17</f>
         <v>29762.9022997928</v>
       </c>
-      <c r="D50" s="86" t="n">
+      <c r="D50" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J17</f>
         <v>116562.636218956</v>
       </c>
-      <c r="E50" s="86" t="n">
+      <c r="E50" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K17</f>
         <v>0</v>
       </c>
-      <c r="F50" s="86" t="n">
+      <c r="F50" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L17</f>
         <v>0</v>
       </c>
-      <c r="G50" s="86" t="n">
+      <c r="G50" s="85" t="n">
         <f aca="false">B50+C50+D50+E50+F50</f>
         <v>210428.319437624</v>
       </c>
-      <c r="H50" s="86" t="n">
+      <c r="H50" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G17</f>
         <v>147952.985038585</v>
       </c>
-      <c r="I50" s="86" t="n">
+      <c r="I50" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N17</f>
         <v>27737</v>
       </c>
-      <c r="J50" s="86" t="n">
+      <c r="J50" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O17</f>
         <v>7425.03992714749</v>
       </c>
-      <c r="K50" s="86" t="n">
+      <c r="K50" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P17</f>
         <v>27313.2944718917</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="85" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A18</f>
         <v>80</v>
       </c>
-      <c r="B51" s="86" t="n">
+      <c r="B51" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H18</f>
         <v>65705.3504418474</v>
       </c>
-      <c r="C51" s="86" t="n">
+      <c r="C51" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I18</f>
         <v>30506.9748572876</v>
       </c>
-      <c r="D51" s="86" t="n">
+      <c r="D51" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J18</f>
         <v>115200.45212443</v>
       </c>
-      <c r="E51" s="86" t="n">
+      <c r="E51" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K18</f>
         <v>0</v>
       </c>
-      <c r="F51" s="86" t="n">
+      <c r="F51" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L18</f>
         <v>0</v>
       </c>
-      <c r="G51" s="86" t="n">
+      <c r="G51" s="85" t="n">
         <f aca="false">B51+C51+D51+E51+F51</f>
         <v>211412.777423565</v>
       </c>
-      <c r="H51" s="86" t="n">
+      <c r="H51" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G18</f>
         <v>151984.483552758</v>
       </c>
-      <c r="I51" s="86" t="n">
+      <c r="I51" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N18</f>
         <v>27737</v>
       </c>
-      <c r="J51" s="86" t="n">
+      <c r="J51" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O18</f>
         <v>7338.26880032618</v>
       </c>
-      <c r="K51" s="86" t="n">
+      <c r="K51" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P18</f>
         <v>24353.025070481</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="85" t="n">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A19</f>
         <v>81</v>
       </c>
-      <c r="B52" s="86" t="n">
+      <c r="B52" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H19</f>
         <v>67347.9842028936</v>
       </c>
-      <c r="C52" s="86" t="n">
+      <c r="C52" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I19</f>
         <v>31269.6492287198</v>
       </c>
-      <c r="D52" s="86" t="n">
+      <c r="D52" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J19</f>
         <v>113804.21342754</v>
       </c>
-      <c r="E52" s="86" t="n">
+      <c r="E52" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K19</f>
         <v>0</v>
       </c>
-      <c r="F52" s="86" t="n">
+      <c r="F52" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L19</f>
         <v>0</v>
       </c>
-      <c r="G52" s="86" t="n">
+      <c r="G52" s="85" t="n">
         <f aca="false">B52+C52+D52+E52+F52</f>
         <v>212421.846859154</v>
       </c>
-      <c r="H52" s="86" t="n">
+      <c r="H52" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G19</f>
         <v>156141.322470506</v>
       </c>
-      <c r="I52" s="86" t="n">
+      <c r="I52" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N19</f>
         <v>27737</v>
       </c>
-      <c r="J52" s="86" t="n">
+      <c r="J52" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O19</f>
         <v>7249.32839533433</v>
       </c>
-      <c r="K52" s="86" t="n">
+      <c r="K52" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P19</f>
         <v>21294.1959933134</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="85" t="n">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A20</f>
         <v>82</v>
       </c>
-      <c r="B53" s="86" t="n">
+      <c r="B53" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H20</f>
         <v>69031.6838079659</v>
       </c>
-      <c r="C53" s="86" t="n">
+      <c r="C53" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I20</f>
         <v>32051.3904594378</v>
       </c>
-      <c r="D53" s="86" t="n">
+      <c r="D53" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J20</f>
         <v>112373.068763229</v>
       </c>
-      <c r="E53" s="86" t="n">
+      <c r="E53" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K20</f>
         <v>0</v>
       </c>
-      <c r="F53" s="86" t="n">
+      <c r="F53" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L20</f>
         <v>0</v>
       </c>
-      <c r="G53" s="86" t="n">
+      <c r="G53" s="85" t="n">
         <f aca="false">B53+C53+D53+E53+F53</f>
         <v>213456.143030633</v>
       </c>
-      <c r="H53" s="86" t="n">
+      <c r="H53" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G20</f>
         <v>160427.481776345</v>
       </c>
-      <c r="I53" s="86" t="n">
+      <c r="I53" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N20</f>
         <v>27737</v>
       </c>
-      <c r="J53" s="86" t="n">
+      <c r="J53" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O20</f>
         <v>7158.16448021769</v>
       </c>
-      <c r="K53" s="86" t="n">
+      <c r="K53" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P20</f>
         <v>18133.4967740695</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="85" t="n">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A21</f>
         <v>83</v>
       </c>
-      <c r="B54" s="86" t="n">
+      <c r="B54" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H21</f>
         <v>70757.475903165</v>
       </c>
-      <c r="C54" s="86" t="n">
+      <c r="C54" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I21</f>
         <v>32852.6752209237</v>
       </c>
-      <c r="D54" s="86" t="n">
+      <c r="D54" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J21</f>
         <v>110906.14548231</v>
       </c>
-      <c r="E54" s="86" t="n">
+      <c r="E54" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K21</f>
         <v>0</v>
       </c>
-      <c r="F54" s="86" t="n">
+      <c r="F54" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L21</f>
         <v>0</v>
       </c>
-      <c r="G54" s="86" t="n">
+      <c r="G54" s="85" t="n">
         <f aca="false">B54+C54+D54+E54+F54</f>
         <v>214516.296606398</v>
       </c>
-      <c r="H54" s="86" t="n">
+      <c r="H54" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G21</f>
         <v>164847.071842946</v>
       </c>
-      <c r="I54" s="86" t="n">
+      <c r="I54" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N21</f>
         <v>27737</v>
       </c>
-      <c r="J54" s="86" t="n">
+      <c r="J54" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O21</f>
         <v>7064.72146722313</v>
       </c>
-      <c r="K54" s="86" t="n">
+      <c r="K54" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P21</f>
         <v>14867.5032962291</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="85" t="n">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A22</f>
         <v>84</v>
       </c>
-      <c r="B55" s="86" t="n">
+      <c r="B55" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H22</f>
         <v>72526.4128007442</v>
       </c>
-      <c r="C55" s="86" t="n">
+      <c r="C55" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I22</f>
         <v>33673.9921014468</v>
       </c>
-      <c r="D55" s="86" t="n">
+      <c r="D55" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J22</f>
         <v>109402.549119367</v>
       </c>
-      <c r="E55" s="86" t="n">
+      <c r="E55" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K22</f>
         <v>0</v>
       </c>
-      <c r="F55" s="86" t="n">
+      <c r="F55" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L22</f>
         <v>0</v>
       </c>
-      <c r="G55" s="86" t="n">
+      <c r="G55" s="85" t="n">
         <f aca="false">B55+C55+D55+E55+F55</f>
         <v>215602.954021558</v>
       </c>
-      <c r="H55" s="86" t="n">
+      <c r="H55" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G22</f>
         <v>169404.33789221</v>
       </c>
-      <c r="I55" s="86" t="n">
+      <c r="I55" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N22</f>
         <v>27737</v>
       </c>
-      <c r="J55" s="86" t="n">
+      <c r="J55" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O22</f>
         <v>6968.94237890371</v>
       </c>
-      <c r="K55" s="86" t="n">
+      <c r="K55" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P22</f>
         <v>11492.6737504442</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="85" t="n">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="47" t="n">
         <f aca="false">'Withdrawal Plan'!A23</f>
         <v>85</v>
       </c>
-      <c r="B56" s="86" t="n">
+      <c r="B56" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!H23</f>
         <v>74339.5731207628</v>
       </c>
-      <c r="C56" s="86" t="n">
+      <c r="C56" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!I23</f>
         <v>34515.8419039829</v>
       </c>
-      <c r="D56" s="86" t="n">
+      <c r="D56" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!J23</f>
         <v>107861.362847352</v>
       </c>
-      <c r="E56" s="86" t="n">
+      <c r="E56" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!K23</f>
         <v>0</v>
       </c>
-      <c r="F56" s="86" t="n">
+      <c r="F56" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!L23</f>
         <v>0</v>
       </c>
-      <c r="G56" s="86" t="n">
+      <c r="G56" s="85" t="n">
         <f aca="false">B56+C56+D56+E56+F56</f>
         <v>216716.777872097</v>
       </c>
-      <c r="H56" s="86" t="n">
+      <c r="H56" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!G23</f>
         <v>174103.664617651</v>
       </c>
-      <c r="I56" s="86" t="n">
+      <c r="I56" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!N23</f>
         <v>27737</v>
       </c>
-      <c r="J56" s="86" t="n">
+      <c r="J56" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!O23</f>
         <v>6870.7688133763</v>
       </c>
-      <c r="K56" s="86" t="n">
+      <c r="K56" s="85" t="n">
         <f aca="false">'Withdrawal Plan'!P23</f>
         <v>8005.34444106957</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="84" t="s">
         <v>60</v>
       </c>
@@ -10125,528 +10158,528 @@
         <v>210</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="85" t="n">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="47" t="n">
         <f aca="false">'Stress Test'!A4</f>
         <v>65</v>
       </c>
-      <c r="B59" s="86" t="n">
+      <c r="B59" s="85" t="n">
         <f aca="false">'Stress Test'!C4</f>
         <v>9132439.10407305</v>
       </c>
-      <c r="C59" s="86" t="n">
+      <c r="C59" s="85" t="n">
         <f aca="false">'Stress Test'!E4</f>
         <v>9490350.99269125</v>
       </c>
-      <c r="D59" s="86" t="n">
+      <c r="D59" s="85" t="n">
         <f aca="false">'Stress Test'!F4</f>
         <v>9669306.93700034</v>
       </c>
-      <c r="E59" s="87" t="n">
+      <c r="E59" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J3+'Withdrawal Plan'!K3+'Withdrawal Plan'!L3+'Withdrawal Plan'!M3)/Portfolio!H12*100,0)</f>
         <v>2.89394044196095</v>
       </c>
-      <c r="F59" s="87" t="n">
+      <c r="F59" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="85" t="n">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="47" t="n">
         <f aca="false">'Stress Test'!A5</f>
         <v>66</v>
       </c>
-      <c r="B60" s="86" t="n">
+      <c r="B60" s="85" t="n">
         <f aca="false">'Stress Test'!C5</f>
         <v>9324355.66823597</v>
       </c>
-      <c r="C60" s="86" t="n">
+      <c r="C60" s="85" t="n">
         <f aca="false">'Stress Test'!E5</f>
         <v>10076198.0721065</v>
       </c>
-      <c r="D60" s="86" t="n">
+      <c r="D60" s="85" t="n">
         <f aca="false">'Stress Test'!F5</f>
         <v>10462856.6307004</v>
       </c>
-      <c r="E60" s="87" t="n">
+      <c r="E60" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J4+'Withdrawal Plan'!K4+'Withdrawal Plan'!L4+'Withdrawal Plan'!M4)/Portfolio!H13*100,0)</f>
         <v>2.85794669385908</v>
       </c>
-      <c r="F60" s="87" t="n">
+      <c r="F60" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="85" t="n">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="47" t="n">
         <f aca="false">'Stress Test'!A6</f>
         <v>67</v>
       </c>
-      <c r="B61" s="86" t="n">
+      <c r="B61" s="85" t="n">
         <f aca="false">'Stress Test'!C6</f>
         <v>9564346.74496541</v>
       </c>
-      <c r="C61" s="86" t="n">
+      <c r="C61" s="85" t="n">
         <f aca="false">'Stress Test'!E6</f>
         <v>10749310.7678751</v>
       </c>
-      <c r="D61" s="86" t="n">
+      <c r="D61" s="85" t="n">
         <f aca="false">'Stress Test'!F6</f>
         <v>11376159.1437704</v>
       </c>
-      <c r="E61" s="87" t="n">
+      <c r="E61" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J5+'Withdrawal Plan'!K5+'Withdrawal Plan'!L5+'Withdrawal Plan'!M5)/Portfolio!H14*100,0)</f>
         <v>2.14269729372886</v>
       </c>
-      <c r="F61" s="87" t="n">
+      <c r="F61" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="85" t="n">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="47" t="n">
         <f aca="false">'Stress Test'!A7</f>
         <v>68</v>
       </c>
-      <c r="B62" s="86" t="n">
+      <c r="B62" s="85" t="n">
         <f aca="false">'Stress Test'!C7</f>
         <v>9814827.94726403</v>
       </c>
-      <c r="C62" s="86" t="n">
+      <c r="C62" s="85" t="n">
         <f aca="false">'Stress Test'!E7</f>
         <v>11477162.9618051</v>
       </c>
-      <c r="D62" s="86" t="n">
+      <c r="D62" s="85" t="n">
         <f aca="false">'Stress Test'!F7</f>
         <v>12381682.3906475</v>
       </c>
-      <c r="E62" s="87" t="n">
+      <c r="E62" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J6+'Withdrawal Plan'!K6+'Withdrawal Plan'!L6+'Withdrawal Plan'!M6)/Portfolio!H15*100,0)</f>
         <v>2.07413421408362</v>
       </c>
-      <c r="F62" s="87" t="n">
+      <c r="F62" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="85" t="n">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="47" t="n">
         <f aca="false">'Stress Test'!A8</f>
         <v>69</v>
       </c>
-      <c r="B63" s="86" t="n">
+      <c r="B63" s="85" t="n">
         <f aca="false">'Stress Test'!C8</f>
         <v>10076238.0827796</v>
       </c>
-      <c r="C63" s="86" t="n">
+      <c r="C63" s="85" t="n">
         <f aca="false">'Stress Test'!E8</f>
         <v>12264153.0163745</v>
       </c>
-      <c r="D63" s="86" t="n">
+      <c r="D63" s="85" t="n">
         <f aca="false">'Stress Test'!F8</f>
         <v>13488667.6473372</v>
       </c>
-      <c r="E63" s="87" t="n">
+      <c r="E63" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J7+'Withdrawal Plan'!K7+'Withdrawal Plan'!L7+'Withdrawal Plan'!M7)/Portfolio!H16*100,0)</f>
         <v>2.00125246142858</v>
       </c>
-      <c r="F63" s="87" t="n">
+      <c r="F63" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="85" t="n">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="47" t="n">
         <f aca="false">'Stress Test'!A9</f>
         <v>70</v>
       </c>
-      <c r="B64" s="86" t="n">
+      <c r="B64" s="85" t="n">
         <f aca="false">'Stress Test'!C9</f>
         <v>10349033.8385595</v>
       </c>
-      <c r="C64" s="86" t="n">
+      <c r="C64" s="85" t="n">
         <f aca="false">'Stress Test'!E9</f>
         <v>13115031.4901532</v>
       </c>
-      <c r="D64" s="86" t="n">
+      <c r="D64" s="85" t="n">
         <f aca="false">'Stress Test'!F9</f>
         <v>14707280.6445397</v>
       </c>
-      <c r="E64" s="87" t="n">
+      <c r="E64" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J8+'Withdrawal Plan'!K8+'Withdrawal Plan'!L8+'Withdrawal Plan'!M8)/Portfolio!H17*100,0)</f>
         <v>1.92465415799426</v>
       </c>
-      <c r="F64" s="87" t="n">
+      <c r="F64" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="85" t="n">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="47" t="n">
         <f aca="false">'Stress Test'!A10</f>
         <v>71</v>
       </c>
-      <c r="B65" s="86" t="n">
+      <c r="B65" s="85" t="n">
         <f aca="false">'Stress Test'!C10</f>
         <v>10633690.4967557</v>
       </c>
-      <c r="C65" s="86" t="n">
+      <c r="C65" s="85" t="n">
         <f aca="false">'Stress Test'!E10</f>
         <v>14034929.3140192</v>
       </c>
-      <c r="D65" s="86" t="n">
+      <c r="D65" s="85" t="n">
         <f aca="false">'Stress Test'!F10</f>
         <v>16048704.0136474</v>
       </c>
-      <c r="E65" s="87" t="n">
+      <c r="E65" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J9+'Withdrawal Plan'!K9+'Withdrawal Plan'!L9+'Withdrawal Plan'!M9)/Portfolio!H18*100,0)</f>
         <v>1.84499663787272</v>
       </c>
-      <c r="F65" s="87" t="n">
+      <c r="F65" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="85" t="n">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="47" t="n">
         <f aca="false">'Stress Test'!A11</f>
         <v>72</v>
       </c>
-      <c r="B66" s="86" t="n">
+      <c r="B66" s="85" t="n">
         <f aca="false">'Stress Test'!C11</f>
         <v>10930702.6785879</v>
       </c>
-      <c r="C66" s="86" t="n">
+      <c r="C66" s="85" t="n">
         <f aca="false">'Stress Test'!E11</f>
         <v>15029388.2211028</v>
       </c>
-      <c r="D66" s="86" t="n">
+      <c r="D66" s="85" t="n">
         <f aca="false">'Stress Test'!F11</f>
         <v>17525238.9769742</v>
       </c>
-      <c r="E66" s="87" t="n">
+      <c r="E66" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J10+'Withdrawal Plan'!K10+'Withdrawal Plan'!L10+'Withdrawal Plan'!M10)/Portfolio!H19*100,0)</f>
         <v>1.76297410735805</v>
       </c>
-      <c r="F66" s="87" t="n">
+      <c r="F66" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="85" t="n">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="47" t="n">
         <f aca="false">'Stress Test'!A12</f>
         <v>73</v>
       </c>
-      <c r="B67" s="86" t="n">
+      <c r="B67" s="85" t="n">
         <f aca="false">'Stress Test'!C12</f>
         <v>11240585.1176691</v>
       </c>
-      <c r="C67" s="86" t="n">
+      <c r="C67" s="85" t="n">
         <f aca="false">'Stress Test'!E12</f>
         <v>16104393.6107286</v>
       </c>
-      <c r="D67" s="86" t="n">
+      <c r="D67" s="85" t="n">
         <f aca="false">'Stress Test'!F12</f>
         <v>19150417.2066092</v>
       </c>
-      <c r="E67" s="87" t="n">
+      <c r="E67" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J11+'Withdrawal Plan'!K11+'Withdrawal Plan'!L11+'Withdrawal Plan'!M11)/Portfolio!H20*100,0)</f>
         <v>1.67929830174105</v>
       </c>
-      <c r="F67" s="87" t="n">
+      <c r="F67" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="85" t="n">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="47" t="n">
         <f aca="false">'Stress Test'!A13</f>
         <v>74</v>
       </c>
-      <c r="B68" s="86" t="n">
+      <c r="B68" s="85" t="n">
         <f aca="false">'Stress Test'!C13</f>
         <v>11563873.4638348</v>
       </c>
-      <c r="C68" s="86" t="n">
+      <c r="C68" s="85" t="n">
         <f aca="false">'Stress Test'!E13</f>
         <v>17266410.0410459</v>
       </c>
-      <c r="D68" s="86" t="n">
+      <c r="D68" s="85" t="n">
         <f aca="false">'Stress Test'!F13</f>
         <v>20939123.8687291</v>
       </c>
-      <c r="E68" s="87" t="n">
+      <c r="E68" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J12+'Withdrawal Plan'!K12+'Withdrawal Plan'!L12+'Withdrawal Plan'!M12)/Portfolio!H21*100,0)</f>
         <v>1.59467923394917</v>
       </c>
-      <c r="F68" s="87" t="n">
+      <c r="F68" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="85" t="n">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="47" t="n">
         <f aca="false">'Stress Test'!A14</f>
         <v>75</v>
       </c>
-      <c r="B69" s="86" t="n">
+      <c r="B69" s="85" t="n">
         <f aca="false">'Stress Test'!C14</f>
         <v>11901125.1186676</v>
       </c>
-      <c r="C69" s="86" t="n">
+      <c r="C69" s="85" t="n">
         <f aca="false">'Stress Test'!E14</f>
         <v>18522419.560609</v>
       </c>
-      <c r="D69" s="86" t="n">
+      <c r="D69" s="85" t="n">
         <f aca="false">'Stress Test'!F14</f>
         <v>22907732.9718814</v>
       </c>
-      <c r="E69" s="87" t="n">
+      <c r="E69" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J13+'Withdrawal Plan'!K13+'Withdrawal Plan'!L13+'Withdrawal Plan'!M13)/Portfolio!H22*100,0)</f>
         <v>1.50980706631961</v>
       </c>
-      <c r="F69" s="87" t="n">
+      <c r="F69" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="85" t="n">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="47" t="n">
         <f aca="false">'Stress Test'!A15</f>
         <v>76</v>
       </c>
-      <c r="B70" s="86" t="n">
+      <c r="B70" s="85" t="n">
         <f aca="false">'Stress Test'!C15</f>
         <v>12252920.1039489</v>
       </c>
-      <c r="C70" s="86" t="n">
+      <c r="C70" s="85" t="n">
         <f aca="false">'Stress Test'!E15</f>
         <v>19879963.1059923</v>
       </c>
-      <c r="D70" s="86" t="n">
+      <c r="D70" s="85" t="n">
         <f aca="false">'Stress Test'!F15</f>
         <v>25074256.2496042</v>
       </c>
-      <c r="E70" s="87" t="n">
+      <c r="E70" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J14+'Withdrawal Plan'!K14+'Withdrawal Plan'!L14+'Withdrawal Plan'!M14)/Portfolio!H23*100,0)</f>
         <v>1.4253359836682</v>
       </c>
-      <c r="F70" s="87" t="n">
+      <c r="F70" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="85" t="n">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="47" t="n">
         <f aca="false">'Stress Test'!A16</f>
         <v>77</v>
       </c>
-      <c r="B71" s="86" t="n">
+      <c r="B71" s="85" t="n">
         <f aca="false">'Stress Test'!C16</f>
         <v>12619861.9643205</v>
       </c>
-      <c r="C71" s="86" t="n">
+      <c r="C71" s="85" t="n">
         <f aca="false">'Stress Test'!E16</f>
         <v>21347185.2106853</v>
       </c>
-      <c r="D71" s="86" t="n">
+      <c r="D71" s="85" t="n">
         <f aca="false">'Stress Test'!F16</f>
         <v>27458506.9307783</v>
       </c>
-      <c r="E71" s="87" t="n">
+      <c r="E71" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J15+'Withdrawal Plan'!K15+'Withdrawal Plan'!L15+'Withdrawal Plan'!M15)/Portfolio!H24*100,0)</f>
         <v>1.34187072849199</v>
       </c>
-      <c r="F71" s="87" t="n">
+      <c r="F71" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="85" t="n">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="47" t="n">
         <f aca="false">'Stress Test'!A17</f>
         <v>78</v>
       </c>
-      <c r="B72" s="86" t="n">
+      <c r="B72" s="85" t="n">
         <f aca="false">'Stress Test'!C17</f>
         <v>13002578.7054862</v>
       </c>
-      <c r="C72" s="86" t="n">
+      <c r="C72" s="85" t="n">
         <f aca="false">'Stress Test'!E17</f>
         <v>22932882.290133</v>
       </c>
-      <c r="D72" s="86" t="n">
+      <c r="D72" s="85" t="n">
         <f aca="false">'Stress Test'!F17</f>
         <v>30082279.8864489</v>
       </c>
-      <c r="E72" s="87" t="n">
+      <c r="E72" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J16+'Withdrawal Plan'!K16+'Withdrawal Plan'!L16+'Withdrawal Plan'!M16)/Portfolio!H25*100,0)</f>
         <v>1.25995620828742</v>
       </c>
-      <c r="F72" s="87" t="n">
+      <c r="F72" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="85" t="n">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="47" t="n">
         <f aca="false">'Stress Test'!A18</f>
         <v>79</v>
       </c>
-      <c r="B73" s="86" t="n">
+      <c r="B73" s="85" t="n">
         <f aca="false">'Stress Test'!C18</f>
         <v>13401723.7693359</v>
       </c>
-      <c r="C73" s="86" t="n">
+      <c r="C73" s="85" t="n">
         <f aca="false">'Stress Test'!E18</f>
         <v>24646554.7889739</v>
       </c>
-      <c r="D73" s="86" t="n">
+      <c r="D73" s="85" t="n">
         <f aca="false">'Stress Test'!F18</f>
         <v>32969549.7907241</v>
       </c>
-      <c r="E73" s="87" t="n">
+      <c r="E73" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J17+'Withdrawal Plan'!K17+'Withdrawal Plan'!L17+'Withdrawal Plan'!M17)/Portfolio!H26*100,0)</f>
         <v>1.18007033156995</v>
       </c>
-      <c r="F73" s="87" t="n">
+      <c r="F73" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="85" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="47" t="n">
         <f aca="false">'Stress Test'!A19</f>
         <v>80</v>
       </c>
-      <c r="B74" s="86" t="n">
+      <c r="B74" s="85" t="n">
         <f aca="false">'Stress Test'!C19</f>
         <v>13817977.0474267</v>
       </c>
-      <c r="C74" s="86" t="n">
+      <c r="C74" s="85" t="n">
         <f aca="false">'Stress Test'!E19</f>
         <v>26498463.4994091</v>
       </c>
-      <c r="D74" s="86" t="n">
+      <c r="D74" s="85" t="n">
         <f aca="false">'Stress Test'!F19</f>
         <v>36146689.0971138</v>
       </c>
-      <c r="E74" s="87" t="n">
+      <c r="E74" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J18+'Withdrawal Plan'!K18+'Withdrawal Plan'!L18+'Withdrawal Plan'!M18)/Portfolio!H27*100,0)</f>
         <v>1.10261999981401</v>
       </c>
-      <c r="F74" s="87" t="n">
+      <c r="F74" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="85" t="n">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="47" t="n">
         <f aca="false">'Stress Test'!A20</f>
         <v>81</v>
       </c>
-      <c r="B75" s="86" t="n">
+      <c r="B75" s="85" t="n">
         <f aca="false">'Stress Test'!C20</f>
         <v>14252045.93431</v>
       </c>
-      <c r="C75" s="86" t="n">
+      <c r="C75" s="85" t="n">
         <f aca="false">'Stress Test'!E20</f>
         <v>28499690.3843481</v>
       </c>
-      <c r="D75" s="86" t="n">
+      <c r="D75" s="85" t="n">
         <f aca="false">'Stress Test'!F20</f>
         <v>39642707.8118115</v>
       </c>
-      <c r="E75" s="87" t="n">
+      <c r="E75" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J19+'Withdrawal Plan'!K19+'Withdrawal Plan'!L19+'Withdrawal Plan'!M19)/Portfolio!H28*100,0)</f>
         <v>1.02793999619742</v>
       </c>
-      <c r="F75" s="87" t="n">
+      <c r="F75" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="85" t="n">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="47" t="n">
         <f aca="false">'Stress Test'!A21</f>
         <v>82</v>
       </c>
-      <c r="B76" s="86" t="n">
+      <c r="B76" s="85" t="n">
         <f aca="false">'Stress Test'!C21</f>
         <v>14704666.4222536</v>
       </c>
-      <c r="C76" s="86" t="n">
+      <c r="C76" s="85" t="n">
         <f aca="false">'Stress Test'!E21</f>
         <v>30662204.2656672</v>
       </c>
-      <c r="D76" s="86" t="n">
+      <c r="D76" s="85" t="n">
         <f aca="false">'Stress Test'!F21</f>
         <v>43489517.2435639</v>
       </c>
-      <c r="E76" s="87" t="n">
+      <c r="E76" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J20+'Withdrawal Plan'!K20+'Withdrawal Plan'!L20+'Withdrawal Plan'!M20)/Portfolio!H29*100,0)</f>
         <v>0.956294378941346</v>
       </c>
-      <c r="F76" s="87" t="n">
+      <c r="F76" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="85" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="47" t="n">
         <f aca="false">'Stress Test'!A22</f>
         <v>83</v>
       </c>
-      <c r="B77" s="86" t="n">
+      <c r="B77" s="85" t="n">
         <f aca="false">'Stress Test'!C22</f>
         <v>15176604.2389627</v>
       </c>
-      <c r="C77" s="86" t="n">
+      <c r="C77" s="85" t="n">
         <f aca="false">'Stress Test'!E22</f>
         <v>32998931.7667395</v>
       </c>
-      <c r="D77" s="86" t="n">
+      <c r="D77" s="85" t="n">
         <f aca="false">'Stress Test'!F22</f>
         <v>47722220.1277392</v>
       </c>
-      <c r="E77" s="87" t="n">
+      <c r="E77" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J21+'Withdrawal Plan'!K21+'Withdrawal Plan'!L21+'Withdrawal Plan'!M21)/Portfolio!H30*100,0)</f>
         <v>0.887879909078267</v>
       </c>
-      <c r="F77" s="87" t="n">
+      <c r="F77" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="85" t="n">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="47" t="n">
         <f aca="false">'Stress Test'!A23</f>
         <v>84</v>
       </c>
-      <c r="B78" s="86" t="n">
+      <c r="B78" s="85" t="n">
         <f aca="false">'Stress Test'!C23</f>
         <v>15668656.0299681</v>
       </c>
-      <c r="C78" s="86" t="n">
+      <c r="C78" s="85" t="n">
         <f aca="false">'Stress Test'!E23</f>
         <v>35523833.9295256</v>
       </c>
-      <c r="D78" s="86" t="n">
+      <c r="D78" s="85" t="n">
         <f aca="false">'Stress Test'!F23</f>
         <v>52379429.76196</v>
       </c>
-      <c r="E78" s="87" t="n">
+      <c r="E78" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J22+'Withdrawal Plan'!K22+'Withdrawal Plan'!L22+'Withdrawal Plan'!M22)/Portfolio!H31*100,0)</f>
         <v>0.822831014932614</v>
       </c>
-      <c r="F78" s="87" t="n">
+      <c r="F78" s="48" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="85" t="n">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="47" t="n">
         <f aca="false">'Stress Test'!A24</f>
         <v>85</v>
       </c>
-      <c r="B79" s="86" t="n">
+      <c r="B79" s="85" t="n">
         <f aca="false">'Stress Test'!C24</f>
         <v>16181650.587414</v>
       </c>
-      <c r="C79" s="86" t="n">
+      <c r="C79" s="85" t="n">
         <f aca="false">'Stress Test'!E24</f>
         <v>38251988.9601348</v>
       </c>
-      <c r="D79" s="86" t="n">
+      <c r="D79" s="85" t="n">
         <f aca="false">'Stress Test'!F24</f>
         <v>57503621.0544032</v>
       </c>
-      <c r="E79" s="87" t="n">
+      <c r="E79" s="48" t="n">
         <f aca="false">IFERROR(('Withdrawal Plan'!J23+'Withdrawal Plan'!K23+'Withdrawal Plan'!L23+'Withdrawal Plan'!M23)/Portfolio!H32*100,0)</f>
         <v>0.761225809389379</v>
       </c>
-      <c r="F79" s="87" t="n">
+      <c r="F79" s="48" t="n">
         <v>4</v>
       </c>
     </row>

--- a/retirement_planner.xlsx
+++ b/retirement_planner.xlsx
@@ -330,13 +330,13 @@
 Surplus ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">REQUIRED MINIMUM DISTRIBUTIONS  (Ages 73–85)</t>
+    <t xml:space="preserve">REQUIRED MINIMUM DISTRIBUTIONS (SECURE 2.0 — Age 75, Born 1960+)</t>
   </si>
   <si>
     <t xml:space="preserve">IRS Uniform Lifetime Table</t>
   </si>
   <si>
-    <t xml:space="preserve">RMDs begin at age 73 (SECURE 2.0). RMD = Trad 401k balance ÷ IRS Uniform Lifetime Factor. Roth conversion is done first; any remaining capacity can add extra conversions above RMD. RMD is mandatory income — taxed as ordinary income.</t>
+    <t xml:space="preserve">RMDs begin at age 75 (SECURE 2.0 Act, born 1960+, effective 2033). RMD = Trad 401k balance ÷ IRS Uniform Lifetime Factor. Roth conversion is done first; any remaining capacity can add extra conversions above RMD. RMD is mandatory income — taxed as ordinary income.</t>
   </si>
   <si>
     <t xml:space="preserve">Trad 401k
@@ -730,7 +730,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
@@ -738,9 +738,10 @@
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
     <numFmt numFmtId="170" formatCode="0"/>
-    <numFmt numFmtId="171" formatCode="0%"/>
+    <numFmt numFmtId="171" formatCode="#,##0"/>
+    <numFmt numFmtId="172" formatCode="0%"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -952,6 +953,19 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
@@ -1098,14 +1112,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFF4FF"/>
-        <bgColor rgb="FFE8F4FF"/>
+        <fgColor rgb="FFFFF9C4"/>
+        <bgColor rgb="FFFFF0E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8C96A"/>
-        <bgColor rgb="FFD4C9B8"/>
+        <fgColor rgb="FFEFF4FF"/>
+        <bgColor rgb="FFE8F4FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1127,7 +1141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1178,6 +1192,13 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1204,7 +1225,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="92">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1401,23 +1422,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="28" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="28" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="28" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="29" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1433,31 +1474,35 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="16" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="16" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="30" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="32" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1465,11 +1510,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="33" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="35" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1489,7 +1534,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1513,11 +1558,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1541,7 +1586,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1578,7 +1623,7 @@
       <rgbColor rgb="FF8064A2"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF9C27B0"/>
-      <rgbColor rgb="FFFFFDF7"/>
+      <rgbColor rgb="FFFFF9C4"/>
       <rgbColor rgb="FFE8F4FF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFF79646"/>
@@ -1586,7 +1631,7 @@
       <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFFFDF7"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
@@ -3239,11 +3284,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="25963316"/>
-        <c:axId val="99463107"/>
+        <c:axId val="81615781"/>
+        <c:axId val="39758053"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="25963316"/>
+        <c:axId val="81615781"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3308,7 +3353,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99463107"/>
+        <c:crossAx val="39758053"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3316,7 +3361,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99463107"/>
+        <c:axId val="39758053"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3390,7 +3435,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25963316"/>
+        <c:crossAx val="81615781"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4531,11 +4576,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="94463532"/>
-        <c:axId val="24927322"/>
+        <c:axId val="9351744"/>
+        <c:axId val="64287517"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94463532"/>
+        <c:axId val="9351744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4600,7 +4645,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24927322"/>
+        <c:crossAx val="64287517"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4608,7 +4653,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24927322"/>
+        <c:axId val="64287517"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4682,7 +4727,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94463532"/>
+        <c:crossAx val="9351744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4741,7 +4786,6 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="10"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -4810,23 +4854,27 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -5017,23 +5065,27 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -5224,23 +5276,27 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -5410,11 +5466,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="92312010"/>
-        <c:axId val="20534526"/>
+        <c:axId val="27381142"/>
+        <c:axId val="95898223"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="92312010"/>
+        <c:axId val="27381142"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5453,7 +5509,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -5479,7 +5535,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20534526"/>
+        <c:crossAx val="95898223"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5487,7 +5543,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="20534526"/>
+        <c:axId val="95898223"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5535,7 +5591,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="\$#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="\$#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -5561,7 +5617,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92312010"/>
+        <c:crossAx val="27381142"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5620,7 +5676,6 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="10"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -5690,23 +5745,27 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -5897,23 +5956,27 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -6083,11 +6146,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="40997645"/>
-        <c:axId val="34236095"/>
+        <c:axId val="47487095"/>
+        <c:axId val="55775517"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="40997645"/>
+        <c:axId val="47487095"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6126,7 +6189,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -6152,7 +6215,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34236095"/>
+        <c:crossAx val="55775517"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6160,7 +6223,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="34236095"/>
+        <c:axId val="55775517"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6208,7 +6271,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -6234,7 +6297,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40997645"/>
+        <c:crossAx val="47487095"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7164,9 +7227,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>550800</xdr:colOff>
+      <xdr:colOff>549720</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>44280</xdr:rowOff>
+      <xdr:rowOff>43200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7175,7 +7238,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8881200" y="438120"/>
-        <a:ext cx="8639280" cy="5759280"/>
+        <a:ext cx="8638200" cy="5758200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7194,9 +7257,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>550800</xdr:colOff>
+      <xdr:colOff>549720</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>44280</xdr:rowOff>
+      <xdr:rowOff>43200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7205,7 +7268,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8881200" y="6534000"/>
-        <a:ext cx="8639280" cy="5759280"/>
+        <a:ext cx="8638200" cy="5758200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7224,9 +7287,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>745200</xdr:colOff>
+      <xdr:colOff>744120</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>44640</xdr:rowOff>
+      <xdr:rowOff>43560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7235,7 +7298,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="15487560"/>
-        <a:ext cx="8639640" cy="5759640"/>
+        <a:ext cx="8638560" cy="5758560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7254,9 +7317,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>551160</xdr:colOff>
+      <xdr:colOff>550080</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>44640</xdr:rowOff>
+      <xdr:rowOff>43560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7265,7 +7328,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8881200" y="15487560"/>
-        <a:ext cx="8639640" cy="5759640"/>
+        <a:ext cx="8638560" cy="5758560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7849,7 +7912,7 @@
         <v>50</v>
       </c>
       <c r="B44" s="6" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7955,90 +8018,90 @@
       <c r="B1" s="16"/>
     </row>
     <row r="2" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="83" t="s">
         <v>169</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="84" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="85" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="86" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="87" t="s">
         <v>173</v>
       </c>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="88" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="85" t="s">
         <v>175</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="86" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="81" t="s">
+      <c r="A6" s="87" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="82" t="s">
+      <c r="B6" s="88" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="79" t="s">
+      <c r="A7" s="85" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="80" t="s">
+      <c r="B7" s="86" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="81" t="s">
+      <c r="A8" s="87" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="88" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="79" t="s">
+      <c r="A9" s="85" t="s">
         <v>183</v>
       </c>
-      <c r="B9" s="80" t="s">
+      <c r="B9" s="86" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="87" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="82" t="s">
+      <c r="B10" s="88" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="79" t="s">
+      <c r="A11" s="85" t="s">
         <v>187</v>
       </c>
-      <c r="B11" s="80" t="s">
+      <c r="B11" s="86" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="81" t="s">
+      <c r="A12" s="87" t="s">
         <v>189</v>
       </c>
-      <c r="B12" s="82" t="s">
+      <c r="B12" s="88" t="s">
         <v>190</v>
       </c>
     </row>
@@ -8068,52 +8131,52 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="89" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="83"/>
-      <c r="T1" s="83"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="89"/>
+      <c r="Q1" s="89"/>
+      <c r="R1" s="89"/>
+      <c r="S1" s="89"/>
+      <c r="T1" s="89"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="90" t="s">
         <v>192</v>
       </c>
-      <c r="C3" s="84" t="s">
+      <c r="C3" s="90" t="s">
         <v>193</v>
       </c>
-      <c r="D3" s="84" t="s">
+      <c r="D3" s="90" t="s">
         <v>194</v>
       </c>
-      <c r="E3" s="84" t="s">
+      <c r="E3" s="90" t="s">
         <v>195</v>
       </c>
-      <c r="F3" s="84" t="s">
+      <c r="F3" s="90" t="s">
         <v>196</v>
       </c>
-      <c r="G3" s="84" t="s">
+      <c r="G3" s="90" t="s">
         <v>197</v>
       </c>
-      <c r="H3" s="84" t="s">
+      <c r="H3" s="90" t="s">
         <v>198</v>
       </c>
     </row>
@@ -8122,31 +8185,31 @@
         <f aca="false">Portfolio!A3</f>
         <v>56</v>
       </c>
-      <c r="B4" s="85" t="n">
+      <c r="B4" s="91" t="n">
         <f aca="false">Portfolio!B3</f>
         <v>3037518.75</v>
       </c>
-      <c r="C4" s="85" t="n">
+      <c r="C4" s="91" t="n">
         <f aca="false">Portfolio!C3</f>
         <v>810000</v>
       </c>
-      <c r="D4" s="85" t="n">
+      <c r="D4" s="91" t="n">
         <f aca="false">Portfolio!D3</f>
         <v>10800</v>
       </c>
-      <c r="E4" s="85" t="n">
+      <c r="E4" s="91" t="n">
         <f aca="false">Portfolio!E3</f>
         <v>54000</v>
       </c>
-      <c r="F4" s="85" t="n">
+      <c r="F4" s="91" t="n">
         <f aca="false">Portfolio!F3</f>
         <v>116640</v>
       </c>
-      <c r="G4" s="85" t="n">
+      <c r="G4" s="91" t="n">
         <f aca="false">Portfolio!G3</f>
         <v>540000</v>
       </c>
-      <c r="H4" s="85" t="n">
+      <c r="H4" s="91" t="n">
         <f aca="false">Portfolio!I3</f>
         <v>5368958.75</v>
       </c>
@@ -8156,31 +8219,31 @@
         <f aca="false">Portfolio!A4</f>
         <v>57</v>
       </c>
-      <c r="B5" s="85" t="n">
+      <c r="B5" s="91" t="n">
         <f aca="false">Portfolio!B4</f>
         <v>3318039</v>
       </c>
-      <c r="C5" s="85" t="n">
+      <c r="C5" s="91" t="n">
         <f aca="false">Portfolio!C4</f>
         <v>874800</v>
       </c>
-      <c r="D5" s="85" t="n">
+      <c r="D5" s="91" t="n">
         <f aca="false">Portfolio!D4</f>
         <v>11664</v>
       </c>
-      <c r="E5" s="85" t="n">
+      <c r="E5" s="91" t="n">
         <f aca="false">Portfolio!E4</f>
         <v>58320</v>
       </c>
-      <c r="F5" s="85" t="n">
+      <c r="F5" s="91" t="n">
         <f aca="false">Portfolio!F4</f>
         <v>134611.2</v>
       </c>
-      <c r="G5" s="85" t="n">
+      <c r="G5" s="91" t="n">
         <f aca="false">Portfolio!G4</f>
         <v>583200</v>
       </c>
-      <c r="H5" s="85" t="n">
+      <c r="H5" s="91" t="n">
         <f aca="false">Portfolio!I4</f>
         <v>5816634.2</v>
       </c>
@@ -8190,31 +8253,31 @@
         <f aca="false">Portfolio!A5</f>
         <v>58</v>
       </c>
-      <c r="B6" s="85" t="n">
+      <c r="B6" s="91" t="n">
         <f aca="false">Portfolio!B5</f>
         <v>3621000.87</v>
       </c>
-      <c r="C6" s="85" t="n">
+      <c r="C6" s="91" t="n">
         <f aca="false">Portfolio!C5</f>
         <v>944784</v>
       </c>
-      <c r="D6" s="85" t="n">
+      <c r="D6" s="91" t="n">
         <f aca="false">Portfolio!D5</f>
         <v>12597.12</v>
       </c>
-      <c r="E6" s="85" t="n">
+      <c r="E6" s="91" t="n">
         <f aca="false">Portfolio!E5</f>
         <v>62985.6</v>
       </c>
-      <c r="F6" s="85" t="n">
+      <c r="F6" s="91" t="n">
         <f aca="false">Portfolio!F5</f>
         <v>154020.096</v>
       </c>
-      <c r="G6" s="85" t="n">
+      <c r="G6" s="91" t="n">
         <f aca="false">Portfolio!G5</f>
         <v>629856</v>
       </c>
-      <c r="H6" s="85" t="n">
+      <c r="H6" s="91" t="n">
         <f aca="false">Portfolio!I5</f>
         <v>6298863.686</v>
       </c>
@@ -8224,31 +8287,31 @@
         <f aca="false">Portfolio!A6</f>
         <v>59</v>
       </c>
-      <c r="B7" s="85" t="n">
+      <c r="B7" s="91" t="n">
         <f aca="false">Portfolio!B6</f>
         <v>3948199.6896</v>
       </c>
-      <c r="C7" s="85" t="n">
+      <c r="C7" s="91" t="n">
         <f aca="false">Portfolio!C6</f>
         <v>1020366.72</v>
       </c>
-      <c r="D7" s="85" t="n">
+      <c r="D7" s="91" t="n">
         <f aca="false">Portfolio!D6</f>
         <v>13604.8896</v>
       </c>
-      <c r="E7" s="85" t="n">
+      <c r="E7" s="91" t="n">
         <f aca="false">Portfolio!E6</f>
         <v>68024.448</v>
       </c>
-      <c r="F7" s="85" t="n">
+      <c r="F7" s="91" t="n">
         <f aca="false">Portfolio!F6</f>
         <v>174981.70368</v>
       </c>
-      <c r="G7" s="85" t="n">
+      <c r="G7" s="91" t="n">
         <f aca="false">Portfolio!G6</f>
         <v>680244.48</v>
       </c>
-      <c r="H7" s="85" t="n">
+      <c r="H7" s="91" t="n">
         <f aca="false">Portfolio!I6</f>
         <v>6818354.83088</v>
       </c>
@@ -8258,31 +8321,31 @@
         <f aca="false">Portfolio!A7</f>
         <v>60</v>
       </c>
-      <c r="B8" s="85" t="n">
+      <c r="B8" s="91" t="n">
         <f aca="false">Portfolio!B7</f>
         <v>4301574.414768</v>
       </c>
-      <c r="C8" s="85" t="n">
+      <c r="C8" s="91" t="n">
         <f aca="false">Portfolio!C7</f>
         <v>1101996.0576</v>
       </c>
-      <c r="D8" s="85" t="n">
+      <c r="D8" s="91" t="n">
         <f aca="false">Portfolio!D7</f>
         <v>14693.280768</v>
       </c>
-      <c r="E8" s="85" t="n">
+      <c r="E8" s="91" t="n">
         <f aca="false">Portfolio!E7</f>
         <v>73466.40384</v>
       </c>
-      <c r="F8" s="85" t="n">
+      <c r="F8" s="91" t="n">
         <f aca="false">Portfolio!F7</f>
         <v>197620.2399744</v>
       </c>
-      <c r="G8" s="85" t="n">
+      <c r="G8" s="91" t="n">
         <f aca="false">Portfolio!G7</f>
         <v>734664.0384</v>
       </c>
-      <c r="H8" s="85" t="n">
+      <c r="H8" s="91" t="n">
         <f aca="false">Portfolio!I7</f>
         <v>7378029.3158504</v>
       </c>
@@ -8292,31 +8355,31 @@
         <f aca="false">Portfolio!A8</f>
         <v>61</v>
       </c>
-      <c r="B9" s="85" t="n">
+      <c r="B9" s="91" t="n">
         <f aca="false">Portfolio!B8</f>
         <v>4683219.11794944</v>
       </c>
-      <c r="C9" s="85" t="n">
+      <c r="C9" s="91" t="n">
         <f aca="false">Portfolio!C8</f>
         <v>1190155.742208</v>
       </c>
-      <c r="D9" s="85" t="n">
+      <c r="D9" s="91" t="n">
         <f aca="false">Portfolio!D8</f>
         <v>15868.74322944</v>
       </c>
-      <c r="E9" s="85" t="n">
+      <c r="E9" s="91" t="n">
         <f aca="false">Portfolio!E8</f>
         <v>79343.7161472</v>
       </c>
-      <c r="F9" s="85" t="n">
+      <c r="F9" s="91" t="n">
         <f aca="false">Portfolio!F8</f>
         <v>222069.859172352</v>
       </c>
-      <c r="G9" s="85" t="n">
+      <c r="G9" s="91" t="n">
         <f aca="false">Portfolio!G8</f>
         <v>793437.161472</v>
       </c>
-      <c r="H9" s="85" t="n">
+      <c r="H9" s="91" t="n">
         <f aca="false">Portfolio!I8</f>
         <v>7981039.89030093</v>
       </c>
@@ -8326,31 +8389,31 @@
         <f aca="false">Portfolio!A9</f>
         <v>62</v>
       </c>
-      <c r="B10" s="85" t="n">
+      <c r="B10" s="91" t="n">
         <f aca="false">Portfolio!B9</f>
         <v>5095395.3973854</v>
       </c>
-      <c r="C10" s="85" t="n">
+      <c r="C10" s="91" t="n">
         <f aca="false">Portfolio!C9</f>
         <v>1285368.20158464</v>
       </c>
-      <c r="D10" s="85" t="n">
+      <c r="D10" s="91" t="n">
         <f aca="false">Portfolio!D9</f>
         <v>17138.2426877952</v>
       </c>
-      <c r="E10" s="85" t="n">
+      <c r="E10" s="91" t="n">
         <f aca="false">Portfolio!E9</f>
         <v>85691.213438976</v>
       </c>
-      <c r="F10" s="85" t="n">
+      <c r="F10" s="91" t="n">
         <f aca="false">Portfolio!F9</f>
         <v>248475.44790614</v>
       </c>
-      <c r="G10" s="85" t="n">
+      <c r="G10" s="91" t="n">
         <f aca="false">Portfolio!G9</f>
         <v>856912.13438976</v>
       </c>
-      <c r="H10" s="85" t="n">
+      <c r="H10" s="91" t="n">
         <f aca="false">Portfolio!I9</f>
         <v>8630788.73727072</v>
       </c>
@@ -8360,31 +8423,31 @@
         <f aca="false">Portfolio!A10</f>
         <v>63</v>
       </c>
-      <c r="B11" s="85" t="n">
+      <c r="B11" s="91" t="n">
         <f aca="false">Portfolio!B10</f>
         <v>5540545.77917623</v>
       </c>
-      <c r="C11" s="85" t="n">
+      <c r="C11" s="91" t="n">
         <f aca="false">Portfolio!C10</f>
         <v>1388197.65771141</v>
       </c>
-      <c r="D11" s="85" t="n">
+      <c r="D11" s="91" t="n">
         <f aca="false">Portfolio!D10</f>
         <v>18509.3021028188</v>
       </c>
-      <c r="E11" s="85" t="n">
+      <c r="E11" s="91" t="n">
         <f aca="false">Portfolio!E10</f>
         <v>92546.5105140941</v>
       </c>
-      <c r="F11" s="85" t="n">
+      <c r="F11" s="91" t="n">
         <f aca="false">Portfolio!F10</f>
         <v>276993.483738632</v>
       </c>
-      <c r="G11" s="85" t="n">
+      <c r="G11" s="91" t="n">
         <f aca="false">Portfolio!G10</f>
         <v>925465.105140941</v>
       </c>
-      <c r="H11" s="85" t="n">
+      <c r="H11" s="91" t="n">
         <f aca="false">Portfolio!I10</f>
         <v>9330947.30275665</v>
       </c>
@@ -8394,31 +8457,31 @@
         <f aca="false">Portfolio!A11</f>
         <v>64</v>
       </c>
-      <c r="B12" s="85" t="n">
+      <c r="B12" s="91" t="n">
         <f aca="false">Portfolio!B11</f>
         <v>6021308.19151033</v>
       </c>
-      <c r="C12" s="85" t="n">
+      <c r="C12" s="91" t="n">
         <f aca="false">Portfolio!C11</f>
         <v>1499253.47032833</v>
       </c>
-      <c r="D12" s="85" t="n">
+      <c r="D12" s="91" t="n">
         <f aca="false">Portfolio!D11</f>
         <v>19990.0462710443</v>
       </c>
-      <c r="E12" s="85" t="n">
+      <c r="E12" s="91" t="n">
         <f aca="false">Portfolio!E11</f>
         <v>99950.2313552217</v>
       </c>
-      <c r="F12" s="85" t="n">
+      <c r="F12" s="91" t="n">
         <f aca="false">Portfolio!F11</f>
         <v>307792.962437722</v>
       </c>
-      <c r="G12" s="85" t="n">
+      <c r="G12" s="91" t="n">
         <f aca="false">Portfolio!G11</f>
         <v>999502.313552217</v>
       </c>
-      <c r="H12" s="85" t="n">
+      <c r="H12" s="91" t="n">
         <f aca="false">Portfolio!I11</f>
         <v>10085477.7057241</v>
       </c>
@@ -8428,31 +8491,31 @@
         <f aca="false">Portfolio!A12</f>
         <v>65</v>
       </c>
-      <c r="B13" s="85" t="n">
+      <c r="B13" s="91" t="n">
         <f aca="false">Portfolio!B12</f>
         <v>2828950</v>
       </c>
-      <c r="C13" s="85" t="n">
+      <c r="C13" s="91" t="n">
         <f aca="false">Portfolio!C12</f>
         <v>1619193.74795459</v>
       </c>
-      <c r="D13" s="85" t="n">
+      <c r="D13" s="91" t="n">
         <f aca="false">Portfolio!D12</f>
         <v>21589.2499727279</v>
       </c>
-      <c r="E13" s="85" t="n">
+      <c r="E13" s="91" t="n">
         <f aca="false">Portfolio!E12</f>
         <v>107946.249863639</v>
       </c>
-      <c r="F13" s="85" t="n">
+      <c r="F13" s="91" t="n">
         <f aca="false">Portfolio!F12</f>
         <v>330196.39943274</v>
       </c>
-      <c r="G13" s="85" t="n">
+      <c r="G13" s="91" t="n">
         <f aca="false">Portfolio!G12</f>
         <v>1079462.49863639</v>
       </c>
-      <c r="H13" s="85" t="n">
+      <c r="H13" s="91" t="n">
         <f aca="false">Portfolio!I12</f>
         <v>7176214.2581915</v>
       </c>
@@ -8462,31 +8525,31 @@
         <f aca="false">Portfolio!A13</f>
         <v>66</v>
       </c>
-      <c r="B14" s="85" t="n">
+      <c r="B14" s="91" t="n">
         <f aca="false">Portfolio!B13</f>
         <v>2657900</v>
       </c>
-      <c r="C14" s="85" t="n">
+      <c r="C14" s="91" t="n">
         <f aca="false">Portfolio!C13</f>
         <v>1748729.24779096</v>
       </c>
-      <c r="D14" s="85" t="n">
+      <c r="D14" s="91" t="n">
         <f aca="false">Portfolio!D13</f>
         <v>23316.3899705461</v>
       </c>
-      <c r="E14" s="85" t="n">
+      <c r="E14" s="91" t="n">
         <f aca="false">Portfolio!E13</f>
         <v>116581.949852731</v>
       </c>
-      <c r="F14" s="85" t="n">
+      <c r="F14" s="91" t="n">
         <f aca="false">Portfolio!F13</f>
         <v>354281.111387359</v>
       </c>
-      <c r="G14" s="85" t="n">
+      <c r="G14" s="91" t="n">
         <f aca="false">Portfolio!G13</f>
         <v>1165819.49852731</v>
       </c>
-      <c r="H14" s="85" t="n">
+      <c r="H14" s="91" t="n">
         <f aca="false">Portfolio!I13</f>
         <v>7309003.73491522</v>
       </c>
@@ -8496,31 +8559,31 @@
         <f aca="false">Portfolio!A14</f>
         <v>67</v>
       </c>
-      <c r="B15" s="85" t="n">
+      <c r="B15" s="91" t="n">
         <f aca="false">Portfolio!B14</f>
         <v>2527364.4</v>
       </c>
-      <c r="C15" s="85" t="n">
+      <c r="C15" s="91" t="n">
         <f aca="false">Portfolio!C14</f>
         <v>1888627.58761424</v>
       </c>
-      <c r="D15" s="85" t="n">
+      <c r="D15" s="91" t="n">
         <f aca="false">Portfolio!D14</f>
         <v>25181.7011681898</v>
       </c>
-      <c r="E15" s="85" t="n">
+      <c r="E15" s="91" t="n">
         <f aca="false">Portfolio!E14</f>
         <v>125908.505840949</v>
       </c>
-      <c r="F15" s="85" t="n">
+      <c r="F15" s="91" t="n">
         <f aca="false">Portfolio!F14</f>
         <v>380176.050298348</v>
       </c>
-      <c r="G15" s="85" t="n">
+      <c r="G15" s="91" t="n">
         <f aca="false">Portfolio!G14</f>
         <v>1259085.05840949</v>
       </c>
-      <c r="H15" s="85" t="n">
+      <c r="H15" s="91" t="n">
         <f aca="false">Portfolio!I14</f>
         <v>7504625.73989991</v>
       </c>
@@ -8530,31 +8593,31 @@
         <f aca="false">Portfolio!A15</f>
         <v>68</v>
       </c>
-      <c r="B16" s="85" t="n">
+      <c r="B16" s="91" t="n">
         <f aca="false">Portfolio!B15</f>
         <v>2397841.66</v>
       </c>
-      <c r="C16" s="85" t="n">
+      <c r="C16" s="91" t="n">
         <f aca="false">Portfolio!C15</f>
         <v>2039717.79462337</v>
       </c>
-      <c r="D16" s="85" t="n">
+      <c r="D16" s="91" t="n">
         <f aca="false">Portfolio!D15</f>
         <v>27196.237261645</v>
       </c>
-      <c r="E16" s="85" t="n">
+      <c r="E16" s="91" t="n">
         <f aca="false">Portfolio!E15</f>
         <v>135981.186308225</v>
       </c>
-      <c r="F16" s="85" t="n">
+      <c r="F16" s="91" t="n">
         <f aca="false">Portfolio!F15</f>
         <v>408020.206822216</v>
       </c>
-      <c r="G16" s="85" t="n">
+      <c r="G16" s="91" t="n">
         <f aca="false">Portfolio!G15</f>
         <v>1359811.86308225</v>
       </c>
-      <c r="H16" s="85" t="n">
+      <c r="H16" s="91" t="n">
         <f aca="false">Portfolio!I15</f>
         <v>7725274.094312</v>
       </c>
@@ -8564,31 +8627,31 @@
         <f aca="false">Portfolio!A16</f>
         <v>69</v>
       </c>
-      <c r="B17" s="85" t="n">
+      <c r="B17" s="91" t="n">
         <f aca="false">Portfolio!B16</f>
         <v>2269357.1015</v>
       </c>
-      <c r="C17" s="85" t="n">
+      <c r="C17" s="91" t="n">
         <f aca="false">Portfolio!C16</f>
         <v>2202895.21819324</v>
       </c>
-      <c r="D17" s="85" t="n">
+      <c r="D17" s="91" t="n">
         <f aca="false">Portfolio!D16</f>
         <v>29371.9362425766</v>
       </c>
-      <c r="E17" s="85" t="n">
+      <c r="E17" s="91" t="n">
         <f aca="false">Portfolio!E16</f>
         <v>146859.681212883</v>
       </c>
-      <c r="F17" s="85" t="n">
+      <c r="F17" s="91" t="n">
         <f aca="false">Portfolio!F16</f>
         <v>437963.399492993</v>
       </c>
-      <c r="G17" s="85" t="n">
+      <c r="G17" s="91" t="n">
         <f aca="false">Portfolio!G16</f>
         <v>1468596.81212883</v>
       </c>
-      <c r="H17" s="85" t="n">
+      <c r="H17" s="91" t="n">
         <f aca="false">Portfolio!I16</f>
         <v>7972801.02656446</v>
       </c>
@@ -8598,31 +8661,31 @@
         <f aca="false">Portfolio!A17</f>
         <v>70</v>
       </c>
-      <c r="B18" s="85" t="n">
+      <c r="B18" s="91" t="n">
         <f aca="false">Portfolio!B17</f>
         <v>2141936.6790375</v>
       </c>
-      <c r="C18" s="85" t="n">
+      <c r="C18" s="91" t="n">
         <f aca="false">Portfolio!C17</f>
         <v>2379126.8356487</v>
       </c>
-      <c r="D18" s="85" t="n">
+      <c r="D18" s="91" t="n">
         <f aca="false">Portfolio!D17</f>
         <v>31721.6911419827</v>
       </c>
-      <c r="E18" s="85" t="n">
+      <c r="E18" s="91" t="n">
         <f aca="false">Portfolio!E17</f>
         <v>158608.455709914</v>
       </c>
-      <c r="F18" s="85" t="n">
+      <c r="F18" s="91" t="n">
         <f aca="false">Portfolio!F17</f>
         <v>470167.126383683</v>
       </c>
-      <c r="G18" s="85" t="n">
+      <c r="G18" s="91" t="n">
         <f aca="false">Portfolio!G17</f>
         <v>1586084.55709914</v>
       </c>
-      <c r="H18" s="85" t="n">
+      <c r="H18" s="91" t="n">
         <f aca="false">Portfolio!I17</f>
         <v>8249201.28231558</v>
       </c>
@@ -8632,31 +8695,31 @@
         <f aca="false">Portfolio!A18</f>
         <v>71</v>
       </c>
-      <c r="B19" s="85" t="n">
+      <c r="B19" s="91" t="n">
         <f aca="false">Portfolio!B18</f>
         <v>2015606.99601344</v>
       </c>
-      <c r="C19" s="85" t="n">
+      <c r="C19" s="91" t="n">
         <f aca="false">Portfolio!C18</f>
         <v>2569456.9825006</v>
       </c>
-      <c r="D19" s="85" t="n">
+      <c r="D19" s="91" t="n">
         <f aca="false">Portfolio!D18</f>
         <v>34259.4264333413</v>
       </c>
-      <c r="E19" s="85" t="n">
+      <c r="E19" s="91" t="n">
         <f aca="false">Portfolio!E18</f>
         <v>171297.132166707</v>
       </c>
-      <c r="F19" s="85" t="n">
+      <c r="F19" s="91" t="n">
         <f aca="false">Portfolio!F18</f>
         <v>504805.48417219</v>
       </c>
-      <c r="G19" s="85" t="n">
+      <c r="G19" s="91" t="n">
         <f aca="false">Portfolio!G18</f>
         <v>1712971.32166707</v>
       </c>
-      <c r="H19" s="85" t="n">
+      <c r="H19" s="91" t="n">
         <f aca="false">Portfolio!I18</f>
         <v>8556623.29742627</v>
       </c>
@@ -8666,31 +8729,31 @@
         <f aca="false">Portfolio!A19</f>
         <v>72</v>
       </c>
-      <c r="B20" s="85" t="n">
+      <c r="B20" s="91" t="n">
         <f aca="false">Portfolio!B19</f>
         <v>1890395.32091377</v>
       </c>
-      <c r="C20" s="85" t="n">
+      <c r="C20" s="91" t="n">
         <f aca="false">Portfolio!C19</f>
         <v>2775013.54110065</v>
       </c>
-      <c r="D20" s="85" t="n">
+      <c r="D20" s="91" t="n">
         <f aca="false">Portfolio!D19</f>
         <v>37000.1805480087</v>
       </c>
-      <c r="E20" s="85" t="n">
+      <c r="E20" s="91" t="n">
         <f aca="false">Portfolio!E19</f>
         <v>185000.902740043</v>
       </c>
-      <c r="F20" s="85" t="n">
+      <c r="F20" s="91" t="n">
         <f aca="false">Portfolio!F19</f>
         <v>542066.159967668</v>
       </c>
-      <c r="G20" s="85" t="n">
+      <c r="G20" s="91" t="n">
         <f aca="false">Portfolio!G19</f>
         <v>1850009.02740043</v>
       </c>
-      <c r="H20" s="85" t="n">
+      <c r="H20" s="91" t="n">
         <f aca="false">Portfolio!I19</f>
         <v>8897381.25509478</v>
       </c>
@@ -8700,31 +8763,31 @@
         <f aca="false">Portfolio!A20</f>
         <v>73</v>
       </c>
-      <c r="B21" s="85" t="n">
+      <c r="B21" s="91" t="n">
         <f aca="false">Portfolio!B20</f>
         <v>1766329.60393662</v>
       </c>
-      <c r="C21" s="85" t="n">
+      <c r="C21" s="91" t="n">
         <f aca="false">Portfolio!C20</f>
         <v>2997014.6243887</v>
       </c>
-      <c r="D21" s="85" t="n">
+      <c r="D21" s="91" t="n">
         <f aca="false">Portfolio!D20</f>
         <v>39960.1949918494</v>
       </c>
-      <c r="E21" s="85" t="n">
+      <c r="E21" s="91" t="n">
         <f aca="false">Portfolio!E20</f>
         <v>199800.974959247</v>
       </c>
-      <c r="F21" s="85" t="n">
+      <c r="F21" s="91" t="n">
         <f aca="false">Portfolio!F20</f>
         <v>582151.50167987</v>
       </c>
-      <c r="G21" s="85" t="n">
+      <c r="G21" s="91" t="n">
         <f aca="false">Portfolio!G20</f>
         <v>1998009.74959247</v>
       </c>
-      <c r="H21" s="85" t="n">
+      <c r="H21" s="91" t="n">
         <f aca="false">Portfolio!I20</f>
         <v>9273968.09748204</v>
       </c>
@@ -8734,31 +8797,31 @@
         <f aca="false">Portfolio!A21</f>
         <v>74</v>
       </c>
-      <c r="B22" s="85" t="n">
+      <c r="B22" s="91" t="n">
         <f aca="false">Portfolio!B21</f>
         <v>1643438.49403503</v>
       </c>
-      <c r="C22" s="85" t="n">
+      <c r="C22" s="91" t="n">
         <f aca="false">Portfolio!C21</f>
         <v>3236775.7943398</v>
       </c>
-      <c r="D22" s="85" t="n">
+      <c r="D22" s="91" t="n">
         <f aca="false">Portfolio!D21</f>
         <v>43157.0105911973</v>
       </c>
-      <c r="E22" s="85" t="n">
+      <c r="E22" s="91" t="n">
         <f aca="false">Portfolio!E21</f>
         <v>215785.052955986</v>
       </c>
-      <c r="F22" s="85" t="n">
+      <c r="F22" s="91" t="n">
         <f aca="false">Portfolio!F21</f>
         <v>625279.673174787</v>
       </c>
-      <c r="G22" s="85" t="n">
+      <c r="G22" s="91" t="n">
         <f aca="false">Portfolio!G21</f>
         <v>2157850.52955986</v>
       </c>
-      <c r="H22" s="85" t="n">
+      <c r="H22" s="91" t="n">
         <f aca="false">Portfolio!I21</f>
         <v>9689069.56774696</v>
       </c>
@@ -8768,31 +8831,31 @@
         <f aca="false">Portfolio!A22</f>
         <v>75</v>
       </c>
-      <c r="B23" s="85" t="n">
+      <c r="B23" s="91" t="n">
         <f aca="false">Portfolio!B22</f>
         <v>1521751.35638591</v>
       </c>
-      <c r="C23" s="85" t="n">
+      <c r="C23" s="91" t="n">
         <f aca="false">Portfolio!C22</f>
         <v>3495717.85788698</v>
       </c>
-      <c r="D23" s="85" t="n">
+      <c r="D23" s="91" t="n">
         <f aca="false">Portfolio!D22</f>
         <v>46609.5714384931</v>
       </c>
-      <c r="E23" s="85" t="n">
+      <c r="E23" s="91" t="n">
         <f aca="false">Portfolio!E22</f>
         <v>233047.857192465</v>
       </c>
-      <c r="F23" s="85" t="n">
+      <c r="F23" s="91" t="n">
         <f aca="false">Portfolio!F22</f>
         <v>671685.900957324</v>
       </c>
-      <c r="G23" s="85" t="n">
+      <c r="G23" s="91" t="n">
         <f aca="false">Portfolio!G22</f>
         <v>2330478.57192465</v>
       </c>
-      <c r="H23" s="85" t="n">
+      <c r="H23" s="91" t="n">
         <f aca="false">Portfolio!I22</f>
         <v>10145579.3644652</v>
       </c>
@@ -8802,31 +8865,31 @@
         <f aca="false">Portfolio!A23</f>
         <v>76</v>
       </c>
-      <c r="B24" s="85" t="n">
+      <c r="B24" s="91" t="n">
         <f aca="false">Portfolio!B23</f>
         <v>1401298.29029556</v>
       </c>
-      <c r="C24" s="85" t="n">
+      <c r="C24" s="91" t="n">
         <f aca="false">Portfolio!C23</f>
         <v>3775375.28651794</v>
       </c>
-      <c r="D24" s="85" t="n">
+      <c r="D24" s="91" t="n">
         <f aca="false">Portfolio!D23</f>
         <v>50338.3371535725</v>
       </c>
-      <c r="E24" s="85" t="n">
+      <c r="E24" s="91" t="n">
         <f aca="false">Portfolio!E23</f>
         <v>251691.685767863</v>
       </c>
-      <c r="F24" s="85" t="n">
+      <c r="F24" s="91" t="n">
         <f aca="false">Portfolio!F23</f>
         <v>721623.819658892</v>
       </c>
-      <c r="G24" s="85" t="n">
+      <c r="G24" s="91" t="n">
         <f aca="false">Portfolio!G23</f>
         <v>2516916.85767863</v>
       </c>
-      <c r="H24" s="85" t="n">
+      <c r="H24" s="91" t="n">
         <f aca="false">Portfolio!I23</f>
         <v>10646615.4969424</v>
       </c>
@@ -8836,31 +8899,31 @@
         <f aca="false">Portfolio!A24</f>
         <v>77</v>
       </c>
-      <c r="B25" s="85" t="n">
+      <c r="B25" s="91" t="n">
         <f aca="false">Portfolio!B24</f>
         <v>1282110.14755295</v>
       </c>
-      <c r="C25" s="85" t="n">
+      <c r="C25" s="91" t="n">
         <f aca="false">Portfolio!C24</f>
         <v>4077405.30943937</v>
       </c>
-      <c r="D25" s="85" t="n">
+      <c r="D25" s="91" t="n">
         <f aca="false">Portfolio!D24</f>
         <v>54365.4041258583</v>
       </c>
-      <c r="E25" s="85" t="n">
+      <c r="E25" s="91" t="n">
         <f aca="false">Portfolio!E24</f>
         <v>271827.020629292</v>
       </c>
-      <c r="F25" s="85" t="n">
+      <c r="F25" s="91" t="n">
         <f aca="false">Portfolio!F24</f>
         <v>775366.924187834</v>
       </c>
-      <c r="G25" s="85" t="n">
+      <c r="G25" s="91" t="n">
         <f aca="false">Portfolio!G24</f>
         <v>2718270.20629292</v>
       </c>
-      <c r="H25" s="85" t="n">
+      <c r="H25" s="91" t="n">
         <f aca="false">Portfolio!I24</f>
         <v>11195537.9369923</v>
       </c>
@@ -8870,31 +8933,31 @@
         <f aca="false">Portfolio!A25</f>
         <v>78</v>
       </c>
-      <c r="B26" s="85" t="n">
+      <c r="B26" s="91" t="n">
         <f aca="false">Portfolio!B25</f>
         <v>1164218.55124177</v>
       </c>
-      <c r="C26" s="85" t="n">
+      <c r="C26" s="91" t="n">
         <f aca="false">Portfolio!C25</f>
         <v>4403597.73419453</v>
       </c>
-      <c r="D26" s="85" t="n">
+      <c r="D26" s="91" t="n">
         <f aca="false">Portfolio!D25</f>
         <v>58714.636455927</v>
       </c>
-      <c r="E26" s="85" t="n">
+      <c r="E26" s="91" t="n">
         <f aca="false">Portfolio!E25</f>
         <v>293573.182279635</v>
       </c>
-      <c r="F26" s="85" t="n">
+      <c r="F26" s="91" t="n">
         <f aca="false">Portfolio!F25</f>
         <v>833210.137026903</v>
       </c>
-      <c r="G26" s="85" t="n">
+      <c r="G26" s="91" t="n">
         <f aca="false">Portfolio!G25</f>
         <v>2935731.82279635</v>
       </c>
-      <c r="H26" s="85" t="n">
+      <c r="H26" s="91" t="n">
         <f aca="false">Portfolio!I25</f>
         <v>11795967.6703736</v>
       </c>
@@ -8904,31 +8967,31 @@
         <f aca="false">Portfolio!A26</f>
         <v>79</v>
       </c>
-      <c r="B27" s="85" t="n">
+      <c r="B27" s="91" t="n">
         <f aca="false">Portfolio!B26</f>
         <v>1047655.91502281</v>
       </c>
-      <c r="C27" s="85" t="n">
+      <c r="C27" s="91" t="n">
         <f aca="false">Portfolio!C26</f>
         <v>4755885.55293009</v>
       </c>
-      <c r="D27" s="85" t="n">
+      <c r="D27" s="91" t="n">
         <f aca="false">Portfolio!D26</f>
         <v>63411.8073724012</v>
       </c>
-      <c r="E27" s="85" t="n">
+      <c r="E27" s="91" t="n">
         <f aca="false">Portfolio!E26</f>
         <v>317059.036862006</v>
       </c>
-      <c r="F27" s="85" t="n">
+      <c r="F27" s="91" t="n">
         <f aca="false">Portfolio!F26</f>
         <v>895471.4998383</v>
       </c>
-      <c r="G27" s="85" t="n">
+      <c r="G27" s="91" t="n">
         <f aca="false">Portfolio!G26</f>
         <v>3170590.36862006</v>
       </c>
-      <c r="H27" s="85" t="n">
+      <c r="H27" s="91" t="n">
         <f aca="false">Portfolio!I26</f>
         <v>12451807.2593111</v>
       </c>
@@ -8938,31 +9001,31 @@
         <f aca="false">Portfolio!A27</f>
         <v>80</v>
       </c>
-      <c r="B28" s="85" t="n">
+      <c r="B28" s="91" t="n">
         <f aca="false">Portfolio!B27</f>
         <v>932455.462898383</v>
       </c>
-      <c r="C28" s="85" t="n">
+      <c r="C28" s="91" t="n">
         <f aca="false">Portfolio!C27</f>
         <v>5136356.39716449</v>
       </c>
-      <c r="D28" s="85" t="n">
+      <c r="D28" s="91" t="n">
         <f aca="false">Portfolio!D27</f>
         <v>68484.7519621933</v>
       </c>
-      <c r="E28" s="85" t="n">
+      <c r="E28" s="91" t="n">
         <f aca="false">Portfolio!E27</f>
         <v>342423.759810966</v>
       </c>
-      <c r="F28" s="85" t="n">
+      <c r="F28" s="91" t="n">
         <f aca="false">Portfolio!F27</f>
         <v>962493.999267071</v>
       </c>
-      <c r="G28" s="85" t="n">
+      <c r="G28" s="91" t="n">
         <f aca="false">Portfolio!G27</f>
         <v>3424237.59810966</v>
       </c>
-      <c r="H28" s="85" t="n">
+      <c r="H28" s="91" t="n">
         <f aca="false">Portfolio!I27</f>
         <v>13167263.0364182</v>
       </c>
@@ -8972,31 +9035,31 @@
         <f aca="false">Portfolio!A28</f>
         <v>81</v>
       </c>
-      <c r="B29" s="85" t="n">
+      <c r="B29" s="91" t="n">
         <f aca="false">Portfolio!B28</f>
         <v>818651.249470843</v>
       </c>
-      <c r="C29" s="85" t="n">
+      <c r="C29" s="91" t="n">
         <f aca="false">Portfolio!C28</f>
         <v>5547264.90893765</v>
       </c>
-      <c r="D29" s="85" t="n">
+      <c r="D29" s="91" t="n">
         <f aca="false">Portfolio!D28</f>
         <v>73963.5321191687</v>
       </c>
-      <c r="E29" s="85" t="n">
+      <c r="E29" s="91" t="n">
         <f aca="false">Portfolio!E28</f>
         <v>369817.660595844</v>
       </c>
-      <c r="F29" s="85" t="n">
+      <c r="F29" s="91" t="n">
         <f aca="false">Portfolio!F28</f>
         <v>1034647.53762223</v>
       </c>
-      <c r="G29" s="85" t="n">
+      <c r="G29" s="91" t="n">
         <f aca="false">Portfolio!G28</f>
         <v>3698176.60595844</v>
       </c>
-      <c r="H29" s="85" t="n">
+      <c r="H29" s="91" t="n">
         <f aca="false">Portfolio!I28</f>
         <v>13946869.0599338</v>
       </c>
@@ -9006,31 +9069,31 @@
         <f aca="false">Portfolio!A29</f>
         <v>82</v>
       </c>
-      <c r="B30" s="85" t="n">
+      <c r="B30" s="91" t="n">
         <f aca="false">Portfolio!B29</f>
         <v>706278.180707614</v>
       </c>
-      <c r="C30" s="85" t="n">
+      <c r="C30" s="91" t="n">
         <f aca="false">Portfolio!C29</f>
         <v>5991046.10165267</v>
       </c>
-      <c r="D30" s="85" t="n">
+      <c r="D30" s="91" t="n">
         <f aca="false">Portfolio!D29</f>
         <v>79880.6146887023</v>
       </c>
-      <c r="E30" s="85" t="n">
+      <c r="E30" s="91" t="n">
         <f aca="false">Portfolio!E29</f>
         <v>399403.073443511</v>
       </c>
-      <c r="F30" s="85" t="n">
+      <c r="F30" s="91" t="n">
         <f aca="false">Portfolio!F29</f>
         <v>1112331.05996649</v>
       </c>
-      <c r="G30" s="85" t="n">
+      <c r="G30" s="91" t="n">
         <f aca="false">Portfolio!G29</f>
         <v>3994030.73443511</v>
       </c>
-      <c r="H30" s="85" t="n">
+      <c r="H30" s="91" t="n">
         <f aca="false">Portfolio!I29</f>
         <v>14795512.9705591</v>
       </c>
@@ -9040,31 +9103,31 @@
         <f aca="false">Portfolio!A30</f>
         <v>83</v>
       </c>
-      <c r="B31" s="85" t="n">
+      <c r="B31" s="91" t="n">
         <f aca="false">Portfolio!B30</f>
         <v>595372.035225304</v>
       </c>
-      <c r="C31" s="85" t="n">
+      <c r="C31" s="91" t="n">
         <f aca="false">Portfolio!C30</f>
         <v>6470329.78978488</v>
       </c>
-      <c r="D31" s="85" t="n">
+      <c r="D31" s="91" t="n">
         <f aca="false">Portfolio!D30</f>
         <v>86271.0638637984</v>
       </c>
-      <c r="E31" s="85" t="n">
+      <c r="E31" s="91" t="n">
         <f aca="false">Portfolio!E30</f>
         <v>431355.319318992</v>
       </c>
-      <c r="F31" s="85" t="n">
+      <c r="F31" s="91" t="n">
         <f aca="false">Portfolio!F30</f>
         <v>1195974.85006501</v>
       </c>
-      <c r="G31" s="85" t="n">
+      <c r="G31" s="91" t="n">
         <f aca="false">Portfolio!G30</f>
         <v>4313553.19318992</v>
       </c>
-      <c r="H31" s="85" t="n">
+      <c r="H31" s="91" t="n">
         <f aca="false">Portfolio!I30</f>
         <v>15718463.9013678</v>
       </c>
@@ -9074,31 +9137,31 @@
         <f aca="false">Portfolio!A31</f>
         <v>84</v>
       </c>
-      <c r="B32" s="85" t="n">
+      <c r="B32" s="91" t="n">
         <f aca="false">Portfolio!B31</f>
         <v>485969.486105936</v>
       </c>
-      <c r="C32" s="85" t="n">
+      <c r="C32" s="91" t="n">
         <f aca="false">Portfolio!C31</f>
         <v>6987956.17296767</v>
       </c>
-      <c r="D32" s="85" t="n">
+      <c r="D32" s="91" t="n">
         <f aca="false">Portfolio!D31</f>
         <v>93172.7489729023</v>
       </c>
-      <c r="E32" s="85" t="n">
+      <c r="E32" s="91" t="n">
         <f aca="false">Portfolio!E31</f>
         <v>465863.744864511</v>
       </c>
-      <c r="F32" s="85" t="n">
+      <c r="F32" s="91" t="n">
         <f aca="false">Portfolio!F31</f>
         <v>1286043.00863648</v>
       </c>
-      <c r="G32" s="85" t="n">
+      <c r="G32" s="91" t="n">
         <f aca="false">Portfolio!G31</f>
         <v>4658637.44864512</v>
       </c>
-      <c r="H32" s="85" t="n">
+      <c r="H32" s="91" t="n">
         <f aca="false">Portfolio!I31</f>
         <v>16721402.604359</v>
       </c>
@@ -9108,67 +9171,67 @@
         <f aca="false">Portfolio!A32</f>
         <v>85</v>
       </c>
-      <c r="B33" s="85" t="n">
+      <c r="B33" s="91" t="n">
         <f aca="false">Portfolio!B32</f>
         <v>378108.123258585</v>
       </c>
-      <c r="C33" s="85" t="n">
+      <c r="C33" s="91" t="n">
         <f aca="false">Portfolio!C32</f>
         <v>7546992.66680509</v>
       </c>
-      <c r="D33" s="85" t="n">
+      <c r="D33" s="91" t="n">
         <f aca="false">Portfolio!D32</f>
         <v>100626.568890735</v>
       </c>
-      <c r="E33" s="85" t="n">
+      <c r="E33" s="91" t="n">
         <f aca="false">Portfolio!E32</f>
         <v>503132.844453672</v>
       </c>
-      <c r="F33" s="85" t="n">
+      <c r="F33" s="91" t="n">
         <f aca="false">Portfolio!F32</f>
         <v>1383036.12842198</v>
       </c>
-      <c r="G33" s="85" t="n">
+      <c r="G33" s="91" t="n">
         <f aca="false">Portfolio!G32</f>
         <v>5031328.44453672</v>
       </c>
-      <c r="H33" s="85" t="n">
+      <c r="H33" s="91" t="n">
         <f aca="false">Portfolio!I32</f>
         <v>17810453.9702706</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="84" t="s">
+      <c r="A35" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="84" t="s">
+      <c r="B35" s="90" t="s">
         <v>199</v>
       </c>
-      <c r="C35" s="84" t="s">
+      <c r="C35" s="90" t="s">
         <v>200</v>
       </c>
-      <c r="D35" s="84" t="s">
+      <c r="D35" s="90" t="s">
         <v>201</v>
       </c>
-      <c r="E35" s="84" t="s">
+      <c r="E35" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F35" s="84" t="s">
+      <c r="F35" s="90" t="s">
         <v>203</v>
       </c>
-      <c r="G35" s="84" t="s">
+      <c r="G35" s="90" t="s">
         <v>204</v>
       </c>
-      <c r="H35" s="84" t="s">
+      <c r="H35" s="90" t="s">
         <v>205</v>
       </c>
-      <c r="I35" s="84" t="s">
+      <c r="I35" s="90" t="s">
         <v>206</v>
       </c>
-      <c r="J35" s="84" t="s">
+      <c r="J35" s="90" t="s">
         <v>207</v>
       </c>
-      <c r="K35" s="84" t="s">
+      <c r="K35" s="90" t="s">
         <v>208</v>
       </c>
     </row>
@@ -9177,43 +9240,43 @@
         <f aca="false">'Withdrawal Plan'!A3</f>
         <v>65</v>
       </c>
-      <c r="B36" s="85" t="n">
+      <c r="B36" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H3</f>
         <v>0</v>
       </c>
-      <c r="C36" s="85" t="n">
+      <c r="C36" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I3</f>
         <v>0</v>
       </c>
-      <c r="D36" s="85" t="n">
+      <c r="D36" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J3</f>
         <v>171050</v>
       </c>
-      <c r="E36" s="85" t="n">
+      <c r="E36" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K3</f>
         <v>0</v>
       </c>
-      <c r="F36" s="85" t="n">
+      <c r="F36" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L3</f>
         <v>0</v>
       </c>
-      <c r="G36" s="85" t="n">
+      <c r="G36" s="91" t="n">
         <f aca="false">B36+C36+D36+E36+F36</f>
         <v>171050</v>
       </c>
-      <c r="H36" s="85" t="n">
+      <c r="H36" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G3</f>
         <v>148320</v>
       </c>
-      <c r="I36" s="85" t="n">
+      <c r="I36" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N3</f>
         <v>27737</v>
       </c>
-      <c r="J36" s="85" t="n">
+      <c r="J36" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O3</f>
         <v>10895.885</v>
       </c>
-      <c r="K36" s="85" t="n">
+      <c r="K36" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P3</f>
         <v>-15902.885</v>
       </c>
@@ -9223,43 +9286,43 @@
         <f aca="false">'Withdrawal Plan'!A4</f>
         <v>66</v>
       </c>
-      <c r="B37" s="85" t="n">
+      <c r="B37" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H4</f>
         <v>0</v>
       </c>
-      <c r="C37" s="85" t="n">
+      <c r="C37" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I4</f>
         <v>0</v>
       </c>
-      <c r="D37" s="85" t="n">
+      <c r="D37" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J4</f>
         <v>171050</v>
       </c>
-      <c r="E37" s="85" t="n">
+      <c r="E37" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K4</f>
         <v>0</v>
       </c>
-      <c r="F37" s="85" t="n">
+      <c r="F37" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L4</f>
         <v>0</v>
       </c>
-      <c r="G37" s="85" t="n">
+      <c r="G37" s="91" t="n">
         <f aca="false">B37+C37+D37+E37+F37</f>
         <v>171050</v>
       </c>
-      <c r="H37" s="85" t="n">
+      <c r="H37" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G4</f>
         <v>150951</v>
       </c>
-      <c r="I37" s="85" t="n">
+      <c r="I37" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N4</f>
         <v>27737</v>
       </c>
-      <c r="J37" s="85" t="n">
+      <c r="J37" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O4</f>
         <v>10895.885</v>
       </c>
-      <c r="K37" s="85" t="n">
+      <c r="K37" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P4</f>
         <v>-18533.885</v>
       </c>
@@ -9269,43 +9332,43 @@
         <f aca="false">'Withdrawal Plan'!A5</f>
         <v>67</v>
       </c>
-      <c r="B38" s="85" t="n">
+      <c r="B38" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H5</f>
         <v>47664</v>
       </c>
-      <c r="C38" s="85" t="n">
+      <c r="C38" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I5</f>
         <v>0</v>
       </c>
-      <c r="D38" s="85" t="n">
+      <c r="D38" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J5</f>
         <v>130535.6</v>
       </c>
-      <c r="E38" s="85" t="n">
+      <c r="E38" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K5</f>
         <v>0</v>
       </c>
-      <c r="F38" s="85" t="n">
+      <c r="F38" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L5</f>
         <v>0</v>
       </c>
-      <c r="G38" s="85" t="n">
+      <c r="G38" s="91" t="n">
         <f aca="false">B38+C38+D38+E38+F38</f>
         <v>178199.6</v>
       </c>
-      <c r="H38" s="85" t="n">
+      <c r="H38" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G5</f>
         <v>153663.15</v>
       </c>
-      <c r="I38" s="85" t="n">
+      <c r="I38" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N5</f>
         <v>27737</v>
       </c>
-      <c r="J38" s="85" t="n">
+      <c r="J38" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O5</f>
         <v>8315.11772</v>
       </c>
-      <c r="K38" s="85" t="n">
+      <c r="K38" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P5</f>
         <v>-11515.66772</v>
       </c>
@@ -9315,43 +9378,43 @@
         <f aca="false">'Withdrawal Plan'!A6</f>
         <v>68</v>
       </c>
-      <c r="B39" s="85" t="n">
+      <c r="B39" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H6</f>
         <v>48855.6</v>
       </c>
-      <c r="C39" s="85" t="n">
+      <c r="C39" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I6</f>
         <v>0</v>
       </c>
-      <c r="D39" s="85" t="n">
+      <c r="D39" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J6</f>
         <v>129522.74</v>
       </c>
-      <c r="E39" s="85" t="n">
+      <c r="E39" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K6</f>
         <v>0</v>
       </c>
-      <c r="F39" s="85" t="n">
+      <c r="F39" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L6</f>
         <v>0</v>
       </c>
-      <c r="G39" s="85" t="n">
+      <c r="G39" s="91" t="n">
         <f aca="false">B39+C39+D39+E39+F39</f>
         <v>178378.34</v>
       </c>
-      <c r="H39" s="85" t="n">
+      <c r="H39" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G6</f>
         <v>156458.9955</v>
       </c>
-      <c r="I39" s="85" t="n">
+      <c r="I39" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N6</f>
         <v>27737</v>
       </c>
-      <c r="J39" s="85" t="n">
+      <c r="J39" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O6</f>
         <v>8250.598538</v>
       </c>
-      <c r="K39" s="85" t="n">
+      <c r="K39" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P6</f>
         <v>-14068.254038</v>
       </c>
@@ -9361,43 +9424,43 @@
         <f aca="false">'Withdrawal Plan'!A7</f>
         <v>69</v>
       </c>
-      <c r="B40" s="85" t="n">
+      <c r="B40" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H7</f>
         <v>50076.99</v>
       </c>
-      <c r="C40" s="85" t="n">
+      <c r="C40" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I7</f>
         <v>0</v>
       </c>
-      <c r="D40" s="85" t="n">
+      <c r="D40" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J7</f>
         <v>128484.5585</v>
       </c>
-      <c r="E40" s="85" t="n">
+      <c r="E40" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K7</f>
         <v>0</v>
       </c>
-      <c r="F40" s="85" t="n">
+      <c r="F40" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L7</f>
         <v>0</v>
       </c>
-      <c r="G40" s="85" t="n">
+      <c r="G40" s="91" t="n">
         <f aca="false">B40+C40+D40+E40+F40</f>
         <v>178561.5485</v>
       </c>
-      <c r="H40" s="85" t="n">
+      <c r="H40" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G7</f>
         <v>159341.163915</v>
       </c>
-      <c r="I40" s="85" t="n">
+      <c r="I40" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N7</f>
         <v>27737</v>
       </c>
-      <c r="J40" s="85" t="n">
+      <c r="J40" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O7</f>
         <v>8184.46637645</v>
       </c>
-      <c r="K40" s="85" t="n">
+      <c r="K40" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P7</f>
         <v>-16701.08179145</v>
       </c>
@@ -9407,43 +9470,43 @@
         <f aca="false">'Withdrawal Plan'!A8</f>
         <v>70</v>
       </c>
-      <c r="B41" s="85" t="n">
+      <c r="B41" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H8</f>
         <v>51328.91475</v>
       </c>
-      <c r="C41" s="85" t="n">
+      <c r="C41" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I8</f>
         <v>23832</v>
       </c>
-      <c r="D41" s="85" t="n">
+      <c r="D41" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J8</f>
         <v>127420.4224625</v>
       </c>
-      <c r="E41" s="85" t="n">
+      <c r="E41" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K8</f>
         <v>0</v>
       </c>
-      <c r="F41" s="85" t="n">
+      <c r="F41" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L8</f>
         <v>0</v>
       </c>
-      <c r="G41" s="85" t="n">
+      <c r="G41" s="91" t="n">
         <f aca="false">B41+C41+D41+E41+F41</f>
         <v>202581.3372125</v>
       </c>
-      <c r="H41" s="85" t="n">
+      <c r="H41" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G8</f>
         <v>152712.36730995</v>
       </c>
-      <c r="I41" s="85" t="n">
+      <c r="I41" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N8</f>
         <v>27737</v>
       </c>
-      <c r="J41" s="85" t="n">
+      <c r="J41" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O8</f>
         <v>8116.68091086125</v>
       </c>
-      <c r="K41" s="85" t="n">
+      <c r="K41" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P8</f>
         <v>14015.2889916887</v>
       </c>
@@ -9453,43 +9516,43 @@
         <f aca="false">'Withdrawal Plan'!A9</f>
         <v>71</v>
       </c>
-      <c r="B42" s="85" t="n">
+      <c r="B42" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H9</f>
         <v>52612.13761875</v>
       </c>
-      <c r="C42" s="85" t="n">
+      <c r="C42" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I9</f>
         <v>24427.8</v>
       </c>
-      <c r="D42" s="85" t="n">
+      <c r="D42" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J9</f>
         <v>126329.683024063</v>
       </c>
-      <c r="E42" s="85" t="n">
+      <c r="E42" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K9</f>
         <v>0</v>
       </c>
-      <c r="F42" s="85" t="n">
+      <c r="F42" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L9</f>
         <v>0</v>
       </c>
-      <c r="G42" s="85" t="n">
+      <c r="G42" s="91" t="n">
         <f aca="false">B42+C42+D42+E42+F42</f>
         <v>203369.620642813</v>
       </c>
-      <c r="H42" s="85" t="n">
+      <c r="H42" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G9</f>
         <v>155775.405230624</v>
       </c>
-      <c r="I42" s="85" t="n">
+      <c r="I42" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N9</f>
         <v>27737</v>
       </c>
-      <c r="J42" s="85" t="n">
+      <c r="J42" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O9</f>
         <v>8047.20080863278</v>
       </c>
-      <c r="K42" s="85" t="n">
+      <c r="K42" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P9</f>
         <v>11810.0146035562</v>
       </c>
@@ -9499,43 +9562,43 @@
         <f aca="false">'Withdrawal Plan'!A10</f>
         <v>72</v>
       </c>
-      <c r="B43" s="85" t="n">
+      <c r="B43" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H10</f>
         <v>53927.4410592187</v>
       </c>
-      <c r="C43" s="85" t="n">
+      <c r="C43" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I10</f>
         <v>25038.495</v>
       </c>
-      <c r="D43" s="85" t="n">
+      <c r="D43" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J10</f>
         <v>125211.675099664</v>
       </c>
-      <c r="E43" s="85" t="n">
+      <c r="E43" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K10</f>
         <v>0</v>
       </c>
-      <c r="F43" s="85" t="n">
+      <c r="F43" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L10</f>
         <v>0</v>
       </c>
-      <c r="G43" s="85" t="n">
+      <c r="G43" s="91" t="n">
         <f aca="false">B43+C43+D43+E43+F43</f>
         <v>204177.611158883</v>
       </c>
-      <c r="H43" s="85" t="n">
+      <c r="H43" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G10</f>
         <v>158933.167633986</v>
       </c>
-      <c r="I43" s="85" t="n">
+      <c r="I43" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N10</f>
         <v>27737</v>
       </c>
-      <c r="J43" s="85" t="n">
+      <c r="J43" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O10</f>
         <v>7975.9837038486</v>
       </c>
-      <c r="K43" s="85" t="n">
+      <c r="K43" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P10</f>
         <v>9531.45982104821</v>
       </c>
@@ -9545,43 +9608,43 @@
         <f aca="false">'Withdrawal Plan'!A11</f>
         <v>73</v>
       </c>
-      <c r="B44" s="85" t="n">
+      <c r="B44" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H11</f>
         <v>55275.6270856992</v>
       </c>
-      <c r="C44" s="85" t="n">
+      <c r="C44" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I11</f>
         <v>25664.457375</v>
       </c>
-      <c r="D44" s="85" t="n">
+      <c r="D44" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J11</f>
         <v>124065.716977156</v>
       </c>
-      <c r="E44" s="85" t="n">
+      <c r="E44" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K11</f>
         <v>0</v>
       </c>
-      <c r="F44" s="85" t="n">
+      <c r="F44" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L11</f>
         <v>0</v>
       </c>
-      <c r="G44" s="85" t="n">
+      <c r="G44" s="91" t="n">
         <f aca="false">B44+C44+D44+E44+F44</f>
         <v>205005.801437855</v>
       </c>
-      <c r="H44" s="85" t="n">
+      <c r="H44" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G11</f>
         <v>162188.637921772</v>
       </c>
-      <c r="I44" s="85" t="n">
+      <c r="I44" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N11</f>
         <v>27737</v>
       </c>
-      <c r="J44" s="85" t="n">
+      <c r="J44" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O11</f>
         <v>7902.98617144482</v>
       </c>
-      <c r="K44" s="85" t="n">
+      <c r="K44" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P11</f>
         <v>7177.17734463854</v>
       </c>
@@ -9591,43 +9654,43 @@
         <f aca="false">'Withdrawal Plan'!A12</f>
         <v>74</v>
       </c>
-      <c r="B45" s="85" t="n">
+      <c r="B45" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H12</f>
         <v>56657.5177628417</v>
       </c>
-      <c r="C45" s="85" t="n">
+      <c r="C45" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I12</f>
         <v>26306.068809375</v>
       </c>
-      <c r="D45" s="85" t="n">
+      <c r="D45" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J12</f>
         <v>122891.109901585</v>
       </c>
-      <c r="E45" s="85" t="n">
+      <c r="E45" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K12</f>
         <v>0</v>
       </c>
-      <c r="F45" s="85" t="n">
+      <c r="F45" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L12</f>
         <v>0</v>
       </c>
-      <c r="G45" s="85" t="n">
+      <c r="G45" s="91" t="n">
         <f aca="false">B45+C45+D45+E45+F45</f>
         <v>205854.696473801</v>
       </c>
-      <c r="H45" s="85" t="n">
+      <c r="H45" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G12</f>
         <v>165544.896081129</v>
       </c>
-      <c r="I45" s="85" t="n">
+      <c r="I45" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N12</f>
         <v>27737</v>
       </c>
-      <c r="J45" s="85" t="n">
+      <c r="J45" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O12</f>
         <v>7828.16370073094</v>
       </c>
-      <c r="K45" s="85" t="n">
+      <c r="K45" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P12</f>
         <v>4744.63669194142</v>
       </c>
@@ -9637,43 +9700,43 @@
         <f aca="false">'Withdrawal Plan'!A13</f>
         <v>75</v>
       </c>
-      <c r="B46" s="85" t="n">
+      <c r="B46" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H13</f>
         <v>58073.9557069127</v>
       </c>
-      <c r="C46" s="85" t="n">
+      <c r="C46" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I13</f>
         <v>26963.7205296094</v>
       </c>
-      <c r="D46" s="85" t="n">
+      <c r="D46" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J13</f>
         <v>121687.137649124</v>
       </c>
-      <c r="E46" s="85" t="n">
+      <c r="E46" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K13</f>
         <v>0</v>
       </c>
-      <c r="F46" s="85" t="n">
+      <c r="F46" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L13</f>
         <v>0</v>
       </c>
-      <c r="G46" s="85" t="n">
+      <c r="G46" s="91" t="n">
         <f aca="false">B46+C46+D46+E46+F46</f>
         <v>206724.813885646</v>
       </c>
-      <c r="H46" s="85" t="n">
+      <c r="H46" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G13</f>
         <v>169005.121936352</v>
       </c>
-      <c r="I46" s="85" t="n">
+      <c r="I46" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N13</f>
         <v>27737</v>
       </c>
-      <c r="J46" s="85" t="n">
+      <c r="J46" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O13</f>
         <v>7751.47066824921</v>
       </c>
-      <c r="K46" s="85" t="n">
+      <c r="K46" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P13</f>
         <v>2231.22128104485</v>
       </c>
@@ -9683,43 +9746,43 @@
         <f aca="false">'Withdrawal Plan'!A14</f>
         <v>76</v>
       </c>
-      <c r="B47" s="85" t="n">
+      <c r="B47" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H14</f>
         <v>59525.8045995855</v>
       </c>
-      <c r="C47" s="85" t="n">
+      <c r="C47" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I14</f>
         <v>27637.8135428496</v>
       </c>
-      <c r="D47" s="85" t="n">
+      <c r="D47" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J14</f>
         <v>120453.066090352</v>
       </c>
-      <c r="E47" s="85" t="n">
+      <c r="E47" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K14</f>
         <v>0</v>
       </c>
-      <c r="F47" s="85" t="n">
+      <c r="F47" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L14</f>
         <v>0</v>
       </c>
-      <c r="G47" s="85" t="n">
+      <c r="G47" s="91" t="n">
         <f aca="false">B47+C47+D47+E47+F47</f>
         <v>207616.684232787</v>
       </c>
-      <c r="H47" s="85" t="n">
+      <c r="H47" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G14</f>
         <v>172572.598515872</v>
       </c>
-      <c r="I47" s="85" t="n">
+      <c r="I47" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N14</f>
         <v>27737</v>
       </c>
-      <c r="J47" s="85" t="n">
+      <c r="J47" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O14</f>
         <v>7672.86030995544</v>
       </c>
-      <c r="K47" s="85" t="n">
+      <c r="K47" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P14</f>
         <v>-365.774593039748</v>
       </c>
@@ -9729,43 +9792,43 @@
         <f aca="false">'Withdrawal Plan'!A15</f>
         <v>77</v>
       </c>
-      <c r="B48" s="85" t="n">
+      <c r="B48" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H15</f>
         <v>61013.9497145751</v>
       </c>
-      <c r="C48" s="85" t="n">
+      <c r="C48" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I15</f>
         <v>28328.7588814208</v>
       </c>
-      <c r="D48" s="85" t="n">
+      <c r="D48" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J15</f>
         <v>119188.142742611</v>
       </c>
-      <c r="E48" s="85" t="n">
+      <c r="E48" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K15</f>
         <v>0</v>
       </c>
-      <c r="F48" s="85" t="n">
+      <c r="F48" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L15</f>
         <v>0</v>
       </c>
-      <c r="G48" s="85" t="n">
+      <c r="G48" s="91" t="n">
         <f aca="false">B48+C48+D48+E48+F48</f>
         <v>208530.851338607</v>
       </c>
-      <c r="H48" s="85" t="n">
+      <c r="H48" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G15</f>
         <v>176250.715538848</v>
       </c>
-      <c r="I48" s="85" t="n">
+      <c r="I48" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N15</f>
         <v>27737</v>
       </c>
-      <c r="J48" s="85" t="n">
+      <c r="J48" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O15</f>
         <v>7592.28469270433</v>
       </c>
-      <c r="K48" s="85" t="n">
+      <c r="K48" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P15</f>
         <v>-3049.14889294547</v>
       </c>
@@ -9775,43 +9838,43 @@
         <f aca="false">'Withdrawal Plan'!A16</f>
         <v>78</v>
       </c>
-      <c r="B49" s="85" t="n">
+      <c r="B49" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H16</f>
         <v>62539.2984574395</v>
       </c>
-      <c r="C49" s="85" t="n">
+      <c r="C49" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I16</f>
         <v>29036.9778534564</v>
       </c>
-      <c r="D49" s="85" t="n">
+      <c r="D49" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J16</f>
         <v>117891.596311176</v>
       </c>
-      <c r="E49" s="85" t="n">
+      <c r="E49" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K16</f>
         <v>0</v>
       </c>
-      <c r="F49" s="85" t="n">
+      <c r="F49" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L16</f>
         <v>0</v>
       </c>
-      <c r="G49" s="85" t="n">
+      <c r="G49" s="91" t="n">
         <f aca="false">B49+C49+D49+E49+F49</f>
         <v>209467.872622072</v>
       </c>
-      <c r="H49" s="85" t="n">
+      <c r="H49" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G16</f>
         <v>144042.973025889</v>
       </c>
-      <c r="I49" s="85" t="n">
+      <c r="I49" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N16</f>
         <v>27737</v>
       </c>
-      <c r="J49" s="85" t="n">
+      <c r="J49" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O16</f>
         <v>7509.69468502194</v>
       </c>
-      <c r="K49" s="85" t="n">
+      <c r="K49" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P16</f>
         <v>30178.2049111613</v>
       </c>
@@ -9821,43 +9884,43 @@
         <f aca="false">'Withdrawal Plan'!A17</f>
         <v>79</v>
       </c>
-      <c r="B50" s="85" t="n">
+      <c r="B50" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H17</f>
         <v>64102.7809188755</v>
       </c>
-      <c r="C50" s="85" t="n">
+      <c r="C50" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I17</f>
         <v>29762.9022997928</v>
       </c>
-      <c r="D50" s="85" t="n">
+      <c r="D50" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J17</f>
         <v>116562.636218956</v>
       </c>
-      <c r="E50" s="85" t="n">
+      <c r="E50" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K17</f>
         <v>0</v>
       </c>
-      <c r="F50" s="85" t="n">
+      <c r="F50" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L17</f>
         <v>0</v>
       </c>
-      <c r="G50" s="85" t="n">
+      <c r="G50" s="91" t="n">
         <f aca="false">B50+C50+D50+E50+F50</f>
         <v>210428.319437624</v>
       </c>
-      <c r="H50" s="85" t="n">
+      <c r="H50" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G17</f>
         <v>147952.985038585</v>
       </c>
-      <c r="I50" s="85" t="n">
+      <c r="I50" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N17</f>
         <v>27737</v>
       </c>
-      <c r="J50" s="85" t="n">
+      <c r="J50" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O17</f>
         <v>7425.03992714749</v>
       </c>
-      <c r="K50" s="85" t="n">
+      <c r="K50" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P17</f>
         <v>27313.2944718917</v>
       </c>
@@ -9867,43 +9930,43 @@
         <f aca="false">'Withdrawal Plan'!A18</f>
         <v>80</v>
       </c>
-      <c r="B51" s="85" t="n">
+      <c r="B51" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H18</f>
         <v>65705.3504418474</v>
       </c>
-      <c r="C51" s="85" t="n">
+      <c r="C51" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I18</f>
         <v>30506.9748572876</v>
       </c>
-      <c r="D51" s="85" t="n">
+      <c r="D51" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J18</f>
         <v>115200.45212443</v>
       </c>
-      <c r="E51" s="85" t="n">
+      <c r="E51" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K18</f>
         <v>0</v>
       </c>
-      <c r="F51" s="85" t="n">
+      <c r="F51" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L18</f>
         <v>0</v>
       </c>
-      <c r="G51" s="85" t="n">
+      <c r="G51" s="91" t="n">
         <f aca="false">B51+C51+D51+E51+F51</f>
         <v>211412.777423565</v>
       </c>
-      <c r="H51" s="85" t="n">
+      <c r="H51" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G18</f>
         <v>151984.483552758</v>
       </c>
-      <c r="I51" s="85" t="n">
+      <c r="I51" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N18</f>
         <v>27737</v>
       </c>
-      <c r="J51" s="85" t="n">
+      <c r="J51" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O18</f>
         <v>7338.26880032618</v>
       </c>
-      <c r="K51" s="85" t="n">
+      <c r="K51" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P18</f>
         <v>24353.025070481</v>
       </c>
@@ -9913,43 +9976,43 @@
         <f aca="false">'Withdrawal Plan'!A19</f>
         <v>81</v>
       </c>
-      <c r="B52" s="85" t="n">
+      <c r="B52" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H19</f>
         <v>67347.9842028936</v>
       </c>
-      <c r="C52" s="85" t="n">
+      <c r="C52" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I19</f>
         <v>31269.6492287198</v>
       </c>
-      <c r="D52" s="85" t="n">
+      <c r="D52" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J19</f>
         <v>113804.21342754</v>
       </c>
-      <c r="E52" s="85" t="n">
+      <c r="E52" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K19</f>
         <v>0</v>
       </c>
-      <c r="F52" s="85" t="n">
+      <c r="F52" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L19</f>
         <v>0</v>
       </c>
-      <c r="G52" s="85" t="n">
+      <c r="G52" s="91" t="n">
         <f aca="false">B52+C52+D52+E52+F52</f>
         <v>212421.846859154</v>
       </c>
-      <c r="H52" s="85" t="n">
+      <c r="H52" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G19</f>
         <v>156141.322470506</v>
       </c>
-      <c r="I52" s="85" t="n">
+      <c r="I52" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N19</f>
         <v>27737</v>
       </c>
-      <c r="J52" s="85" t="n">
+      <c r="J52" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O19</f>
         <v>7249.32839533433</v>
       </c>
-      <c r="K52" s="85" t="n">
+      <c r="K52" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P19</f>
         <v>21294.1959933134</v>
       </c>
@@ -9959,43 +10022,43 @@
         <f aca="false">'Withdrawal Plan'!A20</f>
         <v>82</v>
       </c>
-      <c r="B53" s="85" t="n">
+      <c r="B53" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H20</f>
         <v>69031.6838079659</v>
       </c>
-      <c r="C53" s="85" t="n">
+      <c r="C53" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I20</f>
         <v>32051.3904594378</v>
       </c>
-      <c r="D53" s="85" t="n">
+      <c r="D53" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J20</f>
         <v>112373.068763229</v>
       </c>
-      <c r="E53" s="85" t="n">
+      <c r="E53" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K20</f>
         <v>0</v>
       </c>
-      <c r="F53" s="85" t="n">
+      <c r="F53" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L20</f>
         <v>0</v>
       </c>
-      <c r="G53" s="85" t="n">
+      <c r="G53" s="91" t="n">
         <f aca="false">B53+C53+D53+E53+F53</f>
         <v>213456.143030633</v>
       </c>
-      <c r="H53" s="85" t="n">
+      <c r="H53" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G20</f>
         <v>160427.481776345</v>
       </c>
-      <c r="I53" s="85" t="n">
+      <c r="I53" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N20</f>
         <v>27737</v>
       </c>
-      <c r="J53" s="85" t="n">
+      <c r="J53" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O20</f>
         <v>7158.16448021769</v>
       </c>
-      <c r="K53" s="85" t="n">
+      <c r="K53" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P20</f>
         <v>18133.4967740695</v>
       </c>
@@ -10005,43 +10068,43 @@
         <f aca="false">'Withdrawal Plan'!A21</f>
         <v>83</v>
       </c>
-      <c r="B54" s="85" t="n">
+      <c r="B54" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H21</f>
         <v>70757.475903165</v>
       </c>
-      <c r="C54" s="85" t="n">
+      <c r="C54" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I21</f>
         <v>32852.6752209237</v>
       </c>
-      <c r="D54" s="85" t="n">
+      <c r="D54" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J21</f>
         <v>110906.14548231</v>
       </c>
-      <c r="E54" s="85" t="n">
+      <c r="E54" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K21</f>
         <v>0</v>
       </c>
-      <c r="F54" s="85" t="n">
+      <c r="F54" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L21</f>
         <v>0</v>
       </c>
-      <c r="G54" s="85" t="n">
+      <c r="G54" s="91" t="n">
         <f aca="false">B54+C54+D54+E54+F54</f>
         <v>214516.296606398</v>
       </c>
-      <c r="H54" s="85" t="n">
+      <c r="H54" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G21</f>
         <v>164847.071842946</v>
       </c>
-      <c r="I54" s="85" t="n">
+      <c r="I54" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N21</f>
         <v>27737</v>
       </c>
-      <c r="J54" s="85" t="n">
+      <c r="J54" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O21</f>
         <v>7064.72146722313</v>
       </c>
-      <c r="K54" s="85" t="n">
+      <c r="K54" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P21</f>
         <v>14867.5032962291</v>
       </c>
@@ -10051,43 +10114,43 @@
         <f aca="false">'Withdrawal Plan'!A22</f>
         <v>84</v>
       </c>
-      <c r="B55" s="85" t="n">
+      <c r="B55" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H22</f>
         <v>72526.4128007442</v>
       </c>
-      <c r="C55" s="85" t="n">
+      <c r="C55" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I22</f>
         <v>33673.9921014468</v>
       </c>
-      <c r="D55" s="85" t="n">
+      <c r="D55" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J22</f>
         <v>109402.549119367</v>
       </c>
-      <c r="E55" s="85" t="n">
+      <c r="E55" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K22</f>
         <v>0</v>
       </c>
-      <c r="F55" s="85" t="n">
+      <c r="F55" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L22</f>
         <v>0</v>
       </c>
-      <c r="G55" s="85" t="n">
+      <c r="G55" s="91" t="n">
         <f aca="false">B55+C55+D55+E55+F55</f>
         <v>215602.954021558</v>
       </c>
-      <c r="H55" s="85" t="n">
+      <c r="H55" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G22</f>
         <v>169404.33789221</v>
       </c>
-      <c r="I55" s="85" t="n">
+      <c r="I55" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N22</f>
         <v>27737</v>
       </c>
-      <c r="J55" s="85" t="n">
+      <c r="J55" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O22</f>
         <v>6968.94237890371</v>
       </c>
-      <c r="K55" s="85" t="n">
+      <c r="K55" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P22</f>
         <v>11492.6737504442</v>
       </c>
@@ -10097,64 +10160,64 @@
         <f aca="false">'Withdrawal Plan'!A23</f>
         <v>85</v>
       </c>
-      <c r="B56" s="85" t="n">
+      <c r="B56" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!H23</f>
         <v>74339.5731207628</v>
       </c>
-      <c r="C56" s="85" t="n">
+      <c r="C56" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!I23</f>
         <v>34515.8419039829</v>
       </c>
-      <c r="D56" s="85" t="n">
+      <c r="D56" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!J23</f>
         <v>107861.362847352</v>
       </c>
-      <c r="E56" s="85" t="n">
+      <c r="E56" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!K23</f>
         <v>0</v>
       </c>
-      <c r="F56" s="85" t="n">
+      <c r="F56" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!L23</f>
         <v>0</v>
       </c>
-      <c r="G56" s="85" t="n">
+      <c r="G56" s="91" t="n">
         <f aca="false">B56+C56+D56+E56+F56</f>
         <v>216716.777872097</v>
       </c>
-      <c r="H56" s="85" t="n">
+      <c r="H56" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!G23</f>
         <v>174103.664617651</v>
       </c>
-      <c r="I56" s="85" t="n">
+      <c r="I56" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!N23</f>
         <v>27737</v>
       </c>
-      <c r="J56" s="85" t="n">
+      <c r="J56" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!O23</f>
         <v>6870.7688133763</v>
       </c>
-      <c r="K56" s="85" t="n">
+      <c r="K56" s="91" t="n">
         <f aca="false">'Withdrawal Plan'!P23</f>
         <v>8005.34444106957</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="84" t="s">
+      <c r="A58" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="84" t="s">
+      <c r="B58" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="C58" s="84" t="s">
+      <c r="C58" s="90" t="s">
         <v>126</v>
       </c>
-      <c r="D58" s="84" t="s">
+      <c r="D58" s="90" t="s">
         <v>127</v>
       </c>
-      <c r="E58" s="84" t="s">
+      <c r="E58" s="90" t="s">
         <v>209</v>
       </c>
-      <c r="F58" s="84" t="s">
+      <c r="F58" s="90" t="s">
         <v>210</v>
       </c>
     </row>
@@ -10163,15 +10226,15 @@
         <f aca="false">'Stress Test'!A4</f>
         <v>65</v>
       </c>
-      <c r="B59" s="85" t="n">
+      <c r="B59" s="91" t="n">
         <f aca="false">'Stress Test'!C4</f>
         <v>9132439.10407305</v>
       </c>
-      <c r="C59" s="85" t="n">
+      <c r="C59" s="91" t="n">
         <f aca="false">'Stress Test'!E4</f>
         <v>9490350.99269125</v>
       </c>
-      <c r="D59" s="85" t="n">
+      <c r="D59" s="91" t="n">
         <f aca="false">'Stress Test'!F4</f>
         <v>9669306.93700034</v>
       </c>
@@ -10188,15 +10251,15 @@
         <f aca="false">'Stress Test'!A5</f>
         <v>66</v>
       </c>
-      <c r="B60" s="85" t="n">
+      <c r="B60" s="91" t="n">
         <f aca="false">'Stress Test'!C5</f>
         <v>9324355.66823597</v>
       </c>
-      <c r="C60" s="85" t="n">
+      <c r="C60" s="91" t="n">
         <f aca="false">'Stress Test'!E5</f>
         <v>10076198.0721065</v>
       </c>
-      <c r="D60" s="85" t="n">
+      <c r="D60" s="91" t="n">
         <f aca="false">'Stress Test'!F5</f>
         <v>10462856.6307004</v>
       </c>
@@ -10213,15 +10276,15 @@
         <f aca="false">'Stress Test'!A6</f>
         <v>67</v>
       </c>
-      <c r="B61" s="85" t="n">
+      <c r="B61" s="91" t="n">
         <f aca="false">'Stress Test'!C6</f>
         <v>9564346.74496541</v>
       </c>
-      <c r="C61" s="85" t="n">
+      <c r="C61" s="91" t="n">
         <f aca="false">'Stress Test'!E6</f>
         <v>10749310.7678751</v>
       </c>
-      <c r="D61" s="85" t="n">
+      <c r="D61" s="91" t="n">
         <f aca="false">'Stress Test'!F6</f>
         <v>11376159.1437704</v>
       </c>
@@ -10238,15 +10301,15 @@
         <f aca="false">'Stress Test'!A7</f>
         <v>68</v>
       </c>
-      <c r="B62" s="85" t="n">
+      <c r="B62" s="91" t="n">
         <f aca="false">'Stress Test'!C7</f>
         <v>9814827.94726403</v>
       </c>
-      <c r="C62" s="85" t="n">
+      <c r="C62" s="91" t="n">
         <f aca="false">'Stress Test'!E7</f>
         <v>11477162.9618051</v>
       </c>
-      <c r="D62" s="85" t="n">
+      <c r="D62" s="91" t="n">
         <f aca="false">'Stress Test'!F7</f>
         <v>12381682.3906475</v>
       </c>
@@ -10263,15 +10326,15 @@
         <f aca="false">'Stress Test'!A8</f>
         <v>69</v>
       </c>
-      <c r="B63" s="85" t="n">
+      <c r="B63" s="91" t="n">
         <f aca="false">'Stress Test'!C8</f>
         <v>10076238.0827796</v>
       </c>
-      <c r="C63" s="85" t="n">
+      <c r="C63" s="91" t="n">
         <f aca="false">'Stress Test'!E8</f>
         <v>12264153.0163745</v>
       </c>
-      <c r="D63" s="85" t="n">
+      <c r="D63" s="91" t="n">
         <f aca="false">'Stress Test'!F8</f>
         <v>13488667.6473372</v>
       </c>
@@ -10288,15 +10351,15 @@
         <f aca="false">'Stress Test'!A9</f>
         <v>70</v>
       </c>
-      <c r="B64" s="85" t="n">
+      <c r="B64" s="91" t="n">
         <f aca="false">'Stress Test'!C9</f>
         <v>10349033.8385595</v>
       </c>
-      <c r="C64" s="85" t="n">
+      <c r="C64" s="91" t="n">
         <f aca="false">'Stress Test'!E9</f>
         <v>13115031.4901532</v>
       </c>
-      <c r="D64" s="85" t="n">
+      <c r="D64" s="91" t="n">
         <f aca="false">'Stress Test'!F9</f>
         <v>14707280.6445397</v>
       </c>
@@ -10313,15 +10376,15 @@
         <f aca="false">'Stress Test'!A10</f>
         <v>71</v>
       </c>
-      <c r="B65" s="85" t="n">
+      <c r="B65" s="91" t="n">
         <f aca="false">'Stress Test'!C10</f>
         <v>10633690.4967557</v>
       </c>
-      <c r="C65" s="85" t="n">
+      <c r="C65" s="91" t="n">
         <f aca="false">'Stress Test'!E10</f>
         <v>14034929.3140192</v>
       </c>
-      <c r="D65" s="85" t="n">
+      <c r="D65" s="91" t="n">
         <f aca="false">'Stress Test'!F10</f>
         <v>16048704.0136474</v>
       </c>
@@ -10338,15 +10401,15 @@
         <f aca="false">'Stress Test'!A11</f>
         <v>72</v>
       </c>
-      <c r="B66" s="85" t="n">
+      <c r="B66" s="91" t="n">
         <f aca="false">'Stress Test'!C11</f>
         <v>10930702.6785879</v>
       </c>
-      <c r="C66" s="85" t="n">
+      <c r="C66" s="91" t="n">
         <f aca="false">'Stress Test'!E11</f>
         <v>15029388.2211028</v>
       </c>
-      <c r="D66" s="85" t="n">
+      <c r="D66" s="91" t="n">
         <f aca="false">'Stress Test'!F11</f>
         <v>17525238.9769742</v>
       </c>
@@ -10363,15 +10426,15 @@
         <f aca="false">'Stress Test'!A12</f>
         <v>73</v>
       </c>
-      <c r="B67" s="85" t="n">
+      <c r="B67" s="91" t="n">
         <f aca="false">'Stress Test'!C12</f>
         <v>11240585.1176691</v>
       </c>
-      <c r="C67" s="85" t="n">
+      <c r="C67" s="91" t="n">
         <f aca="false">'Stress Test'!E12</f>
         <v>16104393.6107286</v>
       </c>
-      <c r="D67" s="85" t="n">
+      <c r="D67" s="91" t="n">
         <f aca="false">'Stress Test'!F12</f>
         <v>19150417.2066092</v>
       </c>
@@ -10388,15 +10451,15 @@
         <f aca="false">'Stress Test'!A13</f>
         <v>74</v>
       </c>
-      <c r="B68" s="85" t="n">
+      <c r="B68" s="91" t="n">
         <f aca="false">'Stress Test'!C13</f>
         <v>11563873.4638348</v>
       </c>
-      <c r="C68" s="85" t="n">
+      <c r="C68" s="91" t="n">
         <f aca="false">'Stress Test'!E13</f>
         <v>17266410.0410459</v>
       </c>
-      <c r="D68" s="85" t="n">
+      <c r="D68" s="91" t="n">
         <f aca="false">'Stress Test'!F13</f>
         <v>20939123.8687291</v>
       </c>
@@ -10413,15 +10476,15 @@
         <f aca="false">'Stress Test'!A14</f>
         <v>75</v>
       </c>
-      <c r="B69" s="85" t="n">
+      <c r="B69" s="91" t="n">
         <f aca="false">'Stress Test'!C14</f>
         <v>11901125.1186676</v>
       </c>
-      <c r="C69" s="85" t="n">
+      <c r="C69" s="91" t="n">
         <f aca="false">'Stress Test'!E14</f>
         <v>18522419.560609</v>
       </c>
-      <c r="D69" s="85" t="n">
+      <c r="D69" s="91" t="n">
         <f aca="false">'Stress Test'!F14</f>
         <v>22907732.9718814</v>
       </c>
@@ -10438,15 +10501,15 @@
         <f aca="false">'Stress Test'!A15</f>
         <v>76</v>
       </c>
-      <c r="B70" s="85" t="n">
+      <c r="B70" s="91" t="n">
         <f aca="false">'Stress Test'!C15</f>
         <v>12252920.1039489</v>
       </c>
-      <c r="C70" s="85" t="n">
+      <c r="C70" s="91" t="n">
         <f aca="false">'Stress Test'!E15</f>
         <v>19879963.1059923</v>
       </c>
-      <c r="D70" s="85" t="n">
+      <c r="D70" s="91" t="n">
         <f aca="false">'Stress Test'!F15</f>
         <v>25074256.2496042</v>
       </c>
@@ -10463,15 +10526,15 @@
         <f aca="false">'Stress Test'!A16</f>
         <v>77</v>
       </c>
-      <c r="B71" s="85" t="n">
+      <c r="B71" s="91" t="n">
         <f aca="false">'Stress Test'!C16</f>
         <v>12619861.9643205</v>
       </c>
-      <c r="C71" s="85" t="n">
+      <c r="C71" s="91" t="n">
         <f aca="false">'Stress Test'!E16</f>
         <v>21347185.2106853</v>
       </c>
-      <c r="D71" s="85" t="n">
+      <c r="D71" s="91" t="n">
         <f aca="false">'Stress Test'!F16</f>
         <v>27458506.9307783</v>
       </c>
@@ -10488,15 +10551,15 @@
         <f aca="false">'Stress Test'!A17</f>
         <v>78</v>
       </c>
-      <c r="B72" s="85" t="n">
+      <c r="B72" s="91" t="n">
         <f aca="false">'Stress Test'!C17</f>
         <v>13002578.7054862</v>
       </c>
-      <c r="C72" s="85" t="n">
+      <c r="C72" s="91" t="n">
         <f aca="false">'Stress Test'!E17</f>
         <v>22932882.290133</v>
       </c>
-      <c r="D72" s="85" t="n">
+      <c r="D72" s="91" t="n">
         <f aca="false">'Stress Test'!F17</f>
         <v>30082279.8864489</v>
       </c>
@@ -10513,15 +10576,15 @@
         <f aca="false">'Stress Test'!A18</f>
         <v>79</v>
       </c>
-      <c r="B73" s="85" t="n">
+      <c r="B73" s="91" t="n">
         <f aca="false">'Stress Test'!C18</f>
         <v>13401723.7693359</v>
       </c>
-      <c r="C73" s="85" t="n">
+      <c r="C73" s="91" t="n">
         <f aca="false">'Stress Test'!E18</f>
         <v>24646554.7889739</v>
       </c>
-      <c r="D73" s="85" t="n">
+      <c r="D73" s="91" t="n">
         <f aca="false">'Stress Test'!F18</f>
         <v>32969549.7907241</v>
       </c>
@@ -10538,15 +10601,15 @@
         <f aca="false">'Stress Test'!A19</f>
         <v>80</v>
       </c>
-      <c r="B74" s="85" t="n">
+      <c r="B74" s="91" t="n">
         <f aca="false">'Stress Test'!C19</f>
         <v>13817977.0474267</v>
       </c>
-      <c r="C74" s="85" t="n">
+      <c r="C74" s="91" t="n">
         <f aca="false">'Stress Test'!E19</f>
         <v>26498463.4994091</v>
       </c>
-      <c r="D74" s="85" t="n">
+      <c r="D74" s="91" t="n">
         <f aca="false">'Stress Test'!F19</f>
         <v>36146689.0971138</v>
       </c>
@@ -10563,15 +10626,15 @@
         <f aca="false">'Stress Test'!A20</f>
         <v>81</v>
       </c>
-      <c r="B75" s="85" t="n">
+      <c r="B75" s="91" t="n">
         <f aca="false">'Stress Test'!C20</f>
         <v>14252045.93431</v>
       </c>
-      <c r="C75" s="85" t="n">
+      <c r="C75" s="91" t="n">
         <f aca="false">'Stress Test'!E20</f>
         <v>28499690.3843481</v>
       </c>
-      <c r="D75" s="85" t="n">
+      <c r="D75" s="91" t="n">
         <f aca="false">'Stress Test'!F20</f>
         <v>39642707.8118115</v>
       </c>
@@ -10588,15 +10651,15 @@
         <f aca="false">'Stress Test'!A21</f>
         <v>82</v>
       </c>
-      <c r="B76" s="85" t="n">
+      <c r="B76" s="91" t="n">
         <f aca="false">'Stress Test'!C21</f>
         <v>14704666.4222536</v>
       </c>
-      <c r="C76" s="85" t="n">
+      <c r="C76" s="91" t="n">
         <f aca="false">'Stress Test'!E21</f>
         <v>30662204.2656672</v>
       </c>
-      <c r="D76" s="85" t="n">
+      <c r="D76" s="91" t="n">
         <f aca="false">'Stress Test'!F21</f>
         <v>43489517.2435639</v>
       </c>
@@ -10613,15 +10676,15 @@
         <f aca="false">'Stress Test'!A22</f>
         <v>83</v>
       </c>
-      <c r="B77" s="85" t="n">
+      <c r="B77" s="91" t="n">
         <f aca="false">'Stress Test'!C22</f>
         <v>15176604.2389627</v>
       </c>
-      <c r="C77" s="85" t="n">
+      <c r="C77" s="91" t="n">
         <f aca="false">'Stress Test'!E22</f>
         <v>32998931.7667395</v>
       </c>
-      <c r="D77" s="85" t="n">
+      <c r="D77" s="91" t="n">
         <f aca="false">'Stress Test'!F22</f>
         <v>47722220.1277392</v>
       </c>
@@ -10638,15 +10701,15 @@
         <f aca="false">'Stress Test'!A23</f>
         <v>84</v>
       </c>
-      <c r="B78" s="85" t="n">
+      <c r="B78" s="91" t="n">
         <f aca="false">'Stress Test'!C23</f>
         <v>15668656.0299681</v>
       </c>
-      <c r="C78" s="85" t="n">
+      <c r="C78" s="91" t="n">
         <f aca="false">'Stress Test'!E23</f>
         <v>35523833.9295256</v>
       </c>
-      <c r="D78" s="85" t="n">
+      <c r="D78" s="91" t="n">
         <f aca="false">'Stress Test'!F23</f>
         <v>52379429.76196</v>
       </c>
@@ -10663,15 +10726,15 @@
         <f aca="false">'Stress Test'!A24</f>
         <v>85</v>
       </c>
-      <c r="B79" s="85" t="n">
+      <c r="B79" s="91" t="n">
         <f aca="false">'Stress Test'!C24</f>
         <v>16181650.587414</v>
       </c>
-      <c r="C79" s="85" t="n">
+      <c r="C79" s="91" t="n">
         <f aca="false">'Stress Test'!E24</f>
         <v>38251988.9601348</v>
       </c>
-      <c r="D79" s="85" t="n">
+      <c r="D79" s="91" t="n">
         <f aca="false">'Stress Test'!F24</f>
         <v>57503621.0544032</v>
       </c>
@@ -11096,39 +11159,39 @@
       <c r="A11" s="18" t="n">
         <v>73</v>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="19" t="n">
         <f aca="false">J10</f>
         <v>1890395.32091377</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="19" t="n">
         <f aca="false">IF(73&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,73-Inputs!B25),0)</f>
         <v>55275.6270856992</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="19" t="n">
         <f aca="false">C11*Inputs!B43</f>
         <v>46984.2830228443</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="19" t="n">
         <f aca="false">MAX(0,Inputs!B41-D11-Inputs!B42)</f>
         <v>124065.716977156</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="19" t="n">
         <f aca="false">D11+E11</f>
         <v>171050</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="19" t="n">
         <f aca="false">MAX(0,IF(F11&lt;=23200,F11*0.1,IF(F11&lt;=94300,23200*0.1+(F11-23200)*0.12,IF(F11&lt;=201050,23200*0.1+71100*0.12+(F11-94300)*0.22,IF(F11&lt;=383900,23200*0.1+71100*0.12+106750*0.22+(F11-201050)*0.24,23200*0.1+71100*0.12+106750*0.22+182850*0.24+(F11-383900)*0.32)))))</f>
         <v>27737</v>
       </c>
-      <c r="H11" s="26" t="n">
+      <c r="H11" s="20" t="n">
         <f aca="false">IFERROR(G11/F11,0)</f>
         <v>0.162157263957907</v>
       </c>
-      <c r="I11" s="27" t="str">
+      <c r="I11" s="21" t="str">
         <f aca="false">IF(F11&lt;=206000,"Tier 0 — $0/yr",IF(F11&lt;=258000,"Tier 1 — $594/yr",IF(F11&lt;=322000,"Tier 2 — $1,494/yr",IF(F11&lt;=386000,"Tier 3 — $2,394/yr",IF(F11&lt;=750000,"Tier 4 — $3,270/yr","Tier 5 — $3,564/yr")))))</f>
         <v>Tier 0 — $0/yr</v>
       </c>
-      <c r="J11" s="25" t="n">
+      <c r="J11" s="19" t="n">
         <f aca="false">MAX(0,B11-E11)</f>
         <v>1766329.60393662</v>
       </c>
@@ -11137,39 +11200,39 @@
       <c r="A12" s="18" t="n">
         <v>74</v>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="22" t="n">
         <f aca="false">J11</f>
         <v>1766329.60393662</v>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="22" t="n">
         <f aca="false">IF(74&gt;=Inputs!B25,IF(Inputs!B25=65,Inputs!B22*12,IF(Inputs!B25=70,Inputs!B24*12,Inputs!B23*12))*(1+Inputs!B21)^MAX(0,74-Inputs!B25),0)</f>
         <v>56657.5177628417</v>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="22" t="n">
         <f aca="false">C12*Inputs!B43</f>
         <v>48158.8900984154</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="22" t="n">
         <f aca="false">MAX(0,Inputs!B41-D12-Inputs!B42)</f>
         <v>122891.109901585</v>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F12" s="22" t="n">
         <f aca="false">D12+E12</f>
         <v>171050</v>
       </c>
-      <c r="G12" s="25" t="n">
+      <c r="G12" s="22" t="n">
         <f aca="false">MAX(0,IF(F12&lt;=23200,F12*0.1,IF(F12&lt;=94300,23200*0.1+(F12-23200)*0.12,IF(F12&lt;=201050,23200*0.1+71100*0.12+(F12-94300)*0.22,IF(F12&lt;=383900,23200*0.1+71100*0.12+106750*0.22+(F12-201050)*0.24,23200*0.1+71100*0.12+106750*0.22+182850*0.24+(F12-383900)*0.32)))))</f>
         <v>27737</v>
       </c>
-      <c r="H12" s="26" t="n">
+      <c r="H12" s="23" t="n">
         <f aca="false">IFERROR(G12/F12,0)</f>
         <v>0.162157263957907</v>
       </c>
-      <c r="I12" s="27" t="str">
+      <c r="I12" s="24" t="str">
         <f aca="false">IF(F12&lt;=206000,"Tier 0 — $0/yr",IF(F12&lt;=258000,"Tier 1 — $594/yr",IF(F12&lt;=322000,"Tier 2 — $1,494/yr",IF(F12&lt;=386000,"Tier 3 — $2,394/yr",IF(F12&lt;=750000,"Tier 4 — $3,270/yr","Tier 5 — $3,564/yr")))))</f>
         <v>Tier 0 — $0/yr</v>
       </c>
-      <c r="J12" s="25" t="n">
+      <c r="J12" s="22" t="n">
         <f aca="false">MAX(0,B12-E12)</f>
         <v>1643438.49403503</v>
       </c>
@@ -13229,23 +13292,23 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="44" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B4" s="45" t="n">
-        <f aca="false">'Roth Conversion'!B11</f>
-        <v>1890395.32091377</v>
+        <f aca="false">'Roth Conversion'!B13</f>
+        <v>1643438.49403503</v>
       </c>
       <c r="C4" s="46" t="n">
         <f aca="false">VLOOKUP(A4,L$4:M$16,2,0)</f>
-        <v>26.5</v>
+        <v>24.6</v>
       </c>
       <c r="D4" s="45" t="n">
         <f aca="false">IFERROR(ROUND(B4/C4,0),0)</f>
-        <v>71336</v>
+        <v>66806</v>
       </c>
       <c r="E4" s="45" t="n">
-        <f aca="false">'Roth Conversion'!E11</f>
-        <v>124065.716977156</v>
+        <f aca="false">'Roth Conversion'!E13</f>
+        <v>121687.137649124</v>
       </c>
       <c r="F4" s="45" t="n">
         <f aca="false">MAX(0,D4-E4)</f>
@@ -13253,19 +13316,19 @@
       </c>
       <c r="G4" s="45" t="n">
         <f aca="false">MAX(D4,E4)</f>
-        <v>124065.716977156</v>
+        <v>121687.137649124</v>
       </c>
       <c r="H4" s="45" t="n">
-        <f aca="false">MAX(0,IF((G4+'Withdrawal Plan'!H11*Inputs!B43)&lt;=23200,(G4+'Withdrawal Plan'!H11*Inputs!B43)*0.1,IF((G4+'Withdrawal Plan'!H11*Inputs!B43)&lt;=94300,23200*0.1+(G4+'Withdrawal Plan'!H11*Inputs!B43-23200)*0.12,IF((G4+'Withdrawal Plan'!H11*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+(G4+'Withdrawal Plan'!H11*Inputs!B43-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(G4+'Withdrawal Plan'!H11*Inputs!B43-201050)*0.24))))</f>
+        <f aca="false">MAX(0,IF((G4+'Withdrawal Plan'!H13*Inputs!B43)&lt;=23200,(G4+'Withdrawal Plan'!H13*Inputs!B43)*0.1,IF((G4+'Withdrawal Plan'!H13*Inputs!B43)&lt;=94300,23200*0.1+((G4+'Withdrawal Plan'!H13*Inputs!B43)-23200)*0.12,IF((G4+'Withdrawal Plan'!H13*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+((G4+'Withdrawal Plan'!H13*Inputs!B43)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+((G4+'Withdrawal Plan'!H13*Inputs!B43)-201050)*0.24))))</f>
         <v>27737</v>
       </c>
       <c r="I4" s="45" t="n">
         <f aca="false">ROUND(G4*0.0637,0)</f>
-        <v>7903</v>
+        <v>7751</v>
       </c>
       <c r="J4" s="45" t="n">
         <f aca="false">G4-H4-I4</f>
-        <v>88425.7169771557</v>
+        <v>86199.1376491242</v>
       </c>
       <c r="L4" s="47" t="n">
         <v>73</v>
@@ -13276,43 +13339,43 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="n">
-        <v>74</v>
-      </c>
-      <c r="B5" s="49" t="n">
-        <f aca="false">'Roth Conversion'!B12</f>
-        <v>1766329.60393662</v>
-      </c>
-      <c r="C5" s="50" t="n">
+        <v>76</v>
+      </c>
+      <c r="B5" s="45" t="n">
+        <f aca="false">'Roth Conversion'!B14</f>
+        <v>1521751.35638591</v>
+      </c>
+      <c r="C5" s="46" t="n">
         <f aca="false">VLOOKUP(A5,L$4:M$16,2,0)</f>
-        <v>25.5</v>
-      </c>
-      <c r="D5" s="49" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="D5" s="45" t="n">
         <f aca="false">IFERROR(ROUND(B5/C5,0),0)</f>
-        <v>69268</v>
-      </c>
-      <c r="E5" s="49" t="n">
-        <f aca="false">'Roth Conversion'!E12</f>
-        <v>122891.109901585</v>
-      </c>
-      <c r="F5" s="49" t="n">
+        <v>64209</v>
+      </c>
+      <c r="E5" s="45" t="n">
+        <f aca="false">'Roth Conversion'!E14</f>
+        <v>120453.066090352</v>
+      </c>
+      <c r="F5" s="45" t="n">
         <f aca="false">MAX(0,D5-E5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="49" t="n">
+      <c r="G5" s="45" t="n">
         <f aca="false">MAX(D5,E5)</f>
-        <v>122891.109901585</v>
-      </c>
-      <c r="H5" s="49" t="n">
-        <f aca="false">MAX(0,IF((G5+'Withdrawal Plan'!H12*Inputs!B43)&lt;=23200,(G5+'Withdrawal Plan'!H12*Inputs!B43)*0.1,IF((G5+'Withdrawal Plan'!H12*Inputs!B43)&lt;=94300,23200*0.1+(G5+'Withdrawal Plan'!H12*Inputs!B43-23200)*0.12,IF((G5+'Withdrawal Plan'!H12*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+(G5+'Withdrawal Plan'!H12*Inputs!B43-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(G5+'Withdrawal Plan'!H12*Inputs!B43-201050)*0.24))))</f>
+        <v>120453.066090352</v>
+      </c>
+      <c r="H5" s="45" t="n">
+        <f aca="false">MAX(0,IF((G5+'Withdrawal Plan'!H14*Inputs!B43)&lt;=23200,(G5+'Withdrawal Plan'!H14*Inputs!B43)*0.1,IF((G5+'Withdrawal Plan'!H14*Inputs!B43)&lt;=94300,23200*0.1+((G5+'Withdrawal Plan'!H14*Inputs!B43)-23200)*0.12,IF((G5+'Withdrawal Plan'!H14*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+((G5+'Withdrawal Plan'!H14*Inputs!B43)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+((G5+'Withdrawal Plan'!H14*Inputs!B43)-201050)*0.24))))</f>
         <v>27737</v>
       </c>
-      <c r="I5" s="49" t="n">
+      <c r="I5" s="45" t="n">
         <f aca="false">ROUND(G5*0.0637,0)</f>
-        <v>7828</v>
-      </c>
-      <c r="J5" s="49" t="n">
+        <v>7673</v>
+      </c>
+      <c r="J5" s="45" t="n">
         <f aca="false">G5-H5-I5</f>
-        <v>87326.1099015846</v>
+        <v>85043.0660903523</v>
       </c>
       <c r="L5" s="47" t="n">
         <v>74</v>
@@ -13323,23 +13386,23 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="44" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B6" s="45" t="n">
-        <f aca="false">'Roth Conversion'!B13</f>
-        <v>1643438.49403503</v>
+        <f aca="false">'Roth Conversion'!B15</f>
+        <v>1401298.29029556</v>
       </c>
       <c r="C6" s="46" t="n">
         <f aca="false">VLOOKUP(A6,L$4:M$16,2,0)</f>
-        <v>24.6</v>
+        <v>22.9</v>
       </c>
       <c r="D6" s="45" t="n">
         <f aca="false">IFERROR(ROUND(B6/C6,0),0)</f>
-        <v>66806</v>
+        <v>61192</v>
       </c>
       <c r="E6" s="45" t="n">
-        <f aca="false">'Roth Conversion'!E13</f>
-        <v>121687.137649124</v>
+        <f aca="false">'Roth Conversion'!E15</f>
+        <v>119188.142742611</v>
       </c>
       <c r="F6" s="45" t="n">
         <f aca="false">MAX(0,D6-E6)</f>
@@ -13347,19 +13410,19 @@
       </c>
       <c r="G6" s="45" t="n">
         <f aca="false">MAX(D6,E6)</f>
-        <v>121687.137649124</v>
+        <v>119188.142742611</v>
       </c>
       <c r="H6" s="45" t="n">
-        <f aca="false">MAX(0,IF((G6+'Withdrawal Plan'!H13*Inputs!B43)&lt;=23200,(G6+'Withdrawal Plan'!H13*Inputs!B43)*0.1,IF((G6+'Withdrawal Plan'!H13*Inputs!B43)&lt;=94300,23200*0.1+(G6+'Withdrawal Plan'!H13*Inputs!B43-23200)*0.12,IF((G6+'Withdrawal Plan'!H13*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+(G6+'Withdrawal Plan'!H13*Inputs!B43-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(G6+'Withdrawal Plan'!H13*Inputs!B43-201050)*0.24))))</f>
+        <f aca="false">MAX(0,IF((G6+'Withdrawal Plan'!H15*Inputs!B43)&lt;=23200,(G6+'Withdrawal Plan'!H15*Inputs!B43)*0.1,IF((G6+'Withdrawal Plan'!H15*Inputs!B43)&lt;=94300,23200*0.1+((G6+'Withdrawal Plan'!H15*Inputs!B43)-23200)*0.12,IF((G6+'Withdrawal Plan'!H15*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+((G6+'Withdrawal Plan'!H15*Inputs!B43)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+((G6+'Withdrawal Plan'!H15*Inputs!B43)-201050)*0.24))))</f>
         <v>27737</v>
       </c>
       <c r="I6" s="45" t="n">
         <f aca="false">ROUND(G6*0.0637,0)</f>
-        <v>7751</v>
+        <v>7592</v>
       </c>
       <c r="J6" s="45" t="n">
         <f aca="false">G6-H6-I6</f>
-        <v>86199.1376491242</v>
+        <v>83859.1427426111</v>
       </c>
       <c r="L6" s="47" t="n">
         <v>75</v>
@@ -13370,43 +13433,43 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="44" t="n">
-        <v>76</v>
-      </c>
-      <c r="B7" s="49" t="n">
-        <f aca="false">'Roth Conversion'!B14</f>
-        <v>1521751.35638591</v>
-      </c>
-      <c r="C7" s="50" t="n">
+        <v>78</v>
+      </c>
+      <c r="B7" s="45" t="n">
+        <f aca="false">'Roth Conversion'!B16</f>
+        <v>1282110.14755295</v>
+      </c>
+      <c r="C7" s="46" t="n">
         <f aca="false">VLOOKUP(A7,L$4:M$16,2,0)</f>
-        <v>23.7</v>
-      </c>
-      <c r="D7" s="49" t="n">
+        <v>22</v>
+      </c>
+      <c r="D7" s="45" t="n">
         <f aca="false">IFERROR(ROUND(B7/C7,0),0)</f>
-        <v>64209</v>
-      </c>
-      <c r="E7" s="49" t="n">
-        <f aca="false">'Roth Conversion'!E14</f>
-        <v>120453.066090352</v>
-      </c>
-      <c r="F7" s="49" t="n">
+        <v>58278</v>
+      </c>
+      <c r="E7" s="45" t="n">
+        <f aca="false">'Roth Conversion'!E16</f>
+        <v>117891.596311176</v>
+      </c>
+      <c r="F7" s="45" t="n">
         <f aca="false">MAX(0,D7-E7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="49" t="n">
+      <c r="G7" s="45" t="n">
         <f aca="false">MAX(D7,E7)</f>
-        <v>120453.066090352</v>
-      </c>
-      <c r="H7" s="49" t="n">
-        <f aca="false">MAX(0,IF((G7+'Withdrawal Plan'!H14*Inputs!B43)&lt;=23200,(G7+'Withdrawal Plan'!H14*Inputs!B43)*0.1,IF((G7+'Withdrawal Plan'!H14*Inputs!B43)&lt;=94300,23200*0.1+(G7+'Withdrawal Plan'!H14*Inputs!B43-23200)*0.12,IF((G7+'Withdrawal Plan'!H14*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+(G7+'Withdrawal Plan'!H14*Inputs!B43-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(G7+'Withdrawal Plan'!H14*Inputs!B43-201050)*0.24))))</f>
+        <v>117891.596311176</v>
+      </c>
+      <c r="H7" s="45" t="n">
+        <f aca="false">MAX(0,IF((G7+'Withdrawal Plan'!H16*Inputs!B43)&lt;=23200,(G7+'Withdrawal Plan'!H16*Inputs!B43)*0.1,IF((G7+'Withdrawal Plan'!H16*Inputs!B43)&lt;=94300,23200*0.1+((G7+'Withdrawal Plan'!H16*Inputs!B43)-23200)*0.12,IF((G7+'Withdrawal Plan'!H16*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+((G7+'Withdrawal Plan'!H16*Inputs!B43)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+((G7+'Withdrawal Plan'!H16*Inputs!B43)-201050)*0.24))))</f>
         <v>27737</v>
       </c>
-      <c r="I7" s="49" t="n">
+      <c r="I7" s="45" t="n">
         <f aca="false">ROUND(G7*0.0637,0)</f>
-        <v>7673</v>
-      </c>
-      <c r="J7" s="49" t="n">
+        <v>7510</v>
+      </c>
+      <c r="J7" s="45" t="n">
         <f aca="false">G7-H7-I7</f>
-        <v>85043.0660903523</v>
+        <v>82644.5963111764</v>
       </c>
       <c r="L7" s="47" t="n">
         <v>76</v>
@@ -13417,23 +13480,23 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="44" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B8" s="45" t="n">
-        <f aca="false">'Roth Conversion'!B15</f>
-        <v>1401298.29029556</v>
+        <f aca="false">'Roth Conversion'!B17</f>
+        <v>1164218.55124177</v>
       </c>
       <c r="C8" s="46" t="n">
         <f aca="false">VLOOKUP(A8,L$4:M$16,2,0)</f>
-        <v>22.9</v>
+        <v>21.1</v>
       </c>
       <c r="D8" s="45" t="n">
         <f aca="false">IFERROR(ROUND(B8/C8,0),0)</f>
-        <v>61192</v>
+        <v>55176</v>
       </c>
       <c r="E8" s="45" t="n">
-        <f aca="false">'Roth Conversion'!E15</f>
-        <v>119188.142742611</v>
+        <f aca="false">'Roth Conversion'!E17</f>
+        <v>116562.636218956</v>
       </c>
       <c r="F8" s="45" t="n">
         <f aca="false">MAX(0,D8-E8)</f>
@@ -13441,19 +13504,19 @@
       </c>
       <c r="G8" s="45" t="n">
         <f aca="false">MAX(D8,E8)</f>
-        <v>119188.142742611</v>
+        <v>116562.636218956</v>
       </c>
       <c r="H8" s="45" t="n">
-        <f aca="false">MAX(0,IF((G8+'Withdrawal Plan'!H15*Inputs!B43)&lt;=23200,(G8+'Withdrawal Plan'!H15*Inputs!B43)*0.1,IF((G8+'Withdrawal Plan'!H15*Inputs!B43)&lt;=94300,23200*0.1+(G8+'Withdrawal Plan'!H15*Inputs!B43-23200)*0.12,IF((G8+'Withdrawal Plan'!H15*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+(G8+'Withdrawal Plan'!H15*Inputs!B43-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(G8+'Withdrawal Plan'!H15*Inputs!B43-201050)*0.24))))</f>
+        <f aca="false">MAX(0,IF((G8+'Withdrawal Plan'!H17*Inputs!B43)&lt;=23200,(G8+'Withdrawal Plan'!H17*Inputs!B43)*0.1,IF((G8+'Withdrawal Plan'!H17*Inputs!B43)&lt;=94300,23200*0.1+((G8+'Withdrawal Plan'!H17*Inputs!B43)-23200)*0.12,IF((G8+'Withdrawal Plan'!H17*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+((G8+'Withdrawal Plan'!H17*Inputs!B43)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+((G8+'Withdrawal Plan'!H17*Inputs!B43)-201050)*0.24))))</f>
         <v>27737</v>
       </c>
       <c r="I8" s="45" t="n">
         <f aca="false">ROUND(G8*0.0637,0)</f>
-        <v>7592</v>
+        <v>7425</v>
       </c>
       <c r="J8" s="45" t="n">
         <f aca="false">G8-H8-I8</f>
-        <v>83859.1427426111</v>
+        <v>81400.6362189558</v>
       </c>
       <c r="L8" s="47" t="n">
         <v>77</v>
@@ -13464,43 +13527,43 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="44" t="n">
-        <v>78</v>
-      </c>
-      <c r="B9" s="49" t="n">
-        <f aca="false">'Roth Conversion'!B16</f>
-        <v>1282110.14755295</v>
-      </c>
-      <c r="C9" s="50" t="n">
+        <v>80</v>
+      </c>
+      <c r="B9" s="45" t="n">
+        <f aca="false">'Roth Conversion'!B18</f>
+        <v>1047655.91502281</v>
+      </c>
+      <c r="C9" s="46" t="n">
         <f aca="false">VLOOKUP(A9,L$4:M$16,2,0)</f>
-        <v>22</v>
-      </c>
-      <c r="D9" s="49" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="D9" s="45" t="n">
         <f aca="false">IFERROR(ROUND(B9/C9,0),0)</f>
-        <v>58278</v>
-      </c>
-      <c r="E9" s="49" t="n">
-        <f aca="false">'Roth Conversion'!E16</f>
-        <v>117891.596311176</v>
-      </c>
-      <c r="F9" s="49" t="n">
+        <v>51864</v>
+      </c>
+      <c r="E9" s="45" t="n">
+        <f aca="false">'Roth Conversion'!E18</f>
+        <v>115200.45212443</v>
+      </c>
+      <c r="F9" s="45" t="n">
         <f aca="false">MAX(0,D9-E9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="49" t="n">
+      <c r="G9" s="45" t="n">
         <f aca="false">MAX(D9,E9)</f>
-        <v>117891.596311176</v>
-      </c>
-      <c r="H9" s="49" t="n">
-        <f aca="false">MAX(0,IF((G9+'Withdrawal Plan'!H16*Inputs!B43)&lt;=23200,(G9+'Withdrawal Plan'!H16*Inputs!B43)*0.1,IF((G9+'Withdrawal Plan'!H16*Inputs!B43)&lt;=94300,23200*0.1+(G9+'Withdrawal Plan'!H16*Inputs!B43-23200)*0.12,IF((G9+'Withdrawal Plan'!H16*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+(G9+'Withdrawal Plan'!H16*Inputs!B43-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(G9+'Withdrawal Plan'!H16*Inputs!B43-201050)*0.24))))</f>
+        <v>115200.45212443</v>
+      </c>
+      <c r="H9" s="45" t="n">
+        <f aca="false">MAX(0,IF((G9+'Withdrawal Plan'!H18*Inputs!B43)&lt;=23200,(G9+'Withdrawal Plan'!H18*Inputs!B43)*0.1,IF((G9+'Withdrawal Plan'!H18*Inputs!B43)&lt;=94300,23200*0.1+((G9+'Withdrawal Plan'!H18*Inputs!B43)-23200)*0.12,IF((G9+'Withdrawal Plan'!H18*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+((G9+'Withdrawal Plan'!H18*Inputs!B43)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+((G9+'Withdrawal Plan'!H18*Inputs!B43)-201050)*0.24))))</f>
         <v>27737</v>
       </c>
-      <c r="I9" s="49" t="n">
+      <c r="I9" s="45" t="n">
         <f aca="false">ROUND(G9*0.0637,0)</f>
-        <v>7510</v>
-      </c>
-      <c r="J9" s="49" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J9" s="45" t="n">
         <f aca="false">G9-H9-I9</f>
-        <v>82644.5963111764</v>
+        <v>80125.4521244298</v>
       </c>
       <c r="L9" s="47" t="n">
         <v>78</v>
@@ -13511,23 +13574,23 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="44" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B10" s="45" t="n">
-        <f aca="false">'Roth Conversion'!B17</f>
-        <v>1164218.55124177</v>
+        <f aca="false">'Roth Conversion'!B19</f>
+        <v>932455.462898383</v>
       </c>
       <c r="C10" s="46" t="n">
         <f aca="false">VLOOKUP(A10,L$4:M$16,2,0)</f>
-        <v>21.1</v>
+        <v>19.4</v>
       </c>
       <c r="D10" s="45" t="n">
         <f aca="false">IFERROR(ROUND(B10/C10,0),0)</f>
-        <v>55176</v>
+        <v>48065</v>
       </c>
       <c r="E10" s="45" t="n">
-        <f aca="false">'Roth Conversion'!E17</f>
-        <v>116562.636218956</v>
+        <f aca="false">'Roth Conversion'!E19</f>
+        <v>113804.21342754</v>
       </c>
       <c r="F10" s="45" t="n">
         <f aca="false">MAX(0,D10-E10)</f>
@@ -13535,19 +13598,19 @@
       </c>
       <c r="G10" s="45" t="n">
         <f aca="false">MAX(D10,E10)</f>
-        <v>116562.636218956</v>
+        <v>113804.21342754</v>
       </c>
       <c r="H10" s="45" t="n">
-        <f aca="false">MAX(0,IF((G10+'Withdrawal Plan'!H17*Inputs!B43)&lt;=23200,(G10+'Withdrawal Plan'!H17*Inputs!B43)*0.1,IF((G10+'Withdrawal Plan'!H17*Inputs!B43)&lt;=94300,23200*0.1+(G10+'Withdrawal Plan'!H17*Inputs!B43-23200)*0.12,IF((G10+'Withdrawal Plan'!H17*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+(G10+'Withdrawal Plan'!H17*Inputs!B43-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(G10+'Withdrawal Plan'!H17*Inputs!B43-201050)*0.24))))</f>
+        <f aca="false">MAX(0,IF((G10+'Withdrawal Plan'!H19*Inputs!B43)&lt;=23200,(G10+'Withdrawal Plan'!H19*Inputs!B43)*0.1,IF((G10+'Withdrawal Plan'!H19*Inputs!B43)&lt;=94300,23200*0.1+((G10+'Withdrawal Plan'!H19*Inputs!B43)-23200)*0.12,IF((G10+'Withdrawal Plan'!H19*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+((G10+'Withdrawal Plan'!H19*Inputs!B43)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+((G10+'Withdrawal Plan'!H19*Inputs!B43)-201050)*0.24))))</f>
         <v>27737</v>
       </c>
       <c r="I10" s="45" t="n">
         <f aca="false">ROUND(G10*0.0637,0)</f>
-        <v>7425</v>
+        <v>7249</v>
       </c>
       <c r="J10" s="45" t="n">
         <f aca="false">G10-H10-I10</f>
-        <v>81400.6362189558</v>
+        <v>78818.2134275405</v>
       </c>
       <c r="L10" s="47" t="n">
         <v>79</v>
@@ -13558,43 +13621,43 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="44" t="n">
-        <v>80</v>
-      </c>
-      <c r="B11" s="49" t="n">
-        <f aca="false">'Roth Conversion'!B18</f>
-        <v>1047655.91502281</v>
-      </c>
-      <c r="C11" s="50" t="n">
+        <v>82</v>
+      </c>
+      <c r="B11" s="45" t="n">
+        <f aca="false">'Roth Conversion'!B20</f>
+        <v>818651.249470843</v>
+      </c>
+      <c r="C11" s="46" t="n">
         <f aca="false">VLOOKUP(A11,L$4:M$16,2,0)</f>
-        <v>20.2</v>
-      </c>
-      <c r="D11" s="49" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D11" s="45" t="n">
         <f aca="false">IFERROR(ROUND(B11/C11,0),0)</f>
-        <v>51864</v>
-      </c>
-      <c r="E11" s="49" t="n">
-        <f aca="false">'Roth Conversion'!E18</f>
-        <v>115200.45212443</v>
-      </c>
-      <c r="F11" s="49" t="n">
+        <v>44251</v>
+      </c>
+      <c r="E11" s="45" t="n">
+        <f aca="false">'Roth Conversion'!E20</f>
+        <v>112373.068763229</v>
+      </c>
+      <c r="F11" s="45" t="n">
         <f aca="false">MAX(0,D11-E11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="49" t="n">
+      <c r="G11" s="45" t="n">
         <f aca="false">MAX(D11,E11)</f>
-        <v>115200.45212443</v>
-      </c>
-      <c r="H11" s="49" t="n">
-        <f aca="false">MAX(0,IF((G11+'Withdrawal Plan'!H18*Inputs!B43)&lt;=23200,(G11+'Withdrawal Plan'!H18*Inputs!B43)*0.1,IF((G11+'Withdrawal Plan'!H18*Inputs!B43)&lt;=94300,23200*0.1+(G11+'Withdrawal Plan'!H18*Inputs!B43-23200)*0.12,IF((G11+'Withdrawal Plan'!H18*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+(G11+'Withdrawal Plan'!H18*Inputs!B43-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(G11+'Withdrawal Plan'!H18*Inputs!B43-201050)*0.24))))</f>
+        <v>112373.068763229</v>
+      </c>
+      <c r="H11" s="45" t="n">
+        <f aca="false">MAX(0,IF((G11+'Withdrawal Plan'!H20*Inputs!B43)&lt;=23200,(G11+'Withdrawal Plan'!H20*Inputs!B43)*0.1,IF((G11+'Withdrawal Plan'!H20*Inputs!B43)&lt;=94300,23200*0.1+((G11+'Withdrawal Plan'!H20*Inputs!B43)-23200)*0.12,IF((G11+'Withdrawal Plan'!H20*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+((G11+'Withdrawal Plan'!H20*Inputs!B43)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+((G11+'Withdrawal Plan'!H20*Inputs!B43)-201050)*0.24))))</f>
         <v>27737</v>
       </c>
-      <c r="I11" s="49" t="n">
+      <c r="I11" s="45" t="n">
         <f aca="false">ROUND(G11*0.0637,0)</f>
-        <v>7338</v>
-      </c>
-      <c r="J11" s="49" t="n">
+        <v>7158</v>
+      </c>
+      <c r="J11" s="45" t="n">
         <f aca="false">G11-H11-I11</f>
-        <v>80125.4521244298</v>
+        <v>77478.068763229</v>
       </c>
       <c r="L11" s="47" t="n">
         <v>80</v>
@@ -13605,23 +13668,23 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="44" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B12" s="45" t="n">
-        <f aca="false">'Roth Conversion'!B19</f>
-        <v>932455.462898383</v>
+        <f aca="false">'Roth Conversion'!B21</f>
+        <v>706278.180707614</v>
       </c>
       <c r="C12" s="46" t="n">
         <f aca="false">VLOOKUP(A12,L$4:M$16,2,0)</f>
-        <v>19.4</v>
+        <v>17.7</v>
       </c>
       <c r="D12" s="45" t="n">
         <f aca="false">IFERROR(ROUND(B12/C12,0),0)</f>
-        <v>48065</v>
+        <v>39903</v>
       </c>
       <c r="E12" s="45" t="n">
-        <f aca="false">'Roth Conversion'!E19</f>
-        <v>113804.21342754</v>
+        <f aca="false">'Roth Conversion'!E21</f>
+        <v>110906.14548231</v>
       </c>
       <c r="F12" s="45" t="n">
         <f aca="false">MAX(0,D12-E12)</f>
@@ -13629,19 +13692,19 @@
       </c>
       <c r="G12" s="45" t="n">
         <f aca="false">MAX(D12,E12)</f>
-        <v>113804.21342754</v>
+        <v>110906.14548231</v>
       </c>
       <c r="H12" s="45" t="n">
-        <f aca="false">MAX(0,IF((G12+'Withdrawal Plan'!H19*Inputs!B43)&lt;=23200,(G12+'Withdrawal Plan'!H19*Inputs!B43)*0.1,IF((G12+'Withdrawal Plan'!H19*Inputs!B43)&lt;=94300,23200*0.1+(G12+'Withdrawal Plan'!H19*Inputs!B43-23200)*0.12,IF((G12+'Withdrawal Plan'!H19*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+(G12+'Withdrawal Plan'!H19*Inputs!B43-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(G12+'Withdrawal Plan'!H19*Inputs!B43-201050)*0.24))))</f>
+        <f aca="false">MAX(0,IF((G12+'Withdrawal Plan'!H21*Inputs!B43)&lt;=23200,(G12+'Withdrawal Plan'!H21*Inputs!B43)*0.1,IF((G12+'Withdrawal Plan'!H21*Inputs!B43)&lt;=94300,23200*0.1+((G12+'Withdrawal Plan'!H21*Inputs!B43)-23200)*0.12,IF((G12+'Withdrawal Plan'!H21*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+((G12+'Withdrawal Plan'!H21*Inputs!B43)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+((G12+'Withdrawal Plan'!H21*Inputs!B43)-201050)*0.24))))</f>
         <v>27737</v>
       </c>
       <c r="I12" s="45" t="n">
         <f aca="false">ROUND(G12*0.0637,0)</f>
-        <v>7249</v>
+        <v>7065</v>
       </c>
       <c r="J12" s="45" t="n">
         <f aca="false">G12-H12-I12</f>
-        <v>78818.2134275405</v>
+        <v>76104.1454823097</v>
       </c>
       <c r="L12" s="47" t="n">
         <v>81</v>
@@ -13652,43 +13715,43 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="44" t="n">
-        <v>82</v>
-      </c>
-      <c r="B13" s="49" t="n">
-        <f aca="false">'Roth Conversion'!B20</f>
-        <v>818651.249470843</v>
-      </c>
-      <c r="C13" s="50" t="n">
+        <v>84</v>
+      </c>
+      <c r="B13" s="45" t="n">
+        <f aca="false">'Roth Conversion'!B22</f>
+        <v>595372.035225304</v>
+      </c>
+      <c r="C13" s="46" t="n">
         <f aca="false">VLOOKUP(A13,L$4:M$16,2,0)</f>
-        <v>18.5</v>
-      </c>
-      <c r="D13" s="49" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="D13" s="45" t="n">
         <f aca="false">IFERROR(ROUND(B13/C13,0),0)</f>
-        <v>44251</v>
-      </c>
-      <c r="E13" s="49" t="n">
-        <f aca="false">'Roth Conversion'!E20</f>
-        <v>112373.068763229</v>
-      </c>
-      <c r="F13" s="49" t="n">
+        <v>35439</v>
+      </c>
+      <c r="E13" s="45" t="n">
+        <f aca="false">'Roth Conversion'!E22</f>
+        <v>109402.549119367</v>
+      </c>
+      <c r="F13" s="45" t="n">
         <f aca="false">MAX(0,D13-E13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="49" t="n">
+      <c r="G13" s="45" t="n">
         <f aca="false">MAX(D13,E13)</f>
-        <v>112373.068763229</v>
-      </c>
-      <c r="H13" s="49" t="n">
-        <f aca="false">MAX(0,IF((G13+'Withdrawal Plan'!H20*Inputs!B43)&lt;=23200,(G13+'Withdrawal Plan'!H20*Inputs!B43)*0.1,IF((G13+'Withdrawal Plan'!H20*Inputs!B43)&lt;=94300,23200*0.1+(G13+'Withdrawal Plan'!H20*Inputs!B43-23200)*0.12,IF((G13+'Withdrawal Plan'!H20*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+(G13+'Withdrawal Plan'!H20*Inputs!B43-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(G13+'Withdrawal Plan'!H20*Inputs!B43-201050)*0.24))))</f>
+        <v>109402.549119367</v>
+      </c>
+      <c r="H13" s="45" t="n">
+        <f aca="false">MAX(0,IF((G13+'Withdrawal Plan'!H22*Inputs!B43)&lt;=23200,(G13+'Withdrawal Plan'!H22*Inputs!B43)*0.1,IF((G13+'Withdrawal Plan'!H22*Inputs!B43)&lt;=94300,23200*0.1+((G13+'Withdrawal Plan'!H22*Inputs!B43)-23200)*0.12,IF((G13+'Withdrawal Plan'!H22*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+((G13+'Withdrawal Plan'!H22*Inputs!B43)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+((G13+'Withdrawal Plan'!H22*Inputs!B43)-201050)*0.24))))</f>
         <v>27737</v>
       </c>
-      <c r="I13" s="49" t="n">
+      <c r="I13" s="45" t="n">
         <f aca="false">ROUND(G13*0.0637,0)</f>
-        <v>7158</v>
-      </c>
-      <c r="J13" s="49" t="n">
+        <v>6969</v>
+      </c>
+      <c r="J13" s="45" t="n">
         <f aca="false">G13-H13-I13</f>
-        <v>77478.068763229</v>
+        <v>74696.5491193675</v>
       </c>
       <c r="L13" s="47" t="n">
         <v>82</v>
@@ -13699,23 +13762,23 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="44" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B14" s="45" t="n">
-        <f aca="false">'Roth Conversion'!B21</f>
-        <v>706278.180707614</v>
+        <f aca="false">'Roth Conversion'!B23</f>
+        <v>485969.486105936</v>
       </c>
       <c r="C14" s="46" t="n">
         <f aca="false">VLOOKUP(A14,L$4:M$16,2,0)</f>
-        <v>17.7</v>
+        <v>16</v>
       </c>
       <c r="D14" s="45" t="n">
         <f aca="false">IFERROR(ROUND(B14/C14,0),0)</f>
-        <v>39903</v>
+        <v>30373</v>
       </c>
       <c r="E14" s="45" t="n">
-        <f aca="false">'Roth Conversion'!E21</f>
-        <v>110906.14548231</v>
+        <f aca="false">'Roth Conversion'!E23</f>
+        <v>107861.362847352</v>
       </c>
       <c r="F14" s="45" t="n">
         <f aca="false">MAX(0,D14-E14)</f>
@@ -13723,19 +13786,19 @@
       </c>
       <c r="G14" s="45" t="n">
         <f aca="false">MAX(D14,E14)</f>
-        <v>110906.14548231</v>
+        <v>107861.362847352</v>
       </c>
       <c r="H14" s="45" t="n">
-        <f aca="false">MAX(0,IF((G14+'Withdrawal Plan'!H21*Inputs!B43)&lt;=23200,(G14+'Withdrawal Plan'!H21*Inputs!B43)*0.1,IF((G14+'Withdrawal Plan'!H21*Inputs!B43)&lt;=94300,23200*0.1+(G14+'Withdrawal Plan'!H21*Inputs!B43-23200)*0.12,IF((G14+'Withdrawal Plan'!H21*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+(G14+'Withdrawal Plan'!H21*Inputs!B43-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(G14+'Withdrawal Plan'!H21*Inputs!B43-201050)*0.24))))</f>
+        <f aca="false">MAX(0,IF((G14+'Withdrawal Plan'!H23*Inputs!B43)&lt;=23200,(G14+'Withdrawal Plan'!H23*Inputs!B43)*0.1,IF((G14+'Withdrawal Plan'!H23*Inputs!B43)&lt;=94300,23200*0.1+((G14+'Withdrawal Plan'!H23*Inputs!B43)-23200)*0.12,IF((G14+'Withdrawal Plan'!H23*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+((G14+'Withdrawal Plan'!H23*Inputs!B43)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+((G14+'Withdrawal Plan'!H23*Inputs!B43)-201050)*0.24))))</f>
         <v>27737</v>
       </c>
       <c r="I14" s="45" t="n">
         <f aca="false">ROUND(G14*0.0637,0)</f>
-        <v>7065</v>
+        <v>6871</v>
       </c>
       <c r="J14" s="45" t="n">
         <f aca="false">G14-H14-I14</f>
-        <v>76104.1454823097</v>
+        <v>73253.3628473516</v>
       </c>
       <c r="L14" s="47" t="n">
         <v>83</v>
@@ -13745,44 +13808,38 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="44" t="n">
-        <v>84</v>
-      </c>
-      <c r="B15" s="49" t="n">
-        <f aca="false">'Roth Conversion'!B22</f>
-        <v>595372.035225304</v>
-      </c>
-      <c r="C15" s="50" t="n">
-        <f aca="false">VLOOKUP(A15,L$4:M$16,2,0)</f>
-        <v>16.8</v>
-      </c>
-      <c r="D15" s="49" t="n">
-        <f aca="false">IFERROR(ROUND(B15/C15,0),0)</f>
-        <v>35439</v>
-      </c>
-      <c r="E15" s="49" t="n">
-        <f aca="false">'Roth Conversion'!E22</f>
-        <v>109402.549119367</v>
-      </c>
-      <c r="F15" s="49" t="n">
-        <f aca="false">MAX(0,D15-E15)</f>
+      <c r="A15" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="50"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="52" t="n">
+        <f aca="false">SUM(D4:D14)</f>
+        <v>555556</v>
+      </c>
+      <c r="E15" s="52" t="n">
+        <f aca="false">SUM(E4:E14)</f>
+        <v>1265330.37077645</v>
+      </c>
+      <c r="F15" s="52" t="n">
+        <f aca="false">SUM(F4:F14)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="49" t="n">
-        <f aca="false">MAX(D15,E15)</f>
-        <v>109402.549119367</v>
-      </c>
-      <c r="H15" s="49" t="n">
-        <f aca="false">MAX(0,IF((G15+'Withdrawal Plan'!H22*Inputs!B43)&lt;=23200,(G15+'Withdrawal Plan'!H22*Inputs!B43)*0.1,IF((G15+'Withdrawal Plan'!H22*Inputs!B43)&lt;=94300,23200*0.1+(G15+'Withdrawal Plan'!H22*Inputs!B43-23200)*0.12,IF((G15+'Withdrawal Plan'!H22*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+(G15+'Withdrawal Plan'!H22*Inputs!B43-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(G15+'Withdrawal Plan'!H22*Inputs!B43-201050)*0.24))))</f>
-        <v>27737</v>
-      </c>
-      <c r="I15" s="49" t="n">
-        <f aca="false">ROUND(G15*0.0637,0)</f>
-        <v>6969</v>
-      </c>
-      <c r="J15" s="49" t="n">
-        <f aca="false">G15-H15-I15</f>
-        <v>74696.5491193675</v>
+      <c r="G15" s="52" t="n">
+        <f aca="false">SUM(G4:G14)</f>
+        <v>1265330.37077645</v>
+      </c>
+      <c r="H15" s="52" t="n">
+        <f aca="false">SUM(H4:H14)</f>
+        <v>305107</v>
+      </c>
+      <c r="I15" s="52" t="n">
+        <f aca="false">SUM(I4:I14)</f>
+        <v>80601</v>
+      </c>
+      <c r="J15" s="52" t="n">
+        <f aca="false">SUM(J4:J14)</f>
+        <v>879622.370776448</v>
       </c>
       <c r="L15" s="47" t="n">
         <v>84</v>
@@ -13792,45 +13849,16 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="44" t="n">
-        <v>85</v>
-      </c>
-      <c r="B16" s="45" t="n">
-        <f aca="false">'Roth Conversion'!B23</f>
-        <v>485969.486105936</v>
-      </c>
-      <c r="C16" s="46" t="n">
-        <f aca="false">VLOOKUP(A16,L$4:M$16,2,0)</f>
-        <v>16</v>
-      </c>
-      <c r="D16" s="45" t="n">
-        <f aca="false">IFERROR(ROUND(B16/C16,0),0)</f>
-        <v>30373</v>
-      </c>
-      <c r="E16" s="45" t="n">
-        <f aca="false">'Roth Conversion'!E23</f>
-        <v>107861.362847352</v>
-      </c>
-      <c r="F16" s="45" t="n">
-        <f aca="false">MAX(0,D16-E16)</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="45" t="n">
-        <f aca="false">MAX(D16,E16)</f>
-        <v>107861.362847352</v>
-      </c>
-      <c r="H16" s="45" t="n">
-        <f aca="false">MAX(0,IF((G16+'Withdrawal Plan'!H23*Inputs!B43)&lt;=23200,(G16+'Withdrawal Plan'!H23*Inputs!B43)*0.1,IF((G16+'Withdrawal Plan'!H23*Inputs!B43)&lt;=94300,23200*0.1+(G16+'Withdrawal Plan'!H23*Inputs!B43-23200)*0.12,IF((G16+'Withdrawal Plan'!H23*Inputs!B43)&lt;=201050,23200*0.1+71100*0.12+(G16+'Withdrawal Plan'!H23*Inputs!B43-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(G16+'Withdrawal Plan'!H23*Inputs!B43-201050)*0.24))))</f>
-        <v>27737</v>
-      </c>
-      <c r="I16" s="45" t="n">
-        <f aca="false">ROUND(G16*0.0637,0)</f>
-        <v>6871</v>
-      </c>
-      <c r="J16" s="45" t="n">
-        <f aca="false">G16-H16-I16</f>
-        <v>73253.3628473516</v>
-      </c>
+      <c r="A16" s="53"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="54"/>
       <c r="L16" s="47" t="n">
         <v>85</v>
       </c>
@@ -13839,45 +13867,16 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="52" t="n">
-        <f aca="false">SUM(B4:B16)</f>
-        <v>15255924.0937925</v>
-      </c>
-      <c r="C17" s="52" t="n">
-        <f aca="false">SUM(C4:C16)</f>
-        <v>274.9</v>
-      </c>
-      <c r="D17" s="52" t="n">
-        <f aca="false">SUM(D4:D16)</f>
-        <v>696160</v>
-      </c>
-      <c r="E17" s="52" t="n">
-        <f aca="false">SUM(E4:E16)</f>
-        <v>1512287.19765519</v>
-      </c>
-      <c r="F17" s="52" t="n">
-        <f aca="false">SUM(F4:F16)</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="52" t="n">
-        <f aca="false">SUM(G4:G16)</f>
-        <v>1512287.19765519</v>
-      </c>
-      <c r="H17" s="52" t="n">
-        <f aca="false">SUM(H4:H16)</f>
-        <v>360581</v>
-      </c>
-      <c r="I17" s="52" t="n">
-        <f aca="false">SUM(I4:I16)</f>
-        <v>96332</v>
-      </c>
-      <c r="J17" s="52" t="n">
-        <f aca="false">SUM(J4:J16)</f>
-        <v>1055374.19765519</v>
-      </c>
+      <c r="A17" s="56"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -13993,7 +13992,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="53" t="n">
+      <c r="A4" s="58" t="n">
         <v>65</v>
       </c>
       <c r="B4" s="45" t="n">
@@ -14024,7 +14023,7 @@
         <f aca="false">MAX(0,F4-G4)</f>
         <v>141050</v>
       </c>
-      <c r="I4" s="54" t="str">
+      <c r="I4" s="59" t="str">
         <f aca="false">IF(H4&lt;=23200,"10%",IF(H4&lt;=94300,"12%",IF(H4&lt;=201050,"22%",IF(H4&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
@@ -14032,11 +14031,11 @@
         <f aca="false">MAX(0,IF(H4&lt;=23200,H4*0.1,IF(H4&lt;=94300,23200*0.1+(H4-23200)*0.12,IF(H4&lt;=201050,23200*0.1+71100*0.12+(H4-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H4-201050)*0.24))))</f>
         <v>21137</v>
       </c>
-      <c r="K4" s="55" t="n">
+      <c r="K4" s="60" t="n">
         <f aca="false">IFERROR(J4/MAX(1,H4),0)</f>
         <v>0.149854661467565</v>
       </c>
-      <c r="L4" s="54" t="str">
+      <c r="L4" s="59" t="str">
         <f aca="false">IF(F4&lt;=206000,"Base $0",IF(F4&lt;=258000,"T1 $594",IF(F4&lt;=322000,"T2 $1,488",IF(F4&lt;=386000,"T3 $2,382",IF(F4&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
@@ -14050,64 +14049,64 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="56" t="n">
+      <c r="A5" s="61" t="n">
         <v>66</v>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H4</f>
         <v>0</v>
       </c>
-      <c r="C5" s="49" t="n">
+      <c r="C5" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!I4</f>
         <v>0</v>
       </c>
-      <c r="D5" s="49" t="n">
+      <c r="D5" s="62" t="n">
         <f aca="false">'Roth Conversion'!E4</f>
         <v>171050</v>
       </c>
-      <c r="E5" s="49" t="n">
+      <c r="E5" s="62" t="n">
         <f aca="false">(B5+C5)*Inputs!B43</f>
         <v>0</v>
       </c>
-      <c r="F5" s="49" t="n">
+      <c r="F5" s="62" t="n">
         <f aca="false">D5+E5</f>
         <v>171050</v>
       </c>
-      <c r="G5" s="49" t="n">
+      <c r="G5" s="62" t="n">
         <f aca="false">Inputs!B42</f>
         <v>30000</v>
       </c>
-      <c r="H5" s="49" t="n">
+      <c r="H5" s="62" t="n">
         <f aca="false">MAX(0,F5-G5)</f>
         <v>141050</v>
       </c>
-      <c r="I5" s="57" t="str">
+      <c r="I5" s="63" t="str">
         <f aca="false">IF(H5&lt;=23200,"10%",IF(H5&lt;=94300,"12%",IF(H5&lt;=201050,"22%",IF(H5&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
-      <c r="J5" s="49" t="n">
+      <c r="J5" s="62" t="n">
         <f aca="false">MAX(0,IF(H5&lt;=23200,H5*0.1,IF(H5&lt;=94300,23200*0.1+(H5-23200)*0.12,IF(H5&lt;=201050,23200*0.1+71100*0.12+(H5-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H5-201050)*0.24))))</f>
         <v>21137</v>
       </c>
-      <c r="K5" s="58" t="n">
+      <c r="K5" s="64" t="n">
         <f aca="false">IFERROR(J5/MAX(1,H5),0)</f>
         <v>0.149854661467565</v>
       </c>
-      <c r="L5" s="57" t="str">
+      <c r="L5" s="63" t="str">
         <f aca="false">IF(F5&lt;=206000,"Base $0",IF(F5&lt;=258000,"T1 $594",IF(F5&lt;=322000,"T2 $1,488",IF(F5&lt;=386000,"T3 $2,382",IF(F5&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
-      <c r="M5" s="49" t="n">
+      <c r="M5" s="62" t="n">
         <f aca="false">ROUND(D5*0.0637,0)</f>
         <v>10896</v>
       </c>
-      <c r="N5" s="49" t="n">
+      <c r="N5" s="62" t="n">
         <f aca="false">J5+M5</f>
         <v>32033</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="53" t="n">
+      <c r="A6" s="58" t="n">
         <v>67</v>
       </c>
       <c r="B6" s="45" t="n">
@@ -14138,7 +14137,7 @@
         <f aca="false">MAX(0,F6-G6)</f>
         <v>141050</v>
       </c>
-      <c r="I6" s="54" t="str">
+      <c r="I6" s="59" t="str">
         <f aca="false">IF(H6&lt;=23200,"10%",IF(H6&lt;=94300,"12%",IF(H6&lt;=201050,"22%",IF(H6&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
@@ -14146,11 +14145,11 @@
         <f aca="false">MAX(0,IF(H6&lt;=23200,H6*0.1,IF(H6&lt;=94300,23200*0.1+(H6-23200)*0.12,IF(H6&lt;=201050,23200*0.1+71100*0.12+(H6-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H6-201050)*0.24))))</f>
         <v>21137</v>
       </c>
-      <c r="K6" s="55" t="n">
+      <c r="K6" s="60" t="n">
         <f aca="false">IFERROR(J6/MAX(1,H6),0)</f>
         <v>0.149854661467565</v>
       </c>
-      <c r="L6" s="54" t="str">
+      <c r="L6" s="59" t="str">
         <f aca="false">IF(F6&lt;=206000,"Base $0",IF(F6&lt;=258000,"T1 $594",IF(F6&lt;=322000,"T2 $1,488",IF(F6&lt;=386000,"T3 $2,382",IF(F6&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
@@ -14164,64 +14163,64 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="56" t="n">
+      <c r="A7" s="61" t="n">
         <v>68</v>
       </c>
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H6</f>
         <v>48855.6</v>
       </c>
-      <c r="C7" s="49" t="n">
+      <c r="C7" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!I6</f>
         <v>0</v>
       </c>
-      <c r="D7" s="49" t="n">
+      <c r="D7" s="62" t="n">
         <f aca="false">'Roth Conversion'!E6</f>
         <v>129522.74</v>
       </c>
-      <c r="E7" s="49" t="n">
+      <c r="E7" s="62" t="n">
         <f aca="false">(B7+C7)*Inputs!B43</f>
         <v>41527.26</v>
       </c>
-      <c r="F7" s="49" t="n">
+      <c r="F7" s="62" t="n">
         <f aca="false">D7+E7</f>
         <v>171050</v>
       </c>
-      <c r="G7" s="49" t="n">
+      <c r="G7" s="62" t="n">
         <f aca="false">Inputs!B42</f>
         <v>30000</v>
       </c>
-      <c r="H7" s="49" t="n">
+      <c r="H7" s="62" t="n">
         <f aca="false">MAX(0,F7-G7)</f>
         <v>141050</v>
       </c>
-      <c r="I7" s="57" t="str">
+      <c r="I7" s="63" t="str">
         <f aca="false">IF(H7&lt;=23200,"10%",IF(H7&lt;=94300,"12%",IF(H7&lt;=201050,"22%",IF(H7&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
-      <c r="J7" s="49" t="n">
+      <c r="J7" s="62" t="n">
         <f aca="false">MAX(0,IF(H7&lt;=23200,H7*0.1,IF(H7&lt;=94300,23200*0.1+(H7-23200)*0.12,IF(H7&lt;=201050,23200*0.1+71100*0.12+(H7-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H7-201050)*0.24))))</f>
         <v>21137</v>
       </c>
-      <c r="K7" s="58" t="n">
+      <c r="K7" s="64" t="n">
         <f aca="false">IFERROR(J7/MAX(1,H7),0)</f>
         <v>0.149854661467565</v>
       </c>
-      <c r="L7" s="57" t="str">
+      <c r="L7" s="63" t="str">
         <f aca="false">IF(F7&lt;=206000,"Base $0",IF(F7&lt;=258000,"T1 $594",IF(F7&lt;=322000,"T2 $1,488",IF(F7&lt;=386000,"T3 $2,382",IF(F7&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
-      <c r="M7" s="49" t="n">
+      <c r="M7" s="62" t="n">
         <f aca="false">ROUND(D7*0.0637,0)</f>
         <v>8251</v>
       </c>
-      <c r="N7" s="49" t="n">
+      <c r="N7" s="62" t="n">
         <f aca="false">J7+M7</f>
         <v>29388</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="53" t="n">
+      <c r="A8" s="58" t="n">
         <v>69</v>
       </c>
       <c r="B8" s="45" t="n">
@@ -14252,7 +14251,7 @@
         <f aca="false">MAX(0,F8-G8)</f>
         <v>141050</v>
       </c>
-      <c r="I8" s="54" t="str">
+      <c r="I8" s="59" t="str">
         <f aca="false">IF(H8&lt;=23200,"10%",IF(H8&lt;=94300,"12%",IF(H8&lt;=201050,"22%",IF(H8&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
@@ -14260,11 +14259,11 @@
         <f aca="false">MAX(0,IF(H8&lt;=23200,H8*0.1,IF(H8&lt;=94300,23200*0.1+(H8-23200)*0.12,IF(H8&lt;=201050,23200*0.1+71100*0.12+(H8-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H8-201050)*0.24))))</f>
         <v>21137</v>
       </c>
-      <c r="K8" s="55" t="n">
+      <c r="K8" s="60" t="n">
         <f aca="false">IFERROR(J8/MAX(1,H8),0)</f>
         <v>0.149854661467565</v>
       </c>
-      <c r="L8" s="54" t="str">
+      <c r="L8" s="59" t="str">
         <f aca="false">IF(F8&lt;=206000,"Base $0",IF(F8&lt;=258000,"T1 $594",IF(F8&lt;=322000,"T2 $1,488",IF(F8&lt;=386000,"T3 $2,382",IF(F8&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
@@ -14278,64 +14277,64 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="56" t="n">
+      <c r="A9" s="61" t="n">
         <v>70</v>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H8</f>
         <v>51328.91475</v>
       </c>
-      <c r="C9" s="49" t="n">
+      <c r="C9" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!I8</f>
         <v>23832</v>
       </c>
-      <c r="D9" s="49" t="n">
+      <c r="D9" s="62" t="n">
         <f aca="false">'Roth Conversion'!E8</f>
         <v>127420.4224625</v>
       </c>
-      <c r="E9" s="49" t="n">
+      <c r="E9" s="62" t="n">
         <f aca="false">(B9+C9)*Inputs!B43</f>
         <v>63886.7775375</v>
       </c>
-      <c r="F9" s="49" t="n">
+      <c r="F9" s="62" t="n">
         <f aca="false">D9+E9</f>
         <v>191307.2</v>
       </c>
-      <c r="G9" s="49" t="n">
+      <c r="G9" s="62" t="n">
         <f aca="false">Inputs!B42</f>
         <v>30000</v>
       </c>
-      <c r="H9" s="49" t="n">
+      <c r="H9" s="62" t="n">
         <f aca="false">MAX(0,F9-G9)</f>
         <v>161307.2</v>
       </c>
-      <c r="I9" s="57" t="str">
+      <c r="I9" s="63" t="str">
         <f aca="false">IF(H9&lt;=23200,"10%",IF(H9&lt;=94300,"12%",IF(H9&lt;=201050,"22%",IF(H9&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
-      <c r="J9" s="49" t="n">
+      <c r="J9" s="62" t="n">
         <f aca="false">MAX(0,IF(H9&lt;=23200,H9*0.1,IF(H9&lt;=94300,23200*0.1+(H9-23200)*0.12,IF(H9&lt;=201050,23200*0.1+71100*0.12+(H9-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H9-201050)*0.24))))</f>
         <v>25593.584</v>
       </c>
-      <c r="K9" s="58" t="n">
+      <c r="K9" s="64" t="n">
         <f aca="false">IFERROR(J9/MAX(1,H9),0)</f>
         <v>0.158663618238987</v>
       </c>
-      <c r="L9" s="57" t="str">
+      <c r="L9" s="63" t="str">
         <f aca="false">IF(F9&lt;=206000,"Base $0",IF(F9&lt;=258000,"T1 $594",IF(F9&lt;=322000,"T2 $1,488",IF(F9&lt;=386000,"T3 $2,382",IF(F9&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
-      <c r="M9" s="49" t="n">
+      <c r="M9" s="62" t="n">
         <f aca="false">ROUND(D9*0.0637,0)</f>
         <v>8117</v>
       </c>
-      <c r="N9" s="49" t="n">
+      <c r="N9" s="62" t="n">
         <f aca="false">J9+M9</f>
         <v>33710.584</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="53" t="n">
+      <c r="A10" s="58" t="n">
         <v>71</v>
       </c>
       <c r="B10" s="45" t="n">
@@ -14366,7 +14365,7 @@
         <f aca="false">MAX(0,F10-G10)</f>
         <v>161813.63</v>
       </c>
-      <c r="I10" s="54" t="str">
+      <c r="I10" s="59" t="str">
         <f aca="false">IF(H10&lt;=23200,"10%",IF(H10&lt;=94300,"12%",IF(H10&lt;=201050,"22%",IF(H10&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
@@ -14374,11 +14373,11 @@
         <f aca="false">MAX(0,IF(H10&lt;=23200,H10*0.1,IF(H10&lt;=94300,23200*0.1+(H10-23200)*0.12,IF(H10&lt;=201050,23200*0.1+71100*0.12+(H10-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H10-201050)*0.24))))</f>
         <v>25704.9986</v>
       </c>
-      <c r="K10" s="55" t="n">
+      <c r="K10" s="60" t="n">
         <f aca="false">IFERROR(J10/MAX(1,H10),0)</f>
         <v>0.158855583426439</v>
       </c>
-      <c r="L10" s="54" t="str">
+      <c r="L10" s="59" t="str">
         <f aca="false">IF(F10&lt;=206000,"Base $0",IF(F10&lt;=258000,"T1 $594",IF(F10&lt;=322000,"T2 $1,488",IF(F10&lt;=386000,"T3 $2,382",IF(F10&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
@@ -14392,58 +14391,58 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="56" t="n">
+      <c r="A11" s="61" t="n">
         <v>72</v>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H10</f>
         <v>53927.4410592187</v>
       </c>
-      <c r="C11" s="49" t="n">
+      <c r="C11" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!I10</f>
         <v>25038.495</v>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="62" t="n">
         <f aca="false">'Roth Conversion'!E10</f>
         <v>125211.675099664</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="62" t="n">
         <f aca="false">(B11+C11)*Inputs!B43</f>
         <v>67121.0456503359</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="62" t="n">
         <f aca="false">D11+E11</f>
         <v>192332.72075</v>
       </c>
-      <c r="G11" s="49" t="n">
+      <c r="G11" s="62" t="n">
         <f aca="false">Inputs!B42</f>
         <v>30000</v>
       </c>
-      <c r="H11" s="49" t="n">
+      <c r="H11" s="62" t="n">
         <f aca="false">MAX(0,F11-G11)</f>
         <v>162332.72075</v>
       </c>
-      <c r="I11" s="57" t="str">
+      <c r="I11" s="63" t="str">
         <f aca="false">IF(H11&lt;=23200,"10%",IF(H11&lt;=94300,"12%",IF(H11&lt;=201050,"22%",IF(H11&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
-      <c r="J11" s="49" t="n">
+      <c r="J11" s="62" t="n">
         <f aca="false">MAX(0,IF(H11&lt;=23200,H11*0.1,IF(H11&lt;=94300,23200*0.1+(H11-23200)*0.12,IF(H11&lt;=201050,23200*0.1+71100*0.12+(H11-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H11-201050)*0.24))))</f>
         <v>25819.198565</v>
       </c>
-      <c r="K11" s="58" t="n">
+      <c r="K11" s="64" t="n">
         <f aca="false">IFERROR(J11/MAX(1,H11),0)</f>
         <v>0.159051104704656</v>
       </c>
-      <c r="L11" s="57" t="str">
+      <c r="L11" s="63" t="str">
         <f aca="false">IF(F11&lt;=206000,"Base $0",IF(F11&lt;=258000,"T1 $594",IF(F11&lt;=322000,"T2 $1,488",IF(F11&lt;=386000,"T3 $2,382",IF(F11&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
-      <c r="M11" s="49" t="n">
+      <c r="M11" s="62" t="n">
         <f aca="false">ROUND(D11*0.0637,0)</f>
         <v>7976</v>
       </c>
-      <c r="N11" s="49" t="n">
+      <c r="N11" s="62" t="n">
         <f aca="false">J11+M11</f>
         <v>33795.198565</v>
       </c>
@@ -14480,7 +14479,7 @@
         <f aca="false">MAX(0,F12-G12)</f>
         <v>162864.78876875</v>
       </c>
-      <c r="I12" s="54" t="str">
+      <c r="I12" s="59" t="str">
         <f aca="false">IF(H12&lt;=23200,"10%",IF(H12&lt;=94300,"12%",IF(H12&lt;=201050,"22%",IF(H12&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
@@ -14488,11 +14487,11 @@
         <f aca="false">MAX(0,IF(H12&lt;=23200,H12*0.1,IF(H12&lt;=94300,23200*0.1+(H12-23200)*0.12,IF(H12&lt;=201050,23200*0.1+71100*0.12+(H12-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H12-201050)*0.24))))</f>
         <v>25936.253529125</v>
       </c>
-      <c r="K12" s="55" t="n">
+      <c r="K12" s="60" t="n">
         <f aca="false">IFERROR(J12/MAX(1,H12),0)</f>
         <v>0.159250220536936</v>
       </c>
-      <c r="L12" s="54" t="str">
+      <c r="L12" s="59" t="str">
         <f aca="false">IF(F12&lt;=206000,"Base $0",IF(F12&lt;=258000,"T1 $594",IF(F12&lt;=322000,"T2 $1,488",IF(F12&lt;=386000,"T3 $2,382",IF(F12&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
@@ -14509,55 +14508,55 @@
       <c r="A13" s="44" t="n">
         <v>74</v>
       </c>
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H12</f>
         <v>56657.5177628417</v>
       </c>
-      <c r="C13" s="49" t="n">
+      <c r="C13" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!I12</f>
         <v>26306.068809375</v>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="62" t="n">
         <f aca="false">'Roth Conversion'!E12</f>
         <v>122891.109901585</v>
       </c>
-      <c r="E13" s="49" t="n">
+      <c r="E13" s="62" t="n">
         <f aca="false">(B13+C13)*Inputs!B43</f>
         <v>70519.0485863842</v>
       </c>
-      <c r="F13" s="49" t="n">
+      <c r="F13" s="62" t="n">
         <f aca="false">D13+E13</f>
         <v>193410.158487969</v>
       </c>
-      <c r="G13" s="49" t="n">
+      <c r="G13" s="62" t="n">
         <f aca="false">Inputs!B42</f>
         <v>30000</v>
       </c>
-      <c r="H13" s="49" t="n">
+      <c r="H13" s="62" t="n">
         <f aca="false">MAX(0,F13-G13)</f>
         <v>163410.158487969</v>
       </c>
-      <c r="I13" s="57" t="str">
+      <c r="I13" s="63" t="str">
         <f aca="false">IF(H13&lt;=23200,"10%",IF(H13&lt;=94300,"12%",IF(H13&lt;=201050,"22%",IF(H13&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
-      <c r="J13" s="49" t="n">
+      <c r="J13" s="62" t="n">
         <f aca="false">MAX(0,IF(H13&lt;=23200,H13*0.1,IF(H13&lt;=94300,23200*0.1+(H13-23200)*0.12,IF(H13&lt;=201050,23200*0.1+71100*0.12+(H13-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H13-201050)*0.24))))</f>
         <v>26056.2348673531</v>
       </c>
-      <c r="K13" s="58" t="n">
+      <c r="K13" s="64" t="n">
         <f aca="false">IFERROR(J13/MAX(1,H13),0)</f>
         <v>0.159452968581947</v>
       </c>
-      <c r="L13" s="57" t="str">
+      <c r="L13" s="63" t="str">
         <f aca="false">IF(F13&lt;=206000,"Base $0",IF(F13&lt;=258000,"T1 $594",IF(F13&lt;=322000,"T2 $1,488",IF(F13&lt;=386000,"T3 $2,382",IF(F13&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
-      <c r="M13" s="49" t="n">
+      <c r="M13" s="62" t="n">
         <f aca="false">ROUND(D13*0.0637,0)</f>
         <v>7828</v>
       </c>
-      <c r="N13" s="49" t="n">
+      <c r="N13" s="62" t="n">
         <f aca="false">J13+M13</f>
         <v>33884.2348673531</v>
       </c>
@@ -14594,7 +14593,7 @@
         <f aca="false">MAX(0,F14-G14)</f>
         <v>163969.162450168</v>
       </c>
-      <c r="I14" s="54" t="str">
+      <c r="I14" s="59" t="str">
         <f aca="false">IF(H14&lt;=23200,"10%",IF(H14&lt;=94300,"12%",IF(H14&lt;=201050,"22%",IF(H14&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
@@ -14602,11 +14601,11 @@
         <f aca="false">MAX(0,IF(H14&lt;=23200,H14*0.1,IF(H14&lt;=94300,23200*0.1+(H14-23200)*0.12,IF(H14&lt;=201050,23200*0.1+71100*0.12+(H14-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H14-201050)*0.24))))</f>
         <v>26179.2157390369</v>
       </c>
-      <c r="K14" s="55" t="n">
+      <c r="K14" s="60" t="n">
         <f aca="false">IFERROR(J14/MAX(1,H14),0)</f>
         <v>0.159659385629863</v>
       </c>
-      <c r="L14" s="54" t="str">
+      <c r="L14" s="59" t="str">
         <f aca="false">IF(F14&lt;=206000,"Base $0",IF(F14&lt;=258000,"T1 $594",IF(F14&lt;=322000,"T2 $1,488",IF(F14&lt;=386000,"T3 $2,382",IF(F14&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
@@ -14623,55 +14622,55 @@
       <c r="A15" s="44" t="n">
         <v>76</v>
       </c>
-      <c r="B15" s="49" t="n">
+      <c r="B15" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H14</f>
         <v>59525.8045995855</v>
       </c>
-      <c r="C15" s="49" t="n">
+      <c r="C15" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!I14</f>
         <v>27637.8135428496</v>
       </c>
-      <c r="D15" s="49" t="n">
+      <c r="D15" s="62" t="n">
         <f aca="false">'Roth Conversion'!E14</f>
         <v>120453.066090352</v>
       </c>
-      <c r="E15" s="49" t="n">
+      <c r="E15" s="62" t="n">
         <f aca="false">(B15+C15)*Inputs!B43</f>
         <v>74089.0754210698</v>
       </c>
-      <c r="F15" s="49" t="n">
+      <c r="F15" s="62" t="n">
         <f aca="false">D15+E15</f>
         <v>194542.141511422</v>
       </c>
-      <c r="G15" s="49" t="n">
+      <c r="G15" s="62" t="n">
         <f aca="false">Inputs!B42</f>
         <v>30000</v>
       </c>
-      <c r="H15" s="49" t="n">
+      <c r="H15" s="62" t="n">
         <f aca="false">MAX(0,F15-G15)</f>
         <v>164542.141511422</v>
       </c>
-      <c r="I15" s="57" t="str">
+      <c r="I15" s="63" t="str">
         <f aca="false">IF(H15&lt;=23200,"10%",IF(H15&lt;=94300,"12%",IF(H15&lt;=201050,"22%",IF(H15&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
-      <c r="J15" s="49" t="n">
+      <c r="J15" s="62" t="n">
         <f aca="false">MAX(0,IF(H15&lt;=23200,H15*0.1,IF(H15&lt;=94300,23200*0.1+(H15-23200)*0.12,IF(H15&lt;=201050,23200*0.1+71100*0.12+(H15-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H15-201050)*0.24))))</f>
         <v>26305.2711325129</v>
       </c>
-      <c r="K15" s="58" t="n">
+      <c r="K15" s="64" t="n">
         <f aca="false">IFERROR(J15/MAX(1,H15),0)</f>
         <v>0.159869507536991</v>
       </c>
-      <c r="L15" s="57" t="str">
+      <c r="L15" s="63" t="str">
         <f aca="false">IF(F15&lt;=206000,"Base $0",IF(F15&lt;=258000,"T1 $594",IF(F15&lt;=322000,"T2 $1,488",IF(F15&lt;=386000,"T3 $2,382",IF(F15&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
-      <c r="M15" s="49" t="n">
+      <c r="M15" s="62" t="n">
         <f aca="false">ROUND(D15*0.0637,0)</f>
         <v>7673</v>
       </c>
-      <c r="N15" s="49" t="n">
+      <c r="N15" s="62" t="n">
         <f aca="false">J15+M15</f>
         <v>33978.2711325129</v>
       </c>
@@ -14708,7 +14707,7 @@
         <f aca="false">MAX(0,F16-G16)</f>
         <v>165129.445049208</v>
       </c>
-      <c r="I16" s="54" t="str">
+      <c r="I16" s="59" t="str">
         <f aca="false">IF(H16&lt;=23200,"10%",IF(H16&lt;=94300,"12%",IF(H16&lt;=201050,"22%",IF(H16&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
@@ -14716,11 +14715,11 @@
         <f aca="false">MAX(0,IF(H16&lt;=23200,H16*0.1,IF(H16&lt;=94300,23200*0.1+(H16-23200)*0.12,IF(H16&lt;=201050,23200*0.1+71100*0.12+(H16-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H16-201050)*0.24))))</f>
         <v>26434.4779108257</v>
       </c>
-      <c r="K16" s="55" t="n">
+      <c r="K16" s="60" t="n">
         <f aca="false">IFERROR(J16/MAX(1,H16),0)</f>
         <v>0.160083369158955</v>
       </c>
-      <c r="L16" s="54" t="str">
+      <c r="L16" s="59" t="str">
         <f aca="false">IF(F16&lt;=206000,"Base $0",IF(F16&lt;=258000,"T1 $594",IF(F16&lt;=322000,"T2 $1,488",IF(F16&lt;=386000,"T3 $2,382",IF(F16&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
@@ -14737,55 +14736,55 @@
       <c r="A17" s="44" t="n">
         <v>78</v>
       </c>
-      <c r="B17" s="49" t="n">
+      <c r="B17" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H16</f>
         <v>62539.2984574395</v>
       </c>
-      <c r="C17" s="49" t="n">
+      <c r="C17" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!I16</f>
         <v>29036.9778534564</v>
       </c>
-      <c r="D17" s="49" t="n">
+      <c r="D17" s="62" t="n">
         <f aca="false">'Roth Conversion'!E16</f>
         <v>117891.596311176</v>
       </c>
-      <c r="E17" s="49" t="n">
+      <c r="E17" s="62" t="n">
         <f aca="false">(B17+C17)*Inputs!B43</f>
         <v>77839.8348642615</v>
       </c>
-      <c r="F17" s="49" t="n">
+      <c r="F17" s="62" t="n">
         <f aca="false">D17+E17</f>
         <v>195731.431175438</v>
       </c>
-      <c r="G17" s="49" t="n">
+      <c r="G17" s="62" t="n">
         <f aca="false">Inputs!B42</f>
         <v>30000</v>
       </c>
-      <c r="H17" s="49" t="n">
+      <c r="H17" s="62" t="n">
         <f aca="false">MAX(0,F17-G17)</f>
         <v>165731.431175438</v>
       </c>
-      <c r="I17" s="57" t="str">
+      <c r="I17" s="63" t="str">
         <f aca="false">IF(H17&lt;=23200,"10%",IF(H17&lt;=94300,"12%",IF(H17&lt;=201050,"22%",IF(H17&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
-      <c r="J17" s="49" t="n">
+      <c r="J17" s="62" t="n">
         <f aca="false">MAX(0,IF(H17&lt;=23200,H17*0.1,IF(H17&lt;=94300,23200*0.1+(H17-23200)*0.12,IF(H17&lt;=201050,23200*0.1+71100*0.12+(H17-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H17-201050)*0.24))))</f>
         <v>26566.9148585963</v>
       </c>
-      <c r="K17" s="58" t="n">
+      <c r="K17" s="64" t="n">
         <f aca="false">IFERROR(J17/MAX(1,H17),0)</f>
         <v>0.160301004282486</v>
       </c>
-      <c r="L17" s="57" t="str">
+      <c r="L17" s="63" t="str">
         <f aca="false">IF(F17&lt;=206000,"Base $0",IF(F17&lt;=258000,"T1 $594",IF(F17&lt;=322000,"T2 $1,488",IF(F17&lt;=386000,"T3 $2,382",IF(F17&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
-      <c r="M17" s="49" t="n">
+      <c r="M17" s="62" t="n">
         <f aca="false">ROUND(D17*0.0637,0)</f>
         <v>7510</v>
       </c>
-      <c r="N17" s="49" t="n">
+      <c r="N17" s="62" t="n">
         <f aca="false">J17+M17</f>
         <v>34076.9148585963</v>
       </c>
@@ -14822,7 +14821,7 @@
         <f aca="false">MAX(0,F18-G18)</f>
         <v>166348.466954824</v>
       </c>
-      <c r="I18" s="54" t="str">
+      <c r="I18" s="59" t="str">
         <f aca="false">IF(H18&lt;=23200,"10%",IF(H18&lt;=94300,"12%",IF(H18&lt;=201050,"22%",IF(H18&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
@@ -14830,11 +14829,11 @@
         <f aca="false">MAX(0,IF(H18&lt;=23200,H18*0.1,IF(H18&lt;=94300,23200*0.1+(H18-23200)*0.12,IF(H18&lt;=201050,23200*0.1+71100*0.12+(H18-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H18-201050)*0.24))))</f>
         <v>26702.6627300612</v>
       </c>
-      <c r="K18" s="55" t="n">
+      <c r="K18" s="60" t="n">
         <f aca="false">IFERROR(J18/MAX(1,H18),0)</f>
         <v>0.160522445555889</v>
       </c>
-      <c r="L18" s="54" t="str">
+      <c r="L18" s="59" t="str">
         <f aca="false">IF(F18&lt;=206000,"Base $0",IF(F18&lt;=258000,"T1 $594",IF(F18&lt;=322000,"T2 $1,488",IF(F18&lt;=386000,"T3 $2,382",IF(F18&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
@@ -14851,55 +14850,55 @@
       <c r="A19" s="44" t="n">
         <v>80</v>
       </c>
-      <c r="B19" s="49" t="n">
+      <c r="B19" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H18</f>
         <v>65705.3504418474</v>
       </c>
-      <c r="C19" s="49" t="n">
+      <c r="C19" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!I18</f>
         <v>30506.9748572876</v>
       </c>
-      <c r="D19" s="49" t="n">
+      <c r="D19" s="62" t="n">
         <f aca="false">'Roth Conversion'!E18</f>
         <v>115200.45212443</v>
       </c>
-      <c r="E19" s="49" t="n">
+      <c r="E19" s="62" t="n">
         <f aca="false">(B19+C19)*Inputs!B43</f>
         <v>81780.4765042647</v>
       </c>
-      <c r="F19" s="49" t="n">
+      <c r="F19" s="62" t="n">
         <f aca="false">D19+E19</f>
         <v>196980.928628694</v>
       </c>
-      <c r="G19" s="49" t="n">
+      <c r="G19" s="62" t="n">
         <f aca="false">Inputs!B42</f>
         <v>30000</v>
       </c>
-      <c r="H19" s="49" t="n">
+      <c r="H19" s="62" t="n">
         <f aca="false">MAX(0,F19-G19)</f>
         <v>166980.928628694</v>
       </c>
-      <c r="I19" s="57" t="str">
+      <c r="I19" s="63" t="str">
         <f aca="false">IF(H19&lt;=23200,"10%",IF(H19&lt;=94300,"12%",IF(H19&lt;=201050,"22%",IF(H19&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
-      <c r="J19" s="49" t="n">
+      <c r="J19" s="62" t="n">
         <f aca="false">MAX(0,IF(H19&lt;=23200,H19*0.1,IF(H19&lt;=94300,23200*0.1+(H19-23200)*0.12,IF(H19&lt;=201050,23200*0.1+71100*0.12+(H19-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H19-201050)*0.24))))</f>
         <v>26841.8042983128</v>
       </c>
-      <c r="K19" s="58" t="n">
+      <c r="K19" s="64" t="n">
         <f aca="false">IFERROR(J19/MAX(1,H19),0)</f>
         <v>0.160747724418274</v>
       </c>
-      <c r="L19" s="57" t="str">
+      <c r="L19" s="63" t="str">
         <f aca="false">IF(F19&lt;=206000,"Base $0",IF(F19&lt;=258000,"T1 $594",IF(F19&lt;=322000,"T2 $1,488",IF(F19&lt;=386000,"T3 $2,382",IF(F19&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
-      <c r="M19" s="49" t="n">
+      <c r="M19" s="62" t="n">
         <f aca="false">ROUND(D19*0.0637,0)</f>
         <v>7338</v>
       </c>
-      <c r="N19" s="49" t="n">
+      <c r="N19" s="62" t="n">
         <f aca="false">J19+M19</f>
         <v>34179.8042983128</v>
       </c>
@@ -14936,7 +14935,7 @@
         <f aca="false">MAX(0,F20-G20)</f>
         <v>167629.201844412</v>
       </c>
-      <c r="I20" s="54" t="str">
+      <c r="I20" s="59" t="str">
         <f aca="false">IF(H20&lt;=23200,"10%",IF(H20&lt;=94300,"12%",IF(H20&lt;=201050,"22%",IF(H20&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
@@ -14944,11 +14943,11 @@
         <f aca="false">MAX(0,IF(H20&lt;=23200,H20*0.1,IF(H20&lt;=94300,23200*0.1+(H20-23200)*0.12,IF(H20&lt;=201050,23200*0.1+71100*0.12+(H20-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H20-201050)*0.24))))</f>
         <v>26984.4244057706</v>
       </c>
-      <c r="K20" s="55" t="n">
+      <c r="K20" s="60" t="n">
         <f aca="false">IFERROR(J20/MAX(1,H20),0)</f>
         <v>0.160976871027619</v>
       </c>
-      <c r="L20" s="54" t="str">
+      <c r="L20" s="59" t="str">
         <f aca="false">IF(F20&lt;=206000,"Base $0",IF(F20&lt;=258000,"T1 $594",IF(F20&lt;=322000,"T2 $1,488",IF(F20&lt;=386000,"T3 $2,382",IF(F20&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
@@ -14965,55 +14964,55 @@
       <c r="A21" s="44" t="n">
         <v>82</v>
       </c>
-      <c r="B21" s="49" t="n">
+      <c r="B21" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H20</f>
         <v>69031.6838079659</v>
       </c>
-      <c r="C21" s="49" t="n">
+      <c r="C21" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!I20</f>
         <v>32051.3904594378</v>
       </c>
-      <c r="D21" s="49" t="n">
+      <c r="D21" s="62" t="n">
         <f aca="false">'Roth Conversion'!E20</f>
         <v>112373.068763229</v>
       </c>
-      <c r="E21" s="49" t="n">
+      <c r="E21" s="62" t="n">
         <f aca="false">(B21+C21)*Inputs!B43</f>
         <v>85920.6131272931</v>
       </c>
-      <c r="F21" s="49" t="n">
+      <c r="F21" s="62" t="n">
         <f aca="false">D21+E21</f>
         <v>198293.681890522</v>
       </c>
-      <c r="G21" s="49" t="n">
+      <c r="G21" s="62" t="n">
         <f aca="false">Inputs!B42</f>
         <v>30000</v>
       </c>
-      <c r="H21" s="49" t="n">
+      <c r="H21" s="62" t="n">
         <f aca="false">MAX(0,F21-G21)</f>
         <v>168293.681890522</v>
       </c>
-      <c r="I21" s="57" t="str">
+      <c r="I21" s="63" t="str">
         <f aca="false">IF(H21&lt;=23200,"10%",IF(H21&lt;=94300,"12%",IF(H21&lt;=201050,"22%",IF(H21&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
-      <c r="J21" s="49" t="n">
+      <c r="J21" s="62" t="n">
         <f aca="false">MAX(0,IF(H21&lt;=23200,H21*0.1,IF(H21&lt;=94300,23200*0.1+(H21-23200)*0.12,IF(H21&lt;=201050,23200*0.1+71100*0.12+(H21-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H21-201050)*0.24))))</f>
         <v>27130.6100159149</v>
       </c>
-      <c r="K21" s="58" t="n">
+      <c r="K21" s="64" t="n">
         <f aca="false">IFERROR(J21/MAX(1,H21),0)</f>
         <v>0.16120991418777</v>
       </c>
-      <c r="L21" s="57" t="str">
+      <c r="L21" s="63" t="str">
         <f aca="false">IF(F21&lt;=206000,"Base $0",IF(F21&lt;=258000,"T1 $594",IF(F21&lt;=322000,"T2 $1,488",IF(F21&lt;=386000,"T3 $2,382",IF(F21&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
-      <c r="M21" s="49" t="n">
+      <c r="M21" s="62" t="n">
         <f aca="false">ROUND(D21*0.0637,0)</f>
         <v>7158</v>
       </c>
-      <c r="N21" s="49" t="n">
+      <c r="N21" s="62" t="n">
         <f aca="false">J21+M21</f>
         <v>34288.6100159149</v>
       </c>
@@ -15050,7 +15049,7 @@
         <f aca="false">MAX(0,F22-G22)</f>
         <v>168974.773937785</v>
       </c>
-      <c r="I22" s="54" t="str">
+      <c r="I22" s="59" t="str">
         <f aca="false">IF(H22&lt;=23200,"10%",IF(H22&lt;=94300,"12%",IF(H22&lt;=201050,"22%",IF(H22&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
@@ -15058,11 +15057,11 @@
         <f aca="false">MAX(0,IF(H22&lt;=23200,H22*0.1,IF(H22&lt;=94300,23200*0.1+(H22-23200)*0.12,IF(H22&lt;=201050,23200*0.1+71100*0.12+(H22-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H22-201050)*0.24))))</f>
         <v>27280.4502663127</v>
       </c>
-      <c r="K22" s="55" t="n">
+      <c r="K22" s="60" t="n">
         <f aca="false">IFERROR(J22/MAX(1,H22),0)</f>
         <v>0.161446881274462</v>
       </c>
-      <c r="L22" s="54" t="str">
+      <c r="L22" s="59" t="str">
         <f aca="false">IF(F22&lt;=206000,"Base $0",IF(F22&lt;=258000,"T1 $594",IF(F22&lt;=322000,"T2 $1,488",IF(F22&lt;=386000,"T3 $2,382",IF(F22&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
@@ -15079,55 +15078,55 @@
       <c r="A23" s="44" t="n">
         <v>84</v>
       </c>
-      <c r="B23" s="49" t="n">
+      <c r="B23" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H22</f>
         <v>72526.4128007442</v>
       </c>
-      <c r="C23" s="49" t="n">
+      <c r="C23" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!I22</f>
         <v>33673.9921014468</v>
       </c>
-      <c r="D23" s="49" t="n">
+      <c r="D23" s="62" t="n">
         <f aca="false">'Roth Conversion'!E22</f>
         <v>109402.549119367</v>
       </c>
-      <c r="E23" s="49" t="n">
+      <c r="E23" s="62" t="n">
         <f aca="false">(B23+C23)*Inputs!B43</f>
         <v>90270.3441668623</v>
       </c>
-      <c r="F23" s="49" t="n">
+      <c r="F23" s="62" t="n">
         <f aca="false">D23+E23</f>
         <v>199672.89328623</v>
       </c>
-      <c r="G23" s="49" t="n">
+      <c r="G23" s="62" t="n">
         <f aca="false">Inputs!B42</f>
         <v>30000</v>
       </c>
-      <c r="H23" s="49" t="n">
+      <c r="H23" s="62" t="n">
         <f aca="false">MAX(0,F23-G23)</f>
         <v>169672.89328623</v>
       </c>
-      <c r="I23" s="57" t="str">
+      <c r="I23" s="63" t="str">
         <f aca="false">IF(H23&lt;=23200,"10%",IF(H23&lt;=94300,"12%",IF(H23&lt;=201050,"22%",IF(H23&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
-      <c r="J23" s="49" t="n">
+      <c r="J23" s="62" t="n">
         <f aca="false">MAX(0,IF(H23&lt;=23200,H23*0.1,IF(H23&lt;=94300,23200*0.1+(H23-23200)*0.12,IF(H23&lt;=201050,23200*0.1+71100*0.12+(H23-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H23-201050)*0.24))))</f>
         <v>27434.0365229705</v>
       </c>
-      <c r="K23" s="58" t="n">
+      <c r="K23" s="64" t="n">
         <f aca="false">IFERROR(J23/MAX(1,H23),0)</f>
         <v>0.161687798160492</v>
       </c>
-      <c r="L23" s="57" t="str">
+      <c r="L23" s="63" t="str">
         <f aca="false">IF(F23&lt;=206000,"Base $0",IF(F23&lt;=258000,"T1 $594",IF(F23&lt;=322000,"T2 $1,488",IF(F23&lt;=386000,"T3 $2,382",IF(F23&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
-      <c r="M23" s="49" t="n">
+      <c r="M23" s="62" t="n">
         <f aca="false">ROUND(D23*0.0637,0)</f>
         <v>6969</v>
       </c>
-      <c r="N23" s="49" t="n">
+      <c r="N23" s="62" t="n">
         <f aca="false">J23+M23</f>
         <v>34403.0365229706</v>
       </c>
@@ -15164,7 +15163,7 @@
         <f aca="false">MAX(0,F24-G24)</f>
         <v>170388.465618385</v>
       </c>
-      <c r="I24" s="54" t="str">
+      <c r="I24" s="59" t="str">
         <f aca="false">IF(H24&lt;=23200,"10%",IF(H24&lt;=94300,"12%",IF(H24&lt;=201050,"22%",IF(H24&lt;=383900,"24%","32%+"))))</f>
         <v>22%</v>
       </c>
@@ -15172,11 +15171,11 @@
         <f aca="false">MAX(0,IF(H24&lt;=23200,H24*0.1,IF(H24&lt;=94300,23200*0.1+(H24-23200)*0.12,IF(H24&lt;=201050,23200*0.1+71100*0.12+(H24-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(H24-201050)*0.24))))</f>
         <v>27591.4624360448</v>
       </c>
-      <c r="K24" s="55" t="n">
+      <c r="K24" s="60" t="n">
         <f aca="false">IFERROR(J24/MAX(1,H24),0)</f>
         <v>0.161932689140124</v>
       </c>
-      <c r="L24" s="54" t="str">
+      <c r="L24" s="59" t="str">
         <f aca="false">IF(F24&lt;=206000,"Base $0",IF(F24&lt;=258000,"T1 $594",IF(F24&lt;=322000,"T2 $1,488",IF(F24&lt;=386000,"T3 $2,382",IF(F24&lt;=750000,"T4 $3,276","T5 $4,170")))))</f>
         <v>Base $0</v>
       </c>
@@ -15273,7 +15272,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="53" t="n">
+      <c r="A4" s="58" t="n">
         <v>65</v>
       </c>
       <c r="B4" s="45" t="n">
@@ -15306,40 +15305,40 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="56" t="n">
+      <c r="A5" s="61" t="n">
         <v>66</v>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!J4+'Withdrawal Plan'!K4+'Withdrawal Plan'!L4+'Withdrawal Plan'!M4</f>
         <v>173381</v>
       </c>
-      <c r="C5" s="49" t="n">
+      <c r="C5" s="62" t="n">
         <f aca="false">MAX(0,C4*(1+0.04)-B5)</f>
         <v>9324355.66823597</v>
       </c>
-      <c r="D5" s="49" t="n">
+      <c r="D5" s="62" t="n">
         <f aca="false">MAX(0,D4*(1+0.06)-B5)</f>
         <v>9696697.75128508</v>
       </c>
-      <c r="E5" s="49" t="n">
+      <c r="E5" s="62" t="n">
         <f aca="false">MAX(0,E4*(1+0.08)-B5)</f>
         <v>10076198.0721065</v>
       </c>
-      <c r="F5" s="49" t="n">
+      <c r="F5" s="62" t="n">
         <f aca="false">MAX(0,F4*(1+0.1)-B5)</f>
         <v>10462856.6307004</v>
       </c>
-      <c r="G5" s="49" t="n">
+      <c r="G5" s="62" t="n">
         <f aca="false">C5-E5</f>
         <v>-751842.403870571</v>
       </c>
-      <c r="H5" s="49" t="n">
+      <c r="H5" s="62" t="n">
         <f aca="false">F5-E5</f>
         <v>386658.55859383</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="53" t="n">
+      <c r="A6" s="58" t="n">
         <v>67</v>
       </c>
       <c r="B6" s="45" t="n">
@@ -15372,40 +15371,40 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="56" t="n">
+      <c r="A7" s="61" t="n">
         <v>68</v>
       </c>
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!J6+'Withdrawal Plan'!K6+'Withdrawal Plan'!L6+'Withdrawal Plan'!M6</f>
         <v>132092.6675</v>
       </c>
-      <c r="C7" s="49" t="n">
+      <c r="C7" s="62" t="n">
         <f aca="false">MAX(0,C6*(1+0.04)-B7)</f>
         <v>9814827.94726403</v>
       </c>
-      <c r="D7" s="49" t="n">
+      <c r="D7" s="62" t="n">
         <f aca="false">MAX(0,D6*(1+0.06)-B7)</f>
         <v>10622154.7868439</v>
       </c>
-      <c r="E7" s="49" t="n">
+      <c r="E7" s="62" t="n">
         <f aca="false">MAX(0,E6*(1+0.08)-B7)</f>
         <v>11477162.9618051</v>
       </c>
-      <c r="F7" s="49" t="n">
+      <c r="F7" s="62" t="n">
         <f aca="false">MAX(0,F6*(1+0.1)-B7)</f>
         <v>12381682.3906475</v>
       </c>
-      <c r="G7" s="49" t="n">
+      <c r="G7" s="62" t="n">
         <f aca="false">C7-E7</f>
         <v>-1662335.01454104</v>
       </c>
-      <c r="H7" s="49" t="n">
+      <c r="H7" s="62" t="n">
         <f aca="false">F7-E7</f>
         <v>904519.428842381</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="53" t="n">
+      <c r="A8" s="58" t="n">
         <v>69</v>
       </c>
       <c r="B8" s="45" t="n">
@@ -15438,40 +15437,40 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="56" t="n">
+      <c r="A9" s="61" t="n">
         <v>70</v>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!J8+'Withdrawal Plan'!K8+'Withdrawal Plan'!L8+'Withdrawal Plan'!M8</f>
         <v>130253.76753125</v>
       </c>
-      <c r="C9" s="49" t="n">
+      <c r="C9" s="62" t="n">
         <f aca="false">MAX(0,C8*(1+0.04)-B9)</f>
         <v>10349033.8385595</v>
       </c>
-      <c r="D9" s="49" t="n">
+      <c r="D9" s="62" t="n">
         <f aca="false">MAX(0,D8*(1+0.06)-B9)</f>
         <v>11665745.3896491</v>
       </c>
-      <c r="E9" s="49" t="n">
+      <c r="E9" s="62" t="n">
         <f aca="false">MAX(0,E8*(1+0.08)-B9)</f>
         <v>13115031.4901532</v>
       </c>
-      <c r="F9" s="49" t="n">
+      <c r="F9" s="62" t="n">
         <f aca="false">MAX(0,F8*(1+0.1)-B9)</f>
         <v>14707280.6445397</v>
       </c>
-      <c r="G9" s="49" t="n">
+      <c r="G9" s="62" t="n">
         <f aca="false">C9-E9</f>
         <v>-2765997.65159366</v>
       </c>
-      <c r="H9" s="49" t="n">
+      <c r="H9" s="62" t="n">
         <f aca="false">F9-E9</f>
         <v>1592249.15438649</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="53" t="n">
+      <c r="A10" s="58" t="n">
         <v>71</v>
       </c>
       <c r="B10" s="45" t="n">
@@ -15504,34 +15503,34 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="56" t="n">
+      <c r="A11" s="61" t="n">
         <v>72</v>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!J10+'Withdrawal Plan'!K10+'Withdrawal Plan'!L10+'Withdrawal Plan'!M10</f>
         <v>128335.438037961</v>
       </c>
-      <c r="C11" s="49" t="n">
+      <c r="C11" s="62" t="n">
         <f aca="false">MAX(0,C10*(1+0.04)-B11)</f>
         <v>10930702.6785879</v>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="62" t="n">
         <f aca="false">MAX(0,D10*(1+0.06)-B11)</f>
         <v>12842233.1047047</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="62" t="n">
         <f aca="false">MAX(0,E10*(1+0.08)-B11)</f>
         <v>15029388.2211028</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="62" t="n">
         <f aca="false">MAX(0,F10*(1+0.1)-B11)</f>
         <v>17525238.9769742</v>
       </c>
-      <c r="G11" s="49" t="n">
+      <c r="G11" s="62" t="n">
         <f aca="false">C11-E11</f>
         <v>-4098685.54251485</v>
       </c>
-      <c r="H11" s="49" t="n">
+      <c r="H11" s="62" t="n">
         <f aca="false">F11-E11</f>
         <v>2495850.7558714</v>
       </c>
@@ -15573,31 +15572,31 @@
       <c r="A13" s="44" t="n">
         <v>74</v>
       </c>
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!J12+'Withdrawal Plan'!K12+'Withdrawal Plan'!L12+'Withdrawal Plan'!M12</f>
         <v>126335.058541057</v>
       </c>
-      <c r="C13" s="49" t="n">
+      <c r="C13" s="62" t="n">
         <f aca="false">MAX(0,C12*(1+0.04)-B13)</f>
         <v>11563873.4638348</v>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="62" t="n">
         <f aca="false">MAX(0,D12*(1+0.06)-B13)</f>
         <v>14168211.6497591</v>
       </c>
-      <c r="E13" s="49" t="n">
+      <c r="E13" s="62" t="n">
         <f aca="false">MAX(0,E12*(1+0.08)-B13)</f>
         <v>17266410.0410459</v>
       </c>
-      <c r="F13" s="49" t="n">
+      <c r="F13" s="62" t="n">
         <f aca="false">MAX(0,F12*(1+0.1)-B13)</f>
         <v>20939123.8687291</v>
       </c>
-      <c r="G13" s="49" t="n">
+      <c r="G13" s="62" t="n">
         <f aca="false">C13-E13</f>
         <v>-5702536.57721109</v>
       </c>
-      <c r="H13" s="49" t="n">
+      <c r="H13" s="62" t="n">
         <f aca="false">F13-E13</f>
         <v>3672713.82768323</v>
       </c>
@@ -15639,31 +15638,31 @@
       <c r="A15" s="44" t="n">
         <v>76</v>
       </c>
-      <c r="B15" s="49" t="n">
+      <c r="B15" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!J14+'Withdrawal Plan'!K14+'Withdrawal Plan'!L14+'Withdrawal Plan'!M14</f>
         <v>124250.019465371</v>
       </c>
-      <c r="C15" s="49" t="n">
+      <c r="C15" s="62" t="n">
         <f aca="false">MAX(0,C14*(1+0.04)-B15)</f>
         <v>12252920.1039489</v>
       </c>
-      <c r="D15" s="49" t="n">
+      <c r="D15" s="62" t="n">
         <f aca="false">MAX(0,D14*(1+0.06)-B15)</f>
         <v>15662331.1094601</v>
       </c>
-      <c r="E15" s="49" t="n">
+      <c r="E15" s="62" t="n">
         <f aca="false">MAX(0,E14*(1+0.08)-B15)</f>
         <v>19879963.1059923</v>
       </c>
-      <c r="F15" s="49" t="n">
+      <c r="F15" s="62" t="n">
         <f aca="false">MAX(0,F14*(1+0.1)-B15)</f>
         <v>25074256.2496042</v>
       </c>
-      <c r="G15" s="49" t="n">
+      <c r="G15" s="62" t="n">
         <f aca="false">C15-E15</f>
         <v>-7627043.00204337</v>
       </c>
-      <c r="H15" s="49" t="n">
+      <c r="H15" s="62" t="n">
         <f aca="false">F15-E15</f>
         <v>5194293.1436119</v>
       </c>
@@ -15705,31 +15704,31 @@
       <c r="A17" s="44" t="n">
         <v>78</v>
       </c>
-      <c r="B17" s="49" t="n">
+      <c r="B17" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!J16+'Withdrawal Plan'!K16+'Withdrawal Plan'!L16+'Withdrawal Plan'!M16</f>
         <v>122077.737407134</v>
       </c>
-      <c r="C17" s="49" t="n">
+      <c r="C17" s="62" t="n">
         <f aca="false">MAX(0,C16*(1+0.04)-B17)</f>
         <v>13002578.7054862</v>
       </c>
-      <c r="D17" s="49" t="n">
+      <c r="D17" s="62" t="n">
         <f aca="false">MAX(0,D16*(1+0.06)-B17)</f>
         <v>17345552.0567687</v>
       </c>
-      <c r="E17" s="49" t="n">
+      <c r="E17" s="62" t="n">
         <f aca="false">MAX(0,E16*(1+0.08)-B17)</f>
         <v>22932882.290133</v>
       </c>
-      <c r="F17" s="49" t="n">
+      <c r="F17" s="62" t="n">
         <f aca="false">MAX(0,F16*(1+0.1)-B17)</f>
         <v>30082279.8864489</v>
       </c>
-      <c r="G17" s="49" t="n">
+      <c r="G17" s="62" t="n">
         <f aca="false">C17-E17</f>
         <v>-9930303.58464681</v>
       </c>
-      <c r="H17" s="49" t="n">
+      <c r="H17" s="62" t="n">
         <f aca="false">F17-E17</f>
         <v>7149397.59631594</v>
       </c>
@@ -15771,31 +15770,31 @@
       <c r="A19" s="44" t="n">
         <v>80</v>
       </c>
-      <c r="B19" s="49" t="n">
+      <c r="B19" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!J18+'Withdrawal Plan'!K18+'Withdrawal Plan'!L18+'Withdrawal Plan'!M18</f>
         <v>119815.672682723</v>
       </c>
-      <c r="C19" s="49" t="n">
+      <c r="C19" s="62" t="n">
         <f aca="false">MAX(0,C18*(1+0.04)-B19)</f>
         <v>13817977.0474267</v>
       </c>
-      <c r="D19" s="49" t="n">
+      <c r="D19" s="62" t="n">
         <f aca="false">MAX(0,D18*(1+0.06)-B19)</f>
         <v>19241431.0488707</v>
       </c>
-      <c r="E19" s="49" t="n">
+      <c r="E19" s="62" t="n">
         <f aca="false">MAX(0,E18*(1+0.08)-B19)</f>
         <v>26498463.4994091</v>
       </c>
-      <c r="F19" s="49" t="n">
+      <c r="F19" s="62" t="n">
         <f aca="false">MAX(0,F18*(1+0.1)-B19)</f>
         <v>36146689.0971138</v>
       </c>
-      <c r="G19" s="49" t="n">
+      <c r="G19" s="62" t="n">
         <f aca="false">C19-E19</f>
         <v>-12680486.4519825</v>
       </c>
-      <c r="H19" s="49" t="n">
+      <c r="H19" s="62" t="n">
         <f aca="false">F19-E19</f>
         <v>9648225.59770469</v>
       </c>
@@ -15837,31 +15836,31 @@
       <c r="A21" s="44" t="n">
         <v>82</v>
       </c>
-      <c r="B21" s="49" t="n">
+      <c r="B21" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!J20+'Withdrawal Plan'!K20+'Withdrawal Plan'!L20+'Withdrawal Plan'!M20</f>
         <v>117461.349428747</v>
       </c>
-      <c r="C21" s="49" t="n">
+      <c r="C21" s="62" t="n">
         <f aca="false">MAX(0,C20*(1+0.04)-B21)</f>
         <v>14704666.4222536</v>
       </c>
-      <c r="D21" s="49" t="n">
+      <c r="D21" s="62" t="n">
         <f aca="false">MAX(0,D20*(1+0.06)-B21)</f>
         <v>21376441.3703678</v>
       </c>
-      <c r="E21" s="49" t="n">
+      <c r="E21" s="62" t="n">
         <f aca="false">MAX(0,E20*(1+0.08)-B21)</f>
         <v>30662204.2656672</v>
       </c>
-      <c r="F21" s="49" t="n">
+      <c r="F21" s="62" t="n">
         <f aca="false">MAX(0,F20*(1+0.1)-B21)</f>
         <v>43489517.2435639</v>
       </c>
-      <c r="G21" s="49" t="n">
+      <c r="G21" s="62" t="n">
         <f aca="false">C21-E21</f>
         <v>-15957537.8434136</v>
       </c>
-      <c r="H21" s="49" t="n">
+      <c r="H21" s="62" t="n">
         <f aca="false">F21-E21</f>
         <v>12827312.9778966</v>
       </c>
@@ -15903,31 +15902,31 @@
       <c r="A23" s="44" t="n">
         <v>84</v>
       </c>
-      <c r="B23" s="49" t="n">
+      <c r="B23" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!J22+'Withdrawal Plan'!K22+'Withdrawal Plan'!L22+'Withdrawal Plan'!M22</f>
         <v>115012.378553101</v>
       </c>
-      <c r="C23" s="49" t="n">
+      <c r="C23" s="62" t="n">
         <f aca="false">MAX(0,C22*(1+0.04)-B23)</f>
         <v>15668656.0299681</v>
       </c>
-      <c r="D23" s="49" t="n">
+      <c r="D23" s="62" t="n">
         <f aca="false">MAX(0,D22*(1+0.06)-B23)</f>
         <v>23780333.3746002</v>
       </c>
-      <c r="E23" s="49" t="n">
+      <c r="E23" s="62" t="n">
         <f aca="false">MAX(0,E22*(1+0.08)-B23)</f>
         <v>35523833.9295256</v>
       </c>
-      <c r="F23" s="49" t="n">
+      <c r="F23" s="62" t="n">
         <f aca="false">MAX(0,F22*(1+0.1)-B23)</f>
         <v>52379429.76196</v>
       </c>
-      <c r="G23" s="49" t="n">
+      <c r="G23" s="62" t="n">
         <f aca="false">C23-E23</f>
         <v>-19855177.8995575</v>
       </c>
-      <c r="H23" s="49" t="n">
+      <c r="H23" s="62" t="n">
         <f aca="false">F23-E23</f>
         <v>16855595.8324344</v>
       </c>
@@ -15966,36 +15965,36 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="59" t="s">
+      <c r="A26" s="65" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="60" t="s">
+      <c r="C26" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="D26" s="60" t="s">
+      <c r="D26" s="66" t="s">
         <v>125</v>
       </c>
-      <c r="E26" s="60" t="s">
+      <c r="E26" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="F26" s="60" t="s">
+      <c r="F26" s="66" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C27" s="61" t="n">
+      <c r="C27" s="67" t="n">
         <f aca="false">C24</f>
         <v>16181650.587414</v>
       </c>
-      <c r="D27" s="61" t="n">
+      <c r="D27" s="67" t="n">
         <f aca="false">D24</f>
         <v>25093401.6933234</v>
       </c>
-      <c r="E27" s="61" t="n">
+      <c r="E27" s="67" t="n">
         <f aca="false">E24</f>
         <v>38251988.9601348</v>
       </c>
-      <c r="F27" s="61" t="n">
+      <c r="F27" s="67" t="n">
         <f aca="false">F24</f>
         <v>57503621.0544032</v>
       </c>
@@ -16081,24 +16080,24 @@
       <c r="L2" s="42"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="63" t="n">
+      <c r="C4" s="69" t="n">
         <v>75</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="D4" s="70" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="68" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="65" t="n">
+      <c r="C5" s="71" t="n">
         <v>0.2</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="70" t="s">
         <v>134</v>
       </c>
     </row>
@@ -16141,10 +16140,10 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="56" t="n">
+      <c r="A7" s="61" t="n">
         <v>65</v>
       </c>
-      <c r="B7" s="54" t="str">
+      <c r="B7" s="59" t="str">
         <f aca="false">IF(A7&gt;=C4,"Single","MFJ")</f>
         <v>MFJ</v>
       </c>
@@ -16190,59 +16189,59 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="53" t="n">
+      <c r="A8" s="58" t="n">
         <v>66</v>
       </c>
-      <c r="B8" s="57" t="str">
+      <c r="B8" s="63" t="str">
         <f aca="false">IF(A8&gt;=C4,"Single","MFJ")</f>
         <v>MFJ</v>
       </c>
-      <c r="C8" s="49" t="n">
+      <c r="C8" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H4</f>
         <v>0</v>
       </c>
-      <c r="D8" s="49" t="n">
+      <c r="D8" s="62" t="n">
         <f aca="false">IF(A8&gt;=C4,0,'Withdrawal Plan'!I4)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="49" t="n">
+      <c r="E8" s="62" t="n">
         <f aca="false">C8+D8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="49" t="n">
+      <c r="F8" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!B4*IF(A8&gt;=$C$4,1-$C$5,1)</f>
         <v>86520</v>
       </c>
-      <c r="G8" s="49" t="n">
+      <c r="G8" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!C4</f>
         <v>36000</v>
       </c>
-      <c r="H8" s="49" t="n">
+      <c r="H8" s="62" t="n">
         <f aca="false">F8+G8+'Withdrawal Plan'!D4+IF(A8&gt;=C4,0,'Withdrawal Plan'!E4)+'Withdrawal Plan'!F4</f>
         <v>150951</v>
       </c>
-      <c r="I8" s="49" t="n">
+      <c r="I8" s="62" t="n">
         <f aca="false">'Roth Conversion'!E4</f>
         <v>171050</v>
       </c>
-      <c r="J8" s="49" t="n">
+      <c r="J8" s="62" t="n">
         <f aca="false">IF(A8&gt;=$C$4,MAX(0,IF(MAX(0,I8+E8*Inputs!B43-Inputs!B42)&lt;=11600,MAX(0,I8+E8*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I8+E8*Inputs!B43-Inputs!B42)&lt;=47150,11600*0.1+(MAX(0,I8+E8*Inputs!B43-Inputs!B42)-11600)*0.12,IF(MAX(0,I8+E8*Inputs!B43-Inputs!B42)&lt;=100525,11600*0.1+35550*0.12+(MAX(0,I8+E8*Inputs!B43-Inputs!B42)-47150)*0.22,11600*0.1+35550*0.12+53375*0.22+(MAX(0,I8+E8*Inputs!B43-Inputs!B42)-100525)*0.24)))),MAX(0,IF(MAX(0,I8+E8*Inputs!B43-Inputs!B42)&lt;=23200,MAX(0,I8+E8*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I8+E8*Inputs!B43-Inputs!B42)&lt;=94300,23200*0.1+(MAX(0,I8+E8*Inputs!B43-Inputs!B42)-23200)*0.12,IF(MAX(0,I8+E8*Inputs!B43-Inputs!B42)&lt;=201050,23200*0.1+71100*0.12+(MAX(0,I8+E8*Inputs!B43-Inputs!B42)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(MAX(0,I8+E8*Inputs!B43-Inputs!B42)-201050)*0.24)))))</f>
         <v>21137</v>
       </c>
-      <c r="K8" s="49" t="n">
+      <c r="K8" s="62" t="n">
         <f aca="false">ROUND(I8*0.0637,0)</f>
         <v>10896</v>
       </c>
-      <c r="L8" s="49" t="n">
+      <c r="L8" s="62" t="n">
         <f aca="false">E8+I8-H8-J8-K8</f>
         <v>-11934</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="56" t="n">
+      <c r="A9" s="61" t="n">
         <v>67</v>
       </c>
-      <c r="B9" s="54" t="str">
+      <c r="B9" s="59" t="str">
         <f aca="false">IF(A9&gt;=C4,"Single","MFJ")</f>
         <v>MFJ</v>
       </c>
@@ -16288,59 +16287,59 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="53" t="n">
+      <c r="A10" s="58" t="n">
         <v>68</v>
       </c>
-      <c r="B10" s="57" t="str">
+      <c r="B10" s="63" t="str">
         <f aca="false">IF(A10&gt;=C4,"Single","MFJ")</f>
         <v>MFJ</v>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H6</f>
         <v>48855.6</v>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="62" t="n">
         <f aca="false">IF(A10&gt;=C4,0,'Withdrawal Plan'!I6)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="49" t="n">
+      <c r="E10" s="62" t="n">
         <f aca="false">C10+D10</f>
         <v>48855.6</v>
       </c>
-      <c r="F10" s="49" t="n">
+      <c r="F10" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!B6*IF(A10&gt;=$C$4,1-$C$5,1)</f>
         <v>91789.068</v>
       </c>
-      <c r="G10" s="49" t="n">
+      <c r="G10" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!C6</f>
         <v>36000</v>
       </c>
-      <c r="H10" s="49" t="n">
+      <c r="H10" s="62" t="n">
         <f aca="false">F10+G10+'Withdrawal Plan'!D6+IF(A10&gt;=C4,0,'Withdrawal Plan'!E6)+'Withdrawal Plan'!F6</f>
         <v>156458.9955</v>
       </c>
-      <c r="I10" s="49" t="n">
+      <c r="I10" s="62" t="n">
         <f aca="false">'Roth Conversion'!E6</f>
         <v>129522.74</v>
       </c>
-      <c r="J10" s="49" t="n">
+      <c r="J10" s="62" t="n">
         <f aca="false">IF(A10&gt;=$C$4,MAX(0,IF(MAX(0,I10+E10*Inputs!B43-Inputs!B42)&lt;=11600,MAX(0,I10+E10*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I10+E10*Inputs!B43-Inputs!B42)&lt;=47150,11600*0.1+(MAX(0,I10+E10*Inputs!B43-Inputs!B42)-11600)*0.12,IF(MAX(0,I10+E10*Inputs!B43-Inputs!B42)&lt;=100525,11600*0.1+35550*0.12+(MAX(0,I10+E10*Inputs!B43-Inputs!B42)-47150)*0.22,11600*0.1+35550*0.12+53375*0.22+(MAX(0,I10+E10*Inputs!B43-Inputs!B42)-100525)*0.24)))),MAX(0,IF(MAX(0,I10+E10*Inputs!B43-Inputs!B42)&lt;=23200,MAX(0,I10+E10*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I10+E10*Inputs!B43-Inputs!B42)&lt;=94300,23200*0.1+(MAX(0,I10+E10*Inputs!B43-Inputs!B42)-23200)*0.12,IF(MAX(0,I10+E10*Inputs!B43-Inputs!B42)&lt;=201050,23200*0.1+71100*0.12+(MAX(0,I10+E10*Inputs!B43-Inputs!B42)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(MAX(0,I10+E10*Inputs!B43-Inputs!B42)-201050)*0.24)))))</f>
         <v>21137</v>
       </c>
-      <c r="K10" s="49" t="n">
+      <c r="K10" s="62" t="n">
         <f aca="false">ROUND(I10*0.0637,0)</f>
         <v>8251</v>
       </c>
-      <c r="L10" s="49" t="n">
+      <c r="L10" s="62" t="n">
         <f aca="false">E10+I10-H10-J10-K10</f>
         <v>-7468.65549999999</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="56" t="n">
+      <c r="A11" s="61" t="n">
         <v>69</v>
       </c>
-      <c r="B11" s="54" t="str">
+      <c r="B11" s="59" t="str">
         <f aca="false">IF(A11&gt;=C4,"Single","MFJ")</f>
         <v>MFJ</v>
       </c>
@@ -16386,59 +16385,59 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="53" t="n">
+      <c r="A12" s="58" t="n">
         <v>70</v>
       </c>
-      <c r="B12" s="57" t="str">
+      <c r="B12" s="63" t="str">
         <f aca="false">IF(A12&gt;=C4,"Single","MFJ")</f>
         <v>MFJ</v>
       </c>
-      <c r="C12" s="49" t="n">
+      <c r="C12" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H8</f>
         <v>51328.91475</v>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D12" s="62" t="n">
         <f aca="false">IF(A12&gt;=C4,0,'Withdrawal Plan'!I8)</f>
         <v>23832</v>
       </c>
-      <c r="E12" s="49" t="n">
+      <c r="E12" s="62" t="n">
         <f aca="false">C12+D12</f>
         <v>75160.91475</v>
       </c>
-      <c r="F12" s="49" t="n">
+      <c r="F12" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!B8*IF(A12&gt;=$C$4,1-$C$5,1)</f>
         <v>97379.0222412</v>
       </c>
-      <c r="G12" s="49" t="n">
+      <c r="G12" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!C8</f>
         <v>36000</v>
       </c>
-      <c r="H12" s="49" t="n">
+      <c r="H12" s="62" t="n">
         <f aca="false">F12+G12+'Withdrawal Plan'!D8+IF(A12&gt;=C4,0,'Withdrawal Plan'!E8)+'Withdrawal Plan'!F8</f>
         <v>152712.36730995</v>
       </c>
-      <c r="I12" s="49" t="n">
+      <c r="I12" s="62" t="n">
         <f aca="false">'Roth Conversion'!E8</f>
         <v>127420.4224625</v>
       </c>
-      <c r="J12" s="49" t="n">
+      <c r="J12" s="62" t="n">
         <f aca="false">IF(A12&gt;=$C$4,MAX(0,IF(MAX(0,I12+E12*Inputs!B43-Inputs!B42)&lt;=11600,MAX(0,I12+E12*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I12+E12*Inputs!B43-Inputs!B42)&lt;=47150,11600*0.1+(MAX(0,I12+E12*Inputs!B43-Inputs!B42)-11600)*0.12,IF(MAX(0,I12+E12*Inputs!B43-Inputs!B42)&lt;=100525,11600*0.1+35550*0.12+(MAX(0,I12+E12*Inputs!B43-Inputs!B42)-47150)*0.22,11600*0.1+35550*0.12+53375*0.22+(MAX(0,I12+E12*Inputs!B43-Inputs!B42)-100525)*0.24)))),MAX(0,IF(MAX(0,I12+E12*Inputs!B43-Inputs!B42)&lt;=23200,MAX(0,I12+E12*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I12+E12*Inputs!B43-Inputs!B42)&lt;=94300,23200*0.1+(MAX(0,I12+E12*Inputs!B43-Inputs!B42)-23200)*0.12,IF(MAX(0,I12+E12*Inputs!B43-Inputs!B42)&lt;=201050,23200*0.1+71100*0.12+(MAX(0,I12+E12*Inputs!B43-Inputs!B42)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(MAX(0,I12+E12*Inputs!B43-Inputs!B42)-201050)*0.24)))))</f>
         <v>25593.584</v>
       </c>
-      <c r="K12" s="49" t="n">
+      <c r="K12" s="62" t="n">
         <f aca="false">ROUND(I12*0.0637,0)</f>
         <v>8117</v>
       </c>
-      <c r="L12" s="49" t="n">
+      <c r="L12" s="62" t="n">
         <f aca="false">E12+I12-H12-J12-K12</f>
         <v>16158.38590255</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="56" t="n">
+      <c r="A13" s="61" t="n">
         <v>71</v>
       </c>
-      <c r="B13" s="54" t="str">
+      <c r="B13" s="59" t="str">
         <f aca="false">IF(A13&gt;=C4,"Single","MFJ")</f>
         <v>MFJ</v>
       </c>
@@ -16484,50 +16483,50 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="53" t="n">
+      <c r="A14" s="58" t="n">
         <v>72</v>
       </c>
-      <c r="B14" s="57" t="str">
+      <c r="B14" s="63" t="str">
         <f aca="false">IF(A14&gt;=C4,"Single","MFJ")</f>
         <v>MFJ</v>
       </c>
-      <c r="C14" s="49" t="n">
+      <c r="C14" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H10</f>
         <v>53927.4410592187</v>
       </c>
-      <c r="D14" s="49" t="n">
+      <c r="D14" s="62" t="n">
         <f aca="false">IF(A14&gt;=C4,0,'Withdrawal Plan'!I10)</f>
         <v>25038.495</v>
       </c>
-      <c r="E14" s="49" t="n">
+      <c r="E14" s="62" t="n">
         <f aca="false">C14+D14</f>
         <v>78965.9360592187</v>
       </c>
-      <c r="F14" s="49" t="n">
+      <c r="F14" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!B10*IF(A14&gt;=$C$4,1-$C$5,1)</f>
         <v>103309.404695689</v>
       </c>
-      <c r="G14" s="49" t="n">
+      <c r="G14" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!C10</f>
         <v>36000</v>
       </c>
-      <c r="H14" s="49" t="n">
+      <c r="H14" s="62" t="n">
         <f aca="false">F14+G14+'Withdrawal Plan'!D10+IF(A14&gt;=C4,0,'Withdrawal Plan'!E10)+'Withdrawal Plan'!F10</f>
         <v>158933.167633986</v>
       </c>
-      <c r="I14" s="49" t="n">
+      <c r="I14" s="62" t="n">
         <f aca="false">'Roth Conversion'!E10</f>
         <v>125211.675099664</v>
       </c>
-      <c r="J14" s="49" t="n">
+      <c r="J14" s="62" t="n">
         <f aca="false">IF(A14&gt;=$C$4,MAX(0,IF(MAX(0,I14+E14*Inputs!B43-Inputs!B42)&lt;=11600,MAX(0,I14+E14*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I14+E14*Inputs!B43-Inputs!B42)&lt;=47150,11600*0.1+(MAX(0,I14+E14*Inputs!B43-Inputs!B42)-11600)*0.12,IF(MAX(0,I14+E14*Inputs!B43-Inputs!B42)&lt;=100525,11600*0.1+35550*0.12+(MAX(0,I14+E14*Inputs!B43-Inputs!B42)-47150)*0.22,11600*0.1+35550*0.12+53375*0.22+(MAX(0,I14+E14*Inputs!B43-Inputs!B42)-100525)*0.24)))),MAX(0,IF(MAX(0,I14+E14*Inputs!B43-Inputs!B42)&lt;=23200,MAX(0,I14+E14*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I14+E14*Inputs!B43-Inputs!B42)&lt;=94300,23200*0.1+(MAX(0,I14+E14*Inputs!B43-Inputs!B42)-23200)*0.12,IF(MAX(0,I14+E14*Inputs!B43-Inputs!B42)&lt;=201050,23200*0.1+71100*0.12+(MAX(0,I14+E14*Inputs!B43-Inputs!B42)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(MAX(0,I14+E14*Inputs!B43-Inputs!B42)-201050)*0.24)))))</f>
         <v>25819.198565</v>
       </c>
-      <c r="K14" s="49" t="n">
+      <c r="K14" s="62" t="n">
         <f aca="false">ROUND(I14*0.0637,0)</f>
         <v>7976</v>
       </c>
-      <c r="L14" s="49" t="n">
+      <c r="L14" s="62" t="n">
         <f aca="false">E14+I14-H14-J14-K14</f>
         <v>11449.2449598968</v>
       </c>
@@ -16536,7 +16535,7 @@
       <c r="A15" s="44" t="n">
         <v>73</v>
       </c>
-      <c r="B15" s="54" t="str">
+      <c r="B15" s="59" t="str">
         <f aca="false">IF(A15&gt;=C4,"Single","MFJ")</f>
         <v>MFJ</v>
       </c>
@@ -16585,47 +16584,47 @@
       <c r="A16" s="44" t="n">
         <v>74</v>
       </c>
-      <c r="B16" s="57" t="str">
+      <c r="B16" s="63" t="str">
         <f aca="false">IF(A16&gt;=C4,"Single","MFJ")</f>
         <v>MFJ</v>
       </c>
-      <c r="C16" s="49" t="n">
+      <c r="C16" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H12</f>
         <v>56657.5177628417</v>
       </c>
-      <c r="D16" s="49" t="n">
+      <c r="D16" s="62" t="n">
         <f aca="false">IF(A16&gt;=C4,0,'Withdrawal Plan'!I12)</f>
         <v>26306.068809375</v>
       </c>
-      <c r="E16" s="49" t="n">
+      <c r="E16" s="62" t="n">
         <f aca="false">C16+D16</f>
         <v>82963.5865722167</v>
       </c>
-      <c r="F16" s="49" t="n">
+      <c r="F16" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!B12*IF(A16&gt;=$C$4,1-$C$5,1)</f>
         <v>109600.947441657</v>
       </c>
-      <c r="G16" s="49" t="n">
+      <c r="G16" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!C12</f>
         <v>36000</v>
       </c>
-      <c r="H16" s="49" t="n">
+      <c r="H16" s="62" t="n">
         <f aca="false">F16+G16+'Withdrawal Plan'!D12+IF(A16&gt;=C4,0,'Withdrawal Plan'!E12)+'Withdrawal Plan'!F12</f>
         <v>165544.896081129</v>
       </c>
-      <c r="I16" s="49" t="n">
+      <c r="I16" s="62" t="n">
         <f aca="false">'Roth Conversion'!E12</f>
         <v>122891.109901585</v>
       </c>
-      <c r="J16" s="49" t="n">
+      <c r="J16" s="62" t="n">
         <f aca="false">IF(A16&gt;=$C$4,MAX(0,IF(MAX(0,I16+E16*Inputs!B43-Inputs!B42)&lt;=11600,MAX(0,I16+E16*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I16+E16*Inputs!B43-Inputs!B42)&lt;=47150,11600*0.1+(MAX(0,I16+E16*Inputs!B43-Inputs!B42)-11600)*0.12,IF(MAX(0,I16+E16*Inputs!B43-Inputs!B42)&lt;=100525,11600*0.1+35550*0.12+(MAX(0,I16+E16*Inputs!B43-Inputs!B42)-47150)*0.22,11600*0.1+35550*0.12+53375*0.22+(MAX(0,I16+E16*Inputs!B43-Inputs!B42)-100525)*0.24)))),MAX(0,IF(MAX(0,I16+E16*Inputs!B43-Inputs!B42)&lt;=23200,MAX(0,I16+E16*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I16+E16*Inputs!B43-Inputs!B42)&lt;=94300,23200*0.1+(MAX(0,I16+E16*Inputs!B43-Inputs!B42)-23200)*0.12,IF(MAX(0,I16+E16*Inputs!B43-Inputs!B42)&lt;=201050,23200*0.1+71100*0.12+(MAX(0,I16+E16*Inputs!B43-Inputs!B42)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(MAX(0,I16+E16*Inputs!B43-Inputs!B42)-201050)*0.24)))))</f>
         <v>26056.2348673531</v>
       </c>
-      <c r="K16" s="49" t="n">
+      <c r="K16" s="62" t="n">
         <f aca="false">ROUND(I16*0.0637,0)</f>
         <v>7828</v>
       </c>
-      <c r="L16" s="49" t="n">
+      <c r="L16" s="62" t="n">
         <f aca="false">E16+I16-H16-J16-K16</f>
         <v>6425.56552531924</v>
       </c>
@@ -16634,7 +16633,7 @@
       <c r="A17" s="44" t="n">
         <v>75</v>
       </c>
-      <c r="B17" s="54" t="str">
+      <c r="B17" s="59" t="str">
         <f aca="false">IF(A17&gt;=C4,"Single","MFJ")</f>
         <v>Single</v>
       </c>
@@ -16683,47 +16682,47 @@
       <c r="A18" s="44" t="n">
         <v>76</v>
       </c>
-      <c r="B18" s="57" t="str">
+      <c r="B18" s="63" t="str">
         <f aca="false">IF(A18&gt;=C4,"Single","MFJ")</f>
         <v>Single</v>
       </c>
-      <c r="C18" s="49" t="n">
+      <c r="C18" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H14</f>
         <v>59525.8045995855</v>
       </c>
-      <c r="D18" s="49" t="n">
+      <c r="D18" s="62" t="n">
         <f aca="false">IF(A18&gt;=C4,0,'Withdrawal Plan'!I14)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="49" t="n">
+      <c r="E18" s="62" t="n">
         <f aca="false">C18+D18</f>
         <v>59525.8045995855</v>
       </c>
-      <c r="F18" s="49" t="n">
+      <c r="F18" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!B14*IF(A18&gt;=$C$4,1-$C$5,1)</f>
         <v>93020.5161126828</v>
       </c>
-      <c r="G18" s="49" t="n">
+      <c r="G18" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!C14</f>
         <v>36000</v>
       </c>
-      <c r="H18" s="49" t="n">
+      <c r="H18" s="62" t="n">
         <f aca="false">F18+G18+'Withdrawal Plan'!D14+IF(A18&gt;=C4,0,'Withdrawal Plan'!E14)+'Withdrawal Plan'!F14</f>
         <v>149317.469487701</v>
       </c>
-      <c r="I18" s="49" t="n">
+      <c r="I18" s="62" t="n">
         <f aca="false">'Roth Conversion'!E14</f>
         <v>120453.066090352</v>
       </c>
-      <c r="J18" s="49" t="n">
+      <c r="J18" s="62" t="n">
         <f aca="false">IF(A18&gt;=$C$4,MAX(0,IF(MAX(0,I18+E18*Inputs!B43-Inputs!B42)&lt;=11600,MAX(0,I18+E18*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I18+E18*Inputs!B43-Inputs!B42)&lt;=47150,11600*0.1+(MAX(0,I18+E18*Inputs!B43-Inputs!B42)-11600)*0.12,IF(MAX(0,I18+E18*Inputs!B43-Inputs!B42)&lt;=100525,11600*0.1+35550*0.12+(MAX(0,I18+E18*Inputs!B43-Inputs!B42)-47150)*0.22,11600*0.1+35550*0.12+53375*0.22+(MAX(0,I18+E18*Inputs!B43-Inputs!B42)-100525)*0.24)))),MAX(0,IF(MAX(0,I18+E18*Inputs!B43-Inputs!B42)&lt;=23200,MAX(0,I18+E18*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I18+E18*Inputs!B43-Inputs!B42)&lt;=94300,23200*0.1+(MAX(0,I18+E18*Inputs!B43-Inputs!B42)-23200)*0.12,IF(MAX(0,I18+E18*Inputs!B43-Inputs!B42)&lt;=201050,23200*0.1+71100*0.12+(MAX(0,I18+E18*Inputs!B43-Inputs!B42)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(MAX(0,I18+E18*Inputs!B43-Inputs!B42)-201050)*0.24)))))</f>
         <v>26894.5</v>
       </c>
-      <c r="K18" s="49" t="n">
+      <c r="K18" s="62" t="n">
         <f aca="false">ROUND(I18*0.0637,0)</f>
         <v>7673</v>
       </c>
-      <c r="L18" s="49" t="n">
+      <c r="L18" s="62" t="n">
         <f aca="false">E18+I18-H18-J18-K18</f>
         <v>-3906.09879776317</v>
       </c>
@@ -16732,7 +16731,7 @@
       <c r="A19" s="44" t="n">
         <v>77</v>
       </c>
-      <c r="B19" s="54" t="str">
+      <c r="B19" s="59" t="str">
         <f aca="false">IF(A19&gt;=C4,"Single","MFJ")</f>
         <v>Single</v>
       </c>
@@ -16781,47 +16780,47 @@
       <c r="A20" s="44" t="n">
         <v>78</v>
       </c>
-      <c r="B20" s="57" t="str">
+      <c r="B20" s="63" t="str">
         <f aca="false">IF(A20&gt;=C4,"Single","MFJ")</f>
         <v>Single</v>
       </c>
-      <c r="C20" s="49" t="n">
+      <c r="C20" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H16</f>
         <v>62539.2984574395</v>
       </c>
-      <c r="D20" s="49" t="n">
+      <c r="D20" s="62" t="n">
         <f aca="false">IF(A20&gt;=C4,0,'Withdrawal Plan'!I16)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="49" t="n">
+      <c r="E20" s="62" t="n">
         <f aca="false">C20+D20</f>
         <v>62539.2984574395</v>
       </c>
-      <c r="F20" s="49" t="n">
+      <c r="F20" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!B16*IF(A20&gt;=$C$4,1-$C$5,1)</f>
         <v>98685.4655439452</v>
       </c>
-      <c r="G20" s="49" t="n">
+      <c r="G20" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!C16</f>
         <v>0</v>
       </c>
-      <c r="H20" s="49" t="n">
+      <c r="H20" s="62" t="n">
         <f aca="false">F20+G20+'Withdrawal Plan'!D16+IF(A20&gt;=C4,0,'Withdrawal Plan'!E16)+'Withdrawal Plan'!F16</f>
         <v>119371.606639903</v>
       </c>
-      <c r="I20" s="49" t="n">
+      <c r="I20" s="62" t="n">
         <f aca="false">'Roth Conversion'!E16</f>
         <v>117891.596311176</v>
       </c>
-      <c r="J20" s="49" t="n">
+      <c r="J20" s="62" t="n">
         <f aca="false">IF(A20&gt;=$C$4,MAX(0,IF(MAX(0,I20+E20*Inputs!B43-Inputs!B42)&lt;=11600,MAX(0,I20+E20*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I20+E20*Inputs!B43-Inputs!B42)&lt;=47150,11600*0.1+(MAX(0,I20+E20*Inputs!B43-Inputs!B42)-11600)*0.12,IF(MAX(0,I20+E20*Inputs!B43-Inputs!B42)&lt;=100525,11600*0.1+35550*0.12+(MAX(0,I20+E20*Inputs!B43-Inputs!B42)-47150)*0.22,11600*0.1+35550*0.12+53375*0.22+(MAX(0,I20+E20*Inputs!B43-Inputs!B42)-100525)*0.24)))),MAX(0,IF(MAX(0,I20+E20*Inputs!B43-Inputs!B42)&lt;=23200,MAX(0,I20+E20*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I20+E20*Inputs!B43-Inputs!B42)&lt;=94300,23200*0.1+(MAX(0,I20+E20*Inputs!B43-Inputs!B42)-23200)*0.12,IF(MAX(0,I20+E20*Inputs!B43-Inputs!B42)&lt;=201050,23200*0.1+71100*0.12+(MAX(0,I20+E20*Inputs!B43-Inputs!B42)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(MAX(0,I20+E20*Inputs!B43-Inputs!B42)-201050)*0.24)))))</f>
         <v>26894.5</v>
       </c>
-      <c r="K20" s="49" t="n">
+      <c r="K20" s="62" t="n">
         <f aca="false">ROUND(I20*0.0637,0)</f>
         <v>7510</v>
       </c>
-      <c r="L20" s="49" t="n">
+      <c r="L20" s="62" t="n">
         <f aca="false">E20+I20-H20-J20-K20</f>
         <v>26654.7881287132</v>
       </c>
@@ -16830,7 +16829,7 @@
       <c r="A21" s="44" t="n">
         <v>79</v>
       </c>
-      <c r="B21" s="54" t="str">
+      <c r="B21" s="59" t="str">
         <f aca="false">IF(A21&gt;=C4,"Single","MFJ")</f>
         <v>Single</v>
       </c>
@@ -16879,47 +16878,47 @@
       <c r="A22" s="44" t="n">
         <v>80</v>
       </c>
-      <c r="B22" s="57" t="str">
+      <c r="B22" s="63" t="str">
         <f aca="false">IF(A22&gt;=C4,"Single","MFJ")</f>
         <v>Single</v>
       </c>
-      <c r="C22" s="49" t="n">
+      <c r="C22" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H18</f>
         <v>65705.3504418474</v>
       </c>
-      <c r="D22" s="49" t="n">
+      <c r="D22" s="62" t="n">
         <f aca="false">IF(A22&gt;=C4,0,'Withdrawal Plan'!I18)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="49" t="n">
+      <c r="E22" s="62" t="n">
         <f aca="false">C22+D22</f>
         <v>65705.3504418474</v>
       </c>
-      <c r="F22" s="49" t="n">
+      <c r="F22" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!B18*IF(A22&gt;=$C$4,1-$C$5,1)</f>
         <v>104695.410395571</v>
       </c>
-      <c r="G22" s="49" t="n">
+      <c r="G22" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!C18</f>
         <v>0</v>
       </c>
-      <c r="H22" s="49" t="n">
+      <c r="H22" s="62" t="n">
         <f aca="false">F22+G22+'Withdrawal Plan'!D18+IF(A22&gt;=C4,0,'Withdrawal Plan'!E18)+'Withdrawal Plan'!F18</f>
         <v>125810.630953865</v>
       </c>
-      <c r="I22" s="49" t="n">
+      <c r="I22" s="62" t="n">
         <f aca="false">'Roth Conversion'!E18</f>
         <v>115200.45212443</v>
       </c>
-      <c r="J22" s="49" t="n">
+      <c r="J22" s="62" t="n">
         <f aca="false">IF(A22&gt;=$C$4,MAX(0,IF(MAX(0,I22+E22*Inputs!B43-Inputs!B42)&lt;=11600,MAX(0,I22+E22*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I22+E22*Inputs!B43-Inputs!B42)&lt;=47150,11600*0.1+(MAX(0,I22+E22*Inputs!B43-Inputs!B42)-11600)*0.12,IF(MAX(0,I22+E22*Inputs!B43-Inputs!B42)&lt;=100525,11600*0.1+35550*0.12+(MAX(0,I22+E22*Inputs!B43-Inputs!B42)-47150)*0.22,11600*0.1+35550*0.12+53375*0.22+(MAX(0,I22+E22*Inputs!B43-Inputs!B42)-100525)*0.24)))),MAX(0,IF(MAX(0,I22+E22*Inputs!B43-Inputs!B42)&lt;=23200,MAX(0,I22+E22*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I22+E22*Inputs!B43-Inputs!B42)&lt;=94300,23200*0.1+(MAX(0,I22+E22*Inputs!B43-Inputs!B42)-23200)*0.12,IF(MAX(0,I22+E22*Inputs!B43-Inputs!B42)&lt;=201050,23200*0.1+71100*0.12+(MAX(0,I22+E22*Inputs!B43-Inputs!B42)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(MAX(0,I22+E22*Inputs!B43-Inputs!B42)-201050)*0.24)))))</f>
         <v>26894.5</v>
       </c>
-      <c r="K22" s="49" t="n">
+      <c r="K22" s="62" t="n">
         <f aca="false">ROUND(I22*0.0637,0)</f>
         <v>7338</v>
       </c>
-      <c r="L22" s="49" t="n">
+      <c r="L22" s="62" t="n">
         <f aca="false">E22+I22-H22-J22-K22</f>
         <v>20862.6716124125</v>
       </c>
@@ -16928,7 +16927,7 @@
       <c r="A23" s="44" t="n">
         <v>81</v>
       </c>
-      <c r="B23" s="54" t="str">
+      <c r="B23" s="59" t="str">
         <f aca="false">IF(A23&gt;=C4,"Single","MFJ")</f>
         <v>Single</v>
       </c>
@@ -16977,47 +16976,47 @@
       <c r="A24" s="44" t="n">
         <v>82</v>
       </c>
-      <c r="B24" s="57" t="str">
+      <c r="B24" s="63" t="str">
         <f aca="false">IF(A24&gt;=C4,"Single","MFJ")</f>
         <v>Single</v>
       </c>
-      <c r="C24" s="49" t="n">
+      <c r="C24" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H20</f>
         <v>69031.6838079659</v>
       </c>
-      <c r="D24" s="49" t="n">
+      <c r="D24" s="62" t="n">
         <f aca="false">IF(A24&gt;=C4,0,'Withdrawal Plan'!I20)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="49" t="n">
+      <c r="E24" s="62" t="n">
         <f aca="false">C24+D24</f>
         <v>69031.6838079659</v>
       </c>
-      <c r="F24" s="49" t="n">
+      <c r="F24" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!B20*IF(A24&gt;=$C$4,1-$C$5,1)</f>
         <v>111071.360888662</v>
       </c>
-      <c r="G24" s="49" t="n">
+      <c r="G24" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!C20</f>
         <v>0</v>
       </c>
-      <c r="H24" s="49" t="n">
+      <c r="H24" s="62" t="n">
         <f aca="false">F24+G24+'Withdrawal Plan'!D20+IF(A24&gt;=C4,0,'Withdrawal Plan'!E20)+'Withdrawal Plan'!F20</f>
         <v>132659.64155418</v>
       </c>
-      <c r="I24" s="49" t="n">
+      <c r="I24" s="62" t="n">
         <f aca="false">'Roth Conversion'!E20</f>
         <v>112373.068763229</v>
       </c>
-      <c r="J24" s="49" t="n">
+      <c r="J24" s="62" t="n">
         <f aca="false">IF(A24&gt;=$C$4,MAX(0,IF(MAX(0,I24+E24*Inputs!B43-Inputs!B42)&lt;=11600,MAX(0,I24+E24*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I24+E24*Inputs!B43-Inputs!B42)&lt;=47150,11600*0.1+(MAX(0,I24+E24*Inputs!B43-Inputs!B42)-11600)*0.12,IF(MAX(0,I24+E24*Inputs!B43-Inputs!B42)&lt;=100525,11600*0.1+35550*0.12+(MAX(0,I24+E24*Inputs!B43-Inputs!B42)-47150)*0.22,11600*0.1+35550*0.12+53375*0.22+(MAX(0,I24+E24*Inputs!B43-Inputs!B42)-100525)*0.24)))),MAX(0,IF(MAX(0,I24+E24*Inputs!B43-Inputs!B42)&lt;=23200,MAX(0,I24+E24*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I24+E24*Inputs!B43-Inputs!B42)&lt;=94300,23200*0.1+(MAX(0,I24+E24*Inputs!B43-Inputs!B42)-23200)*0.12,IF(MAX(0,I24+E24*Inputs!B43-Inputs!B42)&lt;=201050,23200*0.1+71100*0.12+(MAX(0,I24+E24*Inputs!B43-Inputs!B42)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(MAX(0,I24+E24*Inputs!B43-Inputs!B42)-201050)*0.24)))))</f>
         <v>26894.5</v>
       </c>
-      <c r="K24" s="49" t="n">
+      <c r="K24" s="62" t="n">
         <f aca="false">ROUND(I24*0.0637,0)</f>
         <v>7158</v>
       </c>
-      <c r="L24" s="49" t="n">
+      <c r="L24" s="62" t="n">
         <f aca="false">E24+I24-H24-J24-K24</f>
         <v>14692.6110170149</v>
       </c>
@@ -17026,7 +17025,7 @@
       <c r="A25" s="44" t="n">
         <v>83</v>
       </c>
-      <c r="B25" s="54" t="str">
+      <c r="B25" s="59" t="str">
         <f aca="false">IF(A25&gt;=C4,"Single","MFJ")</f>
         <v>Single</v>
       </c>
@@ -17075,47 +17074,47 @@
       <c r="A26" s="44" t="n">
         <v>84</v>
       </c>
-      <c r="B26" s="57" t="str">
+      <c r="B26" s="63" t="str">
         <f aca="false">IF(A26&gt;=C4,"Single","MFJ")</f>
         <v>Single</v>
       </c>
-      <c r="C26" s="49" t="n">
+      <c r="C26" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!H22</f>
         <v>72526.4128007442</v>
       </c>
-      <c r="D26" s="49" t="n">
+      <c r="D26" s="62" t="n">
         <f aca="false">IF(A26&gt;=C4,0,'Withdrawal Plan'!I22)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="49" t="n">
+      <c r="E26" s="62" t="n">
         <f aca="false">C26+D26</f>
         <v>72526.4128007442</v>
       </c>
-      <c r="F26" s="49" t="n">
+      <c r="F26" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!B22*IF(A26&gt;=$C$4,1-$C$5,1)</f>
         <v>117835.606766781</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="62" t="n">
         <f aca="false">'Withdrawal Plan'!C22</f>
         <v>0</v>
       </c>
-      <c r="H26" s="49" t="n">
+      <c r="H26" s="62" t="n">
         <f aca="false">F26+G26+'Withdrawal Plan'!D22+IF(A26&gt;=C4,0,'Withdrawal Plan'!E22)+'Withdrawal Plan'!F22</f>
         <v>139945.436200515</v>
       </c>
-      <c r="I26" s="49" t="n">
+      <c r="I26" s="62" t="n">
         <f aca="false">'Roth Conversion'!E22</f>
         <v>109402.549119367</v>
       </c>
-      <c r="J26" s="49" t="n">
+      <c r="J26" s="62" t="n">
         <f aca="false">IF(A26&gt;=$C$4,MAX(0,IF(MAX(0,I26+E26*Inputs!B43-Inputs!B42)&lt;=11600,MAX(0,I26+E26*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I26+E26*Inputs!B43-Inputs!B42)&lt;=47150,11600*0.1+(MAX(0,I26+E26*Inputs!B43-Inputs!B42)-11600)*0.12,IF(MAX(0,I26+E26*Inputs!B43-Inputs!B42)&lt;=100525,11600*0.1+35550*0.12+(MAX(0,I26+E26*Inputs!B43-Inputs!B42)-47150)*0.22,11600*0.1+35550*0.12+53375*0.22+(MAX(0,I26+E26*Inputs!B43-Inputs!B42)-100525)*0.24)))),MAX(0,IF(MAX(0,I26+E26*Inputs!B43-Inputs!B42)&lt;=23200,MAX(0,I26+E26*Inputs!B43-Inputs!B42)*0.1,IF(MAX(0,I26+E26*Inputs!B43-Inputs!B42)&lt;=94300,23200*0.1+(MAX(0,I26+E26*Inputs!B43-Inputs!B42)-23200)*0.12,IF(MAX(0,I26+E26*Inputs!B43-Inputs!B42)&lt;=201050,23200*0.1+71100*0.12+(MAX(0,I26+E26*Inputs!B43-Inputs!B42)-94300)*0.22,23200*0.1+71100*0.12+106750*0.22+(MAX(0,I26+E26*Inputs!B43-Inputs!B42)-201050)*0.24)))))</f>
         <v>26894.5</v>
       </c>
-      <c r="K26" s="49" t="n">
+      <c r="K26" s="62" t="n">
         <f aca="false">ROUND(I26*0.0637,0)</f>
         <v>6969</v>
       </c>
-      <c r="L26" s="49" t="n">
+      <c r="L26" s="62" t="n">
         <f aca="false">E26+I26-H26-J26-K26</f>
         <v>8120.02571959645</v>
       </c>
@@ -17124,7 +17123,7 @@
       <c r="A27" s="44" t="n">
         <v>85</v>
       </c>
-      <c r="B27" s="54" t="str">
+      <c r="B27" s="59" t="str">
         <f aca="false">IF(A27&gt;=C4,"Single","MFJ")</f>
         <v>Single</v>
       </c>
@@ -17244,334 +17243,334 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="66" t="n">
+      <c r="A3" s="72" t="n">
         <v>56</v>
       </c>
-      <c r="B3" s="67" t="n">
+      <c r="B3" s="73" t="n">
         <f aca="false">Inputs!B9+Inputs!B11*(1+Inputs!B12/100)</f>
         <v>3037518.75</v>
       </c>
-      <c r="C3" s="67" t="n">
+      <c r="C3" s="73" t="n">
         <f aca="false">(Inputs!B10+Inputs!B13)*(1+Inputs!B19)</f>
         <v>810000</v>
       </c>
-      <c r="D3" s="67" t="n">
+      <c r="D3" s="73" t="n">
         <f aca="false">Inputs!E11*(1+Inputs!B19)</f>
         <v>10800</v>
       </c>
-      <c r="E3" s="67" t="n">
+      <c r="E3" s="73" t="n">
         <f aca="false">Inputs!E10*(1+Inputs!B19)</f>
         <v>54000</v>
       </c>
-      <c r="F3" s="67" t="n">
+      <c r="F3" s="73" t="n">
         <f aca="false">(Inputs!B14+Inputs!B15)*(1+Inputs!B19)</f>
         <v>116640</v>
       </c>
-      <c r="G3" s="67" t="n">
+      <c r="G3" s="73" t="n">
         <f aca="false">Inputs!B16*(1+Inputs!B19)</f>
         <v>540000</v>
       </c>
-      <c r="H3" s="68" t="n">
+      <c r="H3" s="74" t="n">
         <f aca="false">SUM(B3:G3)</f>
         <v>4568958.75</v>
       </c>
-      <c r="I3" s="69" t="n">
+      <c r="I3" s="75" t="n">
         <f aca="false">H3+Inputs!B36*POWER(1+Inputs!B52,VALUE(A3)-Inputs!B4)</f>
         <v>5368958.75</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="66" t="n">
+      <c r="A4" s="72" t="n">
         <v>57</v>
       </c>
-      <c r="B4" s="67" t="n">
+      <c r="B4" s="73" t="n">
         <f aca="false">B3*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
         <v>3318039</v>
       </c>
-      <c r="C4" s="67" t="n">
+      <c r="C4" s="73" t="n">
         <f aca="false">C3*(1+Inputs!B19)</f>
         <v>874800</v>
       </c>
-      <c r="D4" s="67" t="n">
+      <c r="D4" s="73" t="n">
         <f aca="false">D3*(1+Inputs!B19)</f>
         <v>11664</v>
       </c>
-      <c r="E4" s="67" t="n">
+      <c r="E4" s="73" t="n">
         <f aca="false">E3*(1+Inputs!B19)</f>
         <v>58320</v>
       </c>
-      <c r="F4" s="67" t="n">
+      <c r="F4" s="73" t="n">
         <f aca="false">(F3+Inputs!B15)*(1+Inputs!B19)</f>
         <v>134611.2</v>
       </c>
-      <c r="G4" s="67" t="n">
+      <c r="G4" s="73" t="n">
         <f aca="false">G3*(1+Inputs!B19)</f>
         <v>583200</v>
       </c>
-      <c r="H4" s="68" t="n">
+      <c r="H4" s="74" t="n">
         <f aca="false">SUM(B4:G4)</f>
         <v>4980634.2</v>
       </c>
-      <c r="I4" s="69" t="n">
+      <c r="I4" s="75" t="n">
         <f aca="false">H4+Inputs!B36*POWER(1+Inputs!B52,VALUE(A4)-Inputs!B4)</f>
         <v>5816634.2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="66" t="n">
+      <c r="A5" s="72" t="n">
         <v>58</v>
       </c>
-      <c r="B5" s="67" t="n">
+      <c r="B5" s="73" t="n">
         <f aca="false">B4*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
         <v>3621000.87</v>
       </c>
-      <c r="C5" s="67" t="n">
+      <c r="C5" s="73" t="n">
         <f aca="false">C4*(1+Inputs!B19)</f>
         <v>944784</v>
       </c>
-      <c r="D5" s="67" t="n">
+      <c r="D5" s="73" t="n">
         <f aca="false">D4*(1+Inputs!B19)</f>
         <v>12597.12</v>
       </c>
-      <c r="E5" s="67" t="n">
+      <c r="E5" s="73" t="n">
         <f aca="false">E4*(1+Inputs!B19)</f>
         <v>62985.6</v>
       </c>
-      <c r="F5" s="67" t="n">
+      <c r="F5" s="73" t="n">
         <f aca="false">(F4+Inputs!B15)*(1+Inputs!B19)</f>
         <v>154020.096</v>
       </c>
-      <c r="G5" s="67" t="n">
+      <c r="G5" s="73" t="n">
         <f aca="false">G4*(1+Inputs!B19)</f>
         <v>629856</v>
       </c>
-      <c r="H5" s="68" t="n">
+      <c r="H5" s="74" t="n">
         <f aca="false">SUM(B5:G5)</f>
         <v>5425243.686</v>
       </c>
-      <c r="I5" s="69" t="n">
+      <c r="I5" s="75" t="n">
         <f aca="false">H5+Inputs!B36*POWER(1+Inputs!B52,VALUE(A5)-Inputs!B4)</f>
         <v>6298863.686</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="66" t="n">
+      <c r="A6" s="72" t="n">
         <v>59</v>
       </c>
-      <c r="B6" s="67" t="n">
+      <c r="B6" s="73" t="n">
         <f aca="false">B5*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
         <v>3948199.6896</v>
       </c>
-      <c r="C6" s="67" t="n">
+      <c r="C6" s="73" t="n">
         <f aca="false">C5*(1+Inputs!B19)</f>
         <v>1020366.72</v>
       </c>
-      <c r="D6" s="67" t="n">
+      <c r="D6" s="73" t="n">
         <f aca="false">D5*(1+Inputs!B19)</f>
         <v>13604.8896</v>
       </c>
-      <c r="E6" s="67" t="n">
+      <c r="E6" s="73" t="n">
         <f aca="false">E5*(1+Inputs!B19)</f>
         <v>68024.448</v>
       </c>
-      <c r="F6" s="67" t="n">
+      <c r="F6" s="73" t="n">
         <f aca="false">(F5+Inputs!B15)*(1+Inputs!B19)</f>
         <v>174981.70368</v>
       </c>
-      <c r="G6" s="67" t="n">
+      <c r="G6" s="73" t="n">
         <f aca="false">G5*(1+Inputs!B19)</f>
         <v>680244.48</v>
       </c>
-      <c r="H6" s="68" t="n">
+      <c r="H6" s="74" t="n">
         <f aca="false">SUM(B6:G6)</f>
         <v>5905421.93088</v>
       </c>
-      <c r="I6" s="69" t="n">
+      <c r="I6" s="75" t="n">
         <f aca="false">H6+Inputs!B36*POWER(1+Inputs!B52,VALUE(A6)-Inputs!B4)</f>
         <v>6818354.83088</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="66" t="n">
+      <c r="A7" s="72" t="n">
         <v>60</v>
       </c>
-      <c r="B7" s="67" t="n">
+      <c r="B7" s="73" t="n">
         <f aca="false">B6*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
         <v>4301574.414768</v>
       </c>
-      <c r="C7" s="67" t="n">
+      <c r="C7" s="73" t="n">
         <f aca="false">C6*(1+Inputs!B19)</f>
         <v>1101996.0576</v>
       </c>
-      <c r="D7" s="67" t="n">
+      <c r="D7" s="73" t="n">
         <f aca="false">D6*(1+Inputs!B19)</f>
         <v>14693.280768</v>
       </c>
-      <c r="E7" s="67" t="n">
+      <c r="E7" s="73" t="n">
         <f aca="false">E6*(1+Inputs!B19)</f>
         <v>73466.40384</v>
       </c>
-      <c r="F7" s="67" t="n">
+      <c r="F7" s="73" t="n">
         <f aca="false">(F6+Inputs!B15)*(1+Inputs!B19)</f>
         <v>197620.2399744</v>
       </c>
-      <c r="G7" s="67" t="n">
+      <c r="G7" s="73" t="n">
         <f aca="false">G6*(1+Inputs!B19)</f>
         <v>734664.0384</v>
       </c>
-      <c r="H7" s="68" t="n">
+      <c r="H7" s="74" t="n">
         <f aca="false">SUM(B7:G7)</f>
         <v>6424014.4353504</v>
       </c>
-      <c r="I7" s="69" t="n">
+      <c r="I7" s="75" t="n">
         <f aca="false">H7+Inputs!B36*POWER(1+Inputs!B52,VALUE(A7)-Inputs!B4)</f>
         <v>7378029.3158504</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="66" t="n">
+      <c r="A8" s="72" t="n">
         <v>61</v>
       </c>
-      <c r="B8" s="67" t="n">
+      <c r="B8" s="73" t="n">
         <f aca="false">B7*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
         <v>4683219.11794944</v>
       </c>
-      <c r="C8" s="67" t="n">
+      <c r="C8" s="73" t="n">
         <f aca="false">C7*(1+Inputs!B19)</f>
         <v>1190155.742208</v>
       </c>
-      <c r="D8" s="67" t="n">
+      <c r="D8" s="73" t="n">
         <f aca="false">D7*(1+Inputs!B19)</f>
         <v>15868.74322944</v>
       </c>
-      <c r="E8" s="67" t="n">
+      <c r="E8" s="73" t="n">
         <f aca="false">E7*(1+Inputs!B19)</f>
         <v>79343.7161472</v>
       </c>
-      <c r="F8" s="67" t="n">
+      <c r="F8" s="73" t="n">
         <f aca="false">(F7+Inputs!B15)*(1+Inputs!B19)</f>
         <v>222069.859172352</v>
       </c>
-      <c r="G8" s="67" t="n">
+      <c r="G8" s="73" t="n">
         <f aca="false">G7*(1+Inputs!B19)</f>
         <v>793437.161472</v>
       </c>
-      <c r="H8" s="68" t="n">
+      <c r="H8" s="74" t="n">
         <f aca="false">SUM(B8:G8)</f>
         <v>6984094.34017843</v>
       </c>
-      <c r="I8" s="69" t="n">
+      <c r="I8" s="75" t="n">
         <f aca="false">H8+Inputs!B36*POWER(1+Inputs!B52,VALUE(A8)-Inputs!B4)</f>
         <v>7981039.89030093</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="66" t="n">
+      <c r="A9" s="72" t="n">
         <v>62</v>
       </c>
-      <c r="B9" s="67" t="n">
+      <c r="B9" s="73" t="n">
         <f aca="false">B8*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
         <v>5095395.3973854</v>
       </c>
-      <c r="C9" s="67" t="n">
+      <c r="C9" s="73" t="n">
         <f aca="false">C8*(1+Inputs!B19)</f>
         <v>1285368.20158464</v>
       </c>
-      <c r="D9" s="67" t="n">
+      <c r="D9" s="73" t="n">
         <f aca="false">D8*(1+Inputs!B19)</f>
         <v>17138.2426877952</v>
       </c>
-      <c r="E9" s="67" t="n">
+      <c r="E9" s="73" t="n">
         <f aca="false">E8*(1+Inputs!B19)</f>
         <v>85691.213438976</v>
       </c>
-      <c r="F9" s="67" t="n">
+      <c r="F9" s="73" t="n">
         <f aca="false">(F8+Inputs!B15)*(1+Inputs!B19)</f>
         <v>248475.44790614</v>
       </c>
-      <c r="G9" s="67" t="n">
+      <c r="G9" s="73" t="n">
         <f aca="false">G8*(1+Inputs!B19)</f>
         <v>856912.13438976</v>
       </c>
-      <c r="H9" s="68" t="n">
+      <c r="H9" s="74" t="n">
         <f aca="false">SUM(B9:G9)</f>
         <v>7588980.63739271</v>
       </c>
-      <c r="I9" s="69" t="n">
+      <c r="I9" s="75" t="n">
         <f aca="false">H9+Inputs!B36*POWER(1+Inputs!B52,VALUE(A9)-Inputs!B4)</f>
         <v>8630788.73727072</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="66" t="n">
+      <c r="A10" s="72" t="n">
         <v>63</v>
       </c>
-      <c r="B10" s="67" t="n">
+      <c r="B10" s="73" t="n">
         <f aca="false">B9*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
         <v>5540545.77917623</v>
       </c>
-      <c r="C10" s="67" t="n">
+      <c r="C10" s="73" t="n">
         <f aca="false">C9*(1+Inputs!B19)</f>
         <v>1388197.65771141</v>
       </c>
-      <c r="D10" s="67" t="n">
+      <c r="D10" s="73" t="n">
         <f aca="false">D9*(1+Inputs!B19)</f>
         <v>18509.3021028188</v>
       </c>
-      <c r="E10" s="67" t="n">
+      <c r="E10" s="73" t="n">
         <f aca="false">E9*(1+Inputs!B19)</f>
         <v>92546.5105140941</v>
       </c>
-      <c r="F10" s="67" t="n">
+      <c r="F10" s="73" t="n">
         <f aca="false">(F9+Inputs!B15)*(1+Inputs!B19)</f>
         <v>276993.483738632</v>
       </c>
-      <c r="G10" s="67" t="n">
+      <c r="G10" s="73" t="n">
         <f aca="false">G9*(1+Inputs!B19)</f>
         <v>925465.105140941</v>
       </c>
-      <c r="H10" s="68" t="n">
+      <c r="H10" s="74" t="n">
         <f aca="false">SUM(B10:G10)</f>
         <v>8242257.83838413</v>
       </c>
-      <c r="I10" s="69" t="n">
+      <c r="I10" s="75" t="n">
         <f aca="false">H10+Inputs!B36*POWER(1+Inputs!B52,VALUE(A10)-Inputs!B4)</f>
         <v>9330947.30275665</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="66" t="n">
+      <c r="A11" s="72" t="n">
         <v>64</v>
       </c>
-      <c r="B11" s="67" t="n">
+      <c r="B11" s="73" t="n">
         <f aca="false">B10*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
         <v>6021308.19151033</v>
       </c>
-      <c r="C11" s="67" t="n">
+      <c r="C11" s="73" t="n">
         <f aca="false">C10*(1+Inputs!B19)</f>
         <v>1499253.47032833</v>
       </c>
-      <c r="D11" s="67" t="n">
+      <c r="D11" s="73" t="n">
         <f aca="false">D10*(1+Inputs!B19)</f>
         <v>19990.0462710443</v>
       </c>
-      <c r="E11" s="67" t="n">
+      <c r="E11" s="73" t="n">
         <f aca="false">E10*(1+Inputs!B19)</f>
         <v>99950.2313552217</v>
       </c>
-      <c r="F11" s="67" t="n">
+      <c r="F11" s="73" t="n">
         <f aca="false">(F10+Inputs!B15)*(1+Inputs!B19)</f>
         <v>307792.962437722</v>
       </c>
-      <c r="G11" s="67" t="n">
+      <c r="G11" s="73" t="n">
         <f aca="false">G10*(1+Inputs!B19)</f>
         <v>999502.313552217</v>
       </c>
-      <c r="H11" s="68" t="n">
+      <c r="H11" s="74" t="n">
         <f aca="false">SUM(B11:G11)</f>
         <v>8947797.21545486</v>
       </c>
-      <c r="I11" s="69" t="n">
+      <c r="I11" s="75" t="n">
         <f aca="false">H11+Inputs!B36*POWER(1+Inputs!B52,VALUE(A11)-Inputs!B4)</f>
         <v>10085477.7057241</v>
       </c>
@@ -18354,17 +18353,17 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="70" t="s">
+      <c r="A34" s="76" t="s">
         <v>150</v>
       </c>
-      <c r="B34" s="70"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
+      <c r="B34" s="76"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -18403,112 +18402,112 @@
       <c r="D1" s="16"/>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="77" t="s">
         <v>152</v>
       </c>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="77" t="s">
         <v>153</v>
       </c>
-      <c r="C2" s="71" t="s">
+      <c r="C2" s="77" t="s">
         <v>154</v>
       </c>
-      <c r="D2" s="71" t="s">
+      <c r="D2" s="77" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="78" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="73" t="n">
+      <c r="B3" s="79" t="n">
         <f aca="false">Inputs!B22</f>
         <v>3330</v>
       </c>
-      <c r="C3" s="73" t="n">
+      <c r="C3" s="79" t="n">
         <f aca="false">Inputs!B23</f>
         <v>3972</v>
       </c>
-      <c r="D3" s="73" t="n">
+      <c r="D3" s="79" t="n">
         <f aca="false">Inputs!B24</f>
         <v>5200</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="78" t="s">
         <v>157</v>
       </c>
-      <c r="B4" s="74" t="n">
+      <c r="B4" s="80" t="n">
         <f aca="false">Inputs!B22*12</f>
         <v>39960</v>
       </c>
-      <c r="C4" s="74" t="n">
+      <c r="C4" s="80" t="n">
         <f aca="false">Inputs!B23*12</f>
         <v>47664</v>
       </c>
-      <c r="D4" s="74" t="n">
+      <c r="D4" s="80" t="n">
         <f aca="false">Inputs!B24*12</f>
         <v>62400</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="78" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="75" t="n">
+      <c r="B5" s="81" t="n">
         <f aca="false">85-65</f>
         <v>20</v>
       </c>
-      <c r="C5" s="75" t="n">
+      <c r="C5" s="81" t="n">
         <f aca="false">85-67</f>
         <v>18</v>
       </c>
-      <c r="D5" s="75" t="n">
+      <c r="D5" s="81" t="n">
         <f aca="false">85-70</f>
         <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="B6" s="74" t="n">
+      <c r="B6" s="80" t="n">
         <f aca="false">Inputs!B22*12*20</f>
         <v>799200</v>
       </c>
-      <c r="C6" s="74" t="n">
+      <c r="C6" s="80" t="n">
         <f aca="false">Inputs!B23*12*18</f>
         <v>857952</v>
       </c>
-      <c r="D6" s="74" t="n">
+      <c r="D6" s="80" t="n">
         <f aca="false">Inputs!B24*12*15</f>
         <v>936000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="72" t="s">
+      <c r="A7" s="78" t="s">
         <v>160</v>
       </c>
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="81" t="s">
         <v>161</v>
       </c>
-      <c r="C7" s="75" t="s">
+      <c r="C7" s="81" t="s">
         <v>162</v>
       </c>
-      <c r="D7" s="75" t="s">
+      <c r="D7" s="81" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="72" t="s">
+      <c r="A8" s="78" t="s">
         <v>164</v>
       </c>
-      <c r="B8" s="76" t="s">
+      <c r="B8" s="82" t="s">
         <v>165</v>
       </c>
-      <c r="C8" s="76" t="s">
+      <c r="C8" s="82" t="s">
         <v>166</v>
       </c>
-      <c r="D8" s="76" t="s">
+      <c r="D8" s="82" t="s">
         <v>167</v>
       </c>
     </row>

--- a/retirement_planner.xlsx
+++ b/retirement_planner.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="208">
   <si>
     <t xml:space="preserve">RETIREMENT PLANNING MODEL — INPUTS</t>
   </si>
@@ -207,9 +207,6 @@
   </si>
   <si>
     <t xml:space="preserve">Note: Mortgage balance is auto-calculated from monthly payment, years remaining &amp; rate. Common state rates: NJ 4.5%, WA 6.0%, CA 5.5%, TX 3.5%, FL 4.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROTH CONVERSION PLAN  (Ages 65–85)</t>
   </si>
   <si>
     <t xml:space="preserve">Age</t>
@@ -268,9 +265,6 @@
   </si>
   <si>
     <t xml:space="preserve">Tier 5: MAGI &gt; $750,000 — $4,170/person/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANNUAL WITHDRAWAL PLAN  (Ages 65–85)</t>
   </si>
   <si>
     <t xml:space="preserve">Living+Infl
@@ -504,9 +498,6 @@
   <si>
     <t xml:space="preserve">Fed Tax
 (Single) ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORTFOLIO BALANCE PROJECTION  (Ages 56–85)</t>
   </si>
   <si>
     <t xml:space="preserve">Trad 401k
@@ -3284,11 +3275,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="81615781"/>
-        <c:axId val="39758053"/>
+        <c:axId val="5279268"/>
+        <c:axId val="33845831"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="81615781"/>
+        <c:axId val="5279268"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3353,7 +3344,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39758053"/>
+        <c:crossAx val="33845831"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3361,7 +3352,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="39758053"/>
+        <c:axId val="33845831"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3435,7 +3426,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81615781"/>
+        <c:crossAx val="5279268"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4576,11 +4567,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="9351744"/>
-        <c:axId val="64287517"/>
+        <c:axId val="71553550"/>
+        <c:axId val="39761404"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="9351744"/>
+        <c:axId val="71553550"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4645,7 +4636,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64287517"/>
+        <c:crossAx val="39761404"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4653,7 +4644,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64287517"/>
+        <c:axId val="39761404"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4727,7 +4718,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9351744"/>
+        <c:crossAx val="71553550"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5466,11 +5457,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="27381142"/>
-        <c:axId val="95898223"/>
+        <c:axId val="36840282"/>
+        <c:axId val="66208012"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="27381142"/>
+        <c:axId val="36840282"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5535,7 +5526,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95898223"/>
+        <c:crossAx val="66208012"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5543,7 +5534,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="95898223"/>
+        <c:axId val="66208012"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5617,7 +5608,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27381142"/>
+        <c:crossAx val="36840282"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6146,11 +6137,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="47487095"/>
-        <c:axId val="55775517"/>
+        <c:axId val="81062037"/>
+        <c:axId val="8298479"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="47487095"/>
+        <c:axId val="81062037"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6215,7 +6206,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55775517"/>
+        <c:crossAx val="8298479"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6223,7 +6214,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55775517"/>
+        <c:axId val="8298479"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6297,7 +6288,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47487095"/>
+        <c:crossAx val="81062037"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7227,9 +7218,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>549720</xdr:colOff>
+      <xdr:colOff>548640</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>43200</xdr:rowOff>
+      <xdr:rowOff>42120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7238,7 +7229,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8881200" y="438120"/>
-        <a:ext cx="8638200" cy="5758200"/>
+        <a:ext cx="8637120" cy="5757120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7257,9 +7248,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>549720</xdr:colOff>
+      <xdr:colOff>548640</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>43200</xdr:rowOff>
+      <xdr:rowOff>42120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7268,7 +7259,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8881200" y="6534000"/>
-        <a:ext cx="8638200" cy="5758200"/>
+        <a:ext cx="8637120" cy="5757120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7287,9 +7278,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>744120</xdr:colOff>
+      <xdr:colOff>743040</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>43560</xdr:rowOff>
+      <xdr:rowOff>42480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7298,7 +7289,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="15487560"/>
-        <a:ext cx="8638560" cy="5758560"/>
+        <a:ext cx="8637480" cy="5757480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7317,9 +7308,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>550080</xdr:colOff>
+      <xdr:colOff>549000</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>43560</xdr:rowOff>
+      <xdr:rowOff>42480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7328,7 +7319,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8881200" y="15487560"/>
-        <a:ext cx="8638560" cy="5758560"/>
+        <a:ext cx="8637480" cy="5757480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8013,96 +8004,96 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B1" s="16"/>
     </row>
     <row r="2" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="83" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B2" s="84" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="85" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B3" s="86" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="87" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="85" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B5" s="86" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="87" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B6" s="88" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="85" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="87" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="85" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B9" s="86" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="87" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B10" s="88" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="85" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B11" s="86" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="87" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B12" s="88" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -8132,7 +8123,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="89" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B1" s="89"/>
       <c r="C1" s="89"/>
@@ -8156,28 +8147,28 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="90" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="90" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="90" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" s="90" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="90" t="s">
         <v>192</v>
       </c>
-      <c r="C3" s="90" t="s">
+      <c r="F3" s="90" t="s">
         <v>193</v>
       </c>
-      <c r="D3" s="90" t="s">
+      <c r="G3" s="90" t="s">
         <v>194</v>
       </c>
-      <c r="E3" s="90" t="s">
+      <c r="H3" s="90" t="s">
         <v>195</v>
-      </c>
-      <c r="F3" s="90" t="s">
-        <v>196</v>
-      </c>
-      <c r="G3" s="90" t="s">
-        <v>197</v>
-      </c>
-      <c r="H3" s="90" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9202,37 +9193,37 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="90" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B35" s="90" t="s">
+        <v>196</v>
+      </c>
+      <c r="C35" s="90" t="s">
+        <v>197</v>
+      </c>
+      <c r="D35" s="90" t="s">
+        <v>198</v>
+      </c>
+      <c r="E35" s="90" t="s">
         <v>199</v>
       </c>
-      <c r="C35" s="90" t="s">
+      <c r="F35" s="90" t="s">
         <v>200</v>
       </c>
-      <c r="D35" s="90" t="s">
+      <c r="G35" s="90" t="s">
         <v>201</v>
       </c>
-      <c r="E35" s="90" t="s">
+      <c r="H35" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F35" s="90" t="s">
+      <c r="I35" s="90" t="s">
         <v>203</v>
       </c>
-      <c r="G35" s="90" t="s">
+      <c r="J35" s="90" t="s">
         <v>204</v>
       </c>
-      <c r="H35" s="90" t="s">
+      <c r="K35" s="90" t="s">
         <v>205</v>
-      </c>
-      <c r="I35" s="90" t="s">
-        <v>206</v>
-      </c>
-      <c r="J35" s="90" t="s">
-        <v>207</v>
-      </c>
-      <c r="K35" s="90" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10203,22 +10194,22 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="90" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B58" s="90" t="s">
+        <v>122</v>
+      </c>
+      <c r="C58" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="C58" s="90" t="s">
-        <v>126</v>
-      </c>
       <c r="D58" s="90" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E58" s="90" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F58" s="90" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10782,8 +10773,9 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>59</v>
+      <c r="A1" s="16" t="str">
+        <f aca="false">IFERROR("ROTH CONVERSION PLAN  (Ages "&amp;TEXT(Inputs!B5,"0")&amp;"–"&amp;TEXT(Inputs!B6,"0"),"ROTH CONVERSION PLAN")</f>
+        <v>ROTH CONVERSION PLAN  (Ages 65–85</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -10797,34 +10789,34 @@
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="C2" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="D2" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="E2" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="G2" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="H2" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="I2" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="J2" s="17" t="s">
         <v>68</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11690,37 +11682,37 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -11761,8 +11753,9 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>77</v>
+      <c r="A1" s="16" t="str">
+        <f aca="false">IFERROR("ANNUAL WITHDRAWAL PLAN  (Ages "&amp;TEXT(Inputs!B5,"0")&amp;"–"&amp;TEXT(Inputs!B6,"0"),"ANNUAL WITHDRAWAL PLAN")</f>
+        <v>ANNUAL WITHDRAWAL PLAN  (Ages 65–85</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -11782,52 +11775,52 @@
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="E2" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="F2" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="G2" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="H2" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="I2" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="J2" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="K2" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="L2" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="M2" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="N2" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="O2" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="P2" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="P2" s="17" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13229,7 +13222,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -13241,12 +13234,12 @@
       <c r="I1" s="40"/>
       <c r="J1" s="40"/>
       <c r="L1" s="41" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="42" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
@@ -13260,34 +13253,34 @@
     </row>
     <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="E3" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="F3" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="G3" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="H3" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="I3" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" s="43" t="s">
         <v>100</v>
-      </c>
-      <c r="H3" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="I3" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="J3" s="43" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13809,7 +13802,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="49" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B15" s="50"/>
       <c r="C15" s="51"/>
@@ -13915,7 +13908,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="40" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -13932,7 +13925,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="42" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
@@ -13949,46 +13942,46 @@
     </row>
     <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="H3" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="I3" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="J3" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="43" t="s">
+      <c r="M3" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="J3" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="K3" s="43" t="s">
-        <v>67</v>
-      </c>
-      <c r="L3" s="43" t="s">
+      <c r="N3" s="43" t="s">
         <v>111</v>
-      </c>
-      <c r="M3" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="N3" s="43" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15221,7 +15214,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="40" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -15234,7 +15227,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
@@ -15247,28 +15240,28 @@
     </row>
     <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="E3" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="F3" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="G3" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="H3" s="43" t="s">
         <v>120</v>
-      </c>
-      <c r="G3" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="H3" s="43" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15966,19 +15959,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="65" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" s="66" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="66" t="s">
+      <c r="E26" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="D26" s="66" t="s">
+      <c r="F26" s="66" t="s">
         <v>125</v>
-      </c>
-      <c r="E26" s="66" t="s">
-        <v>126</v>
-      </c>
-      <c r="F26" s="66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16001,7 +15994,7 @@
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="42" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
@@ -16049,7 +16042,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -16065,7 +16058,7 @@
     </row>
     <row r="2" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="42" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
@@ -16081,62 +16074,62 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="68" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C4" s="69" t="n">
         <v>75</v>
       </c>
       <c r="D4" s="70" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="68" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C5" s="71" t="n">
         <v>0.2</v>
       </c>
       <c r="D5" s="70" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="43" t="s">
+      <c r="G6" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="F6" s="43" t="s">
+      <c r="H6" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="I6" s="43" t="s">
         <v>137</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="J6" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="H6" s="43" t="s">
-        <v>83</v>
-      </c>
-      <c r="I6" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="J6" s="43" t="s">
-        <v>140</v>
-      </c>
       <c r="K6" s="43" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L6" s="43" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17201,8 +17194,9 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>141</v>
+      <c r="A1" s="16" t="str">
+        <f aca="false">IFERROR("PORTFOLIO BALANCE PROJECTION  (Ages "&amp;TEXT(Inputs!B4,"0")&amp;"–"&amp;TEXT(Inputs!B6,"0"),"PORTFOLIO BALANCE PROJECTION")</f>
+        <v>PORTFOLIO BALANCE PROJECTION  (Ages 56–85</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -17215,31 +17209,31 @@
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="F2" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="G2" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="H2" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="I2" s="17" t="s">
         <v>146</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17247,7 +17241,7 @@
         <v>56</v>
       </c>
       <c r="B3" s="73" t="n">
-        <f aca="false">Inputs!B9+Inputs!B11*(1+Inputs!B12/100)</f>
+        <f aca="false">Inputs!B9+IF(Inputs!B4&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>3037518.75</v>
       </c>
       <c r="C3" s="73" t="n">
@@ -17263,7 +17257,7 @@
         <v>54000</v>
       </c>
       <c r="F3" s="73" t="n">
-        <f aca="false">(Inputs!B14+Inputs!B15)*(1+Inputs!B19)</f>
+        <f aca="false">(Inputs!B14+IF(Inputs!B4&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>116640</v>
       </c>
       <c r="G3" s="73" t="n">
@@ -17284,7 +17278,7 @@
         <v>57</v>
       </c>
       <c r="B4" s="73" t="n">
-        <f aca="false">B3*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <f aca="false">B3*(1+Inputs!B19)+IF(A4&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>3318039</v>
       </c>
       <c r="C4" s="73" t="n">
@@ -17300,7 +17294,7 @@
         <v>58320</v>
       </c>
       <c r="F4" s="73" t="n">
-        <f aca="false">(F3+Inputs!B15)*(1+Inputs!B19)</f>
+        <f aca="false">(F3+IF(A4&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>134611.2</v>
       </c>
       <c r="G4" s="73" t="n">
@@ -17321,7 +17315,7 @@
         <v>58</v>
       </c>
       <c r="B5" s="73" t="n">
-        <f aca="false">B4*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <f aca="false">B4*(1+Inputs!B19)+IF(A5&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>3621000.87</v>
       </c>
       <c r="C5" s="73" t="n">
@@ -17337,7 +17331,7 @@
         <v>62985.6</v>
       </c>
       <c r="F5" s="73" t="n">
-        <f aca="false">(F4+Inputs!B15)*(1+Inputs!B19)</f>
+        <f aca="false">(F4+IF(A5&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>154020.096</v>
       </c>
       <c r="G5" s="73" t="n">
@@ -17358,7 +17352,7 @@
         <v>59</v>
       </c>
       <c r="B6" s="73" t="n">
-        <f aca="false">B5*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <f aca="false">B5*(1+Inputs!B19)+IF(A6&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>3948199.6896</v>
       </c>
       <c r="C6" s="73" t="n">
@@ -17374,7 +17368,7 @@
         <v>68024.448</v>
       </c>
       <c r="F6" s="73" t="n">
-        <f aca="false">(F5+Inputs!B15)*(1+Inputs!B19)</f>
+        <f aca="false">(F5+IF(A6&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>174981.70368</v>
       </c>
       <c r="G6" s="73" t="n">
@@ -17395,7 +17389,7 @@
         <v>60</v>
       </c>
       <c r="B7" s="73" t="n">
-        <f aca="false">B6*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <f aca="false">B6*(1+Inputs!B19)+IF(A7&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>4301574.414768</v>
       </c>
       <c r="C7" s="73" t="n">
@@ -17411,7 +17405,7 @@
         <v>73466.40384</v>
       </c>
       <c r="F7" s="73" t="n">
-        <f aca="false">(F6+Inputs!B15)*(1+Inputs!B19)</f>
+        <f aca="false">(F6+IF(A7&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>197620.2399744</v>
       </c>
       <c r="G7" s="73" t="n">
@@ -17432,7 +17426,7 @@
         <v>61</v>
       </c>
       <c r="B8" s="73" t="n">
-        <f aca="false">B7*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <f aca="false">B7*(1+Inputs!B19)+IF(A8&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>4683219.11794944</v>
       </c>
       <c r="C8" s="73" t="n">
@@ -17448,7 +17442,7 @@
         <v>79343.7161472</v>
       </c>
       <c r="F8" s="73" t="n">
-        <f aca="false">(F7+Inputs!B15)*(1+Inputs!B19)</f>
+        <f aca="false">(F7+IF(A8&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>222069.859172352</v>
       </c>
       <c r="G8" s="73" t="n">
@@ -17469,7 +17463,7 @@
         <v>62</v>
       </c>
       <c r="B9" s="73" t="n">
-        <f aca="false">B8*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <f aca="false">B8*(1+Inputs!B19)+IF(A9&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>5095395.3973854</v>
       </c>
       <c r="C9" s="73" t="n">
@@ -17485,7 +17479,7 @@
         <v>85691.213438976</v>
       </c>
       <c r="F9" s="73" t="n">
-        <f aca="false">(F8+Inputs!B15)*(1+Inputs!B19)</f>
+        <f aca="false">(F8+IF(A9&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>248475.44790614</v>
       </c>
       <c r="G9" s="73" t="n">
@@ -17506,7 +17500,7 @@
         <v>63</v>
       </c>
       <c r="B10" s="73" t="n">
-        <f aca="false">B9*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <f aca="false">B9*(1+Inputs!B19)+IF(A10&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>5540545.77917623</v>
       </c>
       <c r="C10" s="73" t="n">
@@ -17522,7 +17516,7 @@
         <v>92546.5105140941</v>
       </c>
       <c r="F10" s="73" t="n">
-        <f aca="false">(F9+Inputs!B15)*(1+Inputs!B19)</f>
+        <f aca="false">(F9+IF(A10&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>276993.483738632</v>
       </c>
       <c r="G10" s="73" t="n">
@@ -17543,7 +17537,7 @@
         <v>64</v>
       </c>
       <c r="B11" s="73" t="n">
-        <f aca="false">B10*(1+Inputs!B19)+Inputs!B11*(1+Inputs!B12/100)</f>
+        <f aca="false">B10*(1+Inputs!B19)+IF(A11&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>6021308.19151033</v>
       </c>
       <c r="C11" s="73" t="n">
@@ -17559,7 +17553,7 @@
         <v>99950.2313552217</v>
       </c>
       <c r="F11" s="73" t="n">
-        <f aca="false">(F10+Inputs!B15)*(1+Inputs!B19)</f>
+        <f aca="false">(F10+IF(A11&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>307792.962437722</v>
       </c>
       <c r="G11" s="73" t="n">
@@ -18354,7 +18348,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="76" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B34" s="76"/>
       <c r="C34" s="76"/>
@@ -18395,7 +18389,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -18403,21 +18397,21 @@
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="77" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="77" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="77" t="s">
         <v>152</v>
-      </c>
-      <c r="B2" s="77" t="s">
-        <v>153</v>
-      </c>
-      <c r="C2" s="77" t="s">
-        <v>154</v>
-      </c>
-      <c r="D2" s="77" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="78" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B3" s="79" t="n">
         <f aca="false">Inputs!B22</f>
@@ -18434,7 +18428,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="78" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B4" s="80" t="n">
         <f aca="false">Inputs!B22*12</f>
@@ -18451,7 +18445,7 @@
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="78" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B5" s="81" t="n">
         <f aca="false">85-65</f>
@@ -18468,7 +18462,7 @@
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="78" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B6" s="80" t="n">
         <f aca="false">Inputs!B22*12*20</f>
@@ -18485,30 +18479,30 @@
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="78" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="81" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="81" t="s">
         <v>160</v>
-      </c>
-      <c r="B7" s="81" t="s">
-        <v>161</v>
-      </c>
-      <c r="C7" s="81" t="s">
-        <v>162</v>
-      </c>
-      <c r="D7" s="81" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="78" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8" s="82" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="82" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="82" t="s">
         <v>164</v>
-      </c>
-      <c r="B8" s="82" t="s">
-        <v>165</v>
-      </c>
-      <c r="C8" s="82" t="s">
-        <v>166</v>
-      </c>
-      <c r="D8" s="82" t="s">
-        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/retirement_planner.xlsx
+++ b/retirement_planner.xlsx
@@ -3275,11 +3275,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="5279268"/>
-        <c:axId val="33845831"/>
+        <c:axId val="48485914"/>
+        <c:axId val="89333867"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5279268"/>
+        <c:axId val="48485914"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3344,7 +3344,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33845831"/>
+        <c:crossAx val="89333867"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3352,7 +3352,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33845831"/>
+        <c:axId val="89333867"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3426,7 +3426,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5279268"/>
+        <c:crossAx val="48485914"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4567,11 +4567,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="71553550"/>
-        <c:axId val="39761404"/>
+        <c:axId val="24832143"/>
+        <c:axId val="83548538"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="71553550"/>
+        <c:axId val="24832143"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4636,7 +4636,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39761404"/>
+        <c:crossAx val="83548538"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4644,7 +4644,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="39761404"/>
+        <c:axId val="83548538"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4718,7 +4718,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71553550"/>
+        <c:crossAx val="24832143"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5457,11 +5457,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="36840282"/>
-        <c:axId val="66208012"/>
+        <c:axId val="84775994"/>
+        <c:axId val="36776677"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="36840282"/>
+        <c:axId val="84775994"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5526,7 +5526,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66208012"/>
+        <c:crossAx val="36776677"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5534,7 +5534,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66208012"/>
+        <c:axId val="36776677"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5608,7 +5608,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36840282"/>
+        <c:crossAx val="84775994"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6137,11 +6137,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="81062037"/>
-        <c:axId val="8298479"/>
+        <c:axId val="68259432"/>
+        <c:axId val="83951454"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="81062037"/>
+        <c:axId val="68259432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6206,7 +6206,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8298479"/>
+        <c:crossAx val="83951454"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6214,7 +6214,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8298479"/>
+        <c:axId val="83951454"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6288,7 +6288,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81062037"/>
+        <c:crossAx val="68259432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7218,9 +7218,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>548640</xdr:colOff>
+      <xdr:colOff>548280</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>42120</xdr:rowOff>
+      <xdr:rowOff>41760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7229,7 +7229,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8881200" y="438120"/>
-        <a:ext cx="8637120" cy="5757120"/>
+        <a:ext cx="8636760" cy="5756760"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7248,9 +7248,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>548640</xdr:colOff>
+      <xdr:colOff>548280</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>42120</xdr:rowOff>
+      <xdr:rowOff>41760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7259,7 +7259,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8881200" y="6534000"/>
-        <a:ext cx="8637120" cy="5757120"/>
+        <a:ext cx="8636760" cy="5756760"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7278,9 +7278,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>743040</xdr:colOff>
+      <xdr:colOff>742680</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>42480</xdr:rowOff>
+      <xdr:rowOff>42120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7289,7 +7289,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="15487560"/>
-        <a:ext cx="8637480" cy="5757480"/>
+        <a:ext cx="8637120" cy="5757120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7308,9 +7308,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>549000</xdr:colOff>
+      <xdr:colOff>548640</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>42480</xdr:rowOff>
+      <xdr:rowOff>42120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7319,7 +7319,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8881200" y="15487560"/>
-        <a:ext cx="8637480" cy="5757480"/>
+        <a:ext cx="8637120" cy="5757120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -17278,7 +17278,7 @@
         <v>57</v>
       </c>
       <c r="B4" s="73" t="n">
-        <f aca="false">B3*(1+Inputs!B19)+IF(A4&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
+        <f aca="false">B3*(1+Inputs!B19)+IF(AND(A4&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>3318039</v>
       </c>
       <c r="C4" s="73" t="n">
@@ -17294,7 +17294,7 @@
         <v>58320</v>
       </c>
       <c r="F4" s="73" t="n">
-        <f aca="false">(F3+IF(A4&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
+        <f aca="false">(F3+IF(AND(A4&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>134611.2</v>
       </c>
       <c r="G4" s="73" t="n">
@@ -17315,7 +17315,7 @@
         <v>58</v>
       </c>
       <c r="B5" s="73" t="n">
-        <f aca="false">B4*(1+Inputs!B19)+IF(A5&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
+        <f aca="false">B4*(1+Inputs!B19)+IF(AND(A5&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>3621000.87</v>
       </c>
       <c r="C5" s="73" t="n">
@@ -17331,7 +17331,7 @@
         <v>62985.6</v>
       </c>
       <c r="F5" s="73" t="n">
-        <f aca="false">(F4+IF(A5&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
+        <f aca="false">(F4+IF(AND(A5&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>154020.096</v>
       </c>
       <c r="G5" s="73" t="n">
@@ -17352,7 +17352,7 @@
         <v>59</v>
       </c>
       <c r="B6" s="73" t="n">
-        <f aca="false">B5*(1+Inputs!B19)+IF(A6&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
+        <f aca="false">B5*(1+Inputs!B19)+IF(AND(A6&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>3948199.6896</v>
       </c>
       <c r="C6" s="73" t="n">
@@ -17368,7 +17368,7 @@
         <v>68024.448</v>
       </c>
       <c r="F6" s="73" t="n">
-        <f aca="false">(F5+IF(A6&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
+        <f aca="false">(F5+IF(AND(A6&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>174981.70368</v>
       </c>
       <c r="G6" s="73" t="n">
@@ -17389,7 +17389,7 @@
         <v>60</v>
       </c>
       <c r="B7" s="73" t="n">
-        <f aca="false">B6*(1+Inputs!B19)+IF(A7&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
+        <f aca="false">B6*(1+Inputs!B19)+IF(AND(A7&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>4301574.414768</v>
       </c>
       <c r="C7" s="73" t="n">
@@ -17405,7 +17405,7 @@
         <v>73466.40384</v>
       </c>
       <c r="F7" s="73" t="n">
-        <f aca="false">(F6+IF(A7&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
+        <f aca="false">(F6+IF(AND(A7&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>197620.2399744</v>
       </c>
       <c r="G7" s="73" t="n">
@@ -17426,7 +17426,7 @@
         <v>61</v>
       </c>
       <c r="B8" s="73" t="n">
-        <f aca="false">B7*(1+Inputs!B19)+IF(A8&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
+        <f aca="false">B7*(1+Inputs!B19)+IF(AND(A8&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>4683219.11794944</v>
       </c>
       <c r="C8" s="73" t="n">
@@ -17442,7 +17442,7 @@
         <v>79343.7161472</v>
       </c>
       <c r="F8" s="73" t="n">
-        <f aca="false">(F7+IF(A8&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
+        <f aca="false">(F7+IF(AND(A8&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>222069.859172352</v>
       </c>
       <c r="G8" s="73" t="n">
@@ -17463,7 +17463,7 @@
         <v>62</v>
       </c>
       <c r="B9" s="73" t="n">
-        <f aca="false">B8*(1+Inputs!B19)+IF(A9&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
+        <f aca="false">B8*(1+Inputs!B19)+IF(AND(A9&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>5095395.3973854</v>
       </c>
       <c r="C9" s="73" t="n">
@@ -17479,7 +17479,7 @@
         <v>85691.213438976</v>
       </c>
       <c r="F9" s="73" t="n">
-        <f aca="false">(F8+IF(A9&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
+        <f aca="false">(F8+IF(AND(A9&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>248475.44790614</v>
       </c>
       <c r="G9" s="73" t="n">
@@ -17500,7 +17500,7 @@
         <v>63</v>
       </c>
       <c r="B10" s="73" t="n">
-        <f aca="false">B9*(1+Inputs!B19)+IF(A10&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
+        <f aca="false">B9*(1+Inputs!B19)+IF(AND(A10&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>5540545.77917623</v>
       </c>
       <c r="C10" s="73" t="n">
@@ -17516,7 +17516,7 @@
         <v>92546.5105140941</v>
       </c>
       <c r="F10" s="73" t="n">
-        <f aca="false">(F9+IF(A10&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
+        <f aca="false">(F9+IF(AND(A10&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>276993.483738632</v>
       </c>
       <c r="G10" s="73" t="n">
@@ -17537,7 +17537,7 @@
         <v>64</v>
       </c>
       <c r="B11" s="73" t="n">
-        <f aca="false">B10*(1+Inputs!B19)+IF(A11&lt;Inputs!B5,Inputs!B11*(1+Inputs!B12/100),0)</f>
+        <f aca="false">B10*(1+Inputs!B19)+IF(AND(A11&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B11*(1+Inputs!B12/100),0)</f>
         <v>6021308.19151033</v>
       </c>
       <c r="C11" s="73" t="n">
@@ -17553,7 +17553,7 @@
         <v>99950.2313552217</v>
       </c>
       <c r="F11" s="73" t="n">
-        <f aca="false">(F10+IF(A11&lt;Inputs!B5,Inputs!B15,0))*(1+Inputs!B19)</f>
+        <f aca="false">(F10+IF(AND(A11&lt;Inputs!B5,Inputs!B4&lt;Inputs!B5),Inputs!B15,0))*(1+Inputs!B19)</f>
         <v>307792.962437722</v>
       </c>
       <c r="G11" s="73" t="n">

--- a/retirement_planner.xlsx
+++ b/retirement_planner.xlsx
@@ -529,8 +529,7 @@
   </si>
   <si>
     <t xml:space="preserve">Net Worth
-+Home ($)
-(home appreciates)</t>
+(Home Equity) ($)</t>
   </si>
   <si>
     <t xml:space="preserve">Blue rows = working years (accumulation)  ·  Orange rows = RMD years (age 73+)  ·  White/cream = retirement years  ·  Net Worth includes home value appreciating at Inputs!B52 rate per year</t>
@@ -3275,11 +3274,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="48485914"/>
-        <c:axId val="89333867"/>
+        <c:axId val="96453926"/>
+        <c:axId val="42635581"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48485914"/>
+        <c:axId val="96453926"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3344,7 +3343,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89333867"/>
+        <c:crossAx val="42635581"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3352,7 +3351,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89333867"/>
+        <c:axId val="42635581"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3426,7 +3425,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48485914"/>
+        <c:crossAx val="96453926"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4567,11 +4566,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="24832143"/>
-        <c:axId val="83548538"/>
+        <c:axId val="15244717"/>
+        <c:axId val="2634638"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24832143"/>
+        <c:axId val="15244717"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4636,7 +4635,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83548538"/>
+        <c:crossAx val="2634638"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4644,7 +4643,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83548538"/>
+        <c:axId val="2634638"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4718,7 +4717,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24832143"/>
+        <c:crossAx val="15244717"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5457,11 +5456,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="84775994"/>
-        <c:axId val="36776677"/>
+        <c:axId val="9936751"/>
+        <c:axId val="54546250"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="84775994"/>
+        <c:axId val="9936751"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5526,7 +5525,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36776677"/>
+        <c:crossAx val="54546250"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5534,7 +5533,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36776677"/>
+        <c:axId val="54546250"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5608,7 +5607,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84775994"/>
+        <c:crossAx val="9936751"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6137,11 +6136,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="68259432"/>
-        <c:axId val="83951454"/>
+        <c:axId val="63135169"/>
+        <c:axId val="46458575"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="68259432"/>
+        <c:axId val="63135169"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6206,7 +6205,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83951454"/>
+        <c:crossAx val="46458575"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6214,7 +6213,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83951454"/>
+        <c:axId val="46458575"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6288,7 +6287,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68259432"/>
+        <c:crossAx val="63135169"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7218,9 +7217,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>548280</xdr:colOff>
+      <xdr:colOff>547920</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>41760</xdr:rowOff>
+      <xdr:rowOff>41400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7229,7 +7228,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8881200" y="438120"/>
-        <a:ext cx="8636760" cy="5756760"/>
+        <a:ext cx="8636400" cy="5756400"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7248,9 +7247,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>548280</xdr:colOff>
+      <xdr:colOff>547920</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>41760</xdr:rowOff>
+      <xdr:rowOff>41400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7259,7 +7258,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8881200" y="6534000"/>
-        <a:ext cx="8636760" cy="5756760"/>
+        <a:ext cx="8636400" cy="5756400"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7278,9 +7277,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>742680</xdr:colOff>
+      <xdr:colOff>742320</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>42120</xdr:rowOff>
+      <xdr:rowOff>41760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7289,7 +7288,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="15487560"/>
-        <a:ext cx="8637120" cy="5757120"/>
+        <a:ext cx="8636760" cy="5756760"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7308,9 +7307,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>548640</xdr:colOff>
+      <xdr:colOff>548280</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>42120</xdr:rowOff>
+      <xdr:rowOff>41760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7319,7 +7318,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8881200" y="15487560"/>
-        <a:ext cx="8637120" cy="5757120"/>
+        <a:ext cx="8636760" cy="5756760"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8202,7 +8201,7 @@
       </c>
       <c r="H4" s="91" t="n">
         <f aca="false">Portfolio!I3</f>
-        <v>5368958.75</v>
+        <v>4948165.75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8236,7 +8235,7 @@
       </c>
       <c r="H5" s="91" t="n">
         <f aca="false">Portfolio!I4</f>
-        <v>5816634.2</v>
+        <v>5404751.2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8270,7 +8269,7 @@
       </c>
       <c r="H6" s="91" t="n">
         <f aca="false">Portfolio!I5</f>
-        <v>6298863.686</v>
+        <v>5896488.686</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8304,7 +8303,7 @@
       </c>
       <c r="H7" s="91" t="n">
         <f aca="false">Portfolio!I6</f>
-        <v>6818354.83088</v>
+        <v>6426123.83088</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8338,7 +8337,7 @@
       </c>
       <c r="H8" s="91" t="n">
         <f aca="false">Portfolio!I7</f>
-        <v>7378029.3158504</v>
+        <v>6996622.3158504</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8372,7 +8371,7 @@
       </c>
       <c r="H9" s="91" t="n">
         <f aca="false">Portfolio!I8</f>
-        <v>7981039.89030093</v>
+        <v>7611181.89030093</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8406,7 +8405,7 @@
       </c>
       <c r="H10" s="91" t="n">
         <f aca="false">Portfolio!I9</f>
-        <v>8630788.73727072</v>
+        <v>8273252.73727072</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8440,7 +8439,7 @@
       </c>
       <c r="H11" s="91" t="n">
         <f aca="false">Portfolio!I10</f>
-        <v>9330947.30275665</v>
+        <v>8986558.30275665</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8474,7 +8473,7 @@
       </c>
       <c r="H12" s="91" t="n">
         <f aca="false">Portfolio!I11</f>
-        <v>10085477.7057241</v>
+        <v>9755115.70572414</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8508,7 +8507,7 @@
       </c>
       <c r="H13" s="91" t="n">
         <f aca="false">Portfolio!I12</f>
-        <v>7176214.2581915</v>
+        <v>6860820.2581915</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8542,7 +8541,7 @@
       </c>
       <c r="H14" s="91" t="n">
         <f aca="false">Portfolio!I13</f>
-        <v>7309003.73491522</v>
+        <v>7009578.73491522</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8576,7 +8575,7 @@
       </c>
       <c r="H15" s="91" t="n">
         <f aca="false">Portfolio!I14</f>
-        <v>7504625.73989991</v>
+        <v>7222239.73989991</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8610,7 +8609,7 @@
       </c>
       <c r="H16" s="91" t="n">
         <f aca="false">Portfolio!I15</f>
-        <v>7725274.094312</v>
+        <v>7461069.094312</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8644,7 +8643,7 @@
       </c>
       <c r="H17" s="91" t="n">
         <f aca="false">Portfolio!I16</f>
-        <v>7972801.02656446</v>
+        <v>7727993.02656446</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8678,7 +8677,7 @@
       </c>
       <c r="H18" s="91" t="n">
         <f aca="false">Portfolio!I17</f>
-        <v>8249201.28231558</v>
+        <v>8025090.28231558</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8712,7 +8711,7 @@
       </c>
       <c r="H19" s="91" t="n">
         <f aca="false">Portfolio!I18</f>
-        <v>8556623.29742627</v>
+        <v>8354595.29742627</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8746,7 +8745,7 @@
       </c>
       <c r="H20" s="91" t="n">
         <f aca="false">Portfolio!I19</f>
-        <v>8897381.25509478</v>
+        <v>8718915.25509478</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8780,7 +8779,7 @@
       </c>
       <c r="H21" s="91" t="n">
         <f aca="false">Portfolio!I20</f>
-        <v>9273968.09748204</v>
+        <v>9120642.09748204</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8814,7 +8813,7 @@
       </c>
       <c r="H22" s="91" t="n">
         <f aca="false">Portfolio!I21</f>
-        <v>9689069.56774696</v>
+        <v>9562567.56774696</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8848,7 +8847,7 @@
       </c>
       <c r="H23" s="91" t="n">
         <f aca="false">Portfolio!I22</f>
-        <v>10145579.3644652</v>
+        <v>10047697.3644652</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8882,7 +8881,7 @@
       </c>
       <c r="H24" s="91" t="n">
         <f aca="false">Portfolio!I23</f>
-        <v>10646615.4969424</v>
+        <v>10579269.4969424</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8916,7 +8915,7 @@
       </c>
       <c r="H25" s="91" t="n">
         <f aca="false">Portfolio!I24</f>
-        <v>11195537.9369923</v>
+        <v>11160773.9369923</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17269,8 +17268,8 @@
         <v>4568958.75</v>
       </c>
       <c r="I3" s="75" t="n">
-        <f aca="false">H3+Inputs!B36*POWER(1+Inputs!B52,VALUE(A3)-Inputs!B4)</f>
-        <v>5368958.75</v>
+        <f aca="false">H3+Inputs!B36*POWER(1+Inputs!B52,VALUE(A3)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A3&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A3-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A3-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A3-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>4948165.75</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17306,8 +17305,8 @@
         <v>4980634.2</v>
       </c>
       <c r="I4" s="75" t="n">
-        <f aca="false">H4+Inputs!B36*POWER(1+Inputs!B52,VALUE(A4)-Inputs!B4)</f>
-        <v>5816634.2</v>
+        <f aca="false">H4+Inputs!B36*POWER(1+Inputs!B52,VALUE(A4)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A4&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A4-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A4-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A4-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>5404751.2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17343,8 +17342,8 @@
         <v>5425243.686</v>
       </c>
       <c r="I5" s="75" t="n">
-        <f aca="false">H5+Inputs!B36*POWER(1+Inputs!B52,VALUE(A5)-Inputs!B4)</f>
-        <v>6298863.686</v>
+        <f aca="false">H5+Inputs!B36*POWER(1+Inputs!B52,VALUE(A5)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A5&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A5-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A5-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A5-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>5896488.686</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17380,8 +17379,8 @@
         <v>5905421.93088</v>
       </c>
       <c r="I6" s="75" t="n">
-        <f aca="false">H6+Inputs!B36*POWER(1+Inputs!B52,VALUE(A6)-Inputs!B4)</f>
-        <v>6818354.83088</v>
+        <f aca="false">H6+Inputs!B36*POWER(1+Inputs!B52,VALUE(A6)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A6&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A6-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A6-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A6-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>6426123.83088</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17417,8 +17416,8 @@
         <v>6424014.4353504</v>
       </c>
       <c r="I7" s="75" t="n">
-        <f aca="false">H7+Inputs!B36*POWER(1+Inputs!B52,VALUE(A7)-Inputs!B4)</f>
-        <v>7378029.3158504</v>
+        <f aca="false">H7+Inputs!B36*POWER(1+Inputs!B52,VALUE(A7)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A7&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A7-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A7-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A7-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>6996622.3158504</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17454,8 +17453,8 @@
         <v>6984094.34017843</v>
       </c>
       <c r="I8" s="75" t="n">
-        <f aca="false">H8+Inputs!B36*POWER(1+Inputs!B52,VALUE(A8)-Inputs!B4)</f>
-        <v>7981039.89030093</v>
+        <f aca="false">H8+Inputs!B36*POWER(1+Inputs!B52,VALUE(A8)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A8&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A8-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A8-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A8-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>7611181.89030093</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17491,8 +17490,8 @@
         <v>7588980.63739271</v>
       </c>
       <c r="I9" s="75" t="n">
-        <f aca="false">H9+Inputs!B36*POWER(1+Inputs!B52,VALUE(A9)-Inputs!B4)</f>
-        <v>8630788.73727072</v>
+        <f aca="false">H9+Inputs!B36*POWER(1+Inputs!B52,VALUE(A9)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A9&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A9-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A9-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A9-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>8273252.73727072</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17528,8 +17527,8 @@
         <v>8242257.83838413</v>
       </c>
       <c r="I10" s="75" t="n">
-        <f aca="false">H10+Inputs!B36*POWER(1+Inputs!B52,VALUE(A10)-Inputs!B4)</f>
-        <v>9330947.30275665</v>
+        <f aca="false">H10+Inputs!B36*POWER(1+Inputs!B52,VALUE(A10)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A10&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A10-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A10-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A10-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>8986558.30275665</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17565,8 +17564,8 @@
         <v>8947797.21545486</v>
       </c>
       <c r="I11" s="75" t="n">
-        <f aca="false">H11+Inputs!B36*POWER(1+Inputs!B52,VALUE(A11)-Inputs!B4)</f>
-        <v>10085477.7057241</v>
+        <f aca="false">H11+Inputs!B36*POWER(1+Inputs!B52,VALUE(A11)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A11&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A11-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A11-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A11-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>9755115.70572414</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17602,8 +17601,8 @@
         <v>5987338.14586009</v>
       </c>
       <c r="I12" s="37" t="n">
-        <f aca="false">H12+Inputs!B36*POWER(1+Inputs!B52,VALUE(A12)-Inputs!B4)</f>
-        <v>7176214.2581915</v>
+        <f aca="false">H12+Inputs!B36*POWER(1+Inputs!B52,VALUE(A12)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A12&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A12-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A12-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A12-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>6860820.2581915</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17639,8 +17638,8 @@
         <v>6066628.1975289</v>
       </c>
       <c r="I13" s="35" t="n">
-        <f aca="false">H13+Inputs!B36*POWER(1+Inputs!B52,VALUE(A13)-Inputs!B4)</f>
-        <v>7309003.73491522</v>
+        <f aca="false">H13+Inputs!B36*POWER(1+Inputs!B52,VALUE(A13)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A13&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A13-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A13-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A13-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>7009578.73491522</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17676,8 +17675,8 @@
         <v>6206343.30333121</v>
       </c>
       <c r="I14" s="37" t="n">
-        <f aca="false">H14+Inputs!B36*POWER(1+Inputs!B52,VALUE(A14)-Inputs!B4)</f>
-        <v>7504625.73989991</v>
+        <f aca="false">H14+Inputs!B36*POWER(1+Inputs!B52,VALUE(A14)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A14&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A14-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A14-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A14-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>7222239.73989991</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17713,8 +17712,8 @@
         <v>6368568.94809771</v>
       </c>
       <c r="I15" s="35" t="n">
-        <f aca="false">H15+Inputs!B36*POWER(1+Inputs!B52,VALUE(A15)-Inputs!B4)</f>
-        <v>7725274.094312</v>
+        <f aca="false">H15+Inputs!B36*POWER(1+Inputs!B52,VALUE(A15)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A15&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A15-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A15-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A15-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>7461069.094312</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17750,8 +17749,8 @@
         <v>6555044.14877053</v>
       </c>
       <c r="I16" s="37" t="n">
-        <f aca="false">H16+Inputs!B36*POWER(1+Inputs!B52,VALUE(A16)-Inputs!B4)</f>
-        <v>7972801.02656446</v>
+        <f aca="false">H16+Inputs!B36*POWER(1+Inputs!B52,VALUE(A16)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A16&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A16-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A16-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A16-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>7727993.02656446</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17787,8 +17786,8 @@
         <v>6767645.34502092</v>
       </c>
       <c r="I17" s="35" t="n">
-        <f aca="false">H17+Inputs!B36*POWER(1+Inputs!B52,VALUE(A17)-Inputs!B4)</f>
-        <v>8249201.28231558</v>
+        <f aca="false">H17+Inputs!B36*POWER(1+Inputs!B52,VALUE(A17)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A17&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A17-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A17-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A17-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>8025090.28231558</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17824,8 +17823,8 @@
         <v>7008397.34295334</v>
       </c>
       <c r="I18" s="37" t="n">
-        <f aca="false">H18+Inputs!B36*POWER(1+Inputs!B52,VALUE(A18)-Inputs!B4)</f>
-        <v>8556623.29742627</v>
+        <f aca="false">H18+Inputs!B36*POWER(1+Inputs!B52,VALUE(A18)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A18&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A18-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A18-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A18-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>8354595.29742627</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17861,8 +17860,8 @@
         <v>7279485.13267057</v>
       </c>
       <c r="I19" s="35" t="n">
-        <f aca="false">H19+Inputs!B36*POWER(1+Inputs!B52,VALUE(A19)-Inputs!B4)</f>
-        <v>8897381.25509478</v>
+        <f aca="false">H19+Inputs!B36*POWER(1+Inputs!B52,VALUE(A19)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A19&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A19-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A19-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A19-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>8718915.25509478</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17898,8 +17897,8 @@
         <v>7583266.64954875</v>
       </c>
       <c r="I20" s="39" t="n">
-        <f aca="false">H20+Inputs!B36*POWER(1+Inputs!B52,VALUE(A20)-Inputs!B4)</f>
-        <v>9273968.09748204</v>
+        <f aca="false">H20+Inputs!B36*POWER(1+Inputs!B52,VALUE(A20)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A20&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A20-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A20-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A20-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>9120642.09748204</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17935,8 +17934,8 @@
         <v>7922286.55465667</v>
       </c>
       <c r="I21" s="39" t="n">
-        <f aca="false">H21+Inputs!B36*POWER(1+Inputs!B52,VALUE(A21)-Inputs!B4)</f>
-        <v>9689069.56774696</v>
+        <f aca="false">H21+Inputs!B36*POWER(1+Inputs!B52,VALUE(A21)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A21&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A21-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A21-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A21-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>9562567.56774696</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17972,8 +17971,8 @@
         <v>8299291.11578583</v>
       </c>
       <c r="I22" s="39" t="n">
-        <f aca="false">H22+Inputs!B36*POWER(1+Inputs!B52,VALUE(A22)-Inputs!B4)</f>
-        <v>10145579.3644652</v>
+        <f aca="false">H22+Inputs!B36*POWER(1+Inputs!B52,VALUE(A22)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A22&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A22-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A22-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A22-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>10047697.3644652</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18009,8 +18008,8 @@
         <v>8717244.27707245</v>
       </c>
       <c r="I23" s="39" t="n">
-        <f aca="false">H23+Inputs!B36*POWER(1+Inputs!B52,VALUE(A23)-Inputs!B4)</f>
-        <v>10646615.4969424</v>
+        <f aca="false">H23+Inputs!B36*POWER(1+Inputs!B52,VALUE(A23)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A23&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A23-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A23-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A23-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>10579269.4969424</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18046,8 +18045,8 @@
         <v>9179345.01222822</v>
       </c>
       <c r="I24" s="39" t="n">
-        <f aca="false">H24+Inputs!B36*POWER(1+Inputs!B52,VALUE(A24)-Inputs!B4)</f>
-        <v>11195537.9369923</v>
+        <f aca="false">H24+Inputs!B36*POWER(1+Inputs!B52,VALUE(A24)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A24&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A24-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A24-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A24-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
+        <v>11160773.9369923</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18083,7 +18082,7 @@
         <v>9689046.06399511</v>
       </c>
       <c r="I25" s="39" t="n">
-        <f aca="false">H25+Inputs!B36*POWER(1+Inputs!B52,VALUE(A25)-Inputs!B4)</f>
+        <f aca="false">H25+Inputs!B36*POWER(1+Inputs!B52,VALUE(A25)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A25&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A25-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A25-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A25-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
         <v>11795967.6703736</v>
       </c>
     </row>
@@ -18120,7 +18119,7 @@
         <v>10250074.1806457</v>
       </c>
       <c r="I26" s="39" t="n">
-        <f aca="false">H26+Inputs!B36*POWER(1+Inputs!B52,VALUE(A26)-Inputs!B4)</f>
+        <f aca="false">H26+Inputs!B36*POWER(1+Inputs!B52,VALUE(A26)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A26&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A26-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A26-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A26-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
         <v>12451807.2593111</v>
       </c>
     </row>
@@ -18157,7 +18156,7 @@
         <v>10866451.9692128</v>
       </c>
       <c r="I27" s="39" t="n">
-        <f aca="false">H27+Inputs!B36*POWER(1+Inputs!B52,VALUE(A27)-Inputs!B4)</f>
+        <f aca="false">H27+Inputs!B36*POWER(1+Inputs!B52,VALUE(A27)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A27&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A27-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A27-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A27-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
         <v>13167263.0364182</v>
       </c>
     </row>
@@ -18194,7 +18193,7 @@
         <v>11542521.4947042</v>
       </c>
       <c r="I28" s="39" t="n">
-        <f aca="false">H28+Inputs!B36*POWER(1+Inputs!B52,VALUE(A28)-Inputs!B4)</f>
+        <f aca="false">H28+Inputs!B36*POWER(1+Inputs!B52,VALUE(A28)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A28&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A28-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A28-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A28-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
         <v>13946869.0599338</v>
       </c>
     </row>
@@ -18231,7 +18230,7 @@
         <v>12282969.7648941</v>
       </c>
       <c r="I29" s="39" t="n">
-        <f aca="false">H29+Inputs!B36*POWER(1+Inputs!B52,VALUE(A29)-Inputs!B4)</f>
+        <f aca="false">H29+Inputs!B36*POWER(1+Inputs!B52,VALUE(A29)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A29&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A29-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A29-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A29-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
         <v>14795512.9705591</v>
       </c>
     </row>
@@ -18268,7 +18267,7 @@
         <v>13092856.2514479</v>
       </c>
       <c r="I30" s="39" t="n">
-        <f aca="false">H30+Inputs!B36*POWER(1+Inputs!B52,VALUE(A30)-Inputs!B4)</f>
+        <f aca="false">H30+Inputs!B36*POWER(1+Inputs!B52,VALUE(A30)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A30&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A30-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A30-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A30-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
         <v>15718463.9013678</v>
       </c>
     </row>
@@ -18305,7 +18304,7 @@
         <v>13977642.6101926</v>
       </c>
       <c r="I31" s="39" t="n">
-        <f aca="false">H31+Inputs!B36*POWER(1+Inputs!B52,VALUE(A31)-Inputs!B4)</f>
+        <f aca="false">H31+Inputs!B36*POWER(1+Inputs!B52,VALUE(A31)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A31&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A31-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A31-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A31-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
         <v>16721402.604359</v>
       </c>
     </row>
@@ -18342,7 +18341,7 @@
         <v>14943224.7763668</v>
       </c>
       <c r="I32" s="39" t="n">
-        <f aca="false">H32+Inputs!B36*POWER(1+Inputs!B52,VALUE(A32)-Inputs!B4)</f>
+        <f aca="false">H32+Inputs!B36*POWER(1+Inputs!B52,VALUE(A32)-Inputs!B4)-IFERROR(IF(Inputs!B48&lt;=0,0,IF(AND(Inputs!B51=1,A32&gt;=Inputs!B5),0,IF(MAX(0,Inputs!B48*12-(A32-Inputs!B4)*12)&lt;=0,0,IF(Inputs!B49=0,Inputs!B30*MAX(0,Inputs!B48*12-(A32-Inputs!B4)*12),ROUND(Inputs!B30*(1-POWER(1+Inputs!B49/12,-MAX(0,Inputs!B48*12-(A32-Inputs!B4)*12)))/(Inputs!B49/12),0))))),0)</f>
         <v>17810453.9702706</v>
       </c>
     </row>
